--- a/backend/data/LigaPremier.xlsx
+++ b/backend/data/LigaPremier.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danyl\OneDrive\Desktop\excels\novo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danyl\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{75C7B81D-D8E7-47E2-A74F-F23746395C09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0A4D3BC8-A8AD-48E4-9A76-02D7DF3BCD38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2131" uniqueCount="936">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2129" uniqueCount="938">
   <si>
     <t>Id_jugador</t>
   </si>
@@ -2841,6 +2841,12 @@
   </si>
   <si>
     <t>Ian Torres</t>
+  </si>
+  <si>
+    <t>Sebastian Cardenas</t>
+  </si>
+  <si>
+    <t>Emilio Vargas</t>
   </si>
 </sst>
 </file>
@@ -3139,11 +3145,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{32A8CF84-C284-4FB9-BA95-EA038AE71CB6}" name="Tabla1" displayName="Tabla1" ref="A1:G532" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7">
-  <autoFilter ref="A1:G532" xr:uid="{32A8CF84-C284-4FB9-BA95-EA038AE71CB6}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{32A8CF84-C284-4FB9-BA95-EA038AE71CB6}" name="Tabla1" displayName="Tabla1" ref="A1:G533" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7">
+  <autoFilter ref="A1:G533" xr:uid="{32A8CF84-C284-4FB9-BA95-EA038AE71CB6}">
     <filterColumn colId="6">
       <filters>
-        <filter val="CA Zacatepec"/>
+        <filter val="CD Chilpancingo"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -3360,7 +3366,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G1000"/>
+  <dimension ref="A1:G1001"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.109375" customWidth="1"/>
@@ -4908,7 +4914,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1002021</v>
@@ -4932,7 +4938,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1002025</v>
@@ -4956,7 +4962,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1002001</v>
@@ -4980,7 +4986,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="str">
         <f t="shared" ref="A68:A131" si="1">F68 &amp; TEXT(C68,"000")</f>
         <v>1002108</v>
@@ -5004,7 +5010,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002019</v>
@@ -5028,7 +5034,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002007</v>
@@ -5052,7 +5058,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002003</v>
@@ -5076,7 +5082,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002024</v>
@@ -5100,7 +5106,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002004</v>
@@ -5124,7 +5130,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002018</v>
@@ -5148,7 +5154,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002008</v>
@@ -5172,7 +5178,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002002</v>
@@ -5196,7 +5202,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002006</v>
@@ -5220,7 +5226,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002015</v>
@@ -5244,7 +5250,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002013</v>
@@ -5268,7 +5274,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002012</v>
@@ -5292,7 +5298,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002011</v>
@@ -5316,7 +5322,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="82" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002027</v>
@@ -5340,7 +5346,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="83" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002005</v>
@@ -5364,7 +5370,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002109</v>
@@ -5388,7 +5394,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="85" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002022</v>
@@ -5412,7 +5418,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="86" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002009</v>
@@ -5436,7 +5442,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="87" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002017</v>
@@ -5460,7 +5466,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="88" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002110</v>
@@ -5484,7 +5490,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002020</v>
@@ -5508,7 +5514,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002014</v>
@@ -5532,7 +5538,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="91" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002023</v>
@@ -5556,7 +5562,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="92" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002016</v>
@@ -5580,7 +5586,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="93" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002026</v>
@@ -5604,7 +5610,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="94" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002111</v>
@@ -8054,7 +8060,7 @@
     </row>
     <row r="196" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="str">
-        <f t="shared" ref="A196:A259" si="3">F196 &amp; TEXT(C196,"000")</f>
+        <f t="shared" ref="A196:A258" si="3">F196 &amp; TEXT(C196,"000")</f>
         <v>1011013</v>
       </c>
       <c r="B196" s="1" t="s">
@@ -9084,7 +9090,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="239" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1003001</v>
@@ -9108,19 +9114,19 @@
         <v>441</v>
       </c>
     </row>
-    <row r="240" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>1003125</v>
+        <v>1003028</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C240" s="1">
-        <v>125</v>
+        <v>28</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>443</v>
+        <v>8</v>
       </c>
       <c r="E240" s="1" t="s">
         <v>13</v>
@@ -9132,16 +9138,16 @@
         <v>441</v>
       </c>
     </row>
-    <row r="241" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>1003028</v>
+        <v>1003023</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C241" s="1">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D241" s="2" t="s">
         <v>8</v>
@@ -9156,22 +9162,22 @@
         <v>441</v>
       </c>
     </row>
-    <row r="242" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>1003023</v>
+        <v>1003126</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C242" s="1">
-        <v>23</v>
+        <v>126</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>8</v>
+        <v>447</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F242" s="1">
         <v>1003</v>
@@ -9180,19 +9186,19 @@
         <v>441</v>
       </c>
     </row>
-    <row r="243" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>1003126</v>
+        <v>1003019</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C243" s="1">
-        <v>126</v>
+        <v>19</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="E243" s="1" t="s">
         <v>20</v>
@@ -9204,19 +9210,19 @@
         <v>441</v>
       </c>
     </row>
-    <row r="244" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>1003019</v>
+        <v>1003004</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C244" s="1">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E244" s="1" t="s">
         <v>20</v>
@@ -9228,19 +9234,19 @@
         <v>441</v>
       </c>
     </row>
-    <row r="245" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>1003004</v>
+        <v>1003013</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C245" s="1">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="E245" s="1" t="s">
         <v>20</v>
@@ -9252,19 +9258,19 @@
         <v>441</v>
       </c>
     </row>
-    <row r="246" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>1003013</v>
+        <v>1003127</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C246" s="1">
-        <v>13</v>
+        <v>127</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E246" s="1" t="s">
         <v>20</v>
@@ -9276,19 +9282,19 @@
         <v>441</v>
       </c>
     </row>
-    <row r="247" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>1003127</v>
+        <v>1003002</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C247" s="1">
-        <v>127</v>
+        <v>2</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>455</v>
+        <v>8</v>
       </c>
       <c r="E247" s="1" t="s">
         <v>20</v>
@@ -9300,19 +9306,19 @@
         <v>441</v>
       </c>
     </row>
-    <row r="248" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>1003002</v>
+        <v>1003007</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C248" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>8</v>
+        <v>458</v>
       </c>
       <c r="E248" s="1" t="s">
         <v>20</v>
@@ -9324,19 +9330,19 @@
         <v>441</v>
       </c>
     </row>
-    <row r="249" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>1003007</v>
+        <v>1003030</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C249" s="1">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>458</v>
+        <v>8</v>
       </c>
       <c r="E249" s="1" t="s">
         <v>20</v>
@@ -9348,19 +9354,19 @@
         <v>441</v>
       </c>
     </row>
-    <row r="250" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>1003030</v>
+        <v>1003024</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C250" s="1">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>8</v>
+        <v>461</v>
       </c>
       <c r="E250" s="1" t="s">
         <v>20</v>
@@ -9372,19 +9378,19 @@
         <v>441</v>
       </c>
     </row>
-    <row r="251" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>1003024</v>
+        <v>1003027</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C251" s="1">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>461</v>
+        <v>8</v>
       </c>
       <c r="E251" s="1" t="s">
         <v>20</v>
@@ -9396,16 +9402,16 @@
         <v>441</v>
       </c>
     </row>
-    <row r="252" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>1003027</v>
+        <v>1003005</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C252" s="1">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="D252" s="2" t="s">
         <v>8</v>
@@ -9420,16 +9426,16 @@
         <v>441</v>
       </c>
     </row>
-    <row r="253" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>1003005</v>
+        <v>1003025</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C253" s="1">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="D253" s="2" t="s">
         <v>8</v>
@@ -9444,19 +9450,19 @@
         <v>441</v>
       </c>
     </row>
-    <row r="254" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>1003025</v>
+        <v>1003026</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C254" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>8</v>
+        <v>466</v>
       </c>
       <c r="E254" s="1" t="s">
         <v>20</v>
@@ -9468,19 +9474,19 @@
         <v>441</v>
       </c>
     </row>
-    <row r="255" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>1003026</v>
+        <v>1003016</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C255" s="1">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="D255" s="2" t="s">
-        <v>466</v>
+        <v>8</v>
       </c>
       <c r="E255" s="1" t="s">
         <v>20</v>
@@ -9492,22 +9498,22 @@
         <v>441</v>
       </c>
     </row>
-    <row r="256" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>1003016</v>
+        <v>1003010</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C256" s="1">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>8</v>
+        <v>469</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F256" s="1">
         <v>1003</v>
@@ -9516,19 +9522,19 @@
         <v>441</v>
       </c>
     </row>
-    <row r="257" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>1003010</v>
+        <v>1003036</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C257" s="1">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E257" s="1" t="s">
         <v>33</v>
@@ -9540,19 +9546,19 @@
         <v>441</v>
       </c>
     </row>
-    <row r="258" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>1003128</v>
+        <v>1003017</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C258" s="1">
-        <v>128</v>
+        <v>17</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E258" s="1" t="s">
         <v>33</v>
@@ -9564,19 +9570,19 @@
         <v>441</v>
       </c>
     </row>
-    <row r="259" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>1003017</v>
+        <f t="shared" ref="A259:A324" si="4">F259 &amp; TEXT(C259,"000")</f>
+        <v>1003008</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C259" s="1">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D259" s="2" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="E259" s="1" t="s">
         <v>33</v>
@@ -9588,19 +9594,19 @@
         <v>441</v>
       </c>
     </row>
-    <row r="260" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="1" t="str">
-        <f t="shared" ref="A260:A323" si="4">F260 &amp; TEXT(C260,"000")</f>
-        <v>1003008</v>
+        <f t="shared" si="4"/>
+        <v>1003014</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C260" s="1">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E260" s="1" t="s">
         <v>33</v>
@@ -9612,19 +9618,19 @@
         <v>441</v>
       </c>
     </row>
-    <row r="261" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1003014</v>
+        <v>1003003</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C261" s="1">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>477</v>
+        <v>8</v>
       </c>
       <c r="E261" s="1" t="s">
         <v>33</v>
@@ -9636,16 +9642,16 @@
         <v>441</v>
       </c>
     </row>
-    <row r="262" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1003003</v>
+        <v>1003006</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C262" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D262" s="2" t="s">
         <v>8</v>
@@ -9660,19 +9666,19 @@
         <v>441</v>
       </c>
     </row>
-    <row r="263" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1003006</v>
+        <v>1003011</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>479</v>
+        <v>162</v>
       </c>
       <c r="C263" s="1">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>8</v>
+        <v>163</v>
       </c>
       <c r="E263" s="1" t="s">
         <v>33</v>
@@ -9684,19 +9690,19 @@
         <v>441</v>
       </c>
     </row>
-    <row r="264" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1003011</v>
+        <v>1003021</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>162</v>
+        <v>480</v>
       </c>
       <c r="C264" s="1">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>163</v>
+        <v>481</v>
       </c>
       <c r="E264" s="1" t="s">
         <v>33</v>
@@ -9708,19 +9714,19 @@
         <v>441</v>
       </c>
     </row>
-    <row r="265" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1003021</v>
+        <v>1003033</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C265" s="1">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E265" s="1" t="s">
         <v>33</v>
@@ -9732,19 +9738,19 @@
         <v>441</v>
       </c>
     </row>
-    <row r="266" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1003033</v>
+        <v>1003015</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C266" s="1">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="D266" s="2" t="s">
-        <v>483</v>
+        <v>8</v>
       </c>
       <c r="E266" s="1" t="s">
         <v>33</v>
@@ -9756,22 +9762,22 @@
         <v>441</v>
       </c>
     </row>
-    <row r="267" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1003015</v>
+        <v>1003009</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C267" s="1">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D267" s="2" t="s">
-        <v>8</v>
+        <v>487</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="F267" s="1">
         <v>1003</v>
@@ -9780,22 +9786,22 @@
         <v>441</v>
       </c>
     </row>
-    <row r="268" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1003129</v>
+        <v>1003018</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="C268" s="1">
-        <v>129</v>
+        <v>18</v>
       </c>
       <c r="D268" s="2" t="s">
-        <v>8</v>
+        <v>489</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="F268" s="1">
         <v>1003</v>
@@ -9804,19 +9810,19 @@
         <v>441</v>
       </c>
     </row>
-    <row r="269" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1003009</v>
+        <v>1003029</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="C269" s="1">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="E269" s="1" t="s">
         <v>58</v>
@@ -9828,19 +9834,19 @@
         <v>441</v>
       </c>
     </row>
-    <row r="270" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1003018</v>
+        <v>1003131</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>488</v>
+        <v>341</v>
       </c>
       <c r="C270" s="1">
-        <v>18</v>
+        <v>131</v>
       </c>
       <c r="D270" s="2" t="s">
-        <v>489</v>
+        <v>342</v>
       </c>
       <c r="E270" s="1" t="s">
         <v>58</v>
@@ -9852,19 +9858,19 @@
         <v>441</v>
       </c>
     </row>
-    <row r="271" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1003029</v>
+        <v>1003022</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C271" s="1">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E271" s="1" t="s">
         <v>58</v>
@@ -9876,19 +9882,19 @@
         <v>441</v>
       </c>
     </row>
-    <row r="272" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1003130</v>
+        <v>1003020</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>339</v>
+        <v>494</v>
       </c>
       <c r="C272" s="1">
-        <v>130</v>
+        <v>20</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>340</v>
+        <v>495</v>
       </c>
       <c r="E272" s="1" t="s">
         <v>58</v>
@@ -9900,139 +9906,127 @@
         <v>441</v>
       </c>
     </row>
-    <row r="273" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A273" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>1003131</v>
-      </c>
-      <c r="B273" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="C273" s="1">
-        <v>131</v>
+    <row r="273" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A273" s="7" t="str">
+        <f>F273 &amp; TEXT(C273,"000")</f>
+        <v>1003041</v>
+      </c>
+      <c r="B273" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="C273" s="7">
+        <v>41</v>
       </c>
       <c r="D273" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="E273" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="E273" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F273" s="7">
+        <v>1003</v>
+      </c>
+      <c r="G273" s="7"/>
+    </row>
+    <row r="274" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A274" s="7" t="str">
+        <f>F274 &amp; TEXT(C274,"000")</f>
+        <v>1003038</v>
+      </c>
+      <c r="B274" s="7" t="s">
+        <v>936</v>
+      </c>
+      <c r="C274" s="7">
+        <v>38</v>
+      </c>
+      <c r="D274" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="E274" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="F273" s="1">
+      <c r="F274" s="7">
         <v>1003</v>
       </c>
-      <c r="G273" s="1" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="274" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A274" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>1003022</v>
-      </c>
-      <c r="B274" s="1" t="s">
-        <v>492</v>
-      </c>
-      <c r="C274" s="1">
-        <v>22</v>
-      </c>
-      <c r="D274" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="E274" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F274" s="1">
+      <c r="G274" s="7"/>
+    </row>
+    <row r="275" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A275" s="7" t="str">
+        <f>F275 &amp; TEXT(C275,"000")</f>
+        <v>1003039</v>
+      </c>
+      <c r="B275" s="7" t="s">
+        <v>485</v>
+      </c>
+      <c r="C275" s="7">
+        <v>39</v>
+      </c>
+      <c r="D275" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E275" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F275" s="7">
         <v>1003</v>
       </c>
-      <c r="G274" s="1" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="275" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A275" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>1003020</v>
-      </c>
-      <c r="B275" s="1" t="s">
-        <v>494</v>
-      </c>
-      <c r="C275" s="1">
-        <v>20</v>
-      </c>
-      <c r="D275" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="E275" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F275" s="1">
+      <c r="G275" s="7"/>
+    </row>
+    <row r="276" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A276" s="7" t="str">
+        <f>F276 &amp; TEXT(C276,"000")</f>
+        <v>1003040</v>
+      </c>
+      <c r="B276" s="7" t="s">
+        <v>937</v>
+      </c>
+      <c r="C276" s="7">
+        <v>40</v>
+      </c>
+      <c r="D276" s="3"/>
+      <c r="E276" s="7"/>
+      <c r="F276" s="7">
         <v>1003</v>
       </c>
-      <c r="G275" s="1" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="276" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A276" s="1" t="str">
+      <c r="G276" s="7"/>
+    </row>
+    <row r="277" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A277" s="1" t="str">
         <f t="shared" si="4"/>
         <v>1003132</v>
       </c>
-      <c r="B276" s="1" t="s">
+      <c r="B277" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="C276" s="1">
+      <c r="C277" s="1">
         <v>132</v>
       </c>
-      <c r="D276" s="2" t="s">
+      <c r="D277" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="E276" s="1" t="s">
+      <c r="E277" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F276" s="1">
+      <c r="F277" s="1">
         <v>1003</v>
       </c>
-      <c r="G276" s="1" t="s">
+      <c r="G277" s="1" t="s">
         <v>441</v>
-      </c>
-    </row>
-    <row r="277" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A277" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v>1008001</v>
-      </c>
-      <c r="B277" s="1" t="s">
-        <v>497</v>
-      </c>
-      <c r="C277" s="1">
-        <v>1</v>
-      </c>
-      <c r="D277" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="E277" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F277" s="1">
-        <v>1008</v>
-      </c>
-      <c r="G277" s="1" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="278" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1008023</v>
+        <v>1008001</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="C278" s="1">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="D278" s="2" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="E278" s="1" t="s">
         <v>13</v>
@@ -10047,16 +10041,16 @@
     <row r="279" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1008070</v>
+        <v>1008023</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C279" s="1">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="D279" s="2" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="E279" s="1" t="s">
         <v>13</v>
@@ -10071,19 +10065,19 @@
     <row r="280" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1008003</v>
+        <v>1008070</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C280" s="1">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="D280" s="2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F280" s="1">
         <v>1008</v>
@@ -10095,16 +10089,16 @@
     <row r="281" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1008022</v>
+        <v>1008003</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C281" s="1">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="E281" s="1" t="s">
         <v>20</v>
@@ -10119,16 +10113,16 @@
     <row r="282" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1008002</v>
+        <v>1008022</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C282" s="1">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="E282" s="1" t="s">
         <v>20</v>
@@ -10143,16 +10137,16 @@
     <row r="283" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1008020</v>
+        <v>1008002</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C283" s="1">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E283" s="1" t="s">
         <v>20</v>
@@ -10167,16 +10161,16 @@
     <row r="284" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1008006</v>
+        <v>1008020</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C284" s="1">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D284" s="2" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="E284" s="1" t="s">
         <v>20</v>
@@ -10191,16 +10185,16 @@
     <row r="285" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1008004</v>
+        <v>1008006</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C285" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D285" s="2" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="E285" s="1" t="s">
         <v>20</v>
@@ -10215,16 +10209,16 @@
     <row r="286" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1008015</v>
+        <v>1008004</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C286" s="1">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D286" s="2" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="E286" s="1" t="s">
         <v>20</v>
@@ -10239,16 +10233,16 @@
     <row r="287" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1008061</v>
+        <v>1008015</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C287" s="1">
-        <v>61</v>
+        <v>15</v>
       </c>
       <c r="D287" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="E287" s="1" t="s">
         <v>20</v>
@@ -10263,16 +10257,16 @@
     <row r="288" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1008067</v>
+        <v>1008061</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C288" s="1">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D288" s="2" t="s">
-        <v>8</v>
+        <v>519</v>
       </c>
       <c r="E288" s="1" t="s">
         <v>20</v>
@@ -10287,19 +10281,19 @@
     <row r="289" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A289" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1008001</v>
+        <v>1008067</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C289" s="1">
-        <v>1</v>
+        <v>67</v>
       </c>
       <c r="D289" s="2" t="s">
-        <v>522</v>
+        <v>8</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F289" s="1">
         <v>1008</v>
@@ -10311,16 +10305,16 @@
     <row r="290" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1008017</v>
+        <v>1008001</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C290" s="1">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D290" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="E290" s="1" t="s">
         <v>33</v>
@@ -10335,16 +10329,16 @@
     <row r="291" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1008008</v>
+        <v>1008017</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C291" s="1">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D291" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="E291" s="1" t="s">
         <v>33</v>
@@ -10359,16 +10353,16 @@
     <row r="292" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1008011</v>
+        <v>1008008</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C292" s="1">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D292" s="2" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="E292" s="1" t="s">
         <v>33</v>
@@ -10383,16 +10377,16 @@
     <row r="293" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A293" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1008005</v>
+        <v>1008011</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C293" s="1">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D293" s="2" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="E293" s="1" t="s">
         <v>33</v>
@@ -10407,16 +10401,16 @@
     <row r="294" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A294" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1008007</v>
+        <v>1008005</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C294" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D294" s="2" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E294" s="1" t="s">
         <v>33</v>
@@ -10431,16 +10425,16 @@
     <row r="295" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A295" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1008133</v>
+        <v>1008007</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>95</v>
+        <v>531</v>
       </c>
       <c r="C295" s="1">
-        <v>133</v>
+        <v>7</v>
       </c>
       <c r="D295" s="2" t="s">
-        <v>96</v>
+        <v>532</v>
       </c>
       <c r="E295" s="1" t="s">
         <v>33</v>
@@ -10455,16 +10449,16 @@
     <row r="296" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A296" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1008016</v>
+        <v>1008133</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>533</v>
+        <v>95</v>
       </c>
       <c r="C296" s="1">
-        <v>16</v>
+        <v>133</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>534</v>
+        <v>96</v>
       </c>
       <c r="E296" s="1" t="s">
         <v>33</v>
@@ -10479,16 +10473,16 @@
     <row r="297" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A297" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1008134</v>
+        <v>1008016</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C297" s="1">
-        <v>134</v>
+        <v>16</v>
       </c>
       <c r="D297" s="2" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="E297" s="1" t="s">
         <v>33</v>
@@ -10503,16 +10497,16 @@
     <row r="298" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A298" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1008013</v>
+        <v>1008134</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C298" s="1">
-        <v>13</v>
+        <v>134</v>
       </c>
       <c r="D298" s="2" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E298" s="1" t="s">
         <v>33</v>
@@ -10527,16 +10521,16 @@
     <row r="299" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A299" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1008014</v>
+        <v>1008013</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C299" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D299" s="2" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="E299" s="1" t="s">
         <v>33</v>
@@ -10551,16 +10545,16 @@
     <row r="300" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A300" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1008012</v>
+        <v>1008014</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C300" s="1">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D300" s="2" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="E300" s="1" t="s">
         <v>33</v>
@@ -10575,16 +10569,16 @@
     <row r="301" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A301" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1008019</v>
+        <v>1008012</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C301" s="1">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D301" s="2" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="E301" s="1" t="s">
         <v>33</v>
@@ -10599,16 +10593,16 @@
     <row r="302" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A302" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1008018</v>
+        <v>1008019</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C302" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D302" s="2" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="E302" s="1" t="s">
         <v>33</v>
@@ -10623,16 +10617,16 @@
     <row r="303" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1008135</v>
+        <v>1008018</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C303" s="1">
-        <v>135</v>
+        <v>18</v>
       </c>
       <c r="D303" s="2" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="E303" s="1" t="s">
         <v>33</v>
@@ -10647,19 +10641,19 @@
     <row r="304" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A304" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1008027</v>
+        <v>1008135</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C304" s="1">
-        <v>27</v>
+        <v>135</v>
       </c>
       <c r="D304" s="2" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="F304" s="1">
         <v>1008</v>
@@ -10671,16 +10665,16 @@
     <row r="305" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A305" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1008136</v>
+        <v>1008027</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C305" s="1">
-        <v>136</v>
+        <v>27</v>
       </c>
       <c r="D305" s="2" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E305" s="1" t="s">
         <v>58</v>
@@ -10695,16 +10689,16 @@
     <row r="306" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A306" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1008010</v>
+        <v>1008136</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="C306" s="1">
-        <v>10</v>
+        <v>136</v>
       </c>
       <c r="D306" s="2" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="E306" s="1" t="s">
         <v>58</v>
@@ -10719,16 +10713,16 @@
     <row r="307" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A307" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1008137</v>
+        <v>1008010</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C307" s="1">
-        <v>137</v>
+        <v>10</v>
       </c>
       <c r="D307" s="2" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="E307" s="1" t="s">
         <v>58</v>
@@ -10743,16 +10737,16 @@
     <row r="308" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A308" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1008138</v>
+        <v>1008137</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C308" s="1">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D308" s="2" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="E308" s="1" t="s">
         <v>58</v>
@@ -10767,16 +10761,16 @@
     <row r="309" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A309" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1008009</v>
+        <v>1008138</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>168</v>
+        <v>557</v>
       </c>
       <c r="C309" s="1">
-        <v>9</v>
+        <v>138</v>
       </c>
       <c r="D309" s="2" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="E309" s="1" t="s">
         <v>58</v>
@@ -10791,16 +10785,16 @@
     <row r="310" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A310" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1008029</v>
+        <v>1008009</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>560</v>
+        <v>168</v>
       </c>
       <c r="C310" s="1">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="D310" s="2" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="E310" s="1" t="s">
         <v>58</v>
@@ -10815,16 +10809,16 @@
     <row r="311" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A311" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1008025</v>
+        <v>1008029</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C311" s="1">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D311" s="2" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="E311" s="1" t="s">
         <v>58</v>
@@ -10839,16 +10833,16 @@
     <row r="312" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A312" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1008139</v>
+        <v>1008025</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>553</v>
+        <v>562</v>
       </c>
       <c r="C312" s="1">
-        <v>139</v>
+        <v>25</v>
       </c>
       <c r="D312" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E312" s="1" t="s">
         <v>58</v>
@@ -10863,40 +10857,40 @@
     <row r="313" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A313" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1006001</v>
+        <v>1008139</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="C313" s="1">
-        <v>1</v>
+        <v>139</v>
       </c>
       <c r="D313" s="2" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="F313" s="1">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="G313" s="1" t="s">
-        <v>567</v>
+        <v>499</v>
       </c>
     </row>
     <row r="314" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A314" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1006051</v>
+        <v>1006001</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>185</v>
+        <v>565</v>
       </c>
       <c r="C314" s="1">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="D314" s="2" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="E314" s="1" t="s">
         <v>13</v>
@@ -10911,16 +10905,16 @@
     <row r="315" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A315" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1006012</v>
+        <v>1006051</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>569</v>
+        <v>185</v>
       </c>
       <c r="C315" s="1">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="D315" s="2" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E315" s="1" t="s">
         <v>13</v>
@@ -10935,19 +10929,19 @@
     <row r="316" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A316" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1006025</v>
+        <v>1006012</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C316" s="1">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D316" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F316" s="1">
         <v>1006</v>
@@ -10959,16 +10953,16 @@
     <row r="317" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A317" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1006015</v>
+        <v>1006025</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C317" s="1">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D317" s="2" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="E317" s="1" t="s">
         <v>20</v>
@@ -10983,16 +10977,16 @@
     <row r="318" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A318" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1006004</v>
+        <v>1006015</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C318" s="1">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D318" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E318" s="1" t="s">
         <v>20</v>
@@ -11007,16 +11001,16 @@
     <row r="319" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A319" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1006013</v>
+        <v>1006004</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C319" s="1">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D319" s="2" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="E319" s="1" t="s">
         <v>20</v>
@@ -11031,16 +11025,16 @@
     <row r="320" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A320" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1006062</v>
+        <v>1006013</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C320" s="1">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="D320" s="2" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="E320" s="1" t="s">
         <v>20</v>
@@ -11055,16 +11049,16 @@
     <row r="321" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A321" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1006026</v>
+        <v>1006062</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C321" s="1">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="D321" s="2" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="E321" s="1" t="s">
         <v>20</v>
@@ -11079,16 +11073,16 @@
     <row r="322" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A322" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1006003</v>
+        <v>1006026</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C322" s="1">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="D322" s="2" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="E322" s="1" t="s">
         <v>20</v>
@@ -11103,19 +11097,19 @@
     <row r="323" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A323" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>1006002</v>
+        <v>1006003</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C323" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D323" s="2" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F323" s="1">
         <v>1006</v>
@@ -11126,17 +11120,17 @@
     </row>
     <row r="324" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A324" s="1" t="str">
-        <f t="shared" ref="A324:A386" si="5">F324 &amp; TEXT(C324,"000")</f>
-        <v>1006006</v>
+        <f t="shared" si="4"/>
+        <v>1006002</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C324" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D324" s="2" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E324" s="1" t="s">
         <v>33</v>
@@ -11150,17 +11144,17 @@
     </row>
     <row r="325" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A325" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>1006011</v>
+        <f t="shared" ref="A325:A387" si="5">F325 &amp; TEXT(C325,"000")</f>
+        <v>1006006</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C325" s="1">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D325" s="2" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E325" s="1" t="s">
         <v>33</v>
@@ -11175,16 +11169,16 @@
     <row r="326" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A326" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1006008</v>
+        <v>1006011</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C326" s="1">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D326" s="2" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="E326" s="1" t="s">
         <v>33</v>
@@ -11199,16 +11193,16 @@
     <row r="327" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A327" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1006005</v>
+        <v>1006008</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C327" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D327" s="2" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="E327" s="1" t="s">
         <v>33</v>
@@ -11223,16 +11217,16 @@
     <row r="328" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A328" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1006018</v>
+        <v>1006005</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C328" s="1">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="D328" s="2" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="E328" s="1" t="s">
         <v>33</v>
@@ -11247,16 +11241,16 @@
     <row r="329" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A329" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1006007</v>
+        <v>1006018</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="C329" s="1">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D329" s="2" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="E329" s="1" t="s">
         <v>33</v>
@@ -11271,16 +11265,16 @@
     <row r="330" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A330" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1006016</v>
+        <v>1006007</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="C330" s="1">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D330" s="2" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="E330" s="1" t="s">
         <v>33</v>
@@ -11295,16 +11289,16 @@
     <row r="331" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A331" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1006020</v>
+        <v>1006016</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C331" s="1">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D331" s="2" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E331" s="1" t="s">
         <v>33</v>
@@ -11319,16 +11313,16 @@
     <row r="332" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A332" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1006022</v>
+        <v>1006020</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C332" s="1">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D332" s="2" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="E332" s="1" t="s">
         <v>33</v>
@@ -11343,16 +11337,16 @@
     <row r="333" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A333" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1006017</v>
+        <v>1006022</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C333" s="1">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D333" s="2" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="E333" s="1" t="s">
         <v>33</v>
@@ -11367,16 +11361,16 @@
     <row r="334" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A334" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1006021</v>
+        <v>1006017</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C334" s="1">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D334" s="2" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="E334" s="1" t="s">
         <v>33</v>
@@ -11391,16 +11385,16 @@
     <row r="335" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A335" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1006014</v>
+        <v>1006021</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C335" s="1">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D335" s="2" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="E335" s="1" t="s">
         <v>33</v>
@@ -11415,16 +11409,16 @@
     <row r="336" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A336" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1006065</v>
+        <v>1006014</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="C336" s="1">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="D336" s="2" t="s">
-        <v>8</v>
+        <v>610</v>
       </c>
       <c r="E336" s="1" t="s">
         <v>33</v>
@@ -11439,16 +11433,16 @@
     <row r="337" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A337" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1006141</v>
+        <v>1006065</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C337" s="1">
-        <v>141</v>
+        <v>65</v>
       </c>
       <c r="D337" s="2" t="s">
-        <v>613</v>
+        <v>8</v>
       </c>
       <c r="E337" s="1" t="s">
         <v>33</v>
@@ -11463,16 +11457,16 @@
     <row r="338" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A338" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1006142</v>
+        <v>1006141</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="C338" s="1">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D338" s="2" t="s">
-        <v>8</v>
+        <v>613</v>
       </c>
       <c r="E338" s="1" t="s">
         <v>33</v>
@@ -11487,19 +11481,19 @@
     <row r="339" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A339" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1006009</v>
+        <v>1006142</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C339" s="1">
-        <v>9</v>
+        <v>142</v>
       </c>
       <c r="D339" s="2" t="s">
-        <v>616</v>
+        <v>8</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="F339" s="1">
         <v>1006</v>
@@ -11511,16 +11505,16 @@
     <row r="340" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A340" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1006010</v>
+        <v>1006009</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="C340" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D340" s="2" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="E340" s="1" t="s">
         <v>58</v>
@@ -11535,16 +11529,16 @@
     <row r="341" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A341" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1006019</v>
+        <v>1006010</v>
       </c>
       <c r="B341" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C341" s="1">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D341" s="2" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="E341" s="1" t="s">
         <v>58</v>
@@ -11559,16 +11553,16 @@
     <row r="342" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A342" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1006143</v>
+        <v>1006019</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="C342" s="1">
-        <v>143</v>
+        <v>19</v>
       </c>
       <c r="D342" s="2" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="E342" s="1" t="s">
         <v>58</v>
@@ -11583,16 +11577,16 @@
     <row r="343" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A343" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1006023</v>
+        <v>1006143</v>
       </c>
       <c r="B343" s="1" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="C343" s="1">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="D343" s="2" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E343" s="1" t="s">
         <v>58</v>
@@ -11607,16 +11601,16 @@
     <row r="344" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A344" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1006079</v>
+        <v>1006023</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="C344" s="1">
-        <v>79</v>
+        <v>23</v>
       </c>
       <c r="D344" s="2" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="E344" s="1" t="s">
         <v>58</v>
@@ -11631,16 +11625,16 @@
     <row r="345" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A345" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1006029</v>
+        <v>1006079</v>
       </c>
       <c r="B345" s="1" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C345" s="1">
-        <v>29</v>
+        <v>79</v>
       </c>
       <c r="D345" s="2" t="s">
-        <v>8</v>
+        <v>626</v>
       </c>
       <c r="E345" s="1" t="s">
         <v>58</v>
@@ -11655,43 +11649,43 @@
     <row r="346" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A346" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1014146</v>
+        <v>1006029</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C346" s="1">
-        <v>146</v>
+        <v>29</v>
       </c>
       <c r="D346" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E346" s="1" t="s">
-        <v>9</v>
+        <v>58</v>
       </c>
       <c r="F346" s="1">
-        <v>1014</v>
+        <v>1006</v>
       </c>
       <c r="G346" s="1" t="s">
-        <v>629</v>
+        <v>567</v>
       </c>
     </row>
     <row r="347" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A347" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1014001</v>
+        <v>1014146</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="C347" s="1">
-        <v>1</v>
+        <v>146</v>
       </c>
       <c r="D347" s="2" t="s">
-        <v>631</v>
+        <v>8</v>
       </c>
       <c r="E347" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F347" s="1">
         <v>1014</v>
@@ -11703,16 +11697,16 @@
     <row r="348" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A348" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1014031</v>
+        <v>1014001</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C348" s="1">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="D348" s="2" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="E348" s="1" t="s">
         <v>13</v>
@@ -11727,19 +11721,19 @@
     <row r="349" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A349" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1014012</v>
+        <v>1014031</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C349" s="1">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="D349" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="E349" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F349" s="1">
         <v>1014</v>
@@ -11751,16 +11745,16 @@
     <row r="350" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A350" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1014023</v>
+        <v>1014012</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="C350" s="1">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D350" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="E350" s="1" t="s">
         <v>20</v>
@@ -11775,16 +11769,16 @@
     <row r="351" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A351" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1014004</v>
+        <v>1014023</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="C351" s="1">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="D351" s="2" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="E351" s="1" t="s">
         <v>20</v>
@@ -11799,16 +11793,16 @@
     <row r="352" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A352" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1014005</v>
+        <v>1014004</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="C352" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D352" s="2" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="E352" s="1" t="s">
         <v>20</v>
@@ -11823,16 +11817,16 @@
     <row r="353" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A353" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1014003</v>
+        <v>1014005</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="C353" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D353" s="2" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="E353" s="1" t="s">
         <v>20</v>
@@ -11847,16 +11841,16 @@
     <row r="354" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A354" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1014006</v>
+        <v>1014003</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="C354" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D354" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="E354" s="1" t="s">
         <v>20</v>
@@ -11871,16 +11865,16 @@
     <row r="355" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A355" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1014147</v>
+        <v>1014006</v>
       </c>
       <c r="B355" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="C355" s="1">
-        <v>147</v>
+        <v>6</v>
       </c>
       <c r="D355" s="2" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="E355" s="1" t="s">
         <v>20</v>
@@ -11895,16 +11889,16 @@
     <row r="356" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A356" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1014024</v>
+        <v>1014147</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C356" s="1">
-        <v>24</v>
+        <v>147</v>
       </c>
       <c r="D356" s="2" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="E356" s="1" t="s">
         <v>20</v>
@@ -11919,16 +11913,16 @@
     <row r="357" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A357" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1014018</v>
+        <v>1014024</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C357" s="1">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D357" s="2" t="s">
-        <v>8</v>
+        <v>649</v>
       </c>
       <c r="E357" s="1" t="s">
         <v>20</v>
@@ -11943,16 +11937,16 @@
     <row r="358" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A358" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1014063</v>
+        <v>1014018</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C358" s="1">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="D358" s="2" t="s">
-        <v>652</v>
+        <v>8</v>
       </c>
       <c r="E358" s="1" t="s">
         <v>20</v>
@@ -11967,16 +11961,16 @@
     <row r="359" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A359" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1014148</v>
+        <v>1014063</v>
       </c>
       <c r="B359" s="1" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="C359" s="1">
-        <v>148</v>
+        <v>63</v>
       </c>
       <c r="D359" s="2" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="E359" s="1" t="s">
         <v>20</v>
@@ -11991,19 +11985,19 @@
     <row r="360" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A360" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1014002</v>
+        <v>1014148</v>
       </c>
       <c r="B360" s="1" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C360" s="1">
-        <v>2</v>
+        <v>148</v>
       </c>
       <c r="D360" s="2" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="E360" s="1" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F360" s="1">
         <v>1014</v>
@@ -12015,16 +12009,16 @@
     <row r="361" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A361" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1014010</v>
+        <v>1014002</v>
       </c>
       <c r="B361" s="1" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C361" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D361" s="2" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="E361" s="1" t="s">
         <v>33</v>
@@ -12039,16 +12033,16 @@
     <row r="362" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A362" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1014017</v>
+        <v>1014010</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="C362" s="1">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D362" s="2" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="E362" s="1" t="s">
         <v>33</v>
@@ -12063,16 +12057,16 @@
     <row r="363" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A363" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1014014</v>
+        <v>1014017</v>
       </c>
       <c r="B363" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C363" s="1">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D363" s="2" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="E363" s="1" t="s">
         <v>33</v>
@@ -12087,16 +12081,16 @@
     <row r="364" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A364" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1014020</v>
+        <v>1014014</v>
       </c>
       <c r="B364" s="1" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="C364" s="1">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D364" s="2" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="E364" s="1" t="s">
         <v>33</v>
@@ -12111,16 +12105,16 @@
     <row r="365" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A365" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1014058</v>
+        <v>1014020</v>
       </c>
       <c r="B365" s="1" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="C365" s="1">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="D365" s="2" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="E365" s="1" t="s">
         <v>33</v>
@@ -12135,16 +12129,16 @@
     <row r="366" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A366" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1014149</v>
+        <v>1014058</v>
       </c>
       <c r="B366" s="1" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="C366" s="1">
-        <v>149</v>
+        <v>58</v>
       </c>
       <c r="D366" s="2" t="s">
-        <v>8</v>
+        <v>666</v>
       </c>
       <c r="E366" s="1" t="s">
         <v>33</v>
@@ -12159,16 +12153,16 @@
     <row r="367" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A367" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1014016</v>
+        <v>1014149</v>
       </c>
       <c r="B367" s="1" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C367" s="1">
-        <v>16</v>
+        <v>149</v>
       </c>
       <c r="D367" s="2" t="s">
-        <v>669</v>
+        <v>8</v>
       </c>
       <c r="E367" s="1" t="s">
         <v>33</v>
@@ -12183,16 +12177,16 @@
     <row r="368" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A368" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1014027</v>
+        <v>1014016</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C368" s="1">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D368" s="2" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="E368" s="1" t="s">
         <v>33</v>
@@ -12207,16 +12201,16 @@
     <row r="369" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A369" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1014015</v>
+        <v>1014027</v>
       </c>
       <c r="B369" s="1" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C369" s="1">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="D369" s="2" t="s">
-        <v>8</v>
+        <v>671</v>
       </c>
       <c r="E369" s="1" t="s">
         <v>33</v>
@@ -12231,13 +12225,13 @@
     <row r="370" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A370" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1014150</v>
+        <v>1014015</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C370" s="1">
-        <v>150</v>
+        <v>15</v>
       </c>
       <c r="D370" s="2" t="s">
         <v>8</v>
@@ -12255,16 +12249,16 @@
     <row r="371" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A371" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1014072</v>
+        <v>1014150</v>
       </c>
       <c r="B371" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C371" s="1">
-        <v>72</v>
+        <v>150</v>
       </c>
       <c r="D371" s="2" t="s">
-        <v>675</v>
+        <v>8</v>
       </c>
       <c r="E371" s="1" t="s">
         <v>33</v>
@@ -12279,16 +12273,16 @@
     <row r="372" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A372" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1014052</v>
+        <v>1014072</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="C372" s="1">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="D372" s="2" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="E372" s="1" t="s">
         <v>33</v>
@@ -12303,16 +12297,16 @@
     <row r="373" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A373" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1014008</v>
+        <v>1014052</v>
       </c>
       <c r="B373" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C373" s="1">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="D373" s="2" t="s">
-        <v>8</v>
+        <v>677</v>
       </c>
       <c r="E373" s="1" t="s">
         <v>33</v>
@@ -12327,16 +12321,16 @@
     <row r="374" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A374" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1014026</v>
+        <v>1014008</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C374" s="1">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="D374" s="2" t="s">
-        <v>680</v>
+        <v>8</v>
       </c>
       <c r="E374" s="1" t="s">
         <v>33</v>
@@ -12351,16 +12345,16 @@
     <row r="375" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A375" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1014019</v>
+        <v>1014026</v>
       </c>
       <c r="B375" s="1" t="s">
-        <v>260</v>
+        <v>679</v>
       </c>
       <c r="C375" s="1">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D375" s="2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="E375" s="1" t="s">
         <v>33</v>
@@ -12375,19 +12369,19 @@
     <row r="376" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A376" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1014059</v>
+        <v>1014019</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>682</v>
+        <v>260</v>
       </c>
       <c r="C376" s="1">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="D376" s="2" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="E376" s="1" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="F376" s="1">
         <v>1014</v>
@@ -12399,16 +12393,16 @@
     <row r="377" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A377" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1014007</v>
+        <v>1014059</v>
       </c>
       <c r="B377" s="1" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="C377" s="1">
-        <v>7</v>
+        <v>59</v>
       </c>
       <c r="D377" s="2" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="E377" s="1" t="s">
         <v>58</v>
@@ -12423,16 +12417,16 @@
     <row r="378" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A378" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1014003</v>
+        <v>1014007</v>
       </c>
       <c r="B378" s="1" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="C378" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D378" s="2" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="E378" s="1" t="s">
         <v>58</v>
@@ -12447,16 +12441,16 @@
     <row r="379" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A379" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1014033</v>
+        <v>1014003</v>
       </c>
       <c r="B379" s="1" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="C379" s="1">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="D379" s="2" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="E379" s="1" t="s">
         <v>58</v>
@@ -12471,16 +12465,16 @@
     <row r="380" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A380" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1014056</v>
+        <v>1014033</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="C380" s="1">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="D380" s="2" t="s">
-        <v>8</v>
+        <v>689</v>
       </c>
       <c r="E380" s="1" t="s">
         <v>58</v>
@@ -12495,16 +12489,16 @@
     <row r="381" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A381" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1014035</v>
+        <v>1014056</v>
       </c>
       <c r="B381" s="1" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C381" s="1">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="D381" s="2" t="s">
-        <v>692</v>
+        <v>8</v>
       </c>
       <c r="E381" s="1" t="s">
         <v>58</v>
@@ -12519,16 +12513,16 @@
     <row r="382" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A382" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1014150</v>
+        <v>1014035</v>
       </c>
       <c r="B382" s="1" t="s">
-        <v>682</v>
+        <v>691</v>
       </c>
       <c r="C382" s="1">
-        <v>150</v>
+        <v>35</v>
       </c>
       <c r="D382" s="2" t="s">
-        <v>8</v>
+        <v>692</v>
       </c>
       <c r="E382" s="1" t="s">
         <v>58</v>
@@ -12543,40 +12537,40 @@
     <row r="383" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A383" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1005029</v>
+        <v>1014150</v>
       </c>
       <c r="B383" s="1" t="s">
-        <v>693</v>
+        <v>682</v>
       </c>
       <c r="C383" s="1">
-        <v>29</v>
+        <v>150</v>
       </c>
       <c r="D383" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E383" s="1" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="F383" s="1">
-        <v>1005</v>
+        <v>1014</v>
       </c>
       <c r="G383" s="1" t="s">
-        <v>694</v>
+        <v>629</v>
       </c>
     </row>
     <row r="384" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A384" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1005030</v>
+        <v>1005029</v>
       </c>
       <c r="B384" s="1" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C384" s="1">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D384" s="2" t="s">
-        <v>696</v>
+        <v>8</v>
       </c>
       <c r="E384" s="1" t="s">
         <v>13</v>
@@ -12591,16 +12585,16 @@
     <row r="385" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A385" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1005053</v>
+        <v>1005030</v>
       </c>
       <c r="B385" s="1" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="C385" s="1">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="D385" s="2" t="s">
-        <v>8</v>
+        <v>696</v>
       </c>
       <c r="E385" s="1" t="s">
         <v>13</v>
@@ -12615,19 +12609,19 @@
     <row r="386" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A386" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>1005027</v>
+        <v>1005053</v>
       </c>
       <c r="B386" s="1" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C386" s="1">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="D386" s="2" t="s">
-        <v>699</v>
+        <v>8</v>
       </c>
       <c r="E386" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F386" s="1">
         <v>1005</v>
@@ -12638,17 +12632,17 @@
     </row>
     <row r="387" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A387" s="1" t="str">
-        <f t="shared" ref="A387:A450" si="6">F387 &amp; TEXT(C387,"000")</f>
-        <v>1005019</v>
+        <f t="shared" si="5"/>
+        <v>1005027</v>
       </c>
       <c r="B387" s="1" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="C387" s="1">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D387" s="2" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="E387" s="1" t="s">
         <v>20</v>
@@ -12662,17 +12656,17 @@
     </row>
     <row r="388" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A388" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v>1005016</v>
+        <f t="shared" ref="A388:A451" si="6">F388 &amp; TEXT(C388,"000")</f>
+        <v>1005019</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="C388" s="1">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D388" s="2" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="E388" s="1" t="s">
         <v>20</v>
@@ -12687,16 +12681,16 @@
     <row r="389" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A389" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1005002</v>
+        <v>1005016</v>
       </c>
       <c r="B389" s="1" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="C389" s="1">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D389" s="2" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E389" s="1" t="s">
         <v>20</v>
@@ -12711,16 +12705,16 @@
     <row r="390" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A390" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1005017</v>
+        <v>1005002</v>
       </c>
       <c r="B390" s="1" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="C390" s="1">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="D390" s="2" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E390" s="1" t="s">
         <v>20</v>
@@ -12735,16 +12729,16 @@
     <row r="391" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A391" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1005021</v>
+        <v>1005017</v>
       </c>
       <c r="B391" s="1" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="C391" s="1">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D391" s="2" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="E391" s="1" t="s">
         <v>20</v>
@@ -12759,16 +12753,16 @@
     <row r="392" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A392" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1005022</v>
+        <v>1005021</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>183</v>
+        <v>708</v>
       </c>
       <c r="C392" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D392" s="2" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="E392" s="1" t="s">
         <v>20</v>
@@ -12783,16 +12777,16 @@
     <row r="393" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A393" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1005014</v>
+        <v>1005022</v>
       </c>
       <c r="B393" s="1" t="s">
-        <v>711</v>
+        <v>183</v>
       </c>
       <c r="C393" s="1">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D393" s="2" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="E393" s="1" t="s">
         <v>20</v>
@@ -12807,16 +12801,16 @@
     <row r="394" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A394" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1005013</v>
+        <v>1005014</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="C394" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D394" s="2" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="E394" s="1" t="s">
         <v>20</v>
@@ -12831,19 +12825,19 @@
     <row r="395" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A395" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1005004</v>
+        <v>1005013</v>
       </c>
       <c r="B395" s="1" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C395" s="1">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D395" s="2" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="E395" s="1" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F395" s="1">
         <v>1005</v>
@@ -12855,16 +12849,16 @@
     <row r="396" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A396" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1005020</v>
+        <v>1005004</v>
       </c>
       <c r="B396" s="1" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="C396" s="1">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="D396" s="2" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E396" s="1" t="s">
         <v>33</v>
@@ -12879,16 +12873,16 @@
     <row r="397" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A397" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1005007</v>
+        <v>1005020</v>
       </c>
       <c r="B397" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="C397" s="1">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D397" s="2" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="E397" s="1" t="s">
         <v>33</v>
@@ -12903,16 +12897,16 @@
     <row r="398" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A398" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1005015</v>
+        <v>1005007</v>
       </c>
       <c r="B398" s="1" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="C398" s="1">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D398" s="2" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="E398" s="1" t="s">
         <v>33</v>
@@ -12927,16 +12921,16 @@
     <row r="399" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A399" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1005005</v>
+        <v>1005015</v>
       </c>
       <c r="B399" s="1" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="C399" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D399" s="2" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="E399" s="1" t="s">
         <v>33</v>
@@ -12951,16 +12945,16 @@
     <row r="400" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A400" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1005012</v>
+        <v>1005005</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="C400" s="1">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D400" s="2" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E400" s="1" t="s">
         <v>33</v>
@@ -12975,16 +12969,16 @@
     <row r="401" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A401" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1005018</v>
+        <v>1005012</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>593</v>
+        <v>725</v>
       </c>
       <c r="C401" s="1">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D401" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="E401" s="1" t="s">
         <v>33</v>
@@ -12999,16 +12993,16 @@
     <row r="402" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A402" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1005031</v>
+        <v>1005018</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>728</v>
+        <v>593</v>
       </c>
       <c r="C402" s="1">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="D402" s="2" t="s">
-        <v>8</v>
+        <v>727</v>
       </c>
       <c r="E402" s="1" t="s">
         <v>33</v>
@@ -13023,16 +13017,16 @@
     <row r="403" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A403" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1005008</v>
+        <v>1005031</v>
       </c>
       <c r="B403" s="1" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C403" s="1">
+        <v>31</v>
+      </c>
+      <c r="D403" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="D403" s="2" t="s">
-        <v>730</v>
       </c>
       <c r="E403" s="1" t="s">
         <v>33</v>
@@ -13047,19 +13041,19 @@
     <row r="404" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A404" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1005002</v>
+        <v>1005008</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="C404" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D404" s="2" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="E404" s="1" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="F404" s="1">
         <v>1005</v>
@@ -13071,16 +13065,16 @@
     <row r="405" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A405" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1005009</v>
+        <v>1005002</v>
       </c>
       <c r="B405" s="1" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="C405" s="1">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D405" s="2" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="E405" s="1" t="s">
         <v>58</v>
@@ -13095,16 +13089,16 @@
     <row r="406" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A406" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1005006</v>
+        <v>1005009</v>
       </c>
       <c r="B406" s="1" t="s">
-        <v>267</v>
+        <v>733</v>
       </c>
       <c r="C406" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D406" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="E406" s="1" t="s">
         <v>58</v>
@@ -13119,16 +13113,16 @@
     <row r="407" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A407" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1005003</v>
+        <v>1005006</v>
       </c>
       <c r="B407" s="1" t="s">
-        <v>736</v>
+        <v>267</v>
       </c>
       <c r="C407" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D407" s="2" t="s">
-        <v>8</v>
+        <v>735</v>
       </c>
       <c r="E407" s="1" t="s">
         <v>58</v>
@@ -13143,16 +13137,16 @@
     <row r="408" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A408" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1005023</v>
+        <v>1005003</v>
       </c>
       <c r="B408" s="1" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C408" s="1">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="D408" s="2" t="s">
-        <v>738</v>
+        <v>8</v>
       </c>
       <c r="E408" s="1" t="s">
         <v>58</v>
@@ -13167,16 +13161,16 @@
     <row r="409" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A409" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1005011</v>
+        <v>1005023</v>
       </c>
       <c r="B409" s="1" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="C409" s="1">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="D409" s="2" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="E409" s="1" t="s">
         <v>58</v>
@@ -13191,16 +13185,16 @@
     <row r="410" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A410" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1005025</v>
+        <v>1005011</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C410" s="1">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D410" s="2" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="E410" s="1" t="s">
         <v>58</v>
@@ -13215,16 +13209,16 @@
     <row r="411" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A411" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1005024</v>
+        <v>1005025</v>
       </c>
       <c r="B411" s="1" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="C411" s="1">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D411" s="2" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="E411" s="1" t="s">
         <v>58</v>
@@ -13239,16 +13233,16 @@
     <row r="412" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A412" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1005028</v>
+        <v>1005024</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C412" s="1">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D412" s="2" t="s">
-        <v>8</v>
+        <v>744</v>
       </c>
       <c r="E412" s="1" t="s">
         <v>58</v>
@@ -13263,16 +13257,16 @@
     <row r="413" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A413" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1005151</v>
+        <v>1005028</v>
       </c>
       <c r="B413" s="1" t="s">
-        <v>717</v>
+        <v>745</v>
       </c>
       <c r="C413" s="1">
-        <v>151</v>
+        <v>28</v>
       </c>
       <c r="D413" s="2" t="s">
-        <v>746</v>
+        <v>8</v>
       </c>
       <c r="E413" s="1" t="s">
         <v>58</v>
@@ -13287,25 +13281,25 @@
     <row r="414" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A414" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1001001</v>
+        <v>1005151</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>747</v>
+        <v>717</v>
       </c>
       <c r="C414" s="1">
-        <v>1</v>
+        <v>151</v>
       </c>
       <c r="D414" s="2" t="s">
-        <v>8</v>
+        <v>746</v>
       </c>
       <c r="E414" s="1" t="s">
-        <v>9</v>
+        <v>58</v>
       </c>
       <c r="F414" s="1">
-        <v>1001</v>
+        <v>1005</v>
       </c>
       <c r="G414" s="1" t="s">
-        <v>748</v>
+        <v>694</v>
       </c>
     </row>
     <row r="415" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -13314,7 +13308,7 @@
         <v>1001001</v>
       </c>
       <c r="B415" s="1" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="C415" s="1">
         <v>1</v>
@@ -13335,19 +13329,19 @@
     <row r="416" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A416" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1001021</v>
+        <v>1001001</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="C416" s="1">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D416" s="2" t="s">
-        <v>751</v>
+        <v>8</v>
       </c>
       <c r="E416" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F416" s="1">
         <v>1001</v>
@@ -13359,16 +13353,16 @@
     <row r="417" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A417" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1001152</v>
+        <v>1001021</v>
       </c>
       <c r="B417" s="1" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="C417" s="1">
-        <v>152</v>
+        <v>21</v>
       </c>
       <c r="D417" s="2" t="s">
-        <v>8</v>
+        <v>751</v>
       </c>
       <c r="E417" s="1" t="s">
         <v>13</v>
@@ -13383,13 +13377,13 @@
     <row r="418" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A418" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1001001</v>
+        <v>1001152</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C418" s="1">
-        <v>1</v>
+        <v>152</v>
       </c>
       <c r="D418" s="2" t="s">
         <v>8</v>
@@ -13407,16 +13401,16 @@
     <row r="419" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A419" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1001029</v>
+        <v>1001001</v>
       </c>
       <c r="B419" s="1" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C419" s="1">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D419" s="2" t="s">
-        <v>755</v>
+        <v>8</v>
       </c>
       <c r="E419" s="1" t="s">
         <v>13</v>
@@ -13431,19 +13425,19 @@
     <row r="420" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A420" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1001023</v>
+        <v>1001029</v>
       </c>
       <c r="B420" s="1" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="C420" s="1">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D420" s="2" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="E420" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F420" s="1">
         <v>1001</v>
@@ -13455,16 +13449,16 @@
     <row r="421" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A421" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1001153</v>
+        <v>1001023</v>
       </c>
       <c r="B421" s="1" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="C421" s="1">
-        <v>153</v>
+        <v>23</v>
       </c>
       <c r="D421" s="2" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="E421" s="1" t="s">
         <v>20</v>
@@ -13479,16 +13473,16 @@
     <row r="422" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A422" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1001020</v>
+        <v>1001153</v>
       </c>
       <c r="B422" s="1" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="C422" s="1">
-        <v>20</v>
+        <v>153</v>
       </c>
       <c r="D422" s="2" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="E422" s="1" t="s">
         <v>20</v>
@@ -13503,16 +13497,16 @@
     <row r="423" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A423" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1001013</v>
+        <v>1001020</v>
       </c>
       <c r="B423" s="1" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="C423" s="1">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D423" s="2" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="E423" s="1" t="s">
         <v>20</v>
@@ -13527,16 +13521,16 @@
     <row r="424" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A424" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1001024</v>
+        <v>1001013</v>
       </c>
       <c r="B424" s="1" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="C424" s="1">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D424" s="2" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="E424" s="1" t="s">
         <v>20</v>
@@ -13551,16 +13545,16 @@
     <row r="425" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A425" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1001002</v>
+        <v>1001024</v>
       </c>
       <c r="B425" s="1" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="C425" s="1">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="D425" s="2" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="E425" s="1" t="s">
         <v>20</v>
@@ -13575,16 +13569,16 @@
     <row r="426" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A426" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1001043</v>
+        <v>1001002</v>
       </c>
       <c r="B426" s="1" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="C426" s="1">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="D426" s="2" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="E426" s="1" t="s">
         <v>20</v>
@@ -13599,16 +13593,16 @@
     <row r="427" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A427" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1001041</v>
+        <v>1001043</v>
       </c>
       <c r="B427" s="1" t="s">
-        <v>245</v>
+        <v>768</v>
       </c>
       <c r="C427" s="1">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D427" s="2" t="s">
-        <v>8</v>
+        <v>769</v>
       </c>
       <c r="E427" s="1" t="s">
         <v>20</v>
@@ -13623,16 +13617,16 @@
     <row r="428" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A428" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1001025</v>
+        <v>1001041</v>
       </c>
       <c r="B428" s="1" t="s">
-        <v>770</v>
+        <v>245</v>
       </c>
       <c r="C428" s="1">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="D428" s="2" t="s">
-        <v>771</v>
+        <v>8</v>
       </c>
       <c r="E428" s="1" t="s">
         <v>20</v>
@@ -13647,16 +13641,16 @@
     <row r="429" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A429" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1001012</v>
+        <v>1001025</v>
       </c>
       <c r="B429" s="1" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="C429" s="1">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="D429" s="2" t="s">
-        <v>8</v>
+        <v>771</v>
       </c>
       <c r="E429" s="1" t="s">
         <v>20</v>
@@ -13671,16 +13665,16 @@
     <row r="430" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A430" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1001045</v>
+        <v>1001012</v>
       </c>
       <c r="B430" s="1" t="s">
-        <v>700</v>
+        <v>772</v>
       </c>
       <c r="C430" s="1">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="D430" s="2" t="s">
-        <v>773</v>
+        <v>8</v>
       </c>
       <c r="E430" s="1" t="s">
         <v>20</v>
@@ -13695,16 +13689,16 @@
     <row r="431" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A431" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1001003</v>
+        <v>1001045</v>
       </c>
       <c r="B431" s="1" t="s">
-        <v>774</v>
+        <v>700</v>
       </c>
       <c r="C431" s="1">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="D431" s="2" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="E431" s="1" t="s">
         <v>20</v>
@@ -13719,16 +13713,16 @@
     <row r="432" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A432" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1001154</v>
+        <v>1001003</v>
       </c>
       <c r="B432" s="1" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C432" s="1">
-        <v>154</v>
+        <v>3</v>
       </c>
       <c r="D432" s="2" t="s">
-        <v>8</v>
+        <v>775</v>
       </c>
       <c r="E432" s="1" t="s">
         <v>20</v>
@@ -13743,16 +13737,16 @@
     <row r="433" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A433" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1001155</v>
+        <v>1001154</v>
       </c>
       <c r="B433" s="1" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="C433" s="1">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D433" s="2" t="s">
-        <v>778</v>
+        <v>8</v>
       </c>
       <c r="E433" s="1" t="s">
         <v>20</v>
@@ -13767,19 +13761,19 @@
     <row r="434" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A434" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1001010</v>
+        <v>1001155</v>
       </c>
       <c r="B434" s="1" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="C434" s="1">
-        <v>10</v>
+        <v>155</v>
       </c>
       <c r="D434" s="2" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="E434" s="1" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F434" s="1">
         <v>1001</v>
@@ -13791,16 +13785,16 @@
     <row r="435" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A435" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1001011</v>
+        <v>1001010</v>
       </c>
       <c r="B435" s="1" t="s">
-        <v>535</v>
+        <v>779</v>
       </c>
       <c r="C435" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D435" s="2" t="s">
-        <v>536</v>
+        <v>780</v>
       </c>
       <c r="E435" s="1" t="s">
         <v>33</v>
@@ -13815,16 +13809,16 @@
     <row r="436" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A436" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1001005</v>
+        <v>1001011</v>
       </c>
       <c r="B436" s="1" t="s">
-        <v>781</v>
+        <v>535</v>
       </c>
       <c r="C436" s="1">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D436" s="2" t="s">
-        <v>782</v>
+        <v>536</v>
       </c>
       <c r="E436" s="1" t="s">
         <v>33</v>
@@ -13839,16 +13833,16 @@
     <row r="437" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A437" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1001004</v>
+        <v>1001005</v>
       </c>
       <c r="B437" s="1" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C437" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D437" s="2" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="E437" s="1" t="s">
         <v>33</v>
@@ -13863,16 +13857,16 @@
     <row r="438" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A438" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1001018</v>
+        <v>1001004</v>
       </c>
       <c r="B438" s="1" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="C438" s="1">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="D438" s="2" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="E438" s="1" t="s">
         <v>33</v>
@@ -13887,16 +13881,16 @@
     <row r="439" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A439" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1001016</v>
+        <v>1001018</v>
       </c>
       <c r="B439" s="1" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="C439" s="1">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D439" s="2" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="E439" s="1" t="s">
         <v>33</v>
@@ -13911,16 +13905,16 @@
     <row r="440" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A440" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1001006</v>
+        <v>1001016</v>
       </c>
       <c r="B440" s="1" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="C440" s="1">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D440" s="2" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="E440" s="1" t="s">
         <v>33</v>
@@ -13935,16 +13929,16 @@
     <row r="441" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A441" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1001008</v>
+        <v>1001006</v>
       </c>
       <c r="B441" s="1" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="C441" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D441" s="2" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="E441" s="1" t="s">
         <v>33</v>
@@ -13959,16 +13953,16 @@
     <row r="442" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A442" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1001156</v>
+        <v>1001008</v>
       </c>
       <c r="B442" s="1" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="C442" s="1">
-        <v>156</v>
+        <v>8</v>
       </c>
       <c r="D442" s="2" t="s">
-        <v>8</v>
+        <v>792</v>
       </c>
       <c r="E442" s="1" t="s">
         <v>33</v>
@@ -13983,16 +13977,16 @@
     <row r="443" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A443" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1001030</v>
+        <v>1001156</v>
       </c>
       <c r="B443" s="1" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="C443" s="1">
-        <v>30</v>
+        <v>156</v>
       </c>
       <c r="D443" s="2" t="s">
-        <v>795</v>
+        <v>8</v>
       </c>
       <c r="E443" s="1" t="s">
         <v>33</v>
@@ -14007,16 +14001,16 @@
     <row r="444" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A444" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1001022</v>
+        <v>1001030</v>
       </c>
       <c r="B444" s="1" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="C444" s="1">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D444" s="2" t="s">
-        <v>8</v>
+        <v>795</v>
       </c>
       <c r="E444" s="1" t="s">
         <v>33</v>
@@ -14031,13 +14025,13 @@
     <row r="445" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A445" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1001044</v>
+        <v>1001022</v>
       </c>
       <c r="B445" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C445" s="1">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="D445" s="2" t="s">
         <v>8</v>
@@ -14055,13 +14049,13 @@
     <row r="446" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A446" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1001007</v>
+        <v>1001044</v>
       </c>
       <c r="B446" s="1" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="C446" s="1">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="D446" s="2" t="s">
         <v>8</v>
@@ -14079,13 +14073,13 @@
     <row r="447" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A447" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1001033</v>
+        <v>1001007</v>
       </c>
       <c r="B447" s="1" t="s">
-        <v>560</v>
+        <v>798</v>
       </c>
       <c r="C447" s="1">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="D447" s="2" t="s">
         <v>8</v>
@@ -14103,13 +14097,13 @@
     <row r="448" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A448" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1001157</v>
+        <v>1001033</v>
       </c>
       <c r="B448" s="1" t="s">
-        <v>799</v>
+        <v>560</v>
       </c>
       <c r="C448" s="1">
-        <v>157</v>
+        <v>33</v>
       </c>
       <c r="D448" s="2" t="s">
         <v>8</v>
@@ -14127,13 +14121,13 @@
     <row r="449" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A449" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1001158</v>
+        <v>1001157</v>
       </c>
       <c r="B449" s="1" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="C449" s="1">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D449" s="2" t="s">
         <v>8</v>
@@ -14151,19 +14145,19 @@
     <row r="450" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A450" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>1001039</v>
+        <v>1001158</v>
       </c>
       <c r="B450" s="1" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="C450" s="1">
-        <v>39</v>
+        <v>158</v>
       </c>
       <c r="D450" s="2" t="s">
-        <v>802</v>
+        <v>8</v>
       </c>
       <c r="E450" s="1" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="F450" s="1">
         <v>1001</v>
@@ -14174,17 +14168,17 @@
     </row>
     <row r="451" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A451" s="1" t="str">
-        <f t="shared" ref="A451:A514" si="7">F451 &amp; TEXT(C451,"000")</f>
-        <v>1001009</v>
+        <f t="shared" si="6"/>
+        <v>1001039</v>
       </c>
       <c r="B451" s="1" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="C451" s="1">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="D451" s="2" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="E451" s="1" t="s">
         <v>58</v>
@@ -14198,17 +14192,17 @@
     </row>
     <row r="452" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A452" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>1001046</v>
+        <f t="shared" ref="A452:A515" si="7">F452 &amp; TEXT(C452,"000")</f>
+        <v>1001009</v>
       </c>
       <c r="B452" s="1" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="C452" s="1">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="D452" s="2" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="E452" s="1" t="s">
         <v>58</v>
@@ -14223,16 +14217,16 @@
     <row r="453" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A453" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1001028</v>
+        <v>1001046</v>
       </c>
       <c r="B453" s="1" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="C453" s="1">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="D453" s="2" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="E453" s="1" t="s">
         <v>58</v>
@@ -14247,16 +14241,16 @@
     <row r="454" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A454" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1001159</v>
+        <v>1001028</v>
       </c>
       <c r="B454" s="1" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="C454" s="1">
-        <v>159</v>
+        <v>28</v>
       </c>
       <c r="D454" s="2" t="s">
-        <v>8</v>
+        <v>808</v>
       </c>
       <c r="E454" s="1" t="s">
         <v>58</v>
@@ -14271,16 +14265,16 @@
     <row r="455" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A455" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1001017</v>
+        <v>1001159</v>
       </c>
       <c r="B455" s="1" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="C455" s="1">
-        <v>17</v>
+        <v>159</v>
       </c>
       <c r="D455" s="2" t="s">
-        <v>811</v>
+        <v>8</v>
       </c>
       <c r="E455" s="1" t="s">
         <v>58</v>
@@ -14295,16 +14289,16 @@
     <row r="456" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A456" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1001160</v>
+        <v>1001017</v>
       </c>
       <c r="B456" s="1" t="s">
-        <v>267</v>
+        <v>810</v>
       </c>
       <c r="C456" s="1">
-        <v>160</v>
+        <v>17</v>
       </c>
       <c r="D456" s="2" t="s">
-        <v>8</v>
+        <v>811</v>
       </c>
       <c r="E456" s="1" t="s">
         <v>58</v>
@@ -14319,16 +14313,16 @@
     <row r="457" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A457" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1001161</v>
+        <v>1001160</v>
       </c>
       <c r="B457" s="1" t="s">
-        <v>801</v>
+        <v>267</v>
       </c>
       <c r="C457" s="1">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D457" s="2" t="s">
-        <v>812</v>
+        <v>8</v>
       </c>
       <c r="E457" s="1" t="s">
         <v>58</v>
@@ -14343,40 +14337,40 @@
     <row r="458" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A458" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1016001</v>
+        <v>1001161</v>
       </c>
       <c r="B458" s="1" t="s">
-        <v>813</v>
+        <v>801</v>
       </c>
       <c r="C458" s="1">
-        <v>1</v>
-      </c>
-      <c r="D458" s="3" t="s">
-        <v>814</v>
+        <v>161</v>
+      </c>
+      <c r="D458" s="2" t="s">
+        <v>812</v>
       </c>
       <c r="E458" s="1" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="F458" s="1">
-        <v>1016</v>
-      </c>
-      <c r="G458" s="4" t="s">
-        <v>815</v>
+        <v>1001</v>
+      </c>
+      <c r="G458" s="1" t="s">
+        <v>748</v>
       </c>
     </row>
     <row r="459" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A459" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1016012</v>
+        <v>1016001</v>
       </c>
       <c r="B459" s="1" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="C459" s="1">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D459" s="3" t="s">
-        <v>8</v>
+        <v>814</v>
       </c>
       <c r="E459" s="1" t="s">
         <v>13</v>
@@ -14391,13 +14385,13 @@
     <row r="460" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A460" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1016101</v>
+        <v>1016012</v>
       </c>
       <c r="B460" s="1" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="C460" s="1">
-        <v>101</v>
+        <v>12</v>
       </c>
       <c r="D460" s="3" t="s">
         <v>8</v>
@@ -14415,13 +14409,13 @@
     <row r="461" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A461" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1016102</v>
+        <v>1016101</v>
       </c>
       <c r="B461" s="1" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C461" s="1">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D461" s="3" t="s">
         <v>8</v>
@@ -14439,13 +14433,13 @@
     <row r="462" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A462" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1016103</v>
+        <v>1016102</v>
       </c>
       <c r="B462" s="1" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C462" s="1">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D462" s="3" t="s">
         <v>8</v>
@@ -14463,19 +14457,19 @@
     <row r="463" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A463" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1016004</v>
+        <v>1016103</v>
       </c>
       <c r="B463" s="1" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C463" s="1">
-        <v>4</v>
+        <v>103</v>
       </c>
       <c r="D463" s="3" t="s">
-        <v>821</v>
+        <v>8</v>
       </c>
       <c r="E463" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F463" s="1">
         <v>1016</v>
@@ -14487,16 +14481,16 @@
     <row r="464" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A464" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1016005</v>
+        <v>1016004</v>
       </c>
       <c r="B464" s="1" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="C464" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D464" s="3" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="E464" s="1" t="s">
         <v>20</v>
@@ -14511,16 +14505,16 @@
     <row r="465" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A465" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1016104</v>
+        <v>1016005</v>
       </c>
       <c r="B465" s="1" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="C465" s="1">
-        <v>104</v>
+        <v>5</v>
       </c>
       <c r="D465" s="3" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="E465" s="1" t="s">
         <v>20</v>
@@ -14535,16 +14529,16 @@
     <row r="466" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A466" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1016003</v>
+        <v>1016104</v>
       </c>
       <c r="B466" s="1" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="C466" s="1">
-        <v>3</v>
+        <v>104</v>
       </c>
       <c r="D466" s="3" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="E466" s="1" t="s">
         <v>20</v>
@@ -14559,16 +14553,16 @@
     <row r="467" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A467" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1016052</v>
+        <v>1016003</v>
       </c>
       <c r="B467" s="1" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="C467" s="1">
-        <v>52</v>
+        <v>3</v>
       </c>
       <c r="D467" s="3" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="E467" s="1" t="s">
         <v>20</v>
@@ -14583,16 +14577,16 @@
     <row r="468" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A468" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1016020</v>
+        <v>1016052</v>
       </c>
       <c r="B468" s="1" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="C468" s="1">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="D468" s="3" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="E468" s="1" t="s">
         <v>20</v>
@@ -14607,16 +14601,16 @@
     <row r="469" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A469" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1016002</v>
+        <v>1016020</v>
       </c>
       <c r="B469" s="1" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="C469" s="1">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D469" s="3" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="E469" s="1" t="s">
         <v>20</v>
@@ -14631,16 +14625,16 @@
     <row r="470" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A470" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1016015</v>
+        <v>1016002</v>
       </c>
       <c r="B470" s="1" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="C470" s="1">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D470" s="3" t="s">
-        <v>8</v>
+        <v>833</v>
       </c>
       <c r="E470" s="1" t="s">
         <v>20</v>
@@ -14655,13 +14649,13 @@
     <row r="471" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A471" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1016037</v>
+        <v>1016015</v>
       </c>
       <c r="B471" s="1" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="C471" s="1">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="D471" s="3" t="s">
         <v>8</v>
@@ -14679,16 +14673,16 @@
     <row r="472" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A472" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1016033</v>
+        <v>1016037</v>
       </c>
       <c r="B472" s="1" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C472" s="1">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D472" s="3" t="s">
-        <v>837</v>
+        <v>8</v>
       </c>
       <c r="E472" s="1" t="s">
         <v>20</v>
@@ -14703,16 +14697,16 @@
     <row r="473" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A473" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1016106</v>
+        <v>1016033</v>
       </c>
       <c r="B473" s="1" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C473" s="1">
-        <v>106</v>
+        <v>33</v>
       </c>
       <c r="D473" s="3" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="E473" s="1" t="s">
         <v>20</v>
@@ -14727,16 +14721,16 @@
     <row r="474" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A474" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1016107</v>
+        <v>1016106</v>
       </c>
       <c r="B474" s="1" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="C474" s="1">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D474" s="3" t="s">
-        <v>707</v>
+        <v>839</v>
       </c>
       <c r="E474" s="1" t="s">
         <v>20</v>
@@ -14751,19 +14745,19 @@
     <row r="475" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A475" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1016108</v>
+        <v>1016107</v>
       </c>
       <c r="B475" s="1" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="C475" s="1">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D475" s="3" t="s">
-        <v>842</v>
+        <v>707</v>
       </c>
       <c r="E475" s="1" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F475" s="1">
         <v>1016</v>
@@ -14775,16 +14769,16 @@
     <row r="476" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A476" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1016010</v>
+        <v>1016108</v>
       </c>
       <c r="B476" s="1" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="C476" s="1">
-        <v>10</v>
+        <v>108</v>
       </c>
       <c r="D476" s="3" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="E476" s="1" t="s">
         <v>33</v>
@@ -14799,16 +14793,16 @@
     <row r="477" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A477" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1016024</v>
+        <v>1016010</v>
       </c>
       <c r="B477" s="1" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="C477" s="1">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D477" s="3" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="E477" s="1" t="s">
         <v>33</v>
@@ -14823,16 +14817,16 @@
     <row r="478" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A478" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1016007</v>
+        <v>1016024</v>
       </c>
       <c r="B478" s="1" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="C478" s="1">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="D478" s="3" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="E478" s="1" t="s">
         <v>33</v>
@@ -14847,16 +14841,16 @@
     <row r="479" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A479" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1016023</v>
+        <v>1016007</v>
       </c>
       <c r="B479" s="1" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="C479" s="1">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="D479" s="3" t="s">
-        <v>8</v>
+        <v>848</v>
       </c>
       <c r="E479" s="1" t="s">
         <v>33</v>
@@ -14871,16 +14865,16 @@
     <row r="480" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A480" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1016053</v>
+        <v>1016023</v>
       </c>
       <c r="B480" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C480" s="1">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="D480" s="3" t="s">
-        <v>851</v>
+        <v>8</v>
       </c>
       <c r="E480" s="1" t="s">
         <v>33</v>
@@ -14895,16 +14889,16 @@
     <row r="481" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A481" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1016009</v>
+        <v>1016053</v>
       </c>
       <c r="B481" s="1" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="C481" s="1">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="D481" s="3" t="s">
-        <v>8</v>
+        <v>851</v>
       </c>
       <c r="E481" s="1" t="s">
         <v>33</v>
@@ -14919,13 +14913,13 @@
     <row r="482" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A482" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1016006</v>
+        <v>1016009</v>
       </c>
       <c r="B482" s="1" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C482" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D482" s="3" t="s">
         <v>8</v>
@@ -14943,13 +14937,13 @@
     <row r="483" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A483" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1016019</v>
+        <v>1016006</v>
       </c>
       <c r="B483" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="C483" s="1">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="D483" s="3" t="s">
         <v>8</v>
@@ -14967,16 +14961,16 @@
     <row r="484" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A484" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1016016</v>
+        <v>1016019</v>
       </c>
       <c r="B484" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="C484" s="1">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D484" s="3" t="s">
-        <v>856</v>
+        <v>8</v>
       </c>
       <c r="E484" s="1" t="s">
         <v>33</v>
@@ -14991,16 +14985,16 @@
     <row r="485" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A485" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1016018</v>
+        <v>1016016</v>
       </c>
       <c r="B485" s="1" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="C485" s="1">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D485" s="3" t="s">
-        <v>8</v>
+        <v>856</v>
       </c>
       <c r="E485" s="1" t="s">
         <v>33</v>
@@ -15015,13 +15009,13 @@
     <row r="486" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A486" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1016025</v>
+        <v>1016018</v>
       </c>
       <c r="B486" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="C486" s="1">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D486" s="3" t="s">
         <v>8</v>
@@ -15039,16 +15033,16 @@
     <row r="487" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A487" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1016017</v>
+        <v>1016025</v>
       </c>
       <c r="B487" s="1" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="C487" s="1">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D487" s="3" t="s">
-        <v>860</v>
+        <v>8</v>
       </c>
       <c r="E487" s="1" t="s">
         <v>33</v>
@@ -15063,16 +15057,16 @@
     <row r="488" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A488" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1016026</v>
+        <v>1016017</v>
       </c>
       <c r="B488" s="1" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="C488" s="1">
-        <v>26</v>
-      </c>
-      <c r="D488" s="5" t="s">
-        <v>8</v>
+        <v>17</v>
+      </c>
+      <c r="D488" s="3" t="s">
+        <v>860</v>
       </c>
       <c r="E488" s="1" t="s">
         <v>33</v>
@@ -15087,15 +15081,15 @@
     <row r="489" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A489" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1016038</v>
+        <v>1016026</v>
       </c>
       <c r="B489" s="1" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="C489" s="1">
-        <v>38</v>
-      </c>
-      <c r="D489" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D489" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E489" s="1" t="s">
@@ -15111,13 +15105,13 @@
     <row r="490" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A490" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1016057</v>
+        <v>1016038</v>
       </c>
       <c r="B490" s="1" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="C490" s="1">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="D490" s="3" t="s">
         <v>8</v>
@@ -15135,16 +15129,16 @@
     <row r="491" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A491" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1016109</v>
+        <v>1016057</v>
       </c>
       <c r="B491" s="1" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="C491" s="1">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="D491" s="3" t="s">
-        <v>865</v>
+        <v>8</v>
       </c>
       <c r="E491" s="1" t="s">
         <v>33</v>
@@ -15159,16 +15153,16 @@
     <row r="492" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A492" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1016110</v>
+        <v>1016109</v>
       </c>
       <c r="B492" s="1" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="C492" s="1">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D492" s="3" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="E492" s="1" t="s">
         <v>33</v>
@@ -15183,16 +15177,16 @@
     <row r="493" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A493" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1016111</v>
+        <v>1016110</v>
       </c>
       <c r="B493" s="1" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="C493" s="1">
-        <v>111</v>
-      </c>
-      <c r="D493" s="5" t="s">
-        <v>8</v>
+        <v>110</v>
+      </c>
+      <c r="D493" s="3" t="s">
+        <v>867</v>
       </c>
       <c r="E493" s="1" t="s">
         <v>33</v>
@@ -15207,13 +15201,13 @@
     <row r="494" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A494" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1016112</v>
+        <v>1016111</v>
       </c>
       <c r="B494" s="1" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="C494" s="1">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D494" s="5" t="s">
         <v>8</v>
@@ -15231,13 +15225,13 @@
     <row r="495" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A495" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1016113</v>
+        <v>1016112</v>
       </c>
       <c r="B495" s="1" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="C495" s="1">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D495" s="5" t="s">
         <v>8</v>
@@ -15255,13 +15249,13 @@
     <row r="496" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A496" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1016114</v>
+        <v>1016113</v>
       </c>
       <c r="B496" s="1" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="C496" s="1">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D496" s="5" t="s">
         <v>8</v>
@@ -15279,19 +15273,19 @@
     <row r="497" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A497" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1016011</v>
+        <v>1016114</v>
       </c>
       <c r="B497" s="1" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="C497" s="1">
-        <v>11</v>
-      </c>
-      <c r="D497" s="3" t="s">
-        <v>873</v>
+        <v>114</v>
+      </c>
+      <c r="D497" s="5" t="s">
+        <v>8</v>
       </c>
       <c r="E497" s="1" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="F497" s="1">
         <v>1016</v>
@@ -15303,16 +15297,16 @@
     <row r="498" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A498" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1016008</v>
+        <v>1016011</v>
       </c>
       <c r="B498" s="1" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="C498" s="1">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D498" s="3" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="E498" s="1" t="s">
         <v>58</v>
@@ -15327,16 +15321,16 @@
     <row r="499" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A499" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1016115</v>
+        <v>1016008</v>
       </c>
       <c r="B499" s="1" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="C499" s="1">
-        <v>115</v>
-      </c>
-      <c r="D499" s="5" t="s">
         <v>8</v>
+      </c>
+      <c r="D499" s="3" t="s">
+        <v>875</v>
       </c>
       <c r="E499" s="1" t="s">
         <v>58</v>
@@ -15351,16 +15345,16 @@
     <row r="500" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A500" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1016055</v>
+        <v>1016115</v>
       </c>
       <c r="B500" s="1" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="C500" s="1">
-        <v>55</v>
-      </c>
-      <c r="D500" s="3" t="s">
-        <v>878</v>
+        <v>115</v>
+      </c>
+      <c r="D500" s="5" t="s">
+        <v>8</v>
       </c>
       <c r="E500" s="1" t="s">
         <v>58</v>
@@ -15375,16 +15369,16 @@
     <row r="501" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A501" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1016116</v>
+        <v>1016055</v>
       </c>
       <c r="B501" s="1" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="C501" s="1">
-        <v>116</v>
-      </c>
-      <c r="D501" s="5" t="s">
-        <v>8</v>
+        <v>55</v>
+      </c>
+      <c r="D501" s="3" t="s">
+        <v>878</v>
       </c>
       <c r="E501" s="1" t="s">
         <v>58</v>
@@ -15399,13 +15393,13 @@
     <row r="502" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A502" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1016117</v>
+        <v>1016116</v>
       </c>
       <c r="B502" s="1" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="C502" s="1">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D502" s="5" t="s">
         <v>8</v>
@@ -15423,40 +15417,40 @@
     <row r="503" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A503" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1017001</v>
+        <v>1016117</v>
       </c>
       <c r="B503" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="C503" s="1">
-        <v>1</v>
+        <v>117</v>
       </c>
       <c r="D503" s="5" t="s">
-        <v>882</v>
+        <v>8</v>
       </c>
       <c r="E503" s="1" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="F503" s="1">
-        <v>1017</v>
-      </c>
-      <c r="G503" s="1" t="s">
-        <v>883</v>
+        <v>1016</v>
+      </c>
+      <c r="G503" s="4" t="s">
+        <v>815</v>
       </c>
     </row>
     <row r="504" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A504" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1017101</v>
+        <v>1017001</v>
       </c>
       <c r="B504" s="1" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="C504" s="1">
-        <v>101</v>
-      </c>
-      <c r="D504" s="3" t="s">
-        <v>885</v>
+        <v>1</v>
+      </c>
+      <c r="D504" s="5" t="s">
+        <v>882</v>
       </c>
       <c r="E504" s="1" t="s">
         <v>13</v>
@@ -15471,16 +15465,16 @@
     <row r="505" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A505" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1017102</v>
+        <v>1017101</v>
       </c>
       <c r="B505" s="1" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="C505" s="1">
-        <v>102</v>
-      </c>
-      <c r="D505" s="5" t="s">
-        <v>8</v>
+        <v>101</v>
+      </c>
+      <c r="D505" s="3" t="s">
+        <v>885</v>
       </c>
       <c r="E505" s="1" t="s">
         <v>13</v>
@@ -15495,19 +15489,19 @@
     <row r="506" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A506" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1017103</v>
+        <v>1017102</v>
       </c>
       <c r="B506" s="1" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="C506" s="1">
-        <v>103</v>
-      </c>
-      <c r="D506" s="3" t="s">
-        <v>888</v>
+        <v>102</v>
+      </c>
+      <c r="D506" s="5" t="s">
+        <v>8</v>
       </c>
       <c r="E506" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F506" s="1">
         <v>1017</v>
@@ -15519,13 +15513,13 @@
     <row r="507" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A507" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1017015</v>
+        <v>1017103</v>
       </c>
       <c r="B507" s="1" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="C507" s="1">
-        <v>15</v>
+        <v>103</v>
       </c>
       <c r="D507" s="3" t="s">
         <v>888</v>
@@ -15543,16 +15537,16 @@
     <row r="508" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A508" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1017004</v>
+        <v>1017015</v>
       </c>
       <c r="B508" s="1" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C508" s="1">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D508" s="3" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="E508" s="1" t="s">
         <v>20</v>
@@ -15567,16 +15561,16 @@
     <row r="509" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A509" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1017013</v>
+        <v>1017004</v>
       </c>
       <c r="B509" s="1" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="C509" s="1">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D509" s="3" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="E509" s="1" t="s">
         <v>20</v>
@@ -15591,16 +15585,16 @@
     <row r="510" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A510" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1017006</v>
+        <v>1017013</v>
       </c>
       <c r="B510" s="1" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="C510" s="1">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D510" s="3" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="E510" s="1" t="s">
         <v>20</v>
@@ -15615,16 +15609,16 @@
     <row r="511" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A511" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1017002</v>
+        <v>1017006</v>
       </c>
       <c r="B511" s="1" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="C511" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D511" s="3" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="E511" s="1" t="s">
         <v>20</v>
@@ -15639,16 +15633,16 @@
     <row r="512" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A512" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1017104</v>
+        <v>1017002</v>
       </c>
       <c r="B512" s="1" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="C512" s="1">
-        <v>104</v>
+        <v>2</v>
       </c>
       <c r="D512" s="3" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="E512" s="1" t="s">
         <v>20</v>
@@ -15663,16 +15657,16 @@
     <row r="513" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A513" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1017024</v>
+        <v>1017104</v>
       </c>
       <c r="B513" s="1" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="C513" s="1">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="D513" s="3" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="E513" s="1" t="s">
         <v>20</v>
@@ -15687,16 +15681,16 @@
     <row r="514" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A514" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>1017005</v>
+        <v>1017024</v>
       </c>
       <c r="B514" s="1" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="C514" s="1">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="D514" s="3" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="E514" s="1" t="s">
         <v>20</v>
@@ -15710,17 +15704,17 @@
     </row>
     <row r="515" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A515" s="1" t="str">
-        <f t="shared" ref="A515:A531" si="8">F515 &amp; TEXT(C515,"000")</f>
-        <v>1017012</v>
+        <f t="shared" si="7"/>
+        <v>1017005</v>
       </c>
       <c r="B515" s="1" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="C515" s="1">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D515" s="3" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="E515" s="1" t="s">
         <v>20</v>
@@ -15734,17 +15728,17 @@
     </row>
     <row r="516" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A516" s="1" t="str">
-        <f t="shared" si="8"/>
-        <v>1017023</v>
+        <f t="shared" ref="A516:A532" si="8">F516 &amp; TEXT(C516,"000")</f>
+        <v>1017012</v>
       </c>
       <c r="B516" s="1" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="C516" s="1">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D516" s="3" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="E516" s="1" t="s">
         <v>20</v>
@@ -15759,16 +15753,16 @@
     <row r="517" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A517" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>1017057</v>
+        <v>1017023</v>
       </c>
       <c r="B517" s="1" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="C517" s="1">
-        <v>57</v>
-      </c>
-      <c r="D517" s="5" t="s">
-        <v>8</v>
+        <v>23</v>
+      </c>
+      <c r="D517" s="3" t="s">
+        <v>907</v>
       </c>
       <c r="E517" s="1" t="s">
         <v>20</v>
@@ -15783,16 +15777,16 @@
     <row r="518" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A518" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>1017106</v>
+        <v>1017057</v>
       </c>
       <c r="B518" s="1" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C518" s="1">
-        <v>106</v>
-      </c>
-      <c r="D518" s="3" t="s">
-        <v>910</v>
+        <v>57</v>
+      </c>
+      <c r="D518" s="5" t="s">
+        <v>8</v>
       </c>
       <c r="E518" s="1" t="s">
         <v>20</v>
@@ -15807,19 +15801,19 @@
     <row r="519" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A519" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>1017019</v>
+        <v>1017106</v>
       </c>
       <c r="B519" s="1" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="C519" s="1">
-        <v>19</v>
+        <v>106</v>
       </c>
       <c r="D519" s="3" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="E519" s="1" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F519" s="1">
         <v>1017</v>
@@ -15831,16 +15825,16 @@
     <row r="520" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A520" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>1017007</v>
+        <v>1017019</v>
       </c>
       <c r="B520" s="1" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="C520" s="1">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D520" s="3" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="E520" s="1" t="s">
         <v>33</v>
@@ -15855,16 +15849,16 @@
     <row r="521" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A521" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>1017008</v>
+        <v>1017007</v>
       </c>
       <c r="B521" s="1" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="C521" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D521" s="3" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="E521" s="1" t="s">
         <v>33</v>
@@ -15879,16 +15873,16 @@
     <row r="522" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A522" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>1017029</v>
+        <v>1017008</v>
       </c>
       <c r="B522" s="1" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="C522" s="1">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D522" s="3" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="E522" s="1" t="s">
         <v>33</v>
@@ -15903,16 +15897,16 @@
     <row r="523" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A523" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>1017016</v>
+        <v>1017029</v>
       </c>
       <c r="B523" s="1" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="C523" s="1">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="D523" s="3" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="E523" s="1" t="s">
         <v>33</v>
@@ -15927,16 +15921,16 @@
     <row r="524" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A524" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>1017010</v>
+        <v>1017016</v>
       </c>
       <c r="B524" s="1" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="C524" s="1">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D524" s="3" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="E524" s="1" t="s">
         <v>33</v>
@@ -15951,16 +15945,16 @@
     <row r="525" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A525" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>1017021</v>
+        <v>1017010</v>
       </c>
       <c r="B525" s="1" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="C525" s="1">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="D525" s="3" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="E525" s="1" t="s">
         <v>33</v>
@@ -15975,16 +15969,16 @@
     <row r="526" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A526" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>1017067</v>
+        <v>1017021</v>
       </c>
       <c r="B526" s="1" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="C526" s="1">
-        <v>67</v>
-      </c>
-      <c r="D526" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
+      </c>
+      <c r="D526" s="3" t="s">
+        <v>924</v>
       </c>
       <c r="E526" s="1" t="s">
         <v>33</v>
@@ -15999,19 +15993,19 @@
     <row r="527" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A527" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>1017011</v>
+        <v>1017067</v>
       </c>
       <c r="B527" s="1" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="C527" s="1">
-        <v>11</v>
-      </c>
-      <c r="D527" s="3" t="s">
-        <v>927</v>
+        <v>67</v>
+      </c>
+      <c r="D527" s="5" t="s">
+        <v>8</v>
       </c>
       <c r="E527" s="1" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="F527" s="1">
         <v>1017</v>
@@ -16023,15 +16017,15 @@
     <row r="528" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A528" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>1017113</v>
+        <v>1017011</v>
       </c>
       <c r="B528" s="1" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="C528" s="1">
-        <v>113</v>
-      </c>
-      <c r="D528" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D528" s="3" t="s">
         <v>927</v>
       </c>
       <c r="E528" s="1" t="s">
@@ -16047,16 +16041,16 @@
     <row r="529" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A529" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>1017009</v>
+        <v>1017113</v>
       </c>
       <c r="B529" s="1" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="C529" s="1">
-        <v>9</v>
-      </c>
-      <c r="D529" s="3" t="s">
-        <v>930</v>
+        <v>113</v>
+      </c>
+      <c r="D529" s="5" t="s">
+        <v>927</v>
       </c>
       <c r="E529" s="1" t="s">
         <v>58</v>
@@ -16071,16 +16065,16 @@
     <row r="530" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A530" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>1017018</v>
+        <v>1017009</v>
       </c>
       <c r="B530" s="1" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="C530" s="1">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D530" s="3" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="E530" s="1" t="s">
         <v>58</v>
@@ -16095,16 +16089,16 @@
     <row r="531" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A531" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>1017026</v>
+        <v>1017018</v>
       </c>
       <c r="B531" s="1" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="C531" s="1">
-        <v>26</v>
-      </c>
-      <c r="D531" s="5" t="s">
-        <v>934</v>
+        <v>18</v>
+      </c>
+      <c r="D531" s="3" t="s">
+        <v>932</v>
       </c>
       <c r="E531" s="1" t="s">
         <v>58</v>
@@ -16116,31 +16110,54 @@
         <v>883</v>
       </c>
     </row>
-    <row r="532" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A532" s="7" t="str">
-        <f>F532 &amp; TEXT(C532,"000")</f>
+    <row r="532" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A532" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v>1017026</v>
+      </c>
+      <c r="B532" s="1" t="s">
+        <v>933</v>
+      </c>
+      <c r="C532" s="1">
+        <v>26</v>
+      </c>
+      <c r="D532" s="5" t="s">
+        <v>934</v>
+      </c>
+      <c r="E532" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F532" s="1">
+        <v>1017</v>
+      </c>
+      <c r="G532" s="1" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="533" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A533" t="str">
+        <f>F533 &amp; TEXT(C533,"000")</f>
         <v>1002029</v>
       </c>
-      <c r="B532" s="7" t="s">
+      <c r="B533" t="s">
         <v>935</v>
       </c>
-      <c r="C532" s="7">
+      <c r="C533">
         <v>29</v>
       </c>
-      <c r="D532" s="3" t="s">
+      <c r="D533" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E532" s="7" t="s">
+      <c r="E533" t="s">
         <v>58</v>
       </c>
-      <c r="F532" s="7">
+      <c r="F533">
         <v>1002</v>
       </c>
-      <c r="G532" s="1" t="s">
+      <c r="G533" s="1" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="533" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="534" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="535" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="536" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -16608,6 +16625,7 @@
     <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -16848,298 +16866,298 @@
     <hyperlink ref="D237" r:id="rId236" xr:uid="{00000000-0004-0000-0000-0000EB000000}"/>
     <hyperlink ref="D238" r:id="rId237" xr:uid="{00000000-0004-0000-0000-0000EC000000}"/>
     <hyperlink ref="D239" r:id="rId238" xr:uid="{00000000-0004-0000-0000-0000ED000000}"/>
-    <hyperlink ref="D240" r:id="rId239" xr:uid="{00000000-0004-0000-0000-0000EE000000}"/>
-    <hyperlink ref="D241" r:id="rId240" xr:uid="{00000000-0004-0000-0000-0000EF000000}"/>
-    <hyperlink ref="D242" r:id="rId241" xr:uid="{00000000-0004-0000-0000-0000F0000000}"/>
-    <hyperlink ref="D243" r:id="rId242" xr:uid="{00000000-0004-0000-0000-0000F1000000}"/>
-    <hyperlink ref="D244" r:id="rId243" xr:uid="{00000000-0004-0000-0000-0000F2000000}"/>
-    <hyperlink ref="D245" r:id="rId244" xr:uid="{00000000-0004-0000-0000-0000F3000000}"/>
-    <hyperlink ref="D246" r:id="rId245" xr:uid="{00000000-0004-0000-0000-0000F4000000}"/>
-    <hyperlink ref="D247" r:id="rId246" xr:uid="{00000000-0004-0000-0000-0000F5000000}"/>
-    <hyperlink ref="D248" r:id="rId247" xr:uid="{00000000-0004-0000-0000-0000F6000000}"/>
-    <hyperlink ref="D249" r:id="rId248" xr:uid="{00000000-0004-0000-0000-0000F7000000}"/>
-    <hyperlink ref="D250" r:id="rId249" xr:uid="{00000000-0004-0000-0000-0000F8000000}"/>
-    <hyperlink ref="D251" r:id="rId250" xr:uid="{00000000-0004-0000-0000-0000F9000000}"/>
-    <hyperlink ref="D252" r:id="rId251" xr:uid="{00000000-0004-0000-0000-0000FA000000}"/>
-    <hyperlink ref="D253" r:id="rId252" xr:uid="{00000000-0004-0000-0000-0000FB000000}"/>
-    <hyperlink ref="D254" r:id="rId253" xr:uid="{00000000-0004-0000-0000-0000FC000000}"/>
-    <hyperlink ref="D255" r:id="rId254" xr:uid="{00000000-0004-0000-0000-0000FD000000}"/>
-    <hyperlink ref="D256" r:id="rId255" xr:uid="{00000000-0004-0000-0000-0000FE000000}"/>
-    <hyperlink ref="D257" r:id="rId256" xr:uid="{00000000-0004-0000-0000-0000FF000000}"/>
-    <hyperlink ref="D258" r:id="rId257" xr:uid="{00000000-0004-0000-0000-000000010000}"/>
-    <hyperlink ref="D259" r:id="rId258" xr:uid="{00000000-0004-0000-0000-000001010000}"/>
-    <hyperlink ref="D260" r:id="rId259" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
-    <hyperlink ref="D261" r:id="rId260" xr:uid="{00000000-0004-0000-0000-000003010000}"/>
-    <hyperlink ref="D262" r:id="rId261" xr:uid="{00000000-0004-0000-0000-000004010000}"/>
-    <hyperlink ref="D263" r:id="rId262" xr:uid="{00000000-0004-0000-0000-000005010000}"/>
-    <hyperlink ref="D264" r:id="rId263" xr:uid="{00000000-0004-0000-0000-000006010000}"/>
-    <hyperlink ref="D265" r:id="rId264" xr:uid="{00000000-0004-0000-0000-000007010000}"/>
-    <hyperlink ref="D266" r:id="rId265" xr:uid="{00000000-0004-0000-0000-000008010000}"/>
-    <hyperlink ref="D267" r:id="rId266" xr:uid="{00000000-0004-0000-0000-000009010000}"/>
-    <hyperlink ref="D268" r:id="rId267" xr:uid="{00000000-0004-0000-0000-00000A010000}"/>
-    <hyperlink ref="D269" r:id="rId268" xr:uid="{00000000-0004-0000-0000-00000B010000}"/>
-    <hyperlink ref="D270" r:id="rId269" xr:uid="{00000000-0004-0000-0000-00000C010000}"/>
-    <hyperlink ref="D271" r:id="rId270" xr:uid="{00000000-0004-0000-0000-00000D010000}"/>
-    <hyperlink ref="D272" r:id="rId271" xr:uid="{00000000-0004-0000-0000-00000E010000}"/>
-    <hyperlink ref="D273" r:id="rId272" xr:uid="{00000000-0004-0000-0000-00000F010000}"/>
-    <hyperlink ref="D274" r:id="rId273" xr:uid="{00000000-0004-0000-0000-000010010000}"/>
-    <hyperlink ref="D275" r:id="rId274" xr:uid="{00000000-0004-0000-0000-000011010000}"/>
-    <hyperlink ref="D276" r:id="rId275" xr:uid="{00000000-0004-0000-0000-000012010000}"/>
-    <hyperlink ref="D277" r:id="rId276" xr:uid="{00000000-0004-0000-0000-000013010000}"/>
-    <hyperlink ref="D278" r:id="rId277" xr:uid="{00000000-0004-0000-0000-000014010000}"/>
-    <hyperlink ref="D279" r:id="rId278" xr:uid="{00000000-0004-0000-0000-000015010000}"/>
-    <hyperlink ref="D280" r:id="rId279" xr:uid="{00000000-0004-0000-0000-000016010000}"/>
-    <hyperlink ref="D281" r:id="rId280" xr:uid="{00000000-0004-0000-0000-000017010000}"/>
-    <hyperlink ref="D282" r:id="rId281" xr:uid="{00000000-0004-0000-0000-000018010000}"/>
-    <hyperlink ref="D283" r:id="rId282" xr:uid="{00000000-0004-0000-0000-000019010000}"/>
-    <hyperlink ref="D284" r:id="rId283" xr:uid="{00000000-0004-0000-0000-00001A010000}"/>
-    <hyperlink ref="D285" r:id="rId284" xr:uid="{00000000-0004-0000-0000-00001B010000}"/>
-    <hyperlink ref="D286" r:id="rId285" xr:uid="{00000000-0004-0000-0000-00001C010000}"/>
-    <hyperlink ref="D287" r:id="rId286" xr:uid="{00000000-0004-0000-0000-00001D010000}"/>
-    <hyperlink ref="D288" r:id="rId287" xr:uid="{00000000-0004-0000-0000-00001E010000}"/>
-    <hyperlink ref="D289" r:id="rId288" xr:uid="{00000000-0004-0000-0000-00001F010000}"/>
-    <hyperlink ref="D290" r:id="rId289" xr:uid="{00000000-0004-0000-0000-000020010000}"/>
-    <hyperlink ref="D291" r:id="rId290" xr:uid="{00000000-0004-0000-0000-000021010000}"/>
-    <hyperlink ref="D292" r:id="rId291" xr:uid="{00000000-0004-0000-0000-000022010000}"/>
-    <hyperlink ref="D293" r:id="rId292" xr:uid="{00000000-0004-0000-0000-000023010000}"/>
-    <hyperlink ref="D294" r:id="rId293" xr:uid="{00000000-0004-0000-0000-000024010000}"/>
-    <hyperlink ref="D295" r:id="rId294" xr:uid="{00000000-0004-0000-0000-000025010000}"/>
-    <hyperlink ref="D296" r:id="rId295" xr:uid="{00000000-0004-0000-0000-000026010000}"/>
-    <hyperlink ref="D297" r:id="rId296" xr:uid="{00000000-0004-0000-0000-000027010000}"/>
-    <hyperlink ref="D298" r:id="rId297" xr:uid="{00000000-0004-0000-0000-000028010000}"/>
-    <hyperlink ref="D299" r:id="rId298" xr:uid="{00000000-0004-0000-0000-000029010000}"/>
-    <hyperlink ref="D300" r:id="rId299" xr:uid="{00000000-0004-0000-0000-00002A010000}"/>
-    <hyperlink ref="D301" r:id="rId300" xr:uid="{00000000-0004-0000-0000-00002B010000}"/>
-    <hyperlink ref="D302" r:id="rId301" xr:uid="{00000000-0004-0000-0000-00002C010000}"/>
-    <hyperlink ref="D303" r:id="rId302" xr:uid="{00000000-0004-0000-0000-00002D010000}"/>
-    <hyperlink ref="D304" r:id="rId303" xr:uid="{00000000-0004-0000-0000-00002E010000}"/>
-    <hyperlink ref="D305" r:id="rId304" xr:uid="{00000000-0004-0000-0000-00002F010000}"/>
-    <hyperlink ref="D306" r:id="rId305" xr:uid="{00000000-0004-0000-0000-000030010000}"/>
-    <hyperlink ref="D307" r:id="rId306" xr:uid="{00000000-0004-0000-0000-000031010000}"/>
-    <hyperlink ref="D308" r:id="rId307" xr:uid="{00000000-0004-0000-0000-000032010000}"/>
-    <hyperlink ref="D309" r:id="rId308" xr:uid="{00000000-0004-0000-0000-000033010000}"/>
-    <hyperlink ref="D310" r:id="rId309" xr:uid="{00000000-0004-0000-0000-000034010000}"/>
-    <hyperlink ref="D311" r:id="rId310" xr:uid="{00000000-0004-0000-0000-000035010000}"/>
-    <hyperlink ref="D312" r:id="rId311" xr:uid="{00000000-0004-0000-0000-000036010000}"/>
-    <hyperlink ref="D313" r:id="rId312" xr:uid="{00000000-0004-0000-0000-000037010000}"/>
-    <hyperlink ref="D314" r:id="rId313" xr:uid="{00000000-0004-0000-0000-000038010000}"/>
-    <hyperlink ref="D315" r:id="rId314" xr:uid="{00000000-0004-0000-0000-000039010000}"/>
-    <hyperlink ref="D316" r:id="rId315" xr:uid="{00000000-0004-0000-0000-00003A010000}"/>
-    <hyperlink ref="D317" r:id="rId316" xr:uid="{00000000-0004-0000-0000-00003B010000}"/>
-    <hyperlink ref="D318" r:id="rId317" xr:uid="{00000000-0004-0000-0000-00003C010000}"/>
-    <hyperlink ref="D319" r:id="rId318" xr:uid="{00000000-0004-0000-0000-00003D010000}"/>
-    <hyperlink ref="D320" r:id="rId319" xr:uid="{00000000-0004-0000-0000-00003E010000}"/>
-    <hyperlink ref="D321" r:id="rId320" xr:uid="{00000000-0004-0000-0000-00003F010000}"/>
-    <hyperlink ref="D322" r:id="rId321" xr:uid="{00000000-0004-0000-0000-000040010000}"/>
-    <hyperlink ref="D323" r:id="rId322" xr:uid="{00000000-0004-0000-0000-000041010000}"/>
-    <hyperlink ref="D324" r:id="rId323" xr:uid="{00000000-0004-0000-0000-000042010000}"/>
-    <hyperlink ref="D325" r:id="rId324" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
-    <hyperlink ref="D326" r:id="rId325" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
-    <hyperlink ref="D327" r:id="rId326" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
-    <hyperlink ref="D328" r:id="rId327" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
-    <hyperlink ref="D329" r:id="rId328" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
-    <hyperlink ref="D330" r:id="rId329" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
-    <hyperlink ref="D331" r:id="rId330" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
-    <hyperlink ref="D332" r:id="rId331" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
-    <hyperlink ref="D333" r:id="rId332" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
-    <hyperlink ref="D334" r:id="rId333" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
-    <hyperlink ref="D335" r:id="rId334" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
-    <hyperlink ref="D336" r:id="rId335" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
-    <hyperlink ref="D337" r:id="rId336" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
-    <hyperlink ref="D338" r:id="rId337" xr:uid="{00000000-0004-0000-0000-000050010000}"/>
-    <hyperlink ref="D339" r:id="rId338" xr:uid="{00000000-0004-0000-0000-000051010000}"/>
-    <hyperlink ref="D340" r:id="rId339" xr:uid="{00000000-0004-0000-0000-000052010000}"/>
-    <hyperlink ref="D341" r:id="rId340" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
-    <hyperlink ref="D342" r:id="rId341" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
-    <hyperlink ref="D343" r:id="rId342" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
-    <hyperlink ref="D344" r:id="rId343" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
-    <hyperlink ref="D345" r:id="rId344" xr:uid="{00000000-0004-0000-0000-000057010000}"/>
-    <hyperlink ref="D346" r:id="rId345" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
-    <hyperlink ref="D347" r:id="rId346" xr:uid="{00000000-0004-0000-0000-00005A010000}"/>
-    <hyperlink ref="D348" r:id="rId347" xr:uid="{00000000-0004-0000-0000-00005B010000}"/>
-    <hyperlink ref="D349" r:id="rId348" xr:uid="{00000000-0004-0000-0000-00005C010000}"/>
-    <hyperlink ref="D350" r:id="rId349" xr:uid="{00000000-0004-0000-0000-00005D010000}"/>
-    <hyperlink ref="D351" r:id="rId350" xr:uid="{00000000-0004-0000-0000-00005E010000}"/>
-    <hyperlink ref="D352" r:id="rId351" xr:uid="{00000000-0004-0000-0000-00005F010000}"/>
-    <hyperlink ref="D353" r:id="rId352" xr:uid="{00000000-0004-0000-0000-000060010000}"/>
-    <hyperlink ref="D354" r:id="rId353" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
-    <hyperlink ref="D355" r:id="rId354" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
-    <hyperlink ref="D356" r:id="rId355" xr:uid="{00000000-0004-0000-0000-000063010000}"/>
-    <hyperlink ref="D357" r:id="rId356" xr:uid="{00000000-0004-0000-0000-000064010000}"/>
-    <hyperlink ref="D358" r:id="rId357" xr:uid="{00000000-0004-0000-0000-000065010000}"/>
-    <hyperlink ref="D359" r:id="rId358" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
-    <hyperlink ref="D360" r:id="rId359" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
-    <hyperlink ref="D361" r:id="rId360" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
-    <hyperlink ref="D362" r:id="rId361" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
-    <hyperlink ref="D363" r:id="rId362" xr:uid="{00000000-0004-0000-0000-00006A010000}"/>
-    <hyperlink ref="D364" r:id="rId363" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
-    <hyperlink ref="D365" r:id="rId364" xr:uid="{00000000-0004-0000-0000-00006C010000}"/>
-    <hyperlink ref="D366" r:id="rId365" xr:uid="{00000000-0004-0000-0000-00006D010000}"/>
-    <hyperlink ref="D367" r:id="rId366" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
-    <hyperlink ref="D368" r:id="rId367" xr:uid="{00000000-0004-0000-0000-00006F010000}"/>
-    <hyperlink ref="D369" r:id="rId368" xr:uid="{00000000-0004-0000-0000-000070010000}"/>
-    <hyperlink ref="D370" r:id="rId369" xr:uid="{00000000-0004-0000-0000-000071010000}"/>
-    <hyperlink ref="D371" r:id="rId370" xr:uid="{00000000-0004-0000-0000-000072010000}"/>
-    <hyperlink ref="D372" r:id="rId371" xr:uid="{00000000-0004-0000-0000-000073010000}"/>
-    <hyperlink ref="D373" r:id="rId372" xr:uid="{00000000-0004-0000-0000-000074010000}"/>
-    <hyperlink ref="D374" r:id="rId373" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
-    <hyperlink ref="D375" r:id="rId374" xr:uid="{00000000-0004-0000-0000-000076010000}"/>
-    <hyperlink ref="D376" r:id="rId375" xr:uid="{00000000-0004-0000-0000-000077010000}"/>
-    <hyperlink ref="D377" r:id="rId376" xr:uid="{00000000-0004-0000-0000-000078010000}"/>
-    <hyperlink ref="D378" r:id="rId377" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
-    <hyperlink ref="D379" r:id="rId378" xr:uid="{00000000-0004-0000-0000-00007A010000}"/>
-    <hyperlink ref="D380" r:id="rId379" xr:uid="{00000000-0004-0000-0000-00007B010000}"/>
-    <hyperlink ref="D381" r:id="rId380" xr:uid="{00000000-0004-0000-0000-00007C010000}"/>
-    <hyperlink ref="D382" r:id="rId381" xr:uid="{00000000-0004-0000-0000-00007D010000}"/>
-    <hyperlink ref="D383" r:id="rId382" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
-    <hyperlink ref="D384" r:id="rId383" xr:uid="{00000000-0004-0000-0000-00007F010000}"/>
-    <hyperlink ref="D385" r:id="rId384" xr:uid="{00000000-0004-0000-0000-000080010000}"/>
-    <hyperlink ref="D386" r:id="rId385" xr:uid="{00000000-0004-0000-0000-000081010000}"/>
-    <hyperlink ref="D387" r:id="rId386" xr:uid="{00000000-0004-0000-0000-000082010000}"/>
-    <hyperlink ref="D388" r:id="rId387" xr:uid="{00000000-0004-0000-0000-000083010000}"/>
-    <hyperlink ref="D389" r:id="rId388" xr:uid="{00000000-0004-0000-0000-000084010000}"/>
-    <hyperlink ref="D390" r:id="rId389" xr:uid="{00000000-0004-0000-0000-000085010000}"/>
-    <hyperlink ref="D391" r:id="rId390" xr:uid="{00000000-0004-0000-0000-000086010000}"/>
-    <hyperlink ref="D392" r:id="rId391" xr:uid="{00000000-0004-0000-0000-000087010000}"/>
-    <hyperlink ref="D393" r:id="rId392" xr:uid="{00000000-0004-0000-0000-000088010000}"/>
-    <hyperlink ref="D394" r:id="rId393" xr:uid="{00000000-0004-0000-0000-000089010000}"/>
-    <hyperlink ref="D395" r:id="rId394" xr:uid="{00000000-0004-0000-0000-00008A010000}"/>
-    <hyperlink ref="D396" r:id="rId395" xr:uid="{00000000-0004-0000-0000-00008B010000}"/>
-    <hyperlink ref="D397" r:id="rId396" xr:uid="{00000000-0004-0000-0000-00008C010000}"/>
-    <hyperlink ref="D398" r:id="rId397" xr:uid="{00000000-0004-0000-0000-00008D010000}"/>
-    <hyperlink ref="D399" r:id="rId398" xr:uid="{00000000-0004-0000-0000-00008E010000}"/>
-    <hyperlink ref="D400" r:id="rId399" xr:uid="{00000000-0004-0000-0000-00008F010000}"/>
-    <hyperlink ref="D401" r:id="rId400" xr:uid="{00000000-0004-0000-0000-000090010000}"/>
-    <hyperlink ref="D402" r:id="rId401" xr:uid="{00000000-0004-0000-0000-000091010000}"/>
-    <hyperlink ref="D403" r:id="rId402" xr:uid="{00000000-0004-0000-0000-000092010000}"/>
-    <hyperlink ref="D404" r:id="rId403" xr:uid="{00000000-0004-0000-0000-000093010000}"/>
-    <hyperlink ref="D405" r:id="rId404" xr:uid="{00000000-0004-0000-0000-000094010000}"/>
-    <hyperlink ref="D406" r:id="rId405" xr:uid="{00000000-0004-0000-0000-000095010000}"/>
-    <hyperlink ref="D407" r:id="rId406" xr:uid="{00000000-0004-0000-0000-000096010000}"/>
-    <hyperlink ref="D408" r:id="rId407" xr:uid="{00000000-0004-0000-0000-000097010000}"/>
-    <hyperlink ref="D409" r:id="rId408" xr:uid="{00000000-0004-0000-0000-000098010000}"/>
-    <hyperlink ref="D410" r:id="rId409" xr:uid="{00000000-0004-0000-0000-000099010000}"/>
-    <hyperlink ref="D411" r:id="rId410" xr:uid="{00000000-0004-0000-0000-00009A010000}"/>
-    <hyperlink ref="D412" r:id="rId411" xr:uid="{00000000-0004-0000-0000-00009B010000}"/>
-    <hyperlink ref="D413" r:id="rId412" xr:uid="{00000000-0004-0000-0000-00009C010000}"/>
-    <hyperlink ref="D414" r:id="rId413" xr:uid="{00000000-0004-0000-0000-00009D010000}"/>
-    <hyperlink ref="D415" r:id="rId414" xr:uid="{00000000-0004-0000-0000-00009E010000}"/>
-    <hyperlink ref="D416" r:id="rId415" xr:uid="{00000000-0004-0000-0000-00009F010000}"/>
-    <hyperlink ref="D417" r:id="rId416" xr:uid="{00000000-0004-0000-0000-0000A0010000}"/>
-    <hyperlink ref="D418" r:id="rId417" xr:uid="{00000000-0004-0000-0000-0000A1010000}"/>
-    <hyperlink ref="D419" r:id="rId418" xr:uid="{00000000-0004-0000-0000-0000A2010000}"/>
-    <hyperlink ref="D420" r:id="rId419" xr:uid="{00000000-0004-0000-0000-0000A3010000}"/>
-    <hyperlink ref="D421" r:id="rId420" xr:uid="{00000000-0004-0000-0000-0000A4010000}"/>
-    <hyperlink ref="D422" r:id="rId421" xr:uid="{00000000-0004-0000-0000-0000A5010000}"/>
-    <hyperlink ref="D423" r:id="rId422" xr:uid="{00000000-0004-0000-0000-0000A6010000}"/>
-    <hyperlink ref="D424" r:id="rId423" xr:uid="{00000000-0004-0000-0000-0000A7010000}"/>
-    <hyperlink ref="D425" r:id="rId424" xr:uid="{00000000-0004-0000-0000-0000A8010000}"/>
-    <hyperlink ref="D426" r:id="rId425" xr:uid="{00000000-0004-0000-0000-0000A9010000}"/>
-    <hyperlink ref="D427" r:id="rId426" xr:uid="{00000000-0004-0000-0000-0000AA010000}"/>
-    <hyperlink ref="D428" r:id="rId427" xr:uid="{00000000-0004-0000-0000-0000AB010000}"/>
-    <hyperlink ref="D429" r:id="rId428" xr:uid="{00000000-0004-0000-0000-0000AC010000}"/>
-    <hyperlink ref="D430" r:id="rId429" xr:uid="{00000000-0004-0000-0000-0000AD010000}"/>
-    <hyperlink ref="D431" r:id="rId430" xr:uid="{00000000-0004-0000-0000-0000AE010000}"/>
-    <hyperlink ref="D432" r:id="rId431" xr:uid="{00000000-0004-0000-0000-0000AF010000}"/>
-    <hyperlink ref="D433" r:id="rId432" xr:uid="{00000000-0004-0000-0000-0000B0010000}"/>
-    <hyperlink ref="D434" r:id="rId433" xr:uid="{00000000-0004-0000-0000-0000B1010000}"/>
-    <hyperlink ref="D435" r:id="rId434" xr:uid="{00000000-0004-0000-0000-0000B2010000}"/>
-    <hyperlink ref="D436" r:id="rId435" xr:uid="{00000000-0004-0000-0000-0000B3010000}"/>
-    <hyperlink ref="D437" r:id="rId436" xr:uid="{00000000-0004-0000-0000-0000B4010000}"/>
-    <hyperlink ref="D438" r:id="rId437" xr:uid="{00000000-0004-0000-0000-0000B5010000}"/>
-    <hyperlink ref="D439" r:id="rId438" xr:uid="{00000000-0004-0000-0000-0000B6010000}"/>
-    <hyperlink ref="D440" r:id="rId439" xr:uid="{00000000-0004-0000-0000-0000B7010000}"/>
-    <hyperlink ref="D441" r:id="rId440" xr:uid="{00000000-0004-0000-0000-0000B8010000}"/>
-    <hyperlink ref="D442" r:id="rId441" xr:uid="{00000000-0004-0000-0000-0000B9010000}"/>
-    <hyperlink ref="D443" r:id="rId442" xr:uid="{00000000-0004-0000-0000-0000BA010000}"/>
-    <hyperlink ref="D444" r:id="rId443" xr:uid="{00000000-0004-0000-0000-0000BB010000}"/>
-    <hyperlink ref="D445" r:id="rId444" xr:uid="{00000000-0004-0000-0000-0000BC010000}"/>
-    <hyperlink ref="D446" r:id="rId445" xr:uid="{00000000-0004-0000-0000-0000BD010000}"/>
-    <hyperlink ref="D447" r:id="rId446" xr:uid="{00000000-0004-0000-0000-0000BE010000}"/>
-    <hyperlink ref="D448" r:id="rId447" xr:uid="{00000000-0004-0000-0000-0000BF010000}"/>
-    <hyperlink ref="D449" r:id="rId448" xr:uid="{00000000-0004-0000-0000-0000C0010000}"/>
-    <hyperlink ref="D450" r:id="rId449" xr:uid="{00000000-0004-0000-0000-0000C1010000}"/>
-    <hyperlink ref="D451" r:id="rId450" xr:uid="{00000000-0004-0000-0000-0000C2010000}"/>
-    <hyperlink ref="D452" r:id="rId451" xr:uid="{00000000-0004-0000-0000-0000C3010000}"/>
-    <hyperlink ref="D453" r:id="rId452" xr:uid="{00000000-0004-0000-0000-0000C4010000}"/>
-    <hyperlink ref="D454" r:id="rId453" xr:uid="{00000000-0004-0000-0000-0000C5010000}"/>
-    <hyperlink ref="D455" r:id="rId454" xr:uid="{00000000-0004-0000-0000-0000C6010000}"/>
-    <hyperlink ref="D456" r:id="rId455" xr:uid="{00000000-0004-0000-0000-0000C7010000}"/>
-    <hyperlink ref="D457" r:id="rId456" xr:uid="{00000000-0004-0000-0000-0000C8010000}"/>
-    <hyperlink ref="D458" r:id="rId457" xr:uid="{00000000-0004-0000-0000-0000C9010000}"/>
-    <hyperlink ref="D459" r:id="rId458" xr:uid="{00000000-0004-0000-0000-0000CA010000}"/>
-    <hyperlink ref="D460" r:id="rId459" xr:uid="{00000000-0004-0000-0000-0000CB010000}"/>
-    <hyperlink ref="D461" r:id="rId460" xr:uid="{00000000-0004-0000-0000-0000CC010000}"/>
-    <hyperlink ref="D462" r:id="rId461" xr:uid="{00000000-0004-0000-0000-0000CD010000}"/>
-    <hyperlink ref="D463" r:id="rId462" xr:uid="{00000000-0004-0000-0000-0000CE010000}"/>
-    <hyperlink ref="D464" r:id="rId463" xr:uid="{00000000-0004-0000-0000-0000CF010000}"/>
-    <hyperlink ref="D465" r:id="rId464" xr:uid="{00000000-0004-0000-0000-0000D0010000}"/>
-    <hyperlink ref="D466" r:id="rId465" xr:uid="{00000000-0004-0000-0000-0000D1010000}"/>
-    <hyperlink ref="D467" r:id="rId466" xr:uid="{00000000-0004-0000-0000-0000D2010000}"/>
-    <hyperlink ref="D468" r:id="rId467" xr:uid="{00000000-0004-0000-0000-0000D3010000}"/>
-    <hyperlink ref="D469" r:id="rId468" xr:uid="{00000000-0004-0000-0000-0000D4010000}"/>
-    <hyperlink ref="D470" r:id="rId469" xr:uid="{00000000-0004-0000-0000-0000D5010000}"/>
-    <hyperlink ref="D471" r:id="rId470" xr:uid="{00000000-0004-0000-0000-0000D6010000}"/>
-    <hyperlink ref="D472" r:id="rId471" xr:uid="{00000000-0004-0000-0000-0000D7010000}"/>
-    <hyperlink ref="D473" r:id="rId472" xr:uid="{00000000-0004-0000-0000-0000D8010000}"/>
-    <hyperlink ref="D474" r:id="rId473" xr:uid="{00000000-0004-0000-0000-0000D9010000}"/>
-    <hyperlink ref="D475" r:id="rId474" xr:uid="{00000000-0004-0000-0000-0000DA010000}"/>
-    <hyperlink ref="D476" r:id="rId475" xr:uid="{00000000-0004-0000-0000-0000DB010000}"/>
-    <hyperlink ref="D477" r:id="rId476" xr:uid="{00000000-0004-0000-0000-0000DC010000}"/>
-    <hyperlink ref="D478" r:id="rId477" xr:uid="{00000000-0004-0000-0000-0000DD010000}"/>
-    <hyperlink ref="D479" r:id="rId478" xr:uid="{00000000-0004-0000-0000-0000DE010000}"/>
-    <hyperlink ref="D480" r:id="rId479" xr:uid="{00000000-0004-0000-0000-0000DF010000}"/>
-    <hyperlink ref="D481" r:id="rId480" xr:uid="{00000000-0004-0000-0000-0000E0010000}"/>
-    <hyperlink ref="D482" r:id="rId481" xr:uid="{00000000-0004-0000-0000-0000E1010000}"/>
-    <hyperlink ref="D483" r:id="rId482" xr:uid="{00000000-0004-0000-0000-0000E2010000}"/>
-    <hyperlink ref="D484" r:id="rId483" xr:uid="{00000000-0004-0000-0000-0000E3010000}"/>
-    <hyperlink ref="D485" r:id="rId484" xr:uid="{00000000-0004-0000-0000-0000E4010000}"/>
-    <hyperlink ref="D486" r:id="rId485" xr:uid="{00000000-0004-0000-0000-0000E5010000}"/>
-    <hyperlink ref="D487" r:id="rId486" xr:uid="{00000000-0004-0000-0000-0000E6010000}"/>
-    <hyperlink ref="D488" r:id="rId487" xr:uid="{00000000-0004-0000-0000-0000E7010000}"/>
-    <hyperlink ref="D489" r:id="rId488" xr:uid="{00000000-0004-0000-0000-0000E8010000}"/>
-    <hyperlink ref="D490" r:id="rId489" xr:uid="{00000000-0004-0000-0000-0000E9010000}"/>
-    <hyperlink ref="D491" r:id="rId490" xr:uid="{00000000-0004-0000-0000-0000EA010000}"/>
-    <hyperlink ref="D492" r:id="rId491" xr:uid="{00000000-0004-0000-0000-0000EB010000}"/>
-    <hyperlink ref="D493" r:id="rId492" xr:uid="{00000000-0004-0000-0000-0000EC010000}"/>
-    <hyperlink ref="D494" r:id="rId493" xr:uid="{00000000-0004-0000-0000-0000ED010000}"/>
-    <hyperlink ref="D495" r:id="rId494" xr:uid="{00000000-0004-0000-0000-0000EE010000}"/>
-    <hyperlink ref="D496" r:id="rId495" xr:uid="{00000000-0004-0000-0000-0000EF010000}"/>
-    <hyperlink ref="D497" r:id="rId496" xr:uid="{00000000-0004-0000-0000-0000F0010000}"/>
-    <hyperlink ref="D498" r:id="rId497" xr:uid="{00000000-0004-0000-0000-0000F1010000}"/>
-    <hyperlink ref="D499" r:id="rId498" xr:uid="{00000000-0004-0000-0000-0000F2010000}"/>
-    <hyperlink ref="D500" r:id="rId499" xr:uid="{00000000-0004-0000-0000-0000F3010000}"/>
-    <hyperlink ref="D501" r:id="rId500" xr:uid="{00000000-0004-0000-0000-0000F4010000}"/>
-    <hyperlink ref="D502" r:id="rId501" xr:uid="{00000000-0004-0000-0000-0000F5010000}"/>
-    <hyperlink ref="D503" r:id="rId502" xr:uid="{00000000-0004-0000-0000-0000F6010000}"/>
-    <hyperlink ref="D504" r:id="rId503" xr:uid="{00000000-0004-0000-0000-0000F7010000}"/>
-    <hyperlink ref="D505" r:id="rId504" xr:uid="{00000000-0004-0000-0000-0000F8010000}"/>
-    <hyperlink ref="D506" r:id="rId505" xr:uid="{00000000-0004-0000-0000-0000F9010000}"/>
-    <hyperlink ref="D507" r:id="rId506" xr:uid="{00000000-0004-0000-0000-0000FA010000}"/>
-    <hyperlink ref="D508" r:id="rId507" xr:uid="{00000000-0004-0000-0000-0000FB010000}"/>
-    <hyperlink ref="D509" r:id="rId508" xr:uid="{00000000-0004-0000-0000-0000FC010000}"/>
-    <hyperlink ref="D510" r:id="rId509" xr:uid="{00000000-0004-0000-0000-0000FD010000}"/>
-    <hyperlink ref="D511" r:id="rId510" xr:uid="{00000000-0004-0000-0000-0000FE010000}"/>
-    <hyperlink ref="D512" r:id="rId511" xr:uid="{00000000-0004-0000-0000-0000FF010000}"/>
-    <hyperlink ref="D513" r:id="rId512" xr:uid="{00000000-0004-0000-0000-000000020000}"/>
-    <hyperlink ref="D514" r:id="rId513" xr:uid="{00000000-0004-0000-0000-000001020000}"/>
-    <hyperlink ref="D515" r:id="rId514" xr:uid="{00000000-0004-0000-0000-000002020000}"/>
-    <hyperlink ref="D516" r:id="rId515" xr:uid="{00000000-0004-0000-0000-000003020000}"/>
-    <hyperlink ref="D517" r:id="rId516" xr:uid="{00000000-0004-0000-0000-000004020000}"/>
-    <hyperlink ref="D518" r:id="rId517" xr:uid="{00000000-0004-0000-0000-000005020000}"/>
-    <hyperlink ref="D519" r:id="rId518" xr:uid="{00000000-0004-0000-0000-000006020000}"/>
-    <hyperlink ref="D520" r:id="rId519" xr:uid="{00000000-0004-0000-0000-000007020000}"/>
-    <hyperlink ref="D521" r:id="rId520" xr:uid="{00000000-0004-0000-0000-000008020000}"/>
-    <hyperlink ref="D522" r:id="rId521" xr:uid="{00000000-0004-0000-0000-000009020000}"/>
-    <hyperlink ref="D523" r:id="rId522" xr:uid="{00000000-0004-0000-0000-00000A020000}"/>
-    <hyperlink ref="D524" r:id="rId523" xr:uid="{00000000-0004-0000-0000-00000B020000}"/>
-    <hyperlink ref="D525" r:id="rId524" xr:uid="{00000000-0004-0000-0000-00000C020000}"/>
-    <hyperlink ref="D526" r:id="rId525" xr:uid="{00000000-0004-0000-0000-00000D020000}"/>
-    <hyperlink ref="D527" r:id="rId526" xr:uid="{00000000-0004-0000-0000-00000E020000}"/>
-    <hyperlink ref="D528" r:id="rId527" xr:uid="{00000000-0004-0000-0000-00000F020000}"/>
-    <hyperlink ref="D529" r:id="rId528" xr:uid="{00000000-0004-0000-0000-000010020000}"/>
-    <hyperlink ref="D530" r:id="rId529" xr:uid="{00000000-0004-0000-0000-000011020000}"/>
-    <hyperlink ref="D531" r:id="rId530" xr:uid="{00000000-0004-0000-0000-000012020000}"/>
+    <hyperlink ref="D240" r:id="rId239" xr:uid="{00000000-0004-0000-0000-0000EF000000}"/>
+    <hyperlink ref="D241" r:id="rId240" xr:uid="{00000000-0004-0000-0000-0000F0000000}"/>
+    <hyperlink ref="D242" r:id="rId241" xr:uid="{00000000-0004-0000-0000-0000F1000000}"/>
+    <hyperlink ref="D243" r:id="rId242" xr:uid="{00000000-0004-0000-0000-0000F2000000}"/>
+    <hyperlink ref="D244" r:id="rId243" xr:uid="{00000000-0004-0000-0000-0000F3000000}"/>
+    <hyperlink ref="D245" r:id="rId244" xr:uid="{00000000-0004-0000-0000-0000F4000000}"/>
+    <hyperlink ref="D246" r:id="rId245" xr:uid="{00000000-0004-0000-0000-0000F5000000}"/>
+    <hyperlink ref="D247" r:id="rId246" xr:uid="{00000000-0004-0000-0000-0000F6000000}"/>
+    <hyperlink ref="D248" r:id="rId247" xr:uid="{00000000-0004-0000-0000-0000F7000000}"/>
+    <hyperlink ref="D249" r:id="rId248" xr:uid="{00000000-0004-0000-0000-0000F8000000}"/>
+    <hyperlink ref="D250" r:id="rId249" xr:uid="{00000000-0004-0000-0000-0000F9000000}"/>
+    <hyperlink ref="D251" r:id="rId250" xr:uid="{00000000-0004-0000-0000-0000FA000000}"/>
+    <hyperlink ref="D252" r:id="rId251" xr:uid="{00000000-0004-0000-0000-0000FB000000}"/>
+    <hyperlink ref="D253" r:id="rId252" xr:uid="{00000000-0004-0000-0000-0000FC000000}"/>
+    <hyperlink ref="D254" r:id="rId253" xr:uid="{00000000-0004-0000-0000-0000FD000000}"/>
+    <hyperlink ref="D255" r:id="rId254" xr:uid="{00000000-0004-0000-0000-0000FE000000}"/>
+    <hyperlink ref="D256" r:id="rId255" xr:uid="{00000000-0004-0000-0000-0000FF000000}"/>
+    <hyperlink ref="D257" r:id="rId256" xr:uid="{00000000-0004-0000-0000-000000010000}"/>
+    <hyperlink ref="D258" r:id="rId257" xr:uid="{00000000-0004-0000-0000-000001010000}"/>
+    <hyperlink ref="D259" r:id="rId258" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
+    <hyperlink ref="D260" r:id="rId259" xr:uid="{00000000-0004-0000-0000-000003010000}"/>
+    <hyperlink ref="D261" r:id="rId260" xr:uid="{00000000-0004-0000-0000-000004010000}"/>
+    <hyperlink ref="D262" r:id="rId261" xr:uid="{00000000-0004-0000-0000-000005010000}"/>
+    <hyperlink ref="D263" r:id="rId262" xr:uid="{00000000-0004-0000-0000-000006010000}"/>
+    <hyperlink ref="D264" r:id="rId263" xr:uid="{00000000-0004-0000-0000-000007010000}"/>
+    <hyperlink ref="D265" r:id="rId264" xr:uid="{00000000-0004-0000-0000-000008010000}"/>
+    <hyperlink ref="D266" r:id="rId265" xr:uid="{00000000-0004-0000-0000-000009010000}"/>
+    <hyperlink ref="D267" r:id="rId266" xr:uid="{00000000-0004-0000-0000-00000B010000}"/>
+    <hyperlink ref="D268" r:id="rId267" xr:uid="{00000000-0004-0000-0000-00000C010000}"/>
+    <hyperlink ref="D269" r:id="rId268" xr:uid="{00000000-0004-0000-0000-00000D010000}"/>
+    <hyperlink ref="D270" r:id="rId269" xr:uid="{00000000-0004-0000-0000-00000F010000}"/>
+    <hyperlink ref="D271" r:id="rId270" xr:uid="{00000000-0004-0000-0000-000010010000}"/>
+    <hyperlink ref="D272" r:id="rId271" xr:uid="{00000000-0004-0000-0000-000011010000}"/>
+    <hyperlink ref="D277" r:id="rId272" xr:uid="{00000000-0004-0000-0000-000012010000}"/>
+    <hyperlink ref="D278" r:id="rId273" xr:uid="{00000000-0004-0000-0000-000013010000}"/>
+    <hyperlink ref="D279" r:id="rId274" xr:uid="{00000000-0004-0000-0000-000014010000}"/>
+    <hyperlink ref="D280" r:id="rId275" xr:uid="{00000000-0004-0000-0000-000015010000}"/>
+    <hyperlink ref="D281" r:id="rId276" xr:uid="{00000000-0004-0000-0000-000016010000}"/>
+    <hyperlink ref="D282" r:id="rId277" xr:uid="{00000000-0004-0000-0000-000017010000}"/>
+    <hyperlink ref="D283" r:id="rId278" xr:uid="{00000000-0004-0000-0000-000018010000}"/>
+    <hyperlink ref="D284" r:id="rId279" xr:uid="{00000000-0004-0000-0000-000019010000}"/>
+    <hyperlink ref="D285" r:id="rId280" xr:uid="{00000000-0004-0000-0000-00001A010000}"/>
+    <hyperlink ref="D286" r:id="rId281" xr:uid="{00000000-0004-0000-0000-00001B010000}"/>
+    <hyperlink ref="D287" r:id="rId282" xr:uid="{00000000-0004-0000-0000-00001C010000}"/>
+    <hyperlink ref="D288" r:id="rId283" xr:uid="{00000000-0004-0000-0000-00001D010000}"/>
+    <hyperlink ref="D289" r:id="rId284" xr:uid="{00000000-0004-0000-0000-00001E010000}"/>
+    <hyperlink ref="D290" r:id="rId285" xr:uid="{00000000-0004-0000-0000-00001F010000}"/>
+    <hyperlink ref="D291" r:id="rId286" xr:uid="{00000000-0004-0000-0000-000020010000}"/>
+    <hyperlink ref="D292" r:id="rId287" xr:uid="{00000000-0004-0000-0000-000021010000}"/>
+    <hyperlink ref="D293" r:id="rId288" xr:uid="{00000000-0004-0000-0000-000022010000}"/>
+    <hyperlink ref="D294" r:id="rId289" xr:uid="{00000000-0004-0000-0000-000023010000}"/>
+    <hyperlink ref="D295" r:id="rId290" xr:uid="{00000000-0004-0000-0000-000024010000}"/>
+    <hyperlink ref="D296" r:id="rId291" xr:uid="{00000000-0004-0000-0000-000025010000}"/>
+    <hyperlink ref="D297" r:id="rId292" xr:uid="{00000000-0004-0000-0000-000026010000}"/>
+    <hyperlink ref="D298" r:id="rId293" xr:uid="{00000000-0004-0000-0000-000027010000}"/>
+    <hyperlink ref="D299" r:id="rId294" xr:uid="{00000000-0004-0000-0000-000028010000}"/>
+    <hyperlink ref="D300" r:id="rId295" xr:uid="{00000000-0004-0000-0000-000029010000}"/>
+    <hyperlink ref="D301" r:id="rId296" xr:uid="{00000000-0004-0000-0000-00002A010000}"/>
+    <hyperlink ref="D302" r:id="rId297" xr:uid="{00000000-0004-0000-0000-00002B010000}"/>
+    <hyperlink ref="D303" r:id="rId298" xr:uid="{00000000-0004-0000-0000-00002C010000}"/>
+    <hyperlink ref="D304" r:id="rId299" xr:uid="{00000000-0004-0000-0000-00002D010000}"/>
+    <hyperlink ref="D305" r:id="rId300" xr:uid="{00000000-0004-0000-0000-00002E010000}"/>
+    <hyperlink ref="D306" r:id="rId301" xr:uid="{00000000-0004-0000-0000-00002F010000}"/>
+    <hyperlink ref="D307" r:id="rId302" xr:uid="{00000000-0004-0000-0000-000030010000}"/>
+    <hyperlink ref="D308" r:id="rId303" xr:uid="{00000000-0004-0000-0000-000031010000}"/>
+    <hyperlink ref="D309" r:id="rId304" xr:uid="{00000000-0004-0000-0000-000032010000}"/>
+    <hyperlink ref="D310" r:id="rId305" xr:uid="{00000000-0004-0000-0000-000033010000}"/>
+    <hyperlink ref="D311" r:id="rId306" xr:uid="{00000000-0004-0000-0000-000034010000}"/>
+    <hyperlink ref="D312" r:id="rId307" xr:uid="{00000000-0004-0000-0000-000035010000}"/>
+    <hyperlink ref="D313" r:id="rId308" xr:uid="{00000000-0004-0000-0000-000036010000}"/>
+    <hyperlink ref="D314" r:id="rId309" xr:uid="{00000000-0004-0000-0000-000037010000}"/>
+    <hyperlink ref="D315" r:id="rId310" xr:uid="{00000000-0004-0000-0000-000038010000}"/>
+    <hyperlink ref="D316" r:id="rId311" xr:uid="{00000000-0004-0000-0000-000039010000}"/>
+    <hyperlink ref="D317" r:id="rId312" xr:uid="{00000000-0004-0000-0000-00003A010000}"/>
+    <hyperlink ref="D318" r:id="rId313" xr:uid="{00000000-0004-0000-0000-00003B010000}"/>
+    <hyperlink ref="D319" r:id="rId314" xr:uid="{00000000-0004-0000-0000-00003C010000}"/>
+    <hyperlink ref="D320" r:id="rId315" xr:uid="{00000000-0004-0000-0000-00003D010000}"/>
+    <hyperlink ref="D321" r:id="rId316" xr:uid="{00000000-0004-0000-0000-00003E010000}"/>
+    <hyperlink ref="D322" r:id="rId317" xr:uid="{00000000-0004-0000-0000-00003F010000}"/>
+    <hyperlink ref="D323" r:id="rId318" xr:uid="{00000000-0004-0000-0000-000040010000}"/>
+    <hyperlink ref="D324" r:id="rId319" xr:uid="{00000000-0004-0000-0000-000041010000}"/>
+    <hyperlink ref="D325" r:id="rId320" xr:uid="{00000000-0004-0000-0000-000042010000}"/>
+    <hyperlink ref="D326" r:id="rId321" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
+    <hyperlink ref="D327" r:id="rId322" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
+    <hyperlink ref="D328" r:id="rId323" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
+    <hyperlink ref="D329" r:id="rId324" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
+    <hyperlink ref="D330" r:id="rId325" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
+    <hyperlink ref="D331" r:id="rId326" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
+    <hyperlink ref="D332" r:id="rId327" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
+    <hyperlink ref="D333" r:id="rId328" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
+    <hyperlink ref="D334" r:id="rId329" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
+    <hyperlink ref="D335" r:id="rId330" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
+    <hyperlink ref="D336" r:id="rId331" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
+    <hyperlink ref="D337" r:id="rId332" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
+    <hyperlink ref="D338" r:id="rId333" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
+    <hyperlink ref="D339" r:id="rId334" xr:uid="{00000000-0004-0000-0000-000050010000}"/>
+    <hyperlink ref="D340" r:id="rId335" xr:uid="{00000000-0004-0000-0000-000051010000}"/>
+    <hyperlink ref="D341" r:id="rId336" xr:uid="{00000000-0004-0000-0000-000052010000}"/>
+    <hyperlink ref="D342" r:id="rId337" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
+    <hyperlink ref="D343" r:id="rId338" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
+    <hyperlink ref="D344" r:id="rId339" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
+    <hyperlink ref="D345" r:id="rId340" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
+    <hyperlink ref="D346" r:id="rId341" xr:uid="{00000000-0004-0000-0000-000057010000}"/>
+    <hyperlink ref="D347" r:id="rId342" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
+    <hyperlink ref="D348" r:id="rId343" xr:uid="{00000000-0004-0000-0000-00005A010000}"/>
+    <hyperlink ref="D349" r:id="rId344" xr:uid="{00000000-0004-0000-0000-00005B010000}"/>
+    <hyperlink ref="D350" r:id="rId345" xr:uid="{00000000-0004-0000-0000-00005C010000}"/>
+    <hyperlink ref="D351" r:id="rId346" xr:uid="{00000000-0004-0000-0000-00005D010000}"/>
+    <hyperlink ref="D352" r:id="rId347" xr:uid="{00000000-0004-0000-0000-00005E010000}"/>
+    <hyperlink ref="D353" r:id="rId348" xr:uid="{00000000-0004-0000-0000-00005F010000}"/>
+    <hyperlink ref="D354" r:id="rId349" xr:uid="{00000000-0004-0000-0000-000060010000}"/>
+    <hyperlink ref="D355" r:id="rId350" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
+    <hyperlink ref="D356" r:id="rId351" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
+    <hyperlink ref="D357" r:id="rId352" xr:uid="{00000000-0004-0000-0000-000063010000}"/>
+    <hyperlink ref="D358" r:id="rId353" xr:uid="{00000000-0004-0000-0000-000064010000}"/>
+    <hyperlink ref="D359" r:id="rId354" xr:uid="{00000000-0004-0000-0000-000065010000}"/>
+    <hyperlink ref="D360" r:id="rId355" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
+    <hyperlink ref="D361" r:id="rId356" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
+    <hyperlink ref="D362" r:id="rId357" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
+    <hyperlink ref="D363" r:id="rId358" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
+    <hyperlink ref="D364" r:id="rId359" xr:uid="{00000000-0004-0000-0000-00006A010000}"/>
+    <hyperlink ref="D365" r:id="rId360" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
+    <hyperlink ref="D366" r:id="rId361" xr:uid="{00000000-0004-0000-0000-00006C010000}"/>
+    <hyperlink ref="D367" r:id="rId362" xr:uid="{00000000-0004-0000-0000-00006D010000}"/>
+    <hyperlink ref="D368" r:id="rId363" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
+    <hyperlink ref="D369" r:id="rId364" xr:uid="{00000000-0004-0000-0000-00006F010000}"/>
+    <hyperlink ref="D370" r:id="rId365" xr:uid="{00000000-0004-0000-0000-000070010000}"/>
+    <hyperlink ref="D371" r:id="rId366" xr:uid="{00000000-0004-0000-0000-000071010000}"/>
+    <hyperlink ref="D372" r:id="rId367" xr:uid="{00000000-0004-0000-0000-000072010000}"/>
+    <hyperlink ref="D373" r:id="rId368" xr:uid="{00000000-0004-0000-0000-000073010000}"/>
+    <hyperlink ref="D374" r:id="rId369" xr:uid="{00000000-0004-0000-0000-000074010000}"/>
+    <hyperlink ref="D375" r:id="rId370" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
+    <hyperlink ref="D376" r:id="rId371" xr:uid="{00000000-0004-0000-0000-000076010000}"/>
+    <hyperlink ref="D377" r:id="rId372" xr:uid="{00000000-0004-0000-0000-000077010000}"/>
+    <hyperlink ref="D378" r:id="rId373" xr:uid="{00000000-0004-0000-0000-000078010000}"/>
+    <hyperlink ref="D379" r:id="rId374" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
+    <hyperlink ref="D380" r:id="rId375" xr:uid="{00000000-0004-0000-0000-00007A010000}"/>
+    <hyperlink ref="D381" r:id="rId376" xr:uid="{00000000-0004-0000-0000-00007B010000}"/>
+    <hyperlink ref="D382" r:id="rId377" xr:uid="{00000000-0004-0000-0000-00007C010000}"/>
+    <hyperlink ref="D383" r:id="rId378" xr:uid="{00000000-0004-0000-0000-00007D010000}"/>
+    <hyperlink ref="D384" r:id="rId379" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
+    <hyperlink ref="D385" r:id="rId380" xr:uid="{00000000-0004-0000-0000-00007F010000}"/>
+    <hyperlink ref="D386" r:id="rId381" xr:uid="{00000000-0004-0000-0000-000080010000}"/>
+    <hyperlink ref="D387" r:id="rId382" xr:uid="{00000000-0004-0000-0000-000081010000}"/>
+    <hyperlink ref="D388" r:id="rId383" xr:uid="{00000000-0004-0000-0000-000082010000}"/>
+    <hyperlink ref="D389" r:id="rId384" xr:uid="{00000000-0004-0000-0000-000083010000}"/>
+    <hyperlink ref="D390" r:id="rId385" xr:uid="{00000000-0004-0000-0000-000084010000}"/>
+    <hyperlink ref="D391" r:id="rId386" xr:uid="{00000000-0004-0000-0000-000085010000}"/>
+    <hyperlink ref="D392" r:id="rId387" xr:uid="{00000000-0004-0000-0000-000086010000}"/>
+    <hyperlink ref="D393" r:id="rId388" xr:uid="{00000000-0004-0000-0000-000087010000}"/>
+    <hyperlink ref="D394" r:id="rId389" xr:uid="{00000000-0004-0000-0000-000088010000}"/>
+    <hyperlink ref="D395" r:id="rId390" xr:uid="{00000000-0004-0000-0000-000089010000}"/>
+    <hyperlink ref="D396" r:id="rId391" xr:uid="{00000000-0004-0000-0000-00008A010000}"/>
+    <hyperlink ref="D397" r:id="rId392" xr:uid="{00000000-0004-0000-0000-00008B010000}"/>
+    <hyperlink ref="D398" r:id="rId393" xr:uid="{00000000-0004-0000-0000-00008C010000}"/>
+    <hyperlink ref="D399" r:id="rId394" xr:uid="{00000000-0004-0000-0000-00008D010000}"/>
+    <hyperlink ref="D400" r:id="rId395" xr:uid="{00000000-0004-0000-0000-00008E010000}"/>
+    <hyperlink ref="D401" r:id="rId396" xr:uid="{00000000-0004-0000-0000-00008F010000}"/>
+    <hyperlink ref="D402" r:id="rId397" xr:uid="{00000000-0004-0000-0000-000090010000}"/>
+    <hyperlink ref="D403" r:id="rId398" xr:uid="{00000000-0004-0000-0000-000091010000}"/>
+    <hyperlink ref="D404" r:id="rId399" xr:uid="{00000000-0004-0000-0000-000092010000}"/>
+    <hyperlink ref="D405" r:id="rId400" xr:uid="{00000000-0004-0000-0000-000093010000}"/>
+    <hyperlink ref="D406" r:id="rId401" xr:uid="{00000000-0004-0000-0000-000094010000}"/>
+    <hyperlink ref="D407" r:id="rId402" xr:uid="{00000000-0004-0000-0000-000095010000}"/>
+    <hyperlink ref="D408" r:id="rId403" xr:uid="{00000000-0004-0000-0000-000096010000}"/>
+    <hyperlink ref="D409" r:id="rId404" xr:uid="{00000000-0004-0000-0000-000097010000}"/>
+    <hyperlink ref="D410" r:id="rId405" xr:uid="{00000000-0004-0000-0000-000098010000}"/>
+    <hyperlink ref="D411" r:id="rId406" xr:uid="{00000000-0004-0000-0000-000099010000}"/>
+    <hyperlink ref="D412" r:id="rId407" xr:uid="{00000000-0004-0000-0000-00009A010000}"/>
+    <hyperlink ref="D413" r:id="rId408" xr:uid="{00000000-0004-0000-0000-00009B010000}"/>
+    <hyperlink ref="D414" r:id="rId409" xr:uid="{00000000-0004-0000-0000-00009C010000}"/>
+    <hyperlink ref="D415" r:id="rId410" xr:uid="{00000000-0004-0000-0000-00009D010000}"/>
+    <hyperlink ref="D416" r:id="rId411" xr:uid="{00000000-0004-0000-0000-00009E010000}"/>
+    <hyperlink ref="D417" r:id="rId412" xr:uid="{00000000-0004-0000-0000-00009F010000}"/>
+    <hyperlink ref="D418" r:id="rId413" xr:uid="{00000000-0004-0000-0000-0000A0010000}"/>
+    <hyperlink ref="D419" r:id="rId414" xr:uid="{00000000-0004-0000-0000-0000A1010000}"/>
+    <hyperlink ref="D420" r:id="rId415" xr:uid="{00000000-0004-0000-0000-0000A2010000}"/>
+    <hyperlink ref="D421" r:id="rId416" xr:uid="{00000000-0004-0000-0000-0000A3010000}"/>
+    <hyperlink ref="D422" r:id="rId417" xr:uid="{00000000-0004-0000-0000-0000A4010000}"/>
+    <hyperlink ref="D423" r:id="rId418" xr:uid="{00000000-0004-0000-0000-0000A5010000}"/>
+    <hyperlink ref="D424" r:id="rId419" xr:uid="{00000000-0004-0000-0000-0000A6010000}"/>
+    <hyperlink ref="D425" r:id="rId420" xr:uid="{00000000-0004-0000-0000-0000A7010000}"/>
+    <hyperlink ref="D426" r:id="rId421" xr:uid="{00000000-0004-0000-0000-0000A8010000}"/>
+    <hyperlink ref="D427" r:id="rId422" xr:uid="{00000000-0004-0000-0000-0000A9010000}"/>
+    <hyperlink ref="D428" r:id="rId423" xr:uid="{00000000-0004-0000-0000-0000AA010000}"/>
+    <hyperlink ref="D429" r:id="rId424" xr:uid="{00000000-0004-0000-0000-0000AB010000}"/>
+    <hyperlink ref="D430" r:id="rId425" xr:uid="{00000000-0004-0000-0000-0000AC010000}"/>
+    <hyperlink ref="D431" r:id="rId426" xr:uid="{00000000-0004-0000-0000-0000AD010000}"/>
+    <hyperlink ref="D432" r:id="rId427" xr:uid="{00000000-0004-0000-0000-0000AE010000}"/>
+    <hyperlink ref="D433" r:id="rId428" xr:uid="{00000000-0004-0000-0000-0000AF010000}"/>
+    <hyperlink ref="D434" r:id="rId429" xr:uid="{00000000-0004-0000-0000-0000B0010000}"/>
+    <hyperlink ref="D435" r:id="rId430" xr:uid="{00000000-0004-0000-0000-0000B1010000}"/>
+    <hyperlink ref="D436" r:id="rId431" xr:uid="{00000000-0004-0000-0000-0000B2010000}"/>
+    <hyperlink ref="D437" r:id="rId432" xr:uid="{00000000-0004-0000-0000-0000B3010000}"/>
+    <hyperlink ref="D438" r:id="rId433" xr:uid="{00000000-0004-0000-0000-0000B4010000}"/>
+    <hyperlink ref="D439" r:id="rId434" xr:uid="{00000000-0004-0000-0000-0000B5010000}"/>
+    <hyperlink ref="D440" r:id="rId435" xr:uid="{00000000-0004-0000-0000-0000B6010000}"/>
+    <hyperlink ref="D441" r:id="rId436" xr:uid="{00000000-0004-0000-0000-0000B7010000}"/>
+    <hyperlink ref="D442" r:id="rId437" xr:uid="{00000000-0004-0000-0000-0000B8010000}"/>
+    <hyperlink ref="D443" r:id="rId438" xr:uid="{00000000-0004-0000-0000-0000B9010000}"/>
+    <hyperlink ref="D444" r:id="rId439" xr:uid="{00000000-0004-0000-0000-0000BA010000}"/>
+    <hyperlink ref="D445" r:id="rId440" xr:uid="{00000000-0004-0000-0000-0000BB010000}"/>
+    <hyperlink ref="D446" r:id="rId441" xr:uid="{00000000-0004-0000-0000-0000BC010000}"/>
+    <hyperlink ref="D447" r:id="rId442" xr:uid="{00000000-0004-0000-0000-0000BD010000}"/>
+    <hyperlink ref="D448" r:id="rId443" xr:uid="{00000000-0004-0000-0000-0000BE010000}"/>
+    <hyperlink ref="D449" r:id="rId444" xr:uid="{00000000-0004-0000-0000-0000BF010000}"/>
+    <hyperlink ref="D450" r:id="rId445" xr:uid="{00000000-0004-0000-0000-0000C0010000}"/>
+    <hyperlink ref="D451" r:id="rId446" xr:uid="{00000000-0004-0000-0000-0000C1010000}"/>
+    <hyperlink ref="D452" r:id="rId447" xr:uid="{00000000-0004-0000-0000-0000C2010000}"/>
+    <hyperlink ref="D453" r:id="rId448" xr:uid="{00000000-0004-0000-0000-0000C3010000}"/>
+    <hyperlink ref="D454" r:id="rId449" xr:uid="{00000000-0004-0000-0000-0000C4010000}"/>
+    <hyperlink ref="D455" r:id="rId450" xr:uid="{00000000-0004-0000-0000-0000C5010000}"/>
+    <hyperlink ref="D456" r:id="rId451" xr:uid="{00000000-0004-0000-0000-0000C6010000}"/>
+    <hyperlink ref="D457" r:id="rId452" xr:uid="{00000000-0004-0000-0000-0000C7010000}"/>
+    <hyperlink ref="D458" r:id="rId453" xr:uid="{00000000-0004-0000-0000-0000C8010000}"/>
+    <hyperlink ref="D459" r:id="rId454" xr:uid="{00000000-0004-0000-0000-0000C9010000}"/>
+    <hyperlink ref="D460" r:id="rId455" xr:uid="{00000000-0004-0000-0000-0000CA010000}"/>
+    <hyperlink ref="D461" r:id="rId456" xr:uid="{00000000-0004-0000-0000-0000CB010000}"/>
+    <hyperlink ref="D462" r:id="rId457" xr:uid="{00000000-0004-0000-0000-0000CC010000}"/>
+    <hyperlink ref="D463" r:id="rId458" xr:uid="{00000000-0004-0000-0000-0000CD010000}"/>
+    <hyperlink ref="D464" r:id="rId459" xr:uid="{00000000-0004-0000-0000-0000CE010000}"/>
+    <hyperlink ref="D465" r:id="rId460" xr:uid="{00000000-0004-0000-0000-0000CF010000}"/>
+    <hyperlink ref="D466" r:id="rId461" xr:uid="{00000000-0004-0000-0000-0000D0010000}"/>
+    <hyperlink ref="D467" r:id="rId462" xr:uid="{00000000-0004-0000-0000-0000D1010000}"/>
+    <hyperlink ref="D468" r:id="rId463" xr:uid="{00000000-0004-0000-0000-0000D2010000}"/>
+    <hyperlink ref="D469" r:id="rId464" xr:uid="{00000000-0004-0000-0000-0000D3010000}"/>
+    <hyperlink ref="D470" r:id="rId465" xr:uid="{00000000-0004-0000-0000-0000D4010000}"/>
+    <hyperlink ref="D471" r:id="rId466" xr:uid="{00000000-0004-0000-0000-0000D5010000}"/>
+    <hyperlink ref="D472" r:id="rId467" xr:uid="{00000000-0004-0000-0000-0000D6010000}"/>
+    <hyperlink ref="D473" r:id="rId468" xr:uid="{00000000-0004-0000-0000-0000D7010000}"/>
+    <hyperlink ref="D474" r:id="rId469" xr:uid="{00000000-0004-0000-0000-0000D8010000}"/>
+    <hyperlink ref="D475" r:id="rId470" xr:uid="{00000000-0004-0000-0000-0000D9010000}"/>
+    <hyperlink ref="D476" r:id="rId471" xr:uid="{00000000-0004-0000-0000-0000DA010000}"/>
+    <hyperlink ref="D477" r:id="rId472" xr:uid="{00000000-0004-0000-0000-0000DB010000}"/>
+    <hyperlink ref="D478" r:id="rId473" xr:uid="{00000000-0004-0000-0000-0000DC010000}"/>
+    <hyperlink ref="D479" r:id="rId474" xr:uid="{00000000-0004-0000-0000-0000DD010000}"/>
+    <hyperlink ref="D480" r:id="rId475" xr:uid="{00000000-0004-0000-0000-0000DE010000}"/>
+    <hyperlink ref="D481" r:id="rId476" xr:uid="{00000000-0004-0000-0000-0000DF010000}"/>
+    <hyperlink ref="D482" r:id="rId477" xr:uid="{00000000-0004-0000-0000-0000E0010000}"/>
+    <hyperlink ref="D483" r:id="rId478" xr:uid="{00000000-0004-0000-0000-0000E1010000}"/>
+    <hyperlink ref="D484" r:id="rId479" xr:uid="{00000000-0004-0000-0000-0000E2010000}"/>
+    <hyperlink ref="D485" r:id="rId480" xr:uid="{00000000-0004-0000-0000-0000E3010000}"/>
+    <hyperlink ref="D486" r:id="rId481" xr:uid="{00000000-0004-0000-0000-0000E4010000}"/>
+    <hyperlink ref="D487" r:id="rId482" xr:uid="{00000000-0004-0000-0000-0000E5010000}"/>
+    <hyperlink ref="D488" r:id="rId483" xr:uid="{00000000-0004-0000-0000-0000E6010000}"/>
+    <hyperlink ref="D489" r:id="rId484" xr:uid="{00000000-0004-0000-0000-0000E7010000}"/>
+    <hyperlink ref="D490" r:id="rId485" xr:uid="{00000000-0004-0000-0000-0000E8010000}"/>
+    <hyperlink ref="D491" r:id="rId486" xr:uid="{00000000-0004-0000-0000-0000E9010000}"/>
+    <hyperlink ref="D492" r:id="rId487" xr:uid="{00000000-0004-0000-0000-0000EA010000}"/>
+    <hyperlink ref="D493" r:id="rId488" xr:uid="{00000000-0004-0000-0000-0000EB010000}"/>
+    <hyperlink ref="D494" r:id="rId489" xr:uid="{00000000-0004-0000-0000-0000EC010000}"/>
+    <hyperlink ref="D495" r:id="rId490" xr:uid="{00000000-0004-0000-0000-0000ED010000}"/>
+    <hyperlink ref="D496" r:id="rId491" xr:uid="{00000000-0004-0000-0000-0000EE010000}"/>
+    <hyperlink ref="D497" r:id="rId492" xr:uid="{00000000-0004-0000-0000-0000EF010000}"/>
+    <hyperlink ref="D498" r:id="rId493" xr:uid="{00000000-0004-0000-0000-0000F0010000}"/>
+    <hyperlink ref="D499" r:id="rId494" xr:uid="{00000000-0004-0000-0000-0000F1010000}"/>
+    <hyperlink ref="D500" r:id="rId495" xr:uid="{00000000-0004-0000-0000-0000F2010000}"/>
+    <hyperlink ref="D501" r:id="rId496" xr:uid="{00000000-0004-0000-0000-0000F3010000}"/>
+    <hyperlink ref="D502" r:id="rId497" xr:uid="{00000000-0004-0000-0000-0000F4010000}"/>
+    <hyperlink ref="D503" r:id="rId498" xr:uid="{00000000-0004-0000-0000-0000F5010000}"/>
+    <hyperlink ref="D504" r:id="rId499" xr:uid="{00000000-0004-0000-0000-0000F6010000}"/>
+    <hyperlink ref="D505" r:id="rId500" xr:uid="{00000000-0004-0000-0000-0000F7010000}"/>
+    <hyperlink ref="D506" r:id="rId501" xr:uid="{00000000-0004-0000-0000-0000F8010000}"/>
+    <hyperlink ref="D507" r:id="rId502" xr:uid="{00000000-0004-0000-0000-0000F9010000}"/>
+    <hyperlink ref="D508" r:id="rId503" xr:uid="{00000000-0004-0000-0000-0000FA010000}"/>
+    <hyperlink ref="D509" r:id="rId504" xr:uid="{00000000-0004-0000-0000-0000FB010000}"/>
+    <hyperlink ref="D510" r:id="rId505" xr:uid="{00000000-0004-0000-0000-0000FC010000}"/>
+    <hyperlink ref="D511" r:id="rId506" xr:uid="{00000000-0004-0000-0000-0000FD010000}"/>
+    <hyperlink ref="D512" r:id="rId507" xr:uid="{00000000-0004-0000-0000-0000FE010000}"/>
+    <hyperlink ref="D513" r:id="rId508" xr:uid="{00000000-0004-0000-0000-0000FF010000}"/>
+    <hyperlink ref="D514" r:id="rId509" xr:uid="{00000000-0004-0000-0000-000000020000}"/>
+    <hyperlink ref="D515" r:id="rId510" xr:uid="{00000000-0004-0000-0000-000001020000}"/>
+    <hyperlink ref="D516" r:id="rId511" xr:uid="{00000000-0004-0000-0000-000002020000}"/>
+    <hyperlink ref="D517" r:id="rId512" xr:uid="{00000000-0004-0000-0000-000003020000}"/>
+    <hyperlink ref="D518" r:id="rId513" xr:uid="{00000000-0004-0000-0000-000004020000}"/>
+    <hyperlink ref="D519" r:id="rId514" xr:uid="{00000000-0004-0000-0000-000005020000}"/>
+    <hyperlink ref="D520" r:id="rId515" xr:uid="{00000000-0004-0000-0000-000006020000}"/>
+    <hyperlink ref="D521" r:id="rId516" xr:uid="{00000000-0004-0000-0000-000007020000}"/>
+    <hyperlink ref="D522" r:id="rId517" xr:uid="{00000000-0004-0000-0000-000008020000}"/>
+    <hyperlink ref="D523" r:id="rId518" xr:uid="{00000000-0004-0000-0000-000009020000}"/>
+    <hyperlink ref="D524" r:id="rId519" xr:uid="{00000000-0004-0000-0000-00000A020000}"/>
+    <hyperlink ref="D525" r:id="rId520" xr:uid="{00000000-0004-0000-0000-00000B020000}"/>
+    <hyperlink ref="D526" r:id="rId521" xr:uid="{00000000-0004-0000-0000-00000C020000}"/>
+    <hyperlink ref="D527" r:id="rId522" xr:uid="{00000000-0004-0000-0000-00000D020000}"/>
+    <hyperlink ref="D528" r:id="rId523" xr:uid="{00000000-0004-0000-0000-00000E020000}"/>
+    <hyperlink ref="D529" r:id="rId524" xr:uid="{00000000-0004-0000-0000-00000F020000}"/>
+    <hyperlink ref="D530" r:id="rId525" xr:uid="{00000000-0004-0000-0000-000010020000}"/>
+    <hyperlink ref="D531" r:id="rId526" xr:uid="{00000000-0004-0000-0000-000011020000}"/>
+    <hyperlink ref="D532" r:id="rId527" xr:uid="{00000000-0004-0000-0000-000012020000}"/>
+    <hyperlink ref="D273" r:id="rId528" xr:uid="{2A4372B6-A319-408F-A9B3-0AEC9F3E5AA3}"/>
+    <hyperlink ref="D275" r:id="rId529" xr:uid="{9DFA0AE0-F62A-430B-A569-2C8234EB7B98}"/>
+    <hyperlink ref="D274" r:id="rId530" xr:uid="{625DEE64-8C3A-4A04-A780-D48D67C7EC96}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>

--- a/backend/data/LigaPremier.xlsx
+++ b/backend/data/LigaPremier.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danyl\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danyl\Downloads\E\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0A4D3BC8-A8AD-48E4-9A76-02D7DF3BCD38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77011D91-FDA3-411F-8768-4FE10BC07C01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2935,7 +2935,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2947,7 +2947,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3146,13 +3145,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{32A8CF84-C284-4FB9-BA95-EA038AE71CB6}" name="Tabla1" displayName="Tabla1" ref="A1:G533" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7">
-  <autoFilter ref="A1:G533" xr:uid="{32A8CF84-C284-4FB9-BA95-EA038AE71CB6}">
-    <filterColumn colId="6">
-      <filters>
-        <filter val="CD Chilpancingo"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:G533" xr:uid="{32A8CF84-C284-4FB9-BA95-EA038AE71CB6}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{B0D88DC9-C933-4F53-9704-684AA9FB65E9}" name="Id_jugador" dataDxfId="6">
       <calculatedColumnFormula>F2 &amp; TEXT(C2,"000")</calculatedColumnFormula>
@@ -3402,7 +3395,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="str">
         <f>F2 &amp; TEXT(C2,"000")</f>
         <v>1011100</v>
@@ -3426,7 +3419,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="str">
         <f>F3 &amp; TEXT(C3,"000")</f>
         <v>1011018</v>
@@ -3450,7 +3443,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="str">
         <f t="shared" ref="A4:A67" si="0">F4 &amp; TEXT(C4,"000")</f>
         <v>1011101</v>
@@ -3474,7 +3467,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1011023</v>
@@ -3498,7 +3491,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1011003</v>
@@ -3522,7 +3515,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1011004</v>
@@ -3546,7 +3539,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1011006</v>
@@ -3570,7 +3563,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1011005</v>
@@ -3594,7 +3587,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1011002</v>
@@ -3618,7 +3611,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1011024</v>
@@ -3642,7 +3635,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1011022</v>
@@ -3666,7 +3659,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1011049</v>
@@ -3690,7 +3683,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1011015</v>
@@ -3714,7 +3707,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1011026</v>
@@ -3738,7 +3731,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1011008</v>
@@ -3762,7 +3755,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1011029</v>
@@ -3786,7 +3779,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1011013</v>
@@ -3810,7 +3803,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1011012</v>
@@ -3834,7 +3827,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1011010</v>
@@ -3858,7 +3851,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1011033</v>
@@ -3882,7 +3875,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1011036</v>
@@ -3906,7 +3899,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1011017</v>
@@ -3930,7 +3923,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1011102</v>
@@ -3954,7 +3947,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1011009</v>
@@ -3978,7 +3971,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1011011</v>
@@ -4002,7 +3995,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1011019</v>
@@ -4026,7 +4019,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1011007</v>
@@ -4050,7 +4043,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1011103</v>
@@ -4074,7 +4067,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1007084</v>
@@ -4098,7 +4091,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1007082</v>
@@ -4122,7 +4115,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1007081</v>
@@ -4146,7 +4139,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1007011</v>
@@ -4170,7 +4163,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1007010</v>
@@ -4194,7 +4187,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1007001</v>
@@ -4218,7 +4211,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1007099</v>
@@ -4242,7 +4235,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1007096</v>
@@ -4266,7 +4259,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1007097</v>
@@ -4290,7 +4283,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1007090</v>
@@ -4314,7 +4307,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1007087</v>
@@ -4338,7 +4331,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1007089</v>
@@ -4362,7 +4355,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1007098</v>
@@ -4386,7 +4379,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1007083</v>
@@ -4410,7 +4403,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1007001</v>
@@ -4434,7 +4427,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1007093</v>
@@ -4458,7 +4451,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1007088</v>
@@ -4482,7 +4475,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1007010</v>
@@ -4506,7 +4499,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1007092</v>
@@ -4530,7 +4523,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1007010</v>
@@ -4554,7 +4547,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1007006</v>
@@ -4578,7 +4571,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1007104</v>
@@ -4602,7 +4595,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1007001</v>
@@ -4626,7 +4619,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1007011</v>
@@ -4650,7 +4643,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1007085</v>
@@ -4674,7 +4667,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1007094</v>
@@ -4698,7 +4691,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1007086</v>
@@ -4722,7 +4715,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1007095</v>
@@ -4746,7 +4739,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1007105</v>
@@ -4770,7 +4763,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1007002</v>
@@ -4794,7 +4787,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1007004</v>
@@ -4818,7 +4811,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1007106</v>
@@ -4842,7 +4835,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1007003</v>
@@ -4866,7 +4859,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1007001</v>
@@ -4890,7 +4883,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1007107</v>
@@ -4914,7 +4907,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1002021</v>
@@ -4938,7 +4931,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1002025</v>
@@ -4962,7 +4955,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1002001</v>
@@ -4986,7 +4979,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="str">
         <f t="shared" ref="A68:A131" si="1">F68 &amp; TEXT(C68,"000")</f>
         <v>1002108</v>
@@ -5010,7 +5003,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002019</v>
@@ -5034,7 +5027,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002007</v>
@@ -5058,7 +5051,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002003</v>
@@ -5082,7 +5075,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002024</v>
@@ -5106,7 +5099,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002004</v>
@@ -5130,7 +5123,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002018</v>
@@ -5154,7 +5147,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002008</v>
@@ -5178,7 +5171,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002002</v>
@@ -5202,7 +5195,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002006</v>
@@ -5226,7 +5219,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002015</v>
@@ -5250,7 +5243,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002013</v>
@@ -5274,7 +5267,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002012</v>
@@ -5298,7 +5291,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002011</v>
@@ -5322,7 +5315,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="82" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002027</v>
@@ -5346,7 +5339,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="83" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002005</v>
@@ -5370,7 +5363,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002109</v>
@@ -5394,7 +5387,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="85" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002022</v>
@@ -5418,7 +5411,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="86" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002009</v>
@@ -5442,7 +5435,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="87" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002017</v>
@@ -5466,7 +5459,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="88" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002110</v>
@@ -5490,7 +5483,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002020</v>
@@ -5514,7 +5507,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002014</v>
@@ -5538,7 +5531,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="91" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002023</v>
@@ -5562,7 +5555,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="92" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002016</v>
@@ -5586,7 +5579,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="93" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002026</v>
@@ -5610,7 +5603,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="94" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1002111</v>
@@ -5634,7 +5627,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="95" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1009028</v>
@@ -5658,7 +5651,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="96" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1009021</v>
@@ -5682,7 +5675,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="97" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1009012</v>
@@ -5706,7 +5699,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="98" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1009036</v>
@@ -5730,7 +5723,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="99" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1009017</v>
@@ -5754,7 +5747,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="100" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1009004</v>
@@ -5778,7 +5771,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="101" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1009024</v>
@@ -5802,7 +5795,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="102" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1009005</v>
@@ -5826,7 +5819,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="103" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1009014</v>
@@ -5850,7 +5843,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="104" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1009020</v>
@@ -5874,7 +5867,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="105" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1009025</v>
@@ -5898,7 +5891,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="106" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1009027</v>
@@ -5922,7 +5915,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="107" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1009023</v>
@@ -5946,7 +5939,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1009006</v>
@@ -5970,7 +5963,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="109" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1009010</v>
@@ -5994,7 +5987,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="110" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1009007</v>
@@ -6018,7 +6011,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="111" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1009022</v>
@@ -6042,7 +6035,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="112" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1009015</v>
@@ -6066,7 +6059,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="113" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1009019</v>
@@ -6090,7 +6083,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="114" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1009056</v>
@@ -6114,7 +6107,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="115" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1009013</v>
@@ -6138,7 +6131,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="116" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1009009</v>
@@ -6162,7 +6155,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="117" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1009008</v>
@@ -6186,7 +6179,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="118" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1009011</v>
@@ -6210,7 +6203,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="119" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1009016</v>
@@ -6234,7 +6227,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="120" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1009112</v>
@@ -6258,7 +6251,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="121" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1012012</v>
@@ -6282,7 +6275,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="122" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1012029</v>
@@ -6306,7 +6299,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="123" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1012001</v>
@@ -6330,7 +6323,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="124" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1012018</v>
@@ -6354,7 +6347,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="125" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1012021</v>
@@ -6378,7 +6371,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="126" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1012014</v>
@@ -6402,7 +6395,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="127" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1012003</v>
@@ -6426,7 +6419,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="128" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1012005</v>
@@ -6450,7 +6443,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="129" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1012054</v>
@@ -6474,7 +6467,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="130" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1012113</v>
@@ -6498,7 +6491,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="131" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1012006</v>
@@ -6522,7 +6515,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="132" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="str">
         <f t="shared" ref="A132:A195" si="2">F132 &amp; TEXT(C132,"000")</f>
         <v>1012010</v>
@@ -6546,7 +6539,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="133" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1012008</v>
@@ -6570,7 +6563,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="134" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1012015</v>
@@ -6594,7 +6587,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="135" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1012016</v>
@@ -6618,7 +6611,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="136" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1012007</v>
@@ -6642,7 +6635,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="137" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1012114</v>
@@ -6666,7 +6659,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="138" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1012002</v>
@@ -6690,7 +6683,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="139" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1012034</v>
@@ -6714,7 +6707,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="140" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1012115</v>
@@ -6738,7 +6731,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="141" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1012116</v>
@@ -6762,7 +6755,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="142" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1012035</v>
@@ -6786,7 +6779,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="143" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1012026</v>
@@ -6810,7 +6803,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="144" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1012033</v>
@@ -6834,7 +6827,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="145" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1012117</v>
@@ -6858,7 +6851,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="146" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1012024</v>
@@ -6882,7 +6875,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="147" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1012017</v>
@@ -6906,7 +6899,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="148" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1012020</v>
@@ -6930,7 +6923,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="149" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1012004</v>
@@ -6954,7 +6947,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="150" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1012009</v>
@@ -6978,7 +6971,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="151" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1012030</v>
@@ -7002,7 +6995,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="152" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1012118</v>
@@ -7026,7 +7019,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="153" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1012028</v>
@@ -7050,7 +7043,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="154" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1012036</v>
@@ -7074,7 +7067,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="155" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1012011</v>
@@ -7098,7 +7091,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="156" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1012022</v>
@@ -7122,7 +7115,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="157" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1012119</v>
@@ -7146,7 +7139,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="158" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1005120</v>
@@ -7170,7 +7163,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="159" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1005012</v>
@@ -7194,7 +7187,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="160" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1005001</v>
@@ -7218,7 +7211,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="161" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1005023</v>
@@ -7242,7 +7235,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="162" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1005005</v>
@@ -7266,7 +7259,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="163" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1005018</v>
@@ -7290,7 +7283,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="164" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1005041</v>
@@ -7314,7 +7307,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="165" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1005002</v>
@@ -7338,7 +7331,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="166" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1005013</v>
@@ -7362,7 +7355,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="167" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1005025</v>
@@ -7386,7 +7379,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="168" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1005016</v>
@@ -7410,7 +7403,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="169" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1005022</v>
@@ -7434,7 +7427,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="170" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1005010</v>
@@ -7458,7 +7451,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="171" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1005032</v>
@@ -7482,7 +7475,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="172" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1005033</v>
@@ -7506,7 +7499,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="173" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1005014</v>
@@ -7530,7 +7523,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="174" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1005007</v>
@@ -7554,7 +7547,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="175" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1005029</v>
@@ -7578,7 +7571,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="176" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1005008</v>
@@ -7602,7 +7595,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="177" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1005024</v>
@@ -7626,7 +7619,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="178" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1005019</v>
@@ -7650,7 +7643,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="179" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1005021</v>
@@ -7674,7 +7667,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="180" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1005020</v>
@@ -7698,7 +7691,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="181" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1005011</v>
@@ -7722,7 +7715,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="182" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1005009</v>
@@ -7746,7 +7739,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="183" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1005017</v>
@@ -7770,7 +7763,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="184" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1005015</v>
@@ -7794,7 +7787,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="185" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1005121</v>
@@ -7818,7 +7811,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="186" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1011008</v>
@@ -7842,7 +7835,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="187" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1011025</v>
@@ -7866,7 +7859,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="188" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1011033</v>
@@ -7890,7 +7883,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="189" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1011020</v>
@@ -7914,7 +7907,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="190" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1011003</v>
@@ -7938,7 +7931,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="191" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1011007</v>
@@ -7962,7 +7955,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="192" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1011023</v>
@@ -7986,7 +7979,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="193" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1011017</v>
@@ -8010,7 +8003,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="194" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1011122</v>
@@ -8034,7 +8027,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="195" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1011022</v>
@@ -8058,7 +8051,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="196" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="str">
         <f t="shared" ref="A196:A258" si="3">F196 &amp; TEXT(C196,"000")</f>
         <v>1011013</v>
@@ -8082,7 +8075,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="197" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1011005</v>
@@ -8106,7 +8099,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="198" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1011012</v>
@@ -8130,7 +8123,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="199" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1011012</v>
@@ -8154,7 +8147,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="200" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1011018</v>
@@ -8178,7 +8171,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="201" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1011019</v>
@@ -8202,7 +8195,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="202" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1011014</v>
@@ -8226,7 +8219,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="203" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1011009</v>
@@ -8250,7 +8243,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="204" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1011030</v>
@@ -8274,7 +8267,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="205" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1011024</v>
@@ -8298,7 +8291,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="206" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1011027</v>
@@ -8322,7 +8315,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="207" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1011021</v>
@@ -8346,7 +8339,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="208" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1011011</v>
@@ -8370,7 +8363,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="209" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1011016</v>
@@ -8394,7 +8387,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="210" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1011036</v>
@@ -8418,7 +8411,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="211" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1011029</v>
@@ -8442,7 +8435,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="212" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1011123</v>
@@ -8466,7 +8459,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="213" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1013012</v>
@@ -8490,7 +8483,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="214" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1013022</v>
@@ -8514,7 +8507,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="215" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1013004</v>
@@ -8538,7 +8531,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="216" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1013028</v>
@@ -8562,7 +8555,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="217" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1013020</v>
@@ -8586,7 +8579,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="218" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1013024</v>
@@ -8610,7 +8603,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="219" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1013005</v>
@@ -8634,7 +8627,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="220" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1013014</v>
@@ -8658,7 +8651,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="221" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1013006</v>
@@ -8682,7 +8675,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="222" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1013010</v>
@@ -8706,7 +8699,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="223" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1013008</v>
@@ -8730,7 +8723,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="224" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1013007</v>
@@ -8754,7 +8747,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="225" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1013023</v>
@@ -8778,7 +8771,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="226" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1013018</v>
@@ -8802,7 +8795,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="227" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1013011</v>
@@ -8826,7 +8819,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="228" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1013021</v>
@@ -8850,7 +8843,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="229" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1013016</v>
@@ -8874,7 +8867,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="230" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1013031</v>
@@ -8898,7 +8891,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="231" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1013015</v>
@@ -8922,7 +8915,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="232" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1013013</v>
@@ -8946,7 +8939,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="233" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1013019</v>
@@ -8970,7 +8963,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="234" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1013002</v>
@@ -8994,7 +8987,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="235" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1013030</v>
@@ -9018,7 +9011,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="236" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1013029</v>
@@ -9042,7 +9035,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="237" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1013017</v>
@@ -9066,7 +9059,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="238" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1013124</v>
@@ -9907,88 +9900,83 @@
       </c>
     </row>
     <row r="273" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A273" s="7" t="str">
+      <c r="A273" t="str">
         <f>F273 &amp; TEXT(C273,"000")</f>
         <v>1003041</v>
       </c>
-      <c r="B273" s="7" t="s">
+      <c r="B273" t="s">
         <v>442</v>
       </c>
-      <c r="C273" s="7">
+      <c r="C273">
         <v>41</v>
       </c>
       <c r="D273" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="E273" s="7" t="s">
+      <c r="E273" t="s">
         <v>13</v>
       </c>
-      <c r="F273" s="7">
+      <c r="F273">
         <v>1003</v>
       </c>
-      <c r="G273" s="7"/>
     </row>
     <row r="274" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A274" s="7" t="str">
+      <c r="A274" t="str">
         <f>F274 &amp; TEXT(C274,"000")</f>
         <v>1003038</v>
       </c>
-      <c r="B274" s="7" t="s">
+      <c r="B274" t="s">
         <v>936</v>
       </c>
-      <c r="C274" s="7">
+      <c r="C274">
         <v>38</v>
       </c>
       <c r="D274" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="E274" s="7" t="s">
+      <c r="E274" t="s">
         <v>58</v>
       </c>
-      <c r="F274" s="7">
+      <c r="F274">
         <v>1003</v>
       </c>
-      <c r="G274" s="7"/>
     </row>
     <row r="275" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A275" s="7" t="str">
+      <c r="A275" t="str">
         <f>F275 &amp; TEXT(C275,"000")</f>
         <v>1003039</v>
       </c>
-      <c r="B275" s="7" t="s">
+      <c r="B275" t="s">
         <v>485</v>
       </c>
-      <c r="C275" s="7">
+      <c r="C275">
         <v>39</v>
       </c>
       <c r="D275" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E275" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F275" s="7">
+      <c r="E275" t="s">
+        <v>33</v>
+      </c>
+      <c r="F275">
         <v>1003</v>
       </c>
-      <c r="G275" s="7"/>
     </row>
     <row r="276" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A276" s="7" t="str">
+      <c r="A276" t="str">
         <f>F276 &amp; TEXT(C276,"000")</f>
         <v>1003040</v>
       </c>
-      <c r="B276" s="7" t="s">
+      <c r="B276" t="s">
         <v>937</v>
       </c>
-      <c r="C276" s="7">
+      <c r="C276">
         <v>40</v>
       </c>
       <c r="D276" s="3"/>
-      <c r="E276" s="7"/>
-      <c r="F276" s="7">
+      <c r="F276">
         <v>1003</v>
       </c>
-      <c r="G276" s="7"/>
     </row>
     <row r="277" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" s="1" t="str">
@@ -10014,7 +10002,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="278" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="1" t="str">
         <f t="shared" si="4"/>
         <v>1008001</v>
@@ -10038,7 +10026,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="279" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" s="1" t="str">
         <f t="shared" si="4"/>
         <v>1008023</v>
@@ -10062,7 +10050,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="280" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" s="1" t="str">
         <f t="shared" si="4"/>
         <v>1008070</v>
@@ -10086,7 +10074,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="281" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" s="1" t="str">
         <f t="shared" si="4"/>
         <v>1008003</v>
@@ -10110,7 +10098,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="282" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" s="1" t="str">
         <f t="shared" si="4"/>
         <v>1008022</v>
@@ -10134,7 +10122,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="283" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" s="1" t="str">
         <f t="shared" si="4"/>
         <v>1008002</v>
@@ -10158,7 +10146,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="284" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" s="1" t="str">
         <f t="shared" si="4"/>
         <v>1008020</v>
@@ -10182,7 +10170,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="285" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" s="1" t="str">
         <f t="shared" si="4"/>
         <v>1008006</v>
@@ -10206,7 +10194,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="286" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" s="1" t="str">
         <f t="shared" si="4"/>
         <v>1008004</v>
@@ -10230,7 +10218,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="287" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" s="1" t="str">
         <f t="shared" si="4"/>
         <v>1008015</v>
@@ -10254,7 +10242,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="288" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" s="1" t="str">
         <f t="shared" si="4"/>
         <v>1008061</v>
@@ -10278,7 +10266,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="289" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A289" s="1" t="str">
         <f t="shared" si="4"/>
         <v>1008067</v>
@@ -10302,7 +10290,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="290" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" s="1" t="str">
         <f t="shared" si="4"/>
         <v>1008001</v>
@@ -10326,7 +10314,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="291" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" s="1" t="str">
         <f t="shared" si="4"/>
         <v>1008017</v>
@@ -10350,7 +10338,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="292" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" s="1" t="str">
         <f t="shared" si="4"/>
         <v>1008008</v>
@@ -10374,7 +10362,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="293" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A293" s="1" t="str">
         <f t="shared" si="4"/>
         <v>1008011</v>
@@ -10398,7 +10386,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="294" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A294" s="1" t="str">
         <f t="shared" si="4"/>
         <v>1008005</v>
@@ -10422,7 +10410,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="295" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A295" s="1" t="str">
         <f t="shared" si="4"/>
         <v>1008007</v>
@@ -10446,7 +10434,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="296" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A296" s="1" t="str">
         <f t="shared" si="4"/>
         <v>1008133</v>
@@ -10470,7 +10458,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="297" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A297" s="1" t="str">
         <f t="shared" si="4"/>
         <v>1008016</v>
@@ -10494,7 +10482,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="298" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A298" s="1" t="str">
         <f t="shared" si="4"/>
         <v>1008134</v>
@@ -10518,7 +10506,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="299" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A299" s="1" t="str">
         <f t="shared" si="4"/>
         <v>1008013</v>
@@ -10542,7 +10530,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="300" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A300" s="1" t="str">
         <f t="shared" si="4"/>
         <v>1008014</v>
@@ -10566,7 +10554,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="301" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A301" s="1" t="str">
         <f t="shared" si="4"/>
         <v>1008012</v>
@@ -10590,7 +10578,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="302" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A302" s="1" t="str">
         <f t="shared" si="4"/>
         <v>1008019</v>
@@ -10614,7 +10602,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="303" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" s="1" t="str">
         <f t="shared" si="4"/>
         <v>1008018</v>
@@ -10638,7 +10626,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="304" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A304" s="1" t="str">
         <f t="shared" si="4"/>
         <v>1008135</v>
@@ -10662,7 +10650,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="305" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A305" s="1" t="str">
         <f t="shared" si="4"/>
         <v>1008027</v>
@@ -10686,7 +10674,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="306" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A306" s="1" t="str">
         <f t="shared" si="4"/>
         <v>1008136</v>
@@ -10710,7 +10698,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="307" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A307" s="1" t="str">
         <f t="shared" si="4"/>
         <v>1008010</v>
@@ -10734,7 +10722,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="308" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A308" s="1" t="str">
         <f t="shared" si="4"/>
         <v>1008137</v>
@@ -10758,7 +10746,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="309" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A309" s="1" t="str">
         <f t="shared" si="4"/>
         <v>1008138</v>
@@ -10782,7 +10770,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="310" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A310" s="1" t="str">
         <f t="shared" si="4"/>
         <v>1008009</v>
@@ -10806,7 +10794,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="311" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A311" s="1" t="str">
         <f t="shared" si="4"/>
         <v>1008029</v>
@@ -10830,7 +10818,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="312" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A312" s="1" t="str">
         <f t="shared" si="4"/>
         <v>1008025</v>
@@ -10854,7 +10842,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="313" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A313" s="1" t="str">
         <f t="shared" si="4"/>
         <v>1008139</v>
@@ -10878,7 +10866,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="314" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A314" s="1" t="str">
         <f t="shared" si="4"/>
         <v>1006001</v>
@@ -10902,7 +10890,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="315" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A315" s="1" t="str">
         <f t="shared" si="4"/>
         <v>1006051</v>
@@ -10926,7 +10914,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="316" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A316" s="1" t="str">
         <f t="shared" si="4"/>
         <v>1006012</v>
@@ -10950,7 +10938,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="317" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A317" s="1" t="str">
         <f t="shared" si="4"/>
         <v>1006025</v>
@@ -10974,7 +10962,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="318" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A318" s="1" t="str">
         <f t="shared" si="4"/>
         <v>1006015</v>
@@ -10998,7 +10986,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="319" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A319" s="1" t="str">
         <f t="shared" si="4"/>
         <v>1006004</v>
@@ -11022,7 +11010,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="320" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A320" s="1" t="str">
         <f t="shared" si="4"/>
         <v>1006013</v>
@@ -11046,7 +11034,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="321" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A321" s="1" t="str">
         <f t="shared" si="4"/>
         <v>1006062</v>
@@ -11070,7 +11058,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="322" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A322" s="1" t="str">
         <f t="shared" si="4"/>
         <v>1006026</v>
@@ -11094,7 +11082,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="323" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A323" s="1" t="str">
         <f t="shared" si="4"/>
         <v>1006003</v>
@@ -11118,7 +11106,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="324" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A324" s="1" t="str">
         <f t="shared" si="4"/>
         <v>1006002</v>
@@ -11142,7 +11130,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="325" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A325" s="1" t="str">
         <f t="shared" ref="A325:A387" si="5">F325 &amp; TEXT(C325,"000")</f>
         <v>1006006</v>
@@ -11166,7 +11154,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="326" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A326" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006011</v>
@@ -11190,7 +11178,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="327" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A327" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006008</v>
@@ -11214,7 +11202,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="328" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A328" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006005</v>
@@ -11238,7 +11226,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="329" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A329" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006018</v>
@@ -11262,7 +11250,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="330" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A330" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006007</v>
@@ -11286,7 +11274,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="331" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A331" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006016</v>
@@ -11310,7 +11298,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="332" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A332" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006020</v>
@@ -11334,7 +11322,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="333" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A333" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006022</v>
@@ -11358,7 +11346,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="334" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A334" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006017</v>
@@ -11382,7 +11370,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="335" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A335" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006021</v>
@@ -11406,7 +11394,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="336" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A336" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006014</v>
@@ -11430,7 +11418,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="337" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A337" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006065</v>
@@ -11454,7 +11442,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="338" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A338" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006141</v>
@@ -11478,7 +11466,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="339" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A339" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006142</v>
@@ -11502,7 +11490,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="340" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A340" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006009</v>
@@ -11526,7 +11514,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="341" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A341" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006010</v>
@@ -11550,7 +11538,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="342" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A342" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006019</v>
@@ -11574,7 +11562,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="343" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A343" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006143</v>
@@ -11598,7 +11586,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="344" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A344" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006023</v>
@@ -11622,7 +11610,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="345" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A345" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006079</v>
@@ -11646,7 +11634,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="346" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A346" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006029</v>
@@ -11670,7 +11658,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="347" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A347" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1014146</v>
@@ -11694,7 +11682,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="348" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A348" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1014001</v>
@@ -11718,7 +11706,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="349" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A349" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1014031</v>
@@ -11742,7 +11730,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="350" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A350" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1014012</v>
@@ -11766,7 +11754,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="351" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A351" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1014023</v>
@@ -11790,7 +11778,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="352" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A352" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1014004</v>
@@ -11814,7 +11802,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="353" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A353" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1014005</v>
@@ -11838,7 +11826,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="354" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A354" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1014003</v>
@@ -11862,7 +11850,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="355" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A355" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1014006</v>
@@ -11886,7 +11874,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="356" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A356" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1014147</v>
@@ -11910,7 +11898,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="357" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A357" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1014024</v>
@@ -11934,7 +11922,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="358" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A358" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1014018</v>
@@ -11958,7 +11946,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="359" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A359" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1014063</v>
@@ -11982,7 +11970,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="360" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A360" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1014148</v>
@@ -12006,7 +11994,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="361" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A361" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1014002</v>
@@ -12030,7 +12018,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="362" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A362" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1014010</v>
@@ -12054,7 +12042,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="363" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A363" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1014017</v>
@@ -12078,7 +12066,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="364" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A364" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1014014</v>
@@ -12102,7 +12090,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="365" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A365" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1014020</v>
@@ -12126,7 +12114,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="366" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A366" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1014058</v>
@@ -12150,7 +12138,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="367" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A367" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1014149</v>
@@ -12174,7 +12162,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="368" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A368" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1014016</v>
@@ -12198,7 +12186,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="369" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A369" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1014027</v>
@@ -12222,7 +12210,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="370" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A370" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1014015</v>
@@ -12246,7 +12234,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="371" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A371" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1014150</v>
@@ -12270,7 +12258,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="372" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A372" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1014072</v>
@@ -12294,7 +12282,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="373" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A373" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1014052</v>
@@ -12318,7 +12306,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="374" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A374" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1014008</v>
@@ -12342,7 +12330,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="375" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A375" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1014026</v>
@@ -12366,7 +12354,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="376" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A376" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1014019</v>
@@ -12390,7 +12378,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="377" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A377" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1014059</v>
@@ -12414,7 +12402,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="378" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A378" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1014007</v>
@@ -12438,7 +12426,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="379" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A379" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1014003</v>
@@ -12462,7 +12450,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="380" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A380" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1014033</v>
@@ -12486,7 +12474,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="381" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A381" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1014056</v>
@@ -12510,7 +12498,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="382" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A382" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1014035</v>
@@ -12534,7 +12522,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="383" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A383" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1014150</v>
@@ -12558,7 +12546,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="384" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A384" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1005029</v>
@@ -12582,7 +12570,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="385" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A385" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1005030</v>
@@ -12606,7 +12594,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="386" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A386" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1005053</v>
@@ -12630,7 +12618,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="387" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A387" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1005027</v>
@@ -12654,7 +12642,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="388" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A388" s="1" t="str">
         <f t="shared" ref="A388:A451" si="6">F388 &amp; TEXT(C388,"000")</f>
         <v>1005019</v>
@@ -12678,7 +12666,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="389" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A389" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1005016</v>
@@ -12702,7 +12690,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="390" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A390" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1005002</v>
@@ -12726,7 +12714,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="391" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A391" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1005017</v>
@@ -12750,7 +12738,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="392" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A392" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1005021</v>
@@ -12774,7 +12762,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="393" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A393" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1005022</v>
@@ -12798,7 +12786,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="394" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A394" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1005014</v>
@@ -12822,7 +12810,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="395" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A395" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1005013</v>
@@ -12846,7 +12834,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="396" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A396" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1005004</v>
@@ -12870,7 +12858,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="397" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A397" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1005020</v>
@@ -12894,7 +12882,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="398" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A398" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1005007</v>
@@ -12918,7 +12906,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="399" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A399" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1005015</v>
@@ -12942,7 +12930,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="400" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A400" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1005005</v>
@@ -12966,7 +12954,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="401" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A401" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1005012</v>
@@ -12990,7 +12978,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="402" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A402" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1005018</v>
@@ -13014,7 +13002,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="403" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A403" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1005031</v>
@@ -13038,7 +13026,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="404" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A404" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1005008</v>
@@ -13062,7 +13050,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="405" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A405" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1005002</v>
@@ -13086,7 +13074,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="406" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A406" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1005009</v>
@@ -13110,7 +13098,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="407" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A407" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1005006</v>
@@ -13134,7 +13122,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="408" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A408" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1005003</v>
@@ -13158,7 +13146,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="409" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A409" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1005023</v>
@@ -13182,7 +13170,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="410" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A410" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1005011</v>
@@ -13206,7 +13194,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="411" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A411" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1005025</v>
@@ -13230,7 +13218,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="412" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A412" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1005024</v>
@@ -13254,7 +13242,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="413" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A413" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1005028</v>
@@ -13278,7 +13266,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="414" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A414" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1005151</v>
@@ -13302,7 +13290,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="415" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A415" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1001001</v>
@@ -13326,7 +13314,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="416" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A416" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1001001</v>
@@ -13350,7 +13338,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="417" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A417" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1001021</v>
@@ -13374,7 +13362,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="418" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A418" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1001152</v>
@@ -13398,7 +13386,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="419" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A419" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1001001</v>
@@ -13422,7 +13410,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="420" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A420" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1001029</v>
@@ -13446,7 +13434,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="421" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A421" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1001023</v>
@@ -13470,7 +13458,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="422" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A422" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1001153</v>
@@ -13494,7 +13482,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="423" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A423" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1001020</v>
@@ -13518,7 +13506,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="424" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A424" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1001013</v>
@@ -13542,7 +13530,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="425" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A425" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1001024</v>
@@ -13566,7 +13554,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="426" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A426" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1001002</v>
@@ -13590,7 +13578,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="427" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A427" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1001043</v>
@@ -13614,7 +13602,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="428" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A428" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1001041</v>
@@ -13638,7 +13626,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="429" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A429" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1001025</v>
@@ -13662,7 +13650,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="430" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A430" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1001012</v>
@@ -13686,7 +13674,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="431" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A431" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1001045</v>
@@ -13710,7 +13698,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="432" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A432" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1001003</v>
@@ -13734,7 +13722,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="433" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A433" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1001154</v>
@@ -13758,7 +13746,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="434" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A434" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1001155</v>
@@ -13782,7 +13770,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="435" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A435" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1001010</v>
@@ -13806,7 +13794,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="436" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A436" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1001011</v>
@@ -13830,7 +13818,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="437" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A437" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1001005</v>
@@ -13854,7 +13842,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="438" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A438" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1001004</v>
@@ -13878,7 +13866,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="439" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A439" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1001018</v>
@@ -13902,7 +13890,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="440" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A440" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1001016</v>
@@ -13926,7 +13914,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="441" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A441" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1001006</v>
@@ -13950,7 +13938,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="442" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A442" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1001008</v>
@@ -13974,7 +13962,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="443" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A443" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1001156</v>
@@ -13998,7 +13986,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="444" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A444" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1001030</v>
@@ -14022,7 +14010,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="445" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A445" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1001022</v>
@@ -14046,7 +14034,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="446" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A446" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1001044</v>
@@ -14070,7 +14058,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="447" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A447" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1001007</v>
@@ -14094,7 +14082,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="448" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A448" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1001033</v>
@@ -14118,7 +14106,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="449" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A449" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1001157</v>
@@ -14142,7 +14130,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="450" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A450" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1001158</v>
@@ -14166,7 +14154,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="451" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A451" s="1" t="str">
         <f t="shared" si="6"/>
         <v>1001039</v>
@@ -14190,7 +14178,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="452" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A452" s="1" t="str">
         <f t="shared" ref="A452:A515" si="7">F452 &amp; TEXT(C452,"000")</f>
         <v>1001009</v>
@@ -14214,7 +14202,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="453" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A453" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1001046</v>
@@ -14238,7 +14226,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="454" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A454" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1001028</v>
@@ -14262,7 +14250,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="455" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A455" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1001159</v>
@@ -14286,7 +14274,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="456" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A456" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1001017</v>
@@ -14310,7 +14298,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="457" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A457" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1001160</v>
@@ -14334,7 +14322,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="458" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A458" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1001161</v>
@@ -14358,7 +14346,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="459" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A459" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1016001</v>
@@ -14382,7 +14370,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="460" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A460" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1016012</v>
@@ -14406,7 +14394,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="461" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A461" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1016101</v>
@@ -14430,7 +14418,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="462" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A462" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1016102</v>
@@ -14454,7 +14442,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="463" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A463" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1016103</v>
@@ -14478,7 +14466,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="464" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A464" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1016004</v>
@@ -14502,7 +14490,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="465" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A465" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1016005</v>
@@ -14526,7 +14514,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="466" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A466" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1016104</v>
@@ -14550,7 +14538,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="467" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A467" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1016003</v>
@@ -14574,7 +14562,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="468" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A468" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1016052</v>
@@ -14598,7 +14586,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="469" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A469" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1016020</v>
@@ -14622,7 +14610,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="470" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A470" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1016002</v>
@@ -14646,7 +14634,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="471" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A471" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1016015</v>
@@ -14670,7 +14658,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="472" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A472" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1016037</v>
@@ -14694,7 +14682,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="473" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A473" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1016033</v>
@@ -14718,7 +14706,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="474" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A474" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1016106</v>
@@ -14742,7 +14730,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="475" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A475" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1016107</v>
@@ -14766,7 +14754,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="476" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A476" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1016108</v>
@@ -14790,7 +14778,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="477" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A477" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1016010</v>
@@ -14814,7 +14802,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="478" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A478" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1016024</v>
@@ -14838,7 +14826,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="479" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A479" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1016007</v>
@@ -14862,7 +14850,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="480" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A480" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1016023</v>
@@ -14886,7 +14874,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="481" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A481" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1016053</v>
@@ -14910,7 +14898,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="482" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A482" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1016009</v>
@@ -14934,7 +14922,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="483" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A483" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1016006</v>
@@ -14958,7 +14946,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="484" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A484" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1016019</v>
@@ -14982,7 +14970,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="485" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A485" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1016016</v>
@@ -15006,7 +14994,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="486" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A486" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1016018</v>
@@ -15030,7 +15018,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="487" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A487" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1016025</v>
@@ -15054,7 +15042,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="488" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A488" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1016017</v>
@@ -15078,7 +15066,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="489" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A489" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1016026</v>
@@ -15102,7 +15090,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="490" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A490" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1016038</v>
@@ -15126,7 +15114,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="491" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A491" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1016057</v>
@@ -15150,7 +15138,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="492" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A492" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1016109</v>
@@ -15174,7 +15162,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="493" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A493" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1016110</v>
@@ -15198,7 +15186,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="494" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A494" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1016111</v>
@@ -15222,7 +15210,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="495" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A495" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1016112</v>
@@ -15246,7 +15234,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="496" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A496" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1016113</v>
@@ -15270,7 +15258,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="497" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A497" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1016114</v>
@@ -15294,7 +15282,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="498" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A498" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1016011</v>
@@ -15318,7 +15306,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="499" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A499" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1016008</v>
@@ -15342,7 +15330,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="500" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A500" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1016115</v>
@@ -15366,7 +15354,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="501" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A501" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1016055</v>
@@ -15390,7 +15378,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="502" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A502" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1016116</v>
@@ -15414,7 +15402,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="503" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A503" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1016117</v>
@@ -15438,7 +15426,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="504" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A504" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1017001</v>
@@ -15462,7 +15450,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="505" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A505" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1017101</v>
@@ -15486,7 +15474,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="506" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A506" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1017102</v>
@@ -15510,7 +15498,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="507" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A507" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1017103</v>
@@ -15534,7 +15522,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="508" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A508" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1017015</v>
@@ -15558,7 +15546,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="509" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A509" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1017004</v>
@@ -15582,7 +15570,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="510" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A510" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1017013</v>
@@ -15606,7 +15594,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="511" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A511" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1017006</v>
@@ -15630,7 +15618,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="512" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A512" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1017002</v>
@@ -15654,7 +15642,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="513" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A513" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1017104</v>
@@ -15678,7 +15666,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="514" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A514" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1017024</v>
@@ -15702,7 +15690,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="515" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A515" s="1" t="str">
         <f t="shared" si="7"/>
         <v>1017005</v>
@@ -15726,7 +15714,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="516" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A516" s="1" t="str">
         <f t="shared" ref="A516:A532" si="8">F516 &amp; TEXT(C516,"000")</f>
         <v>1017012</v>
@@ -15750,7 +15738,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="517" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A517" s="1" t="str">
         <f t="shared" si="8"/>
         <v>1017023</v>
@@ -15774,7 +15762,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="518" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A518" s="1" t="str">
         <f t="shared" si="8"/>
         <v>1017057</v>
@@ -15798,7 +15786,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="519" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A519" s="1" t="str">
         <f t="shared" si="8"/>
         <v>1017106</v>
@@ -15822,7 +15810,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="520" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A520" s="1" t="str">
         <f t="shared" si="8"/>
         <v>1017019</v>
@@ -15846,7 +15834,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="521" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A521" s="1" t="str">
         <f t="shared" si="8"/>
         <v>1017007</v>
@@ -15870,7 +15858,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="522" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A522" s="1" t="str">
         <f t="shared" si="8"/>
         <v>1017008</v>
@@ -15894,7 +15882,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="523" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A523" s="1" t="str">
         <f t="shared" si="8"/>
         <v>1017029</v>
@@ -15918,7 +15906,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="524" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A524" s="1" t="str">
         <f t="shared" si="8"/>
         <v>1017016</v>
@@ -15942,7 +15930,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="525" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A525" s="1" t="str">
         <f t="shared" si="8"/>
         <v>1017010</v>
@@ -15966,7 +15954,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="526" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A526" s="1" t="str">
         <f t="shared" si="8"/>
         <v>1017021</v>
@@ -15990,7 +15978,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="527" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A527" s="1" t="str">
         <f t="shared" si="8"/>
         <v>1017067</v>
@@ -16014,7 +16002,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="528" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A528" s="1" t="str">
         <f t="shared" si="8"/>
         <v>1017011</v>
@@ -16038,7 +16026,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="529" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A529" s="1" t="str">
         <f t="shared" si="8"/>
         <v>1017113</v>
@@ -16062,7 +16050,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="530" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A530" s="1" t="str">
         <f t="shared" si="8"/>
         <v>1017009</v>
@@ -16086,7 +16074,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="531" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A531" s="1" t="str">
         <f t="shared" si="8"/>
         <v>1017018</v>
@@ -16110,7 +16098,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="532" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A532" s="1" t="str">
         <f t="shared" si="8"/>
         <v>1017026</v>
@@ -16134,7 +16122,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="533" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A533" t="str">
         <f>F533 &amp; TEXT(C533,"000")</f>
         <v>1002029</v>

--- a/backend/data/LigaPremier.xlsx
+++ b/backend/data/LigaPremier.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danyl\Downloads\E\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B2EBCADD-4528-49E7-BBF8-99E55DE1FCC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{17F66FC4-7ED5-4490-97D4-5D9BE67B0E87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2133" uniqueCount="938">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2139" uniqueCount="941">
   <si>
     <t>Id_jugador</t>
   </si>
@@ -2847,6 +2847,15 @@
   </si>
   <si>
     <t>Emilio Vargas</t>
+  </si>
+  <si>
+    <t>Andres Mares</t>
+  </si>
+  <si>
+    <t>Jonarhan Gonzales</t>
+  </si>
+  <si>
+    <t>Jovanny Zepeda</t>
   </si>
 </sst>
 </file>
@@ -2935,7 +2944,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2947,6 +2956,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3144,10 +3154,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{32A8CF84-C284-4FB9-BA95-EA038AE71CB6}" name="Tabla1" displayName="Tabla1" ref="A1:G533" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7">
-  <autoFilter ref="A1:G533" xr:uid="{32A8CF84-C284-4FB9-BA95-EA038AE71CB6}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{32A8CF84-C284-4FB9-BA95-EA038AE71CB6}" name="Tabla1" displayName="Tabla1" ref="A1:G536" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7">
+  <autoFilter ref="A1:G536" xr:uid="{32A8CF84-C284-4FB9-BA95-EA038AE71CB6}">
     <filterColumn colId="6">
-      <filters blank="1"/>
+      <filters>
+        <filter val="Lobos ULMX"/>
+      </filters>
     </filterColumn>
   </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G533">
@@ -3404,7 +3416,7 @@
     </row>
     <row r="2" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="str">
-        <f>F2 &amp; TEXT(C2,"000")</f>
+        <f t="shared" ref="A2:A65" si="0">F2 &amp; TEXT(C2,"000")</f>
         <v>1017001</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -3428,7 +3440,7 @@
     </row>
     <row r="3" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="str">
-        <f>F3 &amp; TEXT(C3,"000")</f>
+        <f t="shared" si="0"/>
         <v>1017101</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -3452,7 +3464,7 @@
     </row>
     <row r="4" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="str">
-        <f>F4 &amp; TEXT(C4,"000")</f>
+        <f t="shared" si="0"/>
         <v>1017102</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -3476,7 +3488,7 @@
     </row>
     <row r="5" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="str">
-        <f>F5 &amp; TEXT(C5,"000")</f>
+        <f t="shared" si="0"/>
         <v>1017103</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -3500,7 +3512,7 @@
     </row>
     <row r="6" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="str">
-        <f>F6 &amp; TEXT(C6,"000")</f>
+        <f t="shared" si="0"/>
         <v>1017015</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -3524,7 +3536,7 @@
     </row>
     <row r="7" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="str">
-        <f>F7 &amp; TEXT(C7,"000")</f>
+        <f t="shared" si="0"/>
         <v>1017004</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -3548,7 +3560,7 @@
     </row>
     <row r="8" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="str">
-        <f>F8 &amp; TEXT(C8,"000")</f>
+        <f t="shared" si="0"/>
         <v>1017013</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -3572,7 +3584,7 @@
     </row>
     <row r="9" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="str">
-        <f>F9 &amp; TEXT(C9,"000")</f>
+        <f t="shared" si="0"/>
         <v>1017006</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -3596,7 +3608,7 @@
     </row>
     <row r="10" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="str">
-        <f>F10 &amp; TEXT(C10,"000")</f>
+        <f t="shared" si="0"/>
         <v>1017002</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -3620,7 +3632,7 @@
     </row>
     <row r="11" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="str">
-        <f>F11 &amp; TEXT(C11,"000")</f>
+        <f t="shared" si="0"/>
         <v>1017104</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -3644,7 +3656,7 @@
     </row>
     <row r="12" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="str">
-        <f>F12 &amp; TEXT(C12,"000")</f>
+        <f t="shared" si="0"/>
         <v>1017024</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -3668,7 +3680,7 @@
     </row>
     <row r="13" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="str">
-        <f>F13 &amp; TEXT(C13,"000")</f>
+        <f t="shared" si="0"/>
         <v>1017005</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -3692,7 +3704,7 @@
     </row>
     <row r="14" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="str">
-        <f>F14 &amp; TEXT(C14,"000")</f>
+        <f t="shared" si="0"/>
         <v>1017012</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -3716,7 +3728,7 @@
     </row>
     <row r="15" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="str">
-        <f>F15 &amp; TEXT(C15,"000")</f>
+        <f t="shared" si="0"/>
         <v>1017023</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -3740,7 +3752,7 @@
     </row>
     <row r="16" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="str">
-        <f>F16 &amp; TEXT(C16,"000")</f>
+        <f t="shared" si="0"/>
         <v>1017057</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -3764,7 +3776,7 @@
     </row>
     <row r="17" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="str">
-        <f>F17 &amp; TEXT(C17,"000")</f>
+        <f t="shared" si="0"/>
         <v>1017106</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -3788,7 +3800,7 @@
     </row>
     <row r="18" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="str">
-        <f>F18 &amp; TEXT(C18,"000")</f>
+        <f t="shared" si="0"/>
         <v>1017019</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -3812,7 +3824,7 @@
     </row>
     <row r="19" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="str">
-        <f>F19 &amp; TEXT(C19,"000")</f>
+        <f t="shared" si="0"/>
         <v>1017007</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -3836,7 +3848,7 @@
     </row>
     <row r="20" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="str">
-        <f>F20 &amp; TEXT(C20,"000")</f>
+        <f t="shared" si="0"/>
         <v>1017008</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -3860,7 +3872,7 @@
     </row>
     <row r="21" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="str">
-        <f>F21 &amp; TEXT(C21,"000")</f>
+        <f t="shared" si="0"/>
         <v>1017029</v>
       </c>
       <c r="B21" s="1" t="s">
@@ -3884,7 +3896,7 @@
     </row>
     <row r="22" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="str">
-        <f>F22 &amp; TEXT(C22,"000")</f>
+        <f t="shared" si="0"/>
         <v>1017016</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -3908,7 +3920,7 @@
     </row>
     <row r="23" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="str">
-        <f>F23 &amp; TEXT(C23,"000")</f>
+        <f t="shared" si="0"/>
         <v>1017010</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -3932,7 +3944,7 @@
     </row>
     <row r="24" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="str">
-        <f>F24 &amp; TEXT(C24,"000")</f>
+        <f t="shared" si="0"/>
         <v>1017021</v>
       </c>
       <c r="B24" s="1" t="s">
@@ -3956,7 +3968,7 @@
     </row>
     <row r="25" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="str">
-        <f>F25 &amp; TEXT(C25,"000")</f>
+        <f t="shared" si="0"/>
         <v>1017067</v>
       </c>
       <c r="B25" s="1" t="s">
@@ -3980,7 +3992,7 @@
     </row>
     <row r="26" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="str">
-        <f>F26 &amp; TEXT(C26,"000")</f>
+        <f t="shared" si="0"/>
         <v>1017011</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -4004,7 +4016,7 @@
     </row>
     <row r="27" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="str">
-        <f>F27 &amp; TEXT(C27,"000")</f>
+        <f t="shared" si="0"/>
         <v>1017113</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -4028,7 +4040,7 @@
     </row>
     <row r="28" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="str">
-        <f>F28 &amp; TEXT(C28,"000")</f>
+        <f t="shared" si="0"/>
         <v>1017009</v>
       </c>
       <c r="B28" s="1" t="s">
@@ -4052,7 +4064,7 @@
     </row>
     <row r="29" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="str">
-        <f>F29 &amp; TEXT(C29,"000")</f>
+        <f t="shared" si="0"/>
         <v>1017018</v>
       </c>
       <c r="B29" s="1" t="s">
@@ -4076,7 +4088,7 @@
     </row>
     <row r="30" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="str">
-        <f>F30 &amp; TEXT(C30,"000")</f>
+        <f t="shared" si="0"/>
         <v>1017026</v>
       </c>
       <c r="B30" s="1" t="s">
@@ -4100,7 +4112,7 @@
     </row>
     <row r="31" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="str">
-        <f>F31 &amp; TEXT(C31,"000")</f>
+        <f t="shared" si="0"/>
         <v>1016001</v>
       </c>
       <c r="B31" s="1" t="s">
@@ -4124,7 +4136,7 @@
     </row>
     <row r="32" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="str">
-        <f>F32 &amp; TEXT(C32,"000")</f>
+        <f t="shared" si="0"/>
         <v>1016012</v>
       </c>
       <c r="B32" s="1" t="s">
@@ -4148,7 +4160,7 @@
     </row>
     <row r="33" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="str">
-        <f>F33 &amp; TEXT(C33,"000")</f>
+        <f t="shared" si="0"/>
         <v>1016101</v>
       </c>
       <c r="B33" s="1" t="s">
@@ -4172,7 +4184,7 @@
     </row>
     <row r="34" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="str">
-        <f>F34 &amp; TEXT(C34,"000")</f>
+        <f t="shared" si="0"/>
         <v>1016102</v>
       </c>
       <c r="B34" s="1" t="s">
@@ -4196,7 +4208,7 @@
     </row>
     <row r="35" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="str">
-        <f>F35 &amp; TEXT(C35,"000")</f>
+        <f t="shared" si="0"/>
         <v>1016103</v>
       </c>
       <c r="B35" s="1" t="s">
@@ -4220,7 +4232,7 @@
     </row>
     <row r="36" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="str">
-        <f>F36 &amp; TEXT(C36,"000")</f>
+        <f t="shared" si="0"/>
         <v>1016004</v>
       </c>
       <c r="B36" s="1" t="s">
@@ -4244,7 +4256,7 @@
     </row>
     <row r="37" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="str">
-        <f>F37 &amp; TEXT(C37,"000")</f>
+        <f t="shared" si="0"/>
         <v>1016005</v>
       </c>
       <c r="B37" s="1" t="s">
@@ -4268,7 +4280,7 @@
     </row>
     <row r="38" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="str">
-        <f>F38 &amp; TEXT(C38,"000")</f>
+        <f t="shared" si="0"/>
         <v>1016104</v>
       </c>
       <c r="B38" s="1" t="s">
@@ -4292,7 +4304,7 @@
     </row>
     <row r="39" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="str">
-        <f>F39 &amp; TEXT(C39,"000")</f>
+        <f t="shared" si="0"/>
         <v>1016003</v>
       </c>
       <c r="B39" s="1" t="s">
@@ -4316,7 +4328,7 @@
     </row>
     <row r="40" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="str">
-        <f>F40 &amp; TEXT(C40,"000")</f>
+        <f t="shared" si="0"/>
         <v>1016052</v>
       </c>
       <c r="B40" s="1" t="s">
@@ -4340,7 +4352,7 @@
     </row>
     <row r="41" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="str">
-        <f>F41 &amp; TEXT(C41,"000")</f>
+        <f t="shared" si="0"/>
         <v>1016020</v>
       </c>
       <c r="B41" s="1" t="s">
@@ -4364,7 +4376,7 @@
     </row>
     <row r="42" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="str">
-        <f>F42 &amp; TEXT(C42,"000")</f>
+        <f t="shared" si="0"/>
         <v>1016002</v>
       </c>
       <c r="B42" s="1" t="s">
@@ -4388,7 +4400,7 @@
     </row>
     <row r="43" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="str">
-        <f>F43 &amp; TEXT(C43,"000")</f>
+        <f t="shared" si="0"/>
         <v>1016015</v>
       </c>
       <c r="B43" s="1" t="s">
@@ -4412,7 +4424,7 @@
     </row>
     <row r="44" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="str">
-        <f>F44 &amp; TEXT(C44,"000")</f>
+        <f t="shared" si="0"/>
         <v>1016037</v>
       </c>
       <c r="B44" s="1" t="s">
@@ -4436,7 +4448,7 @@
     </row>
     <row r="45" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="str">
-        <f>F45 &amp; TEXT(C45,"000")</f>
+        <f t="shared" si="0"/>
         <v>1016033</v>
       </c>
       <c r="B45" s="1" t="s">
@@ -4460,7 +4472,7 @@
     </row>
     <row r="46" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="str">
-        <f>F46 &amp; TEXT(C46,"000")</f>
+        <f t="shared" si="0"/>
         <v>1016106</v>
       </c>
       <c r="B46" s="1" t="s">
@@ -4484,7 +4496,7 @@
     </row>
     <row r="47" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="str">
-        <f>F47 &amp; TEXT(C47,"000")</f>
+        <f t="shared" si="0"/>
         <v>1016107</v>
       </c>
       <c r="B47" s="1" t="s">
@@ -4508,7 +4520,7 @@
     </row>
     <row r="48" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="str">
-        <f>F48 &amp; TEXT(C48,"000")</f>
+        <f t="shared" si="0"/>
         <v>1016108</v>
       </c>
       <c r="B48" s="1" t="s">
@@ -4532,7 +4544,7 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="str">
-        <f>F49 &amp; TEXT(C49,"000")</f>
+        <f t="shared" si="0"/>
         <v>1016010</v>
       </c>
       <c r="B49" s="1" t="s">
@@ -4556,7 +4568,7 @@
     </row>
     <row r="50" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="str">
-        <f>F50 &amp; TEXT(C50,"000")</f>
+        <f t="shared" si="0"/>
         <v>1016024</v>
       </c>
       <c r="B50" s="1" t="s">
@@ -4580,7 +4592,7 @@
     </row>
     <row r="51" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="str">
-        <f>F51 &amp; TEXT(C51,"000")</f>
+        <f t="shared" si="0"/>
         <v>1016007</v>
       </c>
       <c r="B51" s="1" t="s">
@@ -4604,7 +4616,7 @@
     </row>
     <row r="52" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="str">
-        <f>F52 &amp; TEXT(C52,"000")</f>
+        <f t="shared" si="0"/>
         <v>1016023</v>
       </c>
       <c r="B52" s="1" t="s">
@@ -4628,7 +4640,7 @@
     </row>
     <row r="53" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="str">
-        <f>F53 &amp; TEXT(C53,"000")</f>
+        <f t="shared" si="0"/>
         <v>1016053</v>
       </c>
       <c r="B53" s="1" t="s">
@@ -4652,7 +4664,7 @@
     </row>
     <row r="54" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="str">
-        <f>F54 &amp; TEXT(C54,"000")</f>
+        <f t="shared" si="0"/>
         <v>1016009</v>
       </c>
       <c r="B54" s="1" t="s">
@@ -4676,7 +4688,7 @@
     </row>
     <row r="55" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="str">
-        <f>F55 &amp; TEXT(C55,"000")</f>
+        <f t="shared" si="0"/>
         <v>1016006</v>
       </c>
       <c r="B55" s="1" t="s">
@@ -4700,7 +4712,7 @@
     </row>
     <row r="56" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="str">
-        <f>F56 &amp; TEXT(C56,"000")</f>
+        <f t="shared" si="0"/>
         <v>1016019</v>
       </c>
       <c r="B56" s="1" t="s">
@@ -4724,7 +4736,7 @@
     </row>
     <row r="57" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="str">
-        <f>F57 &amp; TEXT(C57,"000")</f>
+        <f t="shared" si="0"/>
         <v>1016016</v>
       </c>
       <c r="B57" s="1" t="s">
@@ -4748,7 +4760,7 @@
     </row>
     <row r="58" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="str">
-        <f>F58 &amp; TEXT(C58,"000")</f>
+        <f t="shared" si="0"/>
         <v>1016018</v>
       </c>
       <c r="B58" s="1" t="s">
@@ -4772,7 +4784,7 @@
     </row>
     <row r="59" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="str">
-        <f>F59 &amp; TEXT(C59,"000")</f>
+        <f t="shared" si="0"/>
         <v>1016025</v>
       </c>
       <c r="B59" s="1" t="s">
@@ -4796,7 +4808,7 @@
     </row>
     <row r="60" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="str">
-        <f>F60 &amp; TEXT(C60,"000")</f>
+        <f t="shared" si="0"/>
         <v>1016017</v>
       </c>
       <c r="B60" s="1" t="s">
@@ -4820,7 +4832,7 @@
     </row>
     <row r="61" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="str">
-        <f>F61 &amp; TEXT(C61,"000")</f>
+        <f t="shared" si="0"/>
         <v>1016026</v>
       </c>
       <c r="B61" s="1" t="s">
@@ -4844,7 +4856,7 @@
     </row>
     <row r="62" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="str">
-        <f>F62 &amp; TEXT(C62,"000")</f>
+        <f t="shared" si="0"/>
         <v>1016038</v>
       </c>
       <c r="B62" s="1" t="s">
@@ -4868,7 +4880,7 @@
     </row>
     <row r="63" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="str">
-        <f>F63 &amp; TEXT(C63,"000")</f>
+        <f t="shared" si="0"/>
         <v>1016057</v>
       </c>
       <c r="B63" s="1" t="s">
@@ -4892,7 +4904,7 @@
     </row>
     <row r="64" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="str">
-        <f>F64 &amp; TEXT(C64,"000")</f>
+        <f t="shared" si="0"/>
         <v>1016109</v>
       </c>
       <c r="B64" s="1" t="s">
@@ -4916,7 +4928,7 @@
     </row>
     <row r="65" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="str">
-        <f>F65 &amp; TEXT(C65,"000")</f>
+        <f t="shared" si="0"/>
         <v>1016110</v>
       </c>
       <c r="B65" s="1" t="s">
@@ -4940,7 +4952,7 @@
     </row>
     <row r="66" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="str">
-        <f>F66 &amp; TEXT(C66,"000")</f>
+        <f t="shared" ref="A66:A129" si="1">F66 &amp; TEXT(C66,"000")</f>
         <v>1016111</v>
       </c>
       <c r="B66" s="1" t="s">
@@ -4964,7 +4976,7 @@
     </row>
     <row r="67" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="str">
-        <f>F67 &amp; TEXT(C67,"000")</f>
+        <f t="shared" si="1"/>
         <v>1016112</v>
       </c>
       <c r="B67" s="1" t="s">
@@ -4988,7 +5000,7 @@
     </row>
     <row r="68" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="str">
-        <f>F68 &amp; TEXT(C68,"000")</f>
+        <f t="shared" si="1"/>
         <v>1016113</v>
       </c>
       <c r="B68" s="1" t="s">
@@ -5012,7 +5024,7 @@
     </row>
     <row r="69" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="str">
-        <f>F69 &amp; TEXT(C69,"000")</f>
+        <f t="shared" si="1"/>
         <v>1016114</v>
       </c>
       <c r="B69" s="1" t="s">
@@ -5036,7 +5048,7 @@
     </row>
     <row r="70" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="str">
-        <f>F70 &amp; TEXT(C70,"000")</f>
+        <f t="shared" si="1"/>
         <v>1016011</v>
       </c>
       <c r="B70" s="1" t="s">
@@ -5060,7 +5072,7 @@
     </row>
     <row r="71" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="str">
-        <f>F71 &amp; TEXT(C71,"000")</f>
+        <f t="shared" si="1"/>
         <v>1016008</v>
       </c>
       <c r="B71" s="1" t="s">
@@ -5084,7 +5096,7 @@
     </row>
     <row r="72" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="str">
-        <f>F72 &amp; TEXT(C72,"000")</f>
+        <f t="shared" si="1"/>
         <v>1016115</v>
       </c>
       <c r="B72" s="1" t="s">
@@ -5108,7 +5120,7 @@
     </row>
     <row r="73" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="str">
-        <f>F73 &amp; TEXT(C73,"000")</f>
+        <f t="shared" si="1"/>
         <v>1016055</v>
       </c>
       <c r="B73" s="1" t="s">
@@ -5132,7 +5144,7 @@
     </row>
     <row r="74" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="str">
-        <f>F74 &amp; TEXT(C74,"000")</f>
+        <f t="shared" si="1"/>
         <v>1016116</v>
       </c>
       <c r="B74" s="1" t="s">
@@ -5156,7 +5168,7 @@
     </row>
     <row r="75" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="str">
-        <f>F75 &amp; TEXT(C75,"000")</f>
+        <f t="shared" si="1"/>
         <v>1016117</v>
       </c>
       <c r="B75" s="1" t="s">
@@ -5180,7 +5192,7 @@
     </row>
     <row r="76" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="str">
-        <f>F76 &amp; TEXT(C76,"000")</f>
+        <f t="shared" si="1"/>
         <v>1014146</v>
       </c>
       <c r="B76" s="1" t="s">
@@ -5204,7 +5216,7 @@
     </row>
     <row r="77" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="str">
-        <f>F77 &amp; TEXT(C77,"000")</f>
+        <f t="shared" si="1"/>
         <v>1014001</v>
       </c>
       <c r="B77" s="1" t="s">
@@ -5228,7 +5240,7 @@
     </row>
     <row r="78" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="str">
-        <f>F78 &amp; TEXT(C78,"000")</f>
+        <f t="shared" si="1"/>
         <v>1014031</v>
       </c>
       <c r="B78" s="1" t="s">
@@ -5252,7 +5264,7 @@
     </row>
     <row r="79" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="str">
-        <f>F79 &amp; TEXT(C79,"000")</f>
+        <f t="shared" si="1"/>
         <v>1014012</v>
       </c>
       <c r="B79" s="1" t="s">
@@ -5276,7 +5288,7 @@
     </row>
     <row r="80" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="str">
-        <f>F80 &amp; TEXT(C80,"000")</f>
+        <f t="shared" si="1"/>
         <v>1014023</v>
       </c>
       <c r="B80" s="1" t="s">
@@ -5300,7 +5312,7 @@
     </row>
     <row r="81" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="str">
-        <f>F81 &amp; TEXT(C81,"000")</f>
+        <f t="shared" si="1"/>
         <v>1014004</v>
       </c>
       <c r="B81" s="1" t="s">
@@ -5324,7 +5336,7 @@
     </row>
     <row r="82" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="str">
-        <f>F82 &amp; TEXT(C82,"000")</f>
+        <f t="shared" si="1"/>
         <v>1014005</v>
       </c>
       <c r="B82" s="1" t="s">
@@ -5348,7 +5360,7 @@
     </row>
     <row r="83" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="str">
-        <f>F83 &amp; TEXT(C83,"000")</f>
+        <f t="shared" si="1"/>
         <v>1014003</v>
       </c>
       <c r="B83" s="1" t="s">
@@ -5372,7 +5384,7 @@
     </row>
     <row r="84" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="str">
-        <f>F84 &amp; TEXT(C84,"000")</f>
+        <f t="shared" si="1"/>
         <v>1014006</v>
       </c>
       <c r="B84" s="1" t="s">
@@ -5396,7 +5408,7 @@
     </row>
     <row r="85" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="str">
-        <f>F85 &amp; TEXT(C85,"000")</f>
+        <f t="shared" si="1"/>
         <v>1014147</v>
       </c>
       <c r="B85" s="1" t="s">
@@ -5420,7 +5432,7 @@
     </row>
     <row r="86" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="str">
-        <f>F86 &amp; TEXT(C86,"000")</f>
+        <f t="shared" si="1"/>
         <v>1014024</v>
       </c>
       <c r="B86" s="1" t="s">
@@ -5444,7 +5456,7 @@
     </row>
     <row r="87" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="str">
-        <f>F87 &amp; TEXT(C87,"000")</f>
+        <f t="shared" si="1"/>
         <v>1014018</v>
       </c>
       <c r="B87" s="1" t="s">
@@ -5468,7 +5480,7 @@
     </row>
     <row r="88" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="str">
-        <f>F88 &amp; TEXT(C88,"000")</f>
+        <f t="shared" si="1"/>
         <v>1014063</v>
       </c>
       <c r="B88" s="1" t="s">
@@ -5492,7 +5504,7 @@
     </row>
     <row r="89" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="str">
-        <f>F89 &amp; TEXT(C89,"000")</f>
+        <f t="shared" si="1"/>
         <v>1014148</v>
       </c>
       <c r="B89" s="1" t="s">
@@ -5516,7 +5528,7 @@
     </row>
     <row r="90" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="str">
-        <f>F90 &amp; TEXT(C90,"000")</f>
+        <f t="shared" si="1"/>
         <v>1014002</v>
       </c>
       <c r="B90" s="1" t="s">
@@ -5540,7 +5552,7 @@
     </row>
     <row r="91" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="str">
-        <f>F91 &amp; TEXT(C91,"000")</f>
+        <f t="shared" si="1"/>
         <v>1014010</v>
       </c>
       <c r="B91" s="1" t="s">
@@ -5564,7 +5576,7 @@
     </row>
     <row r="92" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="str">
-        <f>F92 &amp; TEXT(C92,"000")</f>
+        <f t="shared" si="1"/>
         <v>1014017</v>
       </c>
       <c r="B92" s="1" t="s">
@@ -5588,7 +5600,7 @@
     </row>
     <row r="93" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="str">
-        <f>F93 &amp; TEXT(C93,"000")</f>
+        <f t="shared" si="1"/>
         <v>1014014</v>
       </c>
       <c r="B93" s="1" t="s">
@@ -5612,7 +5624,7 @@
     </row>
     <row r="94" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="str">
-        <f>F94 &amp; TEXT(C94,"000")</f>
+        <f t="shared" si="1"/>
         <v>1014020</v>
       </c>
       <c r="B94" s="1" t="s">
@@ -5636,7 +5648,7 @@
     </row>
     <row r="95" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="str">
-        <f>F95 &amp; TEXT(C95,"000")</f>
+        <f t="shared" si="1"/>
         <v>1014058</v>
       </c>
       <c r="B95" s="1" t="s">
@@ -5660,7 +5672,7 @@
     </row>
     <row r="96" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="str">
-        <f>F96 &amp; TEXT(C96,"000")</f>
+        <f t="shared" si="1"/>
         <v>1014149</v>
       </c>
       <c r="B96" s="1" t="s">
@@ -5684,7 +5696,7 @@
     </row>
     <row r="97" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="str">
-        <f>F97 &amp; TEXT(C97,"000")</f>
+        <f t="shared" si="1"/>
         <v>1014016</v>
       </c>
       <c r="B97" s="1" t="s">
@@ -5708,7 +5720,7 @@
     </row>
     <row r="98" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="str">
-        <f>F98 &amp; TEXT(C98,"000")</f>
+        <f t="shared" si="1"/>
         <v>1014027</v>
       </c>
       <c r="B98" s="1" t="s">
@@ -5732,7 +5744,7 @@
     </row>
     <row r="99" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="str">
-        <f>F99 &amp; TEXT(C99,"000")</f>
+        <f t="shared" si="1"/>
         <v>1014015</v>
       </c>
       <c r="B99" s="1" t="s">
@@ -5756,7 +5768,7 @@
     </row>
     <row r="100" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="str">
-        <f>F100 &amp; TEXT(C100,"000")</f>
+        <f t="shared" si="1"/>
         <v>1014150</v>
       </c>
       <c r="B100" s="1" t="s">
@@ -5780,7 +5792,7 @@
     </row>
     <row r="101" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="str">
-        <f>F101 &amp; TEXT(C101,"000")</f>
+        <f t="shared" si="1"/>
         <v>1014072</v>
       </c>
       <c r="B101" s="1" t="s">
@@ -5804,7 +5816,7 @@
     </row>
     <row r="102" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="str">
-        <f>F102 &amp; TEXT(C102,"000")</f>
+        <f t="shared" si="1"/>
         <v>1014052</v>
       </c>
       <c r="B102" s="1" t="s">
@@ -5828,7 +5840,7 @@
     </row>
     <row r="103" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="str">
-        <f>F103 &amp; TEXT(C103,"000")</f>
+        <f t="shared" si="1"/>
         <v>1014008</v>
       </c>
       <c r="B103" s="1" t="s">
@@ -5852,7 +5864,7 @@
     </row>
     <row r="104" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="str">
-        <f>F104 &amp; TEXT(C104,"000")</f>
+        <f t="shared" si="1"/>
         <v>1014026</v>
       </c>
       <c r="B104" s="1" t="s">
@@ -5876,7 +5888,7 @@
     </row>
     <row r="105" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="str">
-        <f>F105 &amp; TEXT(C105,"000")</f>
+        <f t="shared" si="1"/>
         <v>1014019</v>
       </c>
       <c r="B105" s="1" t="s">
@@ -5900,7 +5912,7 @@
     </row>
     <row r="106" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="str">
-        <f>F106 &amp; TEXT(C106,"000")</f>
+        <f t="shared" si="1"/>
         <v>1014059</v>
       </c>
       <c r="B106" s="1" t="s">
@@ -5924,7 +5936,7 @@
     </row>
     <row r="107" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="str">
-        <f>F107 &amp; TEXT(C107,"000")</f>
+        <f t="shared" si="1"/>
         <v>1014007</v>
       </c>
       <c r="B107" s="1" t="s">
@@ -5948,7 +5960,7 @@
     </row>
     <row r="108" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="str">
-        <f>F108 &amp; TEXT(C108,"000")</f>
+        <f t="shared" si="1"/>
         <v>1014003</v>
       </c>
       <c r="B108" s="1" t="s">
@@ -5972,7 +5984,7 @@
     </row>
     <row r="109" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="str">
-        <f>F109 &amp; TEXT(C109,"000")</f>
+        <f t="shared" si="1"/>
         <v>1014033</v>
       </c>
       <c r="B109" s="1" t="s">
@@ -5996,7 +6008,7 @@
     </row>
     <row r="110" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="str">
-        <f>F110 &amp; TEXT(C110,"000")</f>
+        <f t="shared" si="1"/>
         <v>1014056</v>
       </c>
       <c r="B110" s="1" t="s">
@@ -6020,7 +6032,7 @@
     </row>
     <row r="111" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="str">
-        <f>F111 &amp; TEXT(C111,"000")</f>
+        <f t="shared" si="1"/>
         <v>1014035</v>
       </c>
       <c r="B111" s="1" t="s">
@@ -6044,7 +6056,7 @@
     </row>
     <row r="112" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="str">
-        <f>F112 &amp; TEXT(C112,"000")</f>
+        <f t="shared" si="1"/>
         <v>1014150</v>
       </c>
       <c r="B112" s="1" t="s">
@@ -6068,7 +6080,7 @@
     </row>
     <row r="113" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="str">
-        <f>F113 &amp; TEXT(C113,"000")</f>
+        <f t="shared" si="1"/>
         <v>1013012</v>
       </c>
       <c r="B113" s="1" t="s">
@@ -6092,7 +6104,7 @@
     </row>
     <row r="114" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="str">
-        <f>F114 &amp; TEXT(C114,"000")</f>
+        <f t="shared" si="1"/>
         <v>1013022</v>
       </c>
       <c r="B114" s="1" t="s">
@@ -6116,7 +6128,7 @@
     </row>
     <row r="115" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="str">
-        <f>F115 &amp; TEXT(C115,"000")</f>
+        <f t="shared" si="1"/>
         <v>1013004</v>
       </c>
       <c r="B115" s="1" t="s">
@@ -6140,7 +6152,7 @@
     </row>
     <row r="116" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="str">
-        <f>F116 &amp; TEXT(C116,"000")</f>
+        <f t="shared" si="1"/>
         <v>1013028</v>
       </c>
       <c r="B116" s="1" t="s">
@@ -6164,7 +6176,7 @@
     </row>
     <row r="117" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="str">
-        <f>F117 &amp; TEXT(C117,"000")</f>
+        <f t="shared" si="1"/>
         <v>1013020</v>
       </c>
       <c r="B117" s="1" t="s">
@@ -6188,7 +6200,7 @@
     </row>
     <row r="118" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="str">
-        <f>F118 &amp; TEXT(C118,"000")</f>
+        <f t="shared" si="1"/>
         <v>1013024</v>
       </c>
       <c r="B118" s="1" t="s">
@@ -6212,7 +6224,7 @@
     </row>
     <row r="119" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="str">
-        <f>F119 &amp; TEXT(C119,"000")</f>
+        <f t="shared" si="1"/>
         <v>1013005</v>
       </c>
       <c r="B119" s="1" t="s">
@@ -6236,7 +6248,7 @@
     </row>
     <row r="120" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="str">
-        <f>F120 &amp; TEXT(C120,"000")</f>
+        <f t="shared" si="1"/>
         <v>1013014</v>
       </c>
       <c r="B120" s="1" t="s">
@@ -6260,7 +6272,7 @@
     </row>
     <row r="121" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="str">
-        <f>F121 &amp; TEXT(C121,"000")</f>
+        <f t="shared" si="1"/>
         <v>1013006</v>
       </c>
       <c r="B121" s="1" t="s">
@@ -6284,7 +6296,7 @@
     </row>
     <row r="122" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="str">
-        <f>F122 &amp; TEXT(C122,"000")</f>
+        <f t="shared" si="1"/>
         <v>1013010</v>
       </c>
       <c r="B122" s="1" t="s">
@@ -6308,7 +6320,7 @@
     </row>
     <row r="123" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="str">
-        <f>F123 &amp; TEXT(C123,"000")</f>
+        <f t="shared" si="1"/>
         <v>1013008</v>
       </c>
       <c r="B123" s="1" t="s">
@@ -6332,7 +6344,7 @@
     </row>
     <row r="124" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="str">
-        <f>F124 &amp; TEXT(C124,"000")</f>
+        <f t="shared" si="1"/>
         <v>1013007</v>
       </c>
       <c r="B124" s="1" t="s">
@@ -6356,7 +6368,7 @@
     </row>
     <row r="125" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="str">
-        <f>F125 &amp; TEXT(C125,"000")</f>
+        <f t="shared" si="1"/>
         <v>1013023</v>
       </c>
       <c r="B125" s="1" t="s">
@@ -6380,7 +6392,7 @@
     </row>
     <row r="126" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="str">
-        <f>F126 &amp; TEXT(C126,"000")</f>
+        <f t="shared" si="1"/>
         <v>1013018</v>
       </c>
       <c r="B126" s="1" t="s">
@@ -6404,7 +6416,7 @@
     </row>
     <row r="127" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="str">
-        <f>F127 &amp; TEXT(C127,"000")</f>
+        <f t="shared" si="1"/>
         <v>1013011</v>
       </c>
       <c r="B127" s="1" t="s">
@@ -6428,7 +6440,7 @@
     </row>
     <row r="128" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="str">
-        <f>F128 &amp; TEXT(C128,"000")</f>
+        <f t="shared" si="1"/>
         <v>1013021</v>
       </c>
       <c r="B128" s="1" t="s">
@@ -6452,7 +6464,7 @@
     </row>
     <row r="129" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="str">
-        <f>F129 &amp; TEXT(C129,"000")</f>
+        <f t="shared" si="1"/>
         <v>1013016</v>
       </c>
       <c r="B129" s="1" t="s">
@@ -6476,7 +6488,7 @@
     </row>
     <row r="130" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="str">
-        <f>F130 &amp; TEXT(C130,"000")</f>
+        <f t="shared" ref="A130:A193" si="2">F130 &amp; TEXT(C130,"000")</f>
         <v>1013031</v>
       </c>
       <c r="B130" s="1" t="s">
@@ -6500,7 +6512,7 @@
     </row>
     <row r="131" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="str">
-        <f>F131 &amp; TEXT(C131,"000")</f>
+        <f t="shared" si="2"/>
         <v>1013015</v>
       </c>
       <c r="B131" s="1" t="s">
@@ -6524,7 +6536,7 @@
     </row>
     <row r="132" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="str">
-        <f>F132 &amp; TEXT(C132,"000")</f>
+        <f t="shared" si="2"/>
         <v>1013013</v>
       </c>
       <c r="B132" s="1" t="s">
@@ -6548,7 +6560,7 @@
     </row>
     <row r="133" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="str">
-        <f>F133 &amp; TEXT(C133,"000")</f>
+        <f t="shared" si="2"/>
         <v>1013019</v>
       </c>
       <c r="B133" s="1" t="s">
@@ -6572,7 +6584,7 @@
     </row>
     <row r="134" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="str">
-        <f>F134 &amp; TEXT(C134,"000")</f>
+        <f t="shared" si="2"/>
         <v>1013002</v>
       </c>
       <c r="B134" s="1" t="s">
@@ -6596,7 +6608,7 @@
     </row>
     <row r="135" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="str">
-        <f>F135 &amp; TEXT(C135,"000")</f>
+        <f t="shared" si="2"/>
         <v>1013030</v>
       </c>
       <c r="B135" s="1" t="s">
@@ -6620,7 +6632,7 @@
     </row>
     <row r="136" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="str">
-        <f>F136 &amp; TEXT(C136,"000")</f>
+        <f t="shared" si="2"/>
         <v>1013029</v>
       </c>
       <c r="B136" s="1" t="s">
@@ -6644,7 +6656,7 @@
     </row>
     <row r="137" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="str">
-        <f>F137 &amp; TEXT(C137,"000")</f>
+        <f t="shared" si="2"/>
         <v>1013017</v>
       </c>
       <c r="B137" s="1" t="s">
@@ -6668,7 +6680,7 @@
     </row>
     <row r="138" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="str">
-        <f>F138 &amp; TEXT(C138,"000")</f>
+        <f t="shared" si="2"/>
         <v>1013124</v>
       </c>
       <c r="B138" s="1" t="s">
@@ -6692,7 +6704,7 @@
     </row>
     <row r="139" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="str">
-        <f>F139 &amp; TEXT(C139,"000")</f>
+        <f t="shared" si="2"/>
         <v>1012012</v>
       </c>
       <c r="B139" s="1" t="s">
@@ -6716,7 +6728,7 @@
     </row>
     <row r="140" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="str">
-        <f>F140 &amp; TEXT(C140,"000")</f>
+        <f t="shared" si="2"/>
         <v>1012029</v>
       </c>
       <c r="B140" s="1" t="s">
@@ -6740,7 +6752,7 @@
     </row>
     <row r="141" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="str">
-        <f>F141 &amp; TEXT(C141,"000")</f>
+        <f t="shared" si="2"/>
         <v>1012001</v>
       </c>
       <c r="B141" s="1" t="s">
@@ -6764,7 +6776,7 @@
     </row>
     <row r="142" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="str">
-        <f>F142 &amp; TEXT(C142,"000")</f>
+        <f t="shared" si="2"/>
         <v>1012018</v>
       </c>
       <c r="B142" s="1" t="s">
@@ -6788,7 +6800,7 @@
     </row>
     <row r="143" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="str">
-        <f>F143 &amp; TEXT(C143,"000")</f>
+        <f t="shared" si="2"/>
         <v>1012021</v>
       </c>
       <c r="B143" s="1" t="s">
@@ -6812,7 +6824,7 @@
     </row>
     <row r="144" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="str">
-        <f>F144 &amp; TEXT(C144,"000")</f>
+        <f t="shared" si="2"/>
         <v>1012014</v>
       </c>
       <c r="B144" s="1" t="s">
@@ -6836,7 +6848,7 @@
     </row>
     <row r="145" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="str">
-        <f>F145 &amp; TEXT(C145,"000")</f>
+        <f t="shared" si="2"/>
         <v>1012003</v>
       </c>
       <c r="B145" s="1" t="s">
@@ -6860,7 +6872,7 @@
     </row>
     <row r="146" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="str">
-        <f>F146 &amp; TEXT(C146,"000")</f>
+        <f t="shared" si="2"/>
         <v>1012005</v>
       </c>
       <c r="B146" s="1" t="s">
@@ -6884,7 +6896,7 @@
     </row>
     <row r="147" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="str">
-        <f>F147 &amp; TEXT(C147,"000")</f>
+        <f t="shared" si="2"/>
         <v>1012054</v>
       </c>
       <c r="B147" s="1" t="s">
@@ -6908,7 +6920,7 @@
     </row>
     <row r="148" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="str">
-        <f>F148 &amp; TEXT(C148,"000")</f>
+        <f t="shared" si="2"/>
         <v>1012113</v>
       </c>
       <c r="B148" s="1" t="s">
@@ -6932,7 +6944,7 @@
     </row>
     <row r="149" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="str">
-        <f>F149 &amp; TEXT(C149,"000")</f>
+        <f t="shared" si="2"/>
         <v>1012006</v>
       </c>
       <c r="B149" s="1" t="s">
@@ -6956,7 +6968,7 @@
     </row>
     <row r="150" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="str">
-        <f>F150 &amp; TEXT(C150,"000")</f>
+        <f t="shared" si="2"/>
         <v>1012010</v>
       </c>
       <c r="B150" s="1" t="s">
@@ -6980,7 +6992,7 @@
     </row>
     <row r="151" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="str">
-        <f>F151 &amp; TEXT(C151,"000")</f>
+        <f t="shared" si="2"/>
         <v>1012008</v>
       </c>
       <c r="B151" s="1" t="s">
@@ -7004,7 +7016,7 @@
     </row>
     <row r="152" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="str">
-        <f>F152 &amp; TEXT(C152,"000")</f>
+        <f t="shared" si="2"/>
         <v>1012015</v>
       </c>
       <c r="B152" s="1" t="s">
@@ -7028,7 +7040,7 @@
     </row>
     <row r="153" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="str">
-        <f>F153 &amp; TEXT(C153,"000")</f>
+        <f t="shared" si="2"/>
         <v>1012016</v>
       </c>
       <c r="B153" s="1" t="s">
@@ -7052,7 +7064,7 @@
     </row>
     <row r="154" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="str">
-        <f>F154 &amp; TEXT(C154,"000")</f>
+        <f t="shared" si="2"/>
         <v>1012007</v>
       </c>
       <c r="B154" s="1" t="s">
@@ -7076,7 +7088,7 @@
     </row>
     <row r="155" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="str">
-        <f>F155 &amp; TEXT(C155,"000")</f>
+        <f t="shared" si="2"/>
         <v>1012114</v>
       </c>
       <c r="B155" s="1" t="s">
@@ -7100,7 +7112,7 @@
     </row>
     <row r="156" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="str">
-        <f>F156 &amp; TEXT(C156,"000")</f>
+        <f t="shared" si="2"/>
         <v>1012002</v>
       </c>
       <c r="B156" s="1" t="s">
@@ -7124,7 +7136,7 @@
     </row>
     <row r="157" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="str">
-        <f>F157 &amp; TEXT(C157,"000")</f>
+        <f t="shared" si="2"/>
         <v>1012034</v>
       </c>
       <c r="B157" s="1" t="s">
@@ -7148,7 +7160,7 @@
     </row>
     <row r="158" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="str">
-        <f>F158 &amp; TEXT(C158,"000")</f>
+        <f t="shared" si="2"/>
         <v>1012115</v>
       </c>
       <c r="B158" s="1" t="s">
@@ -7172,7 +7184,7 @@
     </row>
     <row r="159" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="str">
-        <f>F159 &amp; TEXT(C159,"000")</f>
+        <f t="shared" si="2"/>
         <v>1012116</v>
       </c>
       <c r="B159" s="1" t="s">
@@ -7196,7 +7208,7 @@
     </row>
     <row r="160" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="str">
-        <f>F160 &amp; TEXT(C160,"000")</f>
+        <f t="shared" si="2"/>
         <v>1012035</v>
       </c>
       <c r="B160" s="1" t="s">
@@ -7220,7 +7232,7 @@
     </row>
     <row r="161" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="str">
-        <f>F161 &amp; TEXT(C161,"000")</f>
+        <f t="shared" si="2"/>
         <v>1012026</v>
       </c>
       <c r="B161" s="1" t="s">
@@ -7244,7 +7256,7 @@
     </row>
     <row r="162" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="str">
-        <f>F162 &amp; TEXT(C162,"000")</f>
+        <f t="shared" si="2"/>
         <v>1012033</v>
       </c>
       <c r="B162" s="1" t="s">
@@ -7268,7 +7280,7 @@
     </row>
     <row r="163" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="str">
-        <f>F163 &amp; TEXT(C163,"000")</f>
+        <f t="shared" si="2"/>
         <v>1012117</v>
       </c>
       <c r="B163" s="1" t="s">
@@ -7292,7 +7304,7 @@
     </row>
     <row r="164" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="str">
-        <f>F164 &amp; TEXT(C164,"000")</f>
+        <f t="shared" si="2"/>
         <v>1012024</v>
       </c>
       <c r="B164" s="1" t="s">
@@ -7316,7 +7328,7 @@
     </row>
     <row r="165" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="str">
-        <f>F165 &amp; TEXT(C165,"000")</f>
+        <f t="shared" si="2"/>
         <v>1012017</v>
       </c>
       <c r="B165" s="1" t="s">
@@ -7340,7 +7352,7 @@
     </row>
     <row r="166" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="str">
-        <f>F166 &amp; TEXT(C166,"000")</f>
+        <f t="shared" si="2"/>
         <v>1012020</v>
       </c>
       <c r="B166" s="1" t="s">
@@ -7364,7 +7376,7 @@
     </row>
     <row r="167" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="str">
-        <f>F167 &amp; TEXT(C167,"000")</f>
+        <f t="shared" si="2"/>
         <v>1012004</v>
       </c>
       <c r="B167" s="1" t="s">
@@ -7388,7 +7400,7 @@
     </row>
     <row r="168" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="str">
-        <f>F168 &amp; TEXT(C168,"000")</f>
+        <f t="shared" si="2"/>
         <v>1012009</v>
       </c>
       <c r="B168" s="1" t="s">
@@ -7412,7 +7424,7 @@
     </row>
     <row r="169" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="str">
-        <f>F169 &amp; TEXT(C169,"000")</f>
+        <f t="shared" si="2"/>
         <v>1012030</v>
       </c>
       <c r="B169" s="1" t="s">
@@ -7436,7 +7448,7 @@
     </row>
     <row r="170" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="str">
-        <f>F170 &amp; TEXT(C170,"000")</f>
+        <f t="shared" si="2"/>
         <v>1012118</v>
       </c>
       <c r="B170" s="1" t="s">
@@ -7460,7 +7472,7 @@
     </row>
     <row r="171" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="str">
-        <f>F171 &amp; TEXT(C171,"000")</f>
+        <f t="shared" si="2"/>
         <v>1012028</v>
       </c>
       <c r="B171" s="1" t="s">
@@ -7484,7 +7496,7 @@
     </row>
     <row r="172" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="str">
-        <f>F172 &amp; TEXT(C172,"000")</f>
+        <f t="shared" si="2"/>
         <v>1012036</v>
       </c>
       <c r="B172" s="1" t="s">
@@ -7508,7 +7520,7 @@
     </row>
     <row r="173" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="str">
-        <f>F173 &amp; TEXT(C173,"000")</f>
+        <f t="shared" si="2"/>
         <v>1012011</v>
       </c>
       <c r="B173" s="1" t="s">
@@ -7532,7 +7544,7 @@
     </row>
     <row r="174" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="str">
-        <f>F174 &amp; TEXT(C174,"000")</f>
+        <f t="shared" si="2"/>
         <v>1012022</v>
       </c>
       <c r="B174" s="1" t="s">
@@ -7556,7 +7568,7 @@
     </row>
     <row r="175" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="str">
-        <f>F175 &amp; TEXT(C175,"000")</f>
+        <f t="shared" si="2"/>
         <v>1012119</v>
       </c>
       <c r="B175" s="1" t="s">
@@ -7580,7 +7592,7 @@
     </row>
     <row r="176" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="str">
-        <f>F176 &amp; TEXT(C176,"000")</f>
+        <f t="shared" si="2"/>
         <v>1011100</v>
       </c>
       <c r="B176" s="1" t="s">
@@ -7604,7 +7616,7 @@
     </row>
     <row r="177" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="1" t="str">
-        <f>F177 &amp; TEXT(C177,"000")</f>
+        <f t="shared" si="2"/>
         <v>1011018</v>
       </c>
       <c r="B177" s="1" t="s">
@@ -7628,7 +7640,7 @@
     </row>
     <row r="178" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="str">
-        <f>F178 &amp; TEXT(C178,"000")</f>
+        <f t="shared" si="2"/>
         <v>1011101</v>
       </c>
       <c r="B178" s="1" t="s">
@@ -7652,7 +7664,7 @@
     </row>
     <row r="179" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="1" t="str">
-        <f>F179 &amp; TEXT(C179,"000")</f>
+        <f t="shared" si="2"/>
         <v>1011023</v>
       </c>
       <c r="B179" s="1" t="s">
@@ -7676,7 +7688,7 @@
     </row>
     <row r="180" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="str">
-        <f>F180 &amp; TEXT(C180,"000")</f>
+        <f t="shared" si="2"/>
         <v>1011003</v>
       </c>
       <c r="B180" s="1" t="s">
@@ -7700,7 +7712,7 @@
     </row>
     <row r="181" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="1" t="str">
-        <f>F181 &amp; TEXT(C181,"000")</f>
+        <f t="shared" si="2"/>
         <v>1011004</v>
       </c>
       <c r="B181" s="1" t="s">
@@ -7724,7 +7736,7 @@
     </row>
     <row r="182" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="str">
-        <f>F182 &amp; TEXT(C182,"000")</f>
+        <f t="shared" si="2"/>
         <v>1011006</v>
       </c>
       <c r="B182" s="1" t="s">
@@ -7748,7 +7760,7 @@
     </row>
     <row r="183" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="1" t="str">
-        <f>F183 &amp; TEXT(C183,"000")</f>
+        <f t="shared" si="2"/>
         <v>1011005</v>
       </c>
       <c r="B183" s="1" t="s">
@@ -7772,7 +7784,7 @@
     </row>
     <row r="184" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="str">
-        <f>F184 &amp; TEXT(C184,"000")</f>
+        <f t="shared" si="2"/>
         <v>1011002</v>
       </c>
       <c r="B184" s="1" t="s">
@@ -7796,7 +7808,7 @@
     </row>
     <row r="185" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="1" t="str">
-        <f>F185 &amp; TEXT(C185,"000")</f>
+        <f t="shared" si="2"/>
         <v>1011024</v>
       </c>
       <c r="B185" s="1" t="s">
@@ -7820,7 +7832,7 @@
     </row>
     <row r="186" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="str">
-        <f>F186 &amp; TEXT(C186,"000")</f>
+        <f t="shared" si="2"/>
         <v>1011022</v>
       </c>
       <c r="B186" s="1" t="s">
@@ -7844,7 +7856,7 @@
     </row>
     <row r="187" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="1" t="str">
-        <f>F187 &amp; TEXT(C187,"000")</f>
+        <f t="shared" si="2"/>
         <v>1011049</v>
       </c>
       <c r="B187" s="1" t="s">
@@ -7868,7 +7880,7 @@
     </row>
     <row r="188" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="str">
-        <f>F188 &amp; TEXT(C188,"000")</f>
+        <f t="shared" si="2"/>
         <v>1011015</v>
       </c>
       <c r="B188" s="1" t="s">
@@ -7892,7 +7904,7 @@
     </row>
     <row r="189" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="1" t="str">
-        <f>F189 &amp; TEXT(C189,"000")</f>
+        <f t="shared" si="2"/>
         <v>1011026</v>
       </c>
       <c r="B189" s="1" t="s">
@@ -7916,7 +7928,7 @@
     </row>
     <row r="190" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="1" t="str">
-        <f>F190 &amp; TEXT(C190,"000")</f>
+        <f t="shared" si="2"/>
         <v>1011008</v>
       </c>
       <c r="B190" s="1" t="s">
@@ -7940,7 +7952,7 @@
     </row>
     <row r="191" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="1" t="str">
-        <f>F191 &amp; TEXT(C191,"000")</f>
+        <f t="shared" si="2"/>
         <v>1011029</v>
       </c>
       <c r="B191" s="1" t="s">
@@ -7964,7 +7976,7 @@
     </row>
     <row r="192" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="str">
-        <f>F192 &amp; TEXT(C192,"000")</f>
+        <f t="shared" si="2"/>
         <v>1011013</v>
       </c>
       <c r="B192" s="1" t="s">
@@ -7988,7 +8000,7 @@
     </row>
     <row r="193" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="1" t="str">
-        <f>F193 &amp; TEXT(C193,"000")</f>
+        <f t="shared" si="2"/>
         <v>1011012</v>
       </c>
       <c r="B193" s="1" t="s">
@@ -8012,7 +8024,7 @@
     </row>
     <row r="194" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="1" t="str">
-        <f>F194 &amp; TEXT(C194,"000")</f>
+        <f t="shared" ref="A194:A257" si="3">F194 &amp; TEXT(C194,"000")</f>
         <v>1011010</v>
       </c>
       <c r="B194" s="1" t="s">
@@ -8036,7 +8048,7 @@
     </row>
     <row r="195" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="1" t="str">
-        <f>F195 &amp; TEXT(C195,"000")</f>
+        <f t="shared" si="3"/>
         <v>1011033</v>
       </c>
       <c r="B195" s="1" t="s">
@@ -8060,7 +8072,7 @@
     </row>
     <row r="196" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="str">
-        <f>F196 &amp; TEXT(C196,"000")</f>
+        <f t="shared" si="3"/>
         <v>1011036</v>
       </c>
       <c r="B196" s="1" t="s">
@@ -8084,7 +8096,7 @@
     </row>
     <row r="197" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="1" t="str">
-        <f>F197 &amp; TEXT(C197,"000")</f>
+        <f t="shared" si="3"/>
         <v>1011017</v>
       </c>
       <c r="B197" s="1" t="s">
@@ -8108,7 +8120,7 @@
     </row>
     <row r="198" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="1" t="str">
-        <f>F198 &amp; TEXT(C198,"000")</f>
+        <f t="shared" si="3"/>
         <v>1011102</v>
       </c>
       <c r="B198" s="1" t="s">
@@ -8132,7 +8144,7 @@
     </row>
     <row r="199" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="1" t="str">
-        <f>F199 &amp; TEXT(C199,"000")</f>
+        <f t="shared" si="3"/>
         <v>1011009</v>
       </c>
       <c r="B199" s="1" t="s">
@@ -8156,7 +8168,7 @@
     </row>
     <row r="200" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="str">
-        <f>F200 &amp; TEXT(C200,"000")</f>
+        <f t="shared" si="3"/>
         <v>1011011</v>
       </c>
       <c r="B200" s="1" t="s">
@@ -8180,7 +8192,7 @@
     </row>
     <row r="201" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="1" t="str">
-        <f>F201 &amp; TEXT(C201,"000")</f>
+        <f t="shared" si="3"/>
         <v>1011019</v>
       </c>
       <c r="B201" s="1" t="s">
@@ -8204,7 +8216,7 @@
     </row>
     <row r="202" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="1" t="str">
-        <f>F202 &amp; TEXT(C202,"000")</f>
+        <f t="shared" si="3"/>
         <v>1011007</v>
       </c>
       <c r="B202" s="1" t="s">
@@ -8228,7 +8240,7 @@
     </row>
     <row r="203" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="1" t="str">
-        <f>F203 &amp; TEXT(C203,"000")</f>
+        <f t="shared" si="3"/>
         <v>1011103</v>
       </c>
       <c r="B203" s="1" t="s">
@@ -8250,9 +8262,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="204" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="1" t="str">
-        <f>F204 &amp; TEXT(C204,"000")</f>
+        <f t="shared" si="3"/>
         <v>1010008</v>
       </c>
       <c r="B204" s="1" t="s">
@@ -8274,9 +8286,9 @@
         <v>347</v>
       </c>
     </row>
-    <row r="205" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="1" t="str">
-        <f>F205 &amp; TEXT(C205,"000")</f>
+        <f t="shared" si="3"/>
         <v>1010025</v>
       </c>
       <c r="B205" s="1" t="s">
@@ -8298,9 +8310,9 @@
         <v>347</v>
       </c>
     </row>
-    <row r="206" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="str">
-        <f>F206 &amp; TEXT(C206,"000")</f>
+        <f t="shared" si="3"/>
         <v>1010033</v>
       </c>
       <c r="B206" s="1" t="s">
@@ -8322,9 +8334,9 @@
         <v>347</v>
       </c>
     </row>
-    <row r="207" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="1" t="str">
-        <f>F207 &amp; TEXT(C207,"000")</f>
+        <f t="shared" si="3"/>
         <v>1010020</v>
       </c>
       <c r="B207" s="1" t="s">
@@ -8346,9 +8358,9 @@
         <v>347</v>
       </c>
     </row>
-    <row r="208" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="1" t="str">
-        <f>F208 &amp; TEXT(C208,"000")</f>
+        <f t="shared" si="3"/>
         <v>1010003</v>
       </c>
       <c r="B208" s="1" t="s">
@@ -8370,9 +8382,9 @@
         <v>347</v>
       </c>
     </row>
-    <row r="209" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="1" t="str">
-        <f>F209 &amp; TEXT(C209,"000")</f>
+        <f t="shared" si="3"/>
         <v>1010007</v>
       </c>
       <c r="B209" s="1" t="s">
@@ -8394,9 +8406,9 @@
         <v>347</v>
       </c>
     </row>
-    <row r="210" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="1" t="str">
-        <f>F210 &amp; TEXT(C210,"000")</f>
+        <f t="shared" si="3"/>
         <v>1010023</v>
       </c>
       <c r="B210" s="1" t="s">
@@ -8418,9 +8430,9 @@
         <v>347</v>
       </c>
     </row>
-    <row r="211" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="1" t="str">
-        <f>F211 &amp; TEXT(C211,"000")</f>
+        <f t="shared" si="3"/>
         <v>1010017</v>
       </c>
       <c r="B211" s="1" t="s">
@@ -8442,9 +8454,9 @@
         <v>347</v>
       </c>
     </row>
-    <row r="212" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="1" t="str">
-        <f>F212 &amp; TEXT(C212,"000")</f>
+        <f t="shared" si="3"/>
         <v>1010122</v>
       </c>
       <c r="B212" s="1" t="s">
@@ -8466,9 +8478,9 @@
         <v>347</v>
       </c>
     </row>
-    <row r="213" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="1" t="str">
-        <f>F213 &amp; TEXT(C213,"000")</f>
+        <f t="shared" si="3"/>
         <v>1010022</v>
       </c>
       <c r="B213" s="1" t="s">
@@ -8490,9 +8502,9 @@
         <v>347</v>
       </c>
     </row>
-    <row r="214" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="str">
-        <f>F214 &amp; TEXT(C214,"000")</f>
+        <f t="shared" si="3"/>
         <v>1010013</v>
       </c>
       <c r="B214" s="1" t="s">
@@ -8514,9 +8526,9 @@
         <v>347</v>
       </c>
     </row>
-    <row r="215" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="1" t="str">
-        <f>F215 &amp; TEXT(C215,"000")</f>
+        <f t="shared" si="3"/>
         <v>1010005</v>
       </c>
       <c r="B215" s="1" t="s">
@@ -8538,9 +8550,9 @@
         <v>347</v>
       </c>
     </row>
-    <row r="216" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="str">
-        <f>F216 &amp; TEXT(C216,"000")</f>
+        <f t="shared" si="3"/>
         <v>1010012</v>
       </c>
       <c r="B216" s="1" t="s">
@@ -8562,9 +8574,9 @@
         <v>347</v>
       </c>
     </row>
-    <row r="217" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="1" t="str">
-        <f>F217 &amp; TEXT(C217,"000")</f>
+        <f t="shared" si="3"/>
         <v>1010012</v>
       </c>
       <c r="B217" s="1" t="s">
@@ -8586,9 +8598,9 @@
         <v>347</v>
       </c>
     </row>
-    <row r="218" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="str">
-        <f>F218 &amp; TEXT(C218,"000")</f>
+        <f t="shared" si="3"/>
         <v>1010018</v>
       </c>
       <c r="B218" s="1" t="s">
@@ -8610,9 +8622,9 @@
         <v>347</v>
       </c>
     </row>
-    <row r="219" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="1" t="str">
-        <f>F219 &amp; TEXT(C219,"000")</f>
+        <f t="shared" si="3"/>
         <v>1010019</v>
       </c>
       <c r="B219" s="1" t="s">
@@ -8634,9 +8646,9 @@
         <v>347</v>
       </c>
     </row>
-    <row r="220" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="str">
-        <f>F220 &amp; TEXT(C220,"000")</f>
+        <f t="shared" si="3"/>
         <v>1010014</v>
       </c>
       <c r="B220" s="1" t="s">
@@ -8658,9 +8670,9 @@
         <v>347</v>
       </c>
     </row>
-    <row r="221" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="1" t="str">
-        <f>F221 &amp; TEXT(C221,"000")</f>
+        <f t="shared" si="3"/>
         <v>1010009</v>
       </c>
       <c r="B221" s="1" t="s">
@@ -8682,9 +8694,9 @@
         <v>347</v>
       </c>
     </row>
-    <row r="222" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="1" t="str">
-        <f>F222 &amp; TEXT(C222,"000")</f>
+        <f t="shared" si="3"/>
         <v>1010030</v>
       </c>
       <c r="B222" s="1" t="s">
@@ -8706,9 +8718,9 @@
         <v>347</v>
       </c>
     </row>
-    <row r="223" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="1" t="str">
-        <f>F223 &amp; TEXT(C223,"000")</f>
+        <f t="shared" si="3"/>
         <v>1010024</v>
       </c>
       <c r="B223" s="1" t="s">
@@ -8730,9 +8742,9 @@
         <v>347</v>
       </c>
     </row>
-    <row r="224" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="1" t="str">
-        <f>F224 &amp; TEXT(C224,"000")</f>
+        <f t="shared" si="3"/>
         <v>1010027</v>
       </c>
       <c r="B224" s="1" t="s">
@@ -8754,9 +8766,9 @@
         <v>347</v>
       </c>
     </row>
-    <row r="225" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="1" t="str">
-        <f>F225 &amp; TEXT(C225,"000")</f>
+        <f t="shared" si="3"/>
         <v>1010021</v>
       </c>
       <c r="B225" s="1" t="s">
@@ -8778,9 +8790,9 @@
         <v>347</v>
       </c>
     </row>
-    <row r="226" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="1" t="str">
-        <f>F226 &amp; TEXT(C226,"000")</f>
+        <f t="shared" si="3"/>
         <v>1010011</v>
       </c>
       <c r="B226" s="1" t="s">
@@ -8802,9 +8814,9 @@
         <v>347</v>
       </c>
     </row>
-    <row r="227" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="1" t="str">
-        <f>F227 &amp; TEXT(C227,"000")</f>
+        <f t="shared" si="3"/>
         <v>1010016</v>
       </c>
       <c r="B227" s="1" t="s">
@@ -8826,9 +8838,9 @@
         <v>347</v>
       </c>
     </row>
-    <row r="228" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="str">
-        <f>F228 &amp; TEXT(C228,"000")</f>
+        <f t="shared" si="3"/>
         <v>1010036</v>
       </c>
       <c r="B228" s="1" t="s">
@@ -8850,9 +8862,9 @@
         <v>347</v>
       </c>
     </row>
-    <row r="229" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="1" t="str">
-        <f>F229 &amp; TEXT(C229,"000")</f>
+        <f t="shared" si="3"/>
         <v>1010029</v>
       </c>
       <c r="B229" s="1" t="s">
@@ -8874,9 +8886,9 @@
         <v>347</v>
       </c>
     </row>
-    <row r="230" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="1" t="str">
-        <f>F230 &amp; TEXT(C230,"000")</f>
+        <f t="shared" si="3"/>
         <v>1010123</v>
       </c>
       <c r="B230" s="1" t="s">
@@ -8900,7 +8912,7 @@
     </row>
     <row r="231" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="1" t="str">
-        <f>F231 &amp; TEXT(C231,"000")</f>
+        <f t="shared" si="3"/>
         <v>1009028</v>
       </c>
       <c r="B231" s="1" t="s">
@@ -8924,7 +8936,7 @@
     </row>
     <row r="232" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="1" t="str">
-        <f>F232 &amp; TEXT(C232,"000")</f>
+        <f t="shared" si="3"/>
         <v>1009021</v>
       </c>
       <c r="B232" s="1" t="s">
@@ -8948,7 +8960,7 @@
     </row>
     <row r="233" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="1" t="str">
-        <f>F233 &amp; TEXT(C233,"000")</f>
+        <f t="shared" si="3"/>
         <v>1009012</v>
       </c>
       <c r="B233" s="1" t="s">
@@ -8972,7 +8984,7 @@
     </row>
     <row r="234" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="1" t="str">
-        <f>F234 &amp; TEXT(C234,"000")</f>
+        <f t="shared" si="3"/>
         <v>1009036</v>
       </c>
       <c r="B234" s="1" t="s">
@@ -8996,7 +9008,7 @@
     </row>
     <row r="235" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="1" t="str">
-        <f>F235 &amp; TEXT(C235,"000")</f>
+        <f t="shared" si="3"/>
         <v>1009017</v>
       </c>
       <c r="B235" s="1" t="s">
@@ -9020,7 +9032,7 @@
     </row>
     <row r="236" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="1" t="str">
-        <f>F236 &amp; TEXT(C236,"000")</f>
+        <f t="shared" si="3"/>
         <v>1009004</v>
       </c>
       <c r="B236" s="1" t="s">
@@ -9044,7 +9056,7 @@
     </row>
     <row r="237" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="1" t="str">
-        <f>F237 &amp; TEXT(C237,"000")</f>
+        <f t="shared" si="3"/>
         <v>1009024</v>
       </c>
       <c r="B237" s="1" t="s">
@@ -9068,7 +9080,7 @@
     </row>
     <row r="238" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="1" t="str">
-        <f>F238 &amp; TEXT(C238,"000")</f>
+        <f t="shared" si="3"/>
         <v>1009005</v>
       </c>
       <c r="B238" s="1" t="s">
@@ -9092,7 +9104,7 @@
     </row>
     <row r="239" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="1" t="str">
-        <f>F239 &amp; TEXT(C239,"000")</f>
+        <f t="shared" si="3"/>
         <v>1009014</v>
       </c>
       <c r="B239" s="1" t="s">
@@ -9116,7 +9128,7 @@
     </row>
     <row r="240" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="1" t="str">
-        <f>F240 &amp; TEXT(C240,"000")</f>
+        <f t="shared" si="3"/>
         <v>1009020</v>
       </c>
       <c r="B240" s="1" t="s">
@@ -9140,7 +9152,7 @@
     </row>
     <row r="241" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="1" t="str">
-        <f>F241 &amp; TEXT(C241,"000")</f>
+        <f t="shared" si="3"/>
         <v>1009025</v>
       </c>
       <c r="B241" s="1" t="s">
@@ -9164,7 +9176,7 @@
     </row>
     <row r="242" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="1" t="str">
-        <f>F242 &amp; TEXT(C242,"000")</f>
+        <f t="shared" si="3"/>
         <v>1009027</v>
       </c>
       <c r="B242" s="1" t="s">
@@ -9188,7 +9200,7 @@
     </row>
     <row r="243" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="1" t="str">
-        <f>F243 &amp; TEXT(C243,"000")</f>
+        <f t="shared" si="3"/>
         <v>1009023</v>
       </c>
       <c r="B243" s="1" t="s">
@@ -9212,7 +9224,7 @@
     </row>
     <row r="244" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="1" t="str">
-        <f>F244 &amp; TEXT(C244,"000")</f>
+        <f t="shared" si="3"/>
         <v>1009006</v>
       </c>
       <c r="B244" s="1" t="s">
@@ -9236,7 +9248,7 @@
     </row>
     <row r="245" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="1" t="str">
-        <f>F245 &amp; TEXT(C245,"000")</f>
+        <f t="shared" si="3"/>
         <v>1009010</v>
       </c>
       <c r="B245" s="1" t="s">
@@ -9260,7 +9272,7 @@
     </row>
     <row r="246" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="1" t="str">
-        <f>F246 &amp; TEXT(C246,"000")</f>
+        <f t="shared" si="3"/>
         <v>1009007</v>
       </c>
       <c r="B246" s="1" t="s">
@@ -9284,7 +9296,7 @@
     </row>
     <row r="247" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="1" t="str">
-        <f>F247 &amp; TEXT(C247,"000")</f>
+        <f t="shared" si="3"/>
         <v>1009022</v>
       </c>
       <c r="B247" s="1" t="s">
@@ -9308,7 +9320,7 @@
     </row>
     <row r="248" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="str">
-        <f>F248 &amp; TEXT(C248,"000")</f>
+        <f t="shared" si="3"/>
         <v>1009015</v>
       </c>
       <c r="B248" s="1" t="s">
@@ -9332,7 +9344,7 @@
     </row>
     <row r="249" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="1" t="str">
-        <f>F249 &amp; TEXT(C249,"000")</f>
+        <f t="shared" si="3"/>
         <v>1009019</v>
       </c>
       <c r="B249" s="1" t="s">
@@ -9356,7 +9368,7 @@
     </row>
     <row r="250" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="1" t="str">
-        <f>F250 &amp; TEXT(C250,"000")</f>
+        <f t="shared" si="3"/>
         <v>1009056</v>
       </c>
       <c r="B250" s="1" t="s">
@@ -9380,7 +9392,7 @@
     </row>
     <row r="251" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="1" t="str">
-        <f>F251 &amp; TEXT(C251,"000")</f>
+        <f t="shared" si="3"/>
         <v>1009013</v>
       </c>
       <c r="B251" s="1" t="s">
@@ -9404,7 +9416,7 @@
     </row>
     <row r="252" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="1" t="str">
-        <f>F252 &amp; TEXT(C252,"000")</f>
+        <f t="shared" si="3"/>
         <v>1009009</v>
       </c>
       <c r="B252" s="1" t="s">
@@ -9428,7 +9440,7 @@
     </row>
     <row r="253" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="1" t="str">
-        <f>F253 &amp; TEXT(C253,"000")</f>
+        <f t="shared" si="3"/>
         <v>1009008</v>
       </c>
       <c r="B253" s="1" t="s">
@@ -9452,7 +9464,7 @@
     </row>
     <row r="254" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="1" t="str">
-        <f>F254 &amp; TEXT(C254,"000")</f>
+        <f t="shared" si="3"/>
         <v>1009011</v>
       </c>
       <c r="B254" s="1" t="s">
@@ -9476,7 +9488,7 @@
     </row>
     <row r="255" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="1" t="str">
-        <f>F255 &amp; TEXT(C255,"000")</f>
+        <f t="shared" si="3"/>
         <v>1009016</v>
       </c>
       <c r="B255" s="1" t="s">
@@ -9500,7 +9512,7 @@
     </row>
     <row r="256" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="str">
-        <f>F256 &amp; TEXT(C256,"000")</f>
+        <f t="shared" si="3"/>
         <v>1009112</v>
       </c>
       <c r="B256" s="1" t="s">
@@ -9524,7 +9536,7 @@
     </row>
     <row r="257" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="1" t="str">
-        <f>F257 &amp; TEXT(C257,"000")</f>
+        <f t="shared" si="3"/>
         <v>1008001</v>
       </c>
       <c r="B257" s="1" t="s">
@@ -9548,7 +9560,7 @@
     </row>
     <row r="258" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="1" t="str">
-        <f>F258 &amp; TEXT(C258,"000")</f>
+        <f t="shared" ref="A258:A321" si="4">F258 &amp; TEXT(C258,"000")</f>
         <v>1008023</v>
       </c>
       <c r="B258" s="1" t="s">
@@ -9572,7 +9584,7 @@
     </row>
     <row r="259" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="1" t="str">
-        <f>F259 &amp; TEXT(C259,"000")</f>
+        <f t="shared" si="4"/>
         <v>1008070</v>
       </c>
       <c r="B259" s="1" t="s">
@@ -9596,7 +9608,7 @@
     </row>
     <row r="260" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="1" t="str">
-        <f>F260 &amp; TEXT(C260,"000")</f>
+        <f t="shared" si="4"/>
         <v>1008003</v>
       </c>
       <c r="B260" s="1" t="s">
@@ -9620,7 +9632,7 @@
     </row>
     <row r="261" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="1" t="str">
-        <f>F261 &amp; TEXT(C261,"000")</f>
+        <f t="shared" si="4"/>
         <v>1008022</v>
       </c>
       <c r="B261" s="1" t="s">
@@ -9644,7 +9656,7 @@
     </row>
     <row r="262" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="1" t="str">
-        <f>F262 &amp; TEXT(C262,"000")</f>
+        <f t="shared" si="4"/>
         <v>1008002</v>
       </c>
       <c r="B262" s="1" t="s">
@@ -9668,7 +9680,7 @@
     </row>
     <row r="263" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="1" t="str">
-        <f>F263 &amp; TEXT(C263,"000")</f>
+        <f t="shared" si="4"/>
         <v>1008020</v>
       </c>
       <c r="B263" s="1" t="s">
@@ -9692,7 +9704,7 @@
     </row>
     <row r="264" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="1" t="str">
-        <f>F264 &amp; TEXT(C264,"000")</f>
+        <f t="shared" si="4"/>
         <v>1008006</v>
       </c>
       <c r="B264" s="1" t="s">
@@ -9716,7 +9728,7 @@
     </row>
     <row r="265" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="1" t="str">
-        <f>F265 &amp; TEXT(C265,"000")</f>
+        <f t="shared" si="4"/>
         <v>1008004</v>
       </c>
       <c r="B265" s="1" t="s">
@@ -9740,7 +9752,7 @@
     </row>
     <row r="266" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="1" t="str">
-        <f>F266 &amp; TEXT(C266,"000")</f>
+        <f t="shared" si="4"/>
         <v>1008015</v>
       </c>
       <c r="B266" s="1" t="s">
@@ -9764,7 +9776,7 @@
     </row>
     <row r="267" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" s="1" t="str">
-        <f>F267 &amp; TEXT(C267,"000")</f>
+        <f t="shared" si="4"/>
         <v>1008061</v>
       </c>
       <c r="B267" s="1" t="s">
@@ -9788,7 +9800,7 @@
     </row>
     <row r="268" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" s="1" t="str">
-        <f>F268 &amp; TEXT(C268,"000")</f>
+        <f t="shared" si="4"/>
         <v>1008067</v>
       </c>
       <c r="B268" s="1" t="s">
@@ -9812,7 +9824,7 @@
     </row>
     <row r="269" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" s="1" t="str">
-        <f>F269 &amp; TEXT(C269,"000")</f>
+        <f t="shared" si="4"/>
         <v>1008001</v>
       </c>
       <c r="B269" s="1" t="s">
@@ -9836,7 +9848,7 @@
     </row>
     <row r="270" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" s="1" t="str">
-        <f>F270 &amp; TEXT(C270,"000")</f>
+        <f t="shared" si="4"/>
         <v>1008017</v>
       </c>
       <c r="B270" s="1" t="s">
@@ -9860,7 +9872,7 @@
     </row>
     <row r="271" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" s="1" t="str">
-        <f>F271 &amp; TEXT(C271,"000")</f>
+        <f t="shared" si="4"/>
         <v>1008008</v>
       </c>
       <c r="B271" s="1" t="s">
@@ -9884,7 +9896,7 @@
     </row>
     <row r="272" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" s="1" t="str">
-        <f>F272 &amp; TEXT(C272,"000")</f>
+        <f t="shared" si="4"/>
         <v>1008011</v>
       </c>
       <c r="B272" s="1" t="s">
@@ -9908,7 +9920,7 @@
     </row>
     <row r="273" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A273" s="1" t="str">
-        <f>F273 &amp; TEXT(C273,"000")</f>
+        <f t="shared" si="4"/>
         <v>1008005</v>
       </c>
       <c r="B273" s="1" t="s">
@@ -9932,7 +9944,7 @@
     </row>
     <row r="274" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" s="1" t="str">
-        <f>F274 &amp; TEXT(C274,"000")</f>
+        <f t="shared" si="4"/>
         <v>1008007</v>
       </c>
       <c r="B274" s="1" t="s">
@@ -9956,7 +9968,7 @@
     </row>
     <row r="275" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A275" s="1" t="str">
-        <f>F275 &amp; TEXT(C275,"000")</f>
+        <f t="shared" si="4"/>
         <v>1008133</v>
       </c>
       <c r="B275" s="1" t="s">
@@ -9980,7 +9992,7 @@
     </row>
     <row r="276" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" s="1" t="str">
-        <f>F276 &amp; TEXT(C276,"000")</f>
+        <f t="shared" si="4"/>
         <v>1008016</v>
       </c>
       <c r="B276" s="1" t="s">
@@ -10004,7 +10016,7 @@
     </row>
     <row r="277" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" s="1" t="str">
-        <f>F277 &amp; TEXT(C277,"000")</f>
+        <f t="shared" si="4"/>
         <v>1008134</v>
       </c>
       <c r="B277" s="1" t="s">
@@ -10028,7 +10040,7 @@
     </row>
     <row r="278" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="1" t="str">
-        <f>F278 &amp; TEXT(C278,"000")</f>
+        <f t="shared" si="4"/>
         <v>1008013</v>
       </c>
       <c r="B278" s="1" t="s">
@@ -10052,7 +10064,7 @@
     </row>
     <row r="279" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" s="1" t="str">
-        <f>F279 &amp; TEXT(C279,"000")</f>
+        <f t="shared" si="4"/>
         <v>1008014</v>
       </c>
       <c r="B279" s="1" t="s">
@@ -10076,7 +10088,7 @@
     </row>
     <row r="280" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" s="1" t="str">
-        <f>F280 &amp; TEXT(C280,"000")</f>
+        <f t="shared" si="4"/>
         <v>1008012</v>
       </c>
       <c r="B280" s="1" t="s">
@@ -10100,7 +10112,7 @@
     </row>
     <row r="281" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" s="1" t="str">
-        <f>F281 &amp; TEXT(C281,"000")</f>
+        <f t="shared" si="4"/>
         <v>1008019</v>
       </c>
       <c r="B281" s="1" t="s">
@@ -10124,7 +10136,7 @@
     </row>
     <row r="282" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" s="1" t="str">
-        <f>F282 &amp; TEXT(C282,"000")</f>
+        <f t="shared" si="4"/>
         <v>1008018</v>
       </c>
       <c r="B282" s="1" t="s">
@@ -10148,7 +10160,7 @@
     </row>
     <row r="283" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" s="1" t="str">
-        <f>F283 &amp; TEXT(C283,"000")</f>
+        <f t="shared" si="4"/>
         <v>1008135</v>
       </c>
       <c r="B283" s="1" t="s">
@@ -10172,7 +10184,7 @@
     </row>
     <row r="284" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" s="1" t="str">
-        <f>F284 &amp; TEXT(C284,"000")</f>
+        <f t="shared" si="4"/>
         <v>1008027</v>
       </c>
       <c r="B284" s="1" t="s">
@@ -10196,7 +10208,7 @@
     </row>
     <row r="285" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" s="1" t="str">
-        <f>F285 &amp; TEXT(C285,"000")</f>
+        <f t="shared" si="4"/>
         <v>1008136</v>
       </c>
       <c r="B285" s="1" t="s">
@@ -10220,7 +10232,7 @@
     </row>
     <row r="286" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" s="1" t="str">
-        <f>F286 &amp; TEXT(C286,"000")</f>
+        <f t="shared" si="4"/>
         <v>1008010</v>
       </c>
       <c r="B286" s="1" t="s">
@@ -10244,7 +10256,7 @@
     </row>
     <row r="287" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" s="1" t="str">
-        <f>F287 &amp; TEXT(C287,"000")</f>
+        <f t="shared" si="4"/>
         <v>1008137</v>
       </c>
       <c r="B287" s="1" t="s">
@@ -10268,7 +10280,7 @@
     </row>
     <row r="288" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" s="1" t="str">
-        <f>F288 &amp; TEXT(C288,"000")</f>
+        <f t="shared" si="4"/>
         <v>1008138</v>
       </c>
       <c r="B288" s="1" t="s">
@@ -10292,7 +10304,7 @@
     </row>
     <row r="289" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A289" s="1" t="str">
-        <f>F289 &amp; TEXT(C289,"000")</f>
+        <f t="shared" si="4"/>
         <v>1008009</v>
       </c>
       <c r="B289" s="1" t="s">
@@ -10316,7 +10328,7 @@
     </row>
     <row r="290" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" s="1" t="str">
-        <f>F290 &amp; TEXT(C290,"000")</f>
+        <f t="shared" si="4"/>
         <v>1008029</v>
       </c>
       <c r="B290" s="1" t="s">
@@ -10340,7 +10352,7 @@
     </row>
     <row r="291" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" s="1" t="str">
-        <f>F291 &amp; TEXT(C291,"000")</f>
+        <f t="shared" si="4"/>
         <v>1008025</v>
       </c>
       <c r="B291" s="1" t="s">
@@ -10364,7 +10376,7 @@
     </row>
     <row r="292" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" s="1" t="str">
-        <f>F292 &amp; TEXT(C292,"000")</f>
+        <f t="shared" si="4"/>
         <v>1008139</v>
       </c>
       <c r="B292" s="1" t="s">
@@ -10388,7 +10400,7 @@
     </row>
     <row r="293" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A293" s="1" t="str">
-        <f>F293 &amp; TEXT(C293,"000")</f>
+        <f t="shared" si="4"/>
         <v>1007084</v>
       </c>
       <c r="B293" s="1" t="s">
@@ -10412,7 +10424,7 @@
     </row>
     <row r="294" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A294" s="1" t="str">
-        <f>F294 &amp; TEXT(C294,"000")</f>
+        <f t="shared" si="4"/>
         <v>1007082</v>
       </c>
       <c r="B294" s="1" t="s">
@@ -10436,7 +10448,7 @@
     </row>
     <row r="295" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A295" s="1" t="str">
-        <f>F295 &amp; TEXT(C295,"000")</f>
+        <f t="shared" si="4"/>
         <v>1007081</v>
       </c>
       <c r="B295" s="1" t="s">
@@ -10460,7 +10472,7 @@
     </row>
     <row r="296" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A296" s="1" t="str">
-        <f>F296 &amp; TEXT(C296,"000")</f>
+        <f t="shared" si="4"/>
         <v>1007011</v>
       </c>
       <c r="B296" s="1" t="s">
@@ -10484,7 +10496,7 @@
     </row>
     <row r="297" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A297" s="1" t="str">
-        <f>F297 &amp; TEXT(C297,"000")</f>
+        <f t="shared" si="4"/>
         <v>1007010</v>
       </c>
       <c r="B297" s="1" t="s">
@@ -10508,7 +10520,7 @@
     </row>
     <row r="298" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A298" s="1" t="str">
-        <f>F298 &amp; TEXT(C298,"000")</f>
+        <f t="shared" si="4"/>
         <v>1007001</v>
       </c>
       <c r="B298" s="1" t="s">
@@ -10532,7 +10544,7 @@
     </row>
     <row r="299" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A299" s="1" t="str">
-        <f>F299 &amp; TEXT(C299,"000")</f>
+        <f t="shared" si="4"/>
         <v>1007099</v>
       </c>
       <c r="B299" s="1" t="s">
@@ -10556,7 +10568,7 @@
     </row>
     <row r="300" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A300" s="1" t="str">
-        <f>F300 &amp; TEXT(C300,"000")</f>
+        <f t="shared" si="4"/>
         <v>1007096</v>
       </c>
       <c r="B300" s="1" t="s">
@@ -10580,7 +10592,7 @@
     </row>
     <row r="301" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A301" s="1" t="str">
-        <f>F301 &amp; TEXT(C301,"000")</f>
+        <f t="shared" si="4"/>
         <v>1007097</v>
       </c>
       <c r="B301" s="1" t="s">
@@ -10604,7 +10616,7 @@
     </row>
     <row r="302" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A302" s="1" t="str">
-        <f>F302 &amp; TEXT(C302,"000")</f>
+        <f t="shared" si="4"/>
         <v>1007090</v>
       </c>
       <c r="B302" s="1" t="s">
@@ -10628,7 +10640,7 @@
     </row>
     <row r="303" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" s="1" t="str">
-        <f>F303 &amp; TEXT(C303,"000")</f>
+        <f t="shared" si="4"/>
         <v>1007087</v>
       </c>
       <c r="B303" s="1" t="s">
@@ -10652,7 +10664,7 @@
     </row>
     <row r="304" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A304" s="1" t="str">
-        <f>F304 &amp; TEXT(C304,"000")</f>
+        <f t="shared" si="4"/>
         <v>1007089</v>
       </c>
       <c r="B304" s="1" t="s">
@@ -10676,7 +10688,7 @@
     </row>
     <row r="305" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A305" s="1" t="str">
-        <f>F305 &amp; TEXT(C305,"000")</f>
+        <f t="shared" si="4"/>
         <v>1007098</v>
       </c>
       <c r="B305" s="1" t="s">
@@ -10700,7 +10712,7 @@
     </row>
     <row r="306" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A306" s="1" t="str">
-        <f>F306 &amp; TEXT(C306,"000")</f>
+        <f t="shared" si="4"/>
         <v>1007083</v>
       </c>
       <c r="B306" s="1" t="s">
@@ -10724,7 +10736,7 @@
     </row>
     <row r="307" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A307" s="1" t="str">
-        <f>F307 &amp; TEXT(C307,"000")</f>
+        <f t="shared" si="4"/>
         <v>1007001</v>
       </c>
       <c r="B307" s="1" t="s">
@@ -10748,7 +10760,7 @@
     </row>
     <row r="308" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A308" s="1" t="str">
-        <f>F308 &amp; TEXT(C308,"000")</f>
+        <f t="shared" si="4"/>
         <v>1007093</v>
       </c>
       <c r="B308" s="1" t="s">
@@ -10772,7 +10784,7 @@
     </row>
     <row r="309" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A309" s="1" t="str">
-        <f>F309 &amp; TEXT(C309,"000")</f>
+        <f t="shared" si="4"/>
         <v>1007088</v>
       </c>
       <c r="B309" s="1" t="s">
@@ -10796,7 +10808,7 @@
     </row>
     <row r="310" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A310" s="1" t="str">
-        <f>F310 &amp; TEXT(C310,"000")</f>
+        <f t="shared" si="4"/>
         <v>1007010</v>
       </c>
       <c r="B310" s="1" t="s">
@@ -10820,7 +10832,7 @@
     </row>
     <row r="311" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A311" s="1" t="str">
-        <f>F311 &amp; TEXT(C311,"000")</f>
+        <f t="shared" si="4"/>
         <v>1007092</v>
       </c>
       <c r="B311" s="1" t="s">
@@ -10844,7 +10856,7 @@
     </row>
     <row r="312" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A312" s="1" t="str">
-        <f>F312 &amp; TEXT(C312,"000")</f>
+        <f t="shared" si="4"/>
         <v>1007010</v>
       </c>
       <c r="B312" s="1" t="s">
@@ -10868,7 +10880,7 @@
     </row>
     <row r="313" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A313" s="1" t="str">
-        <f>F313 &amp; TEXT(C313,"000")</f>
+        <f t="shared" si="4"/>
         <v>1007006</v>
       </c>
       <c r="B313" s="1" t="s">
@@ -10892,7 +10904,7 @@
     </row>
     <row r="314" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A314" s="1" t="str">
-        <f>F314 &amp; TEXT(C314,"000")</f>
+        <f t="shared" si="4"/>
         <v>1007104</v>
       </c>
       <c r="B314" s="1" t="s">
@@ -10916,7 +10928,7 @@
     </row>
     <row r="315" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A315" s="1" t="str">
-        <f>F315 &amp; TEXT(C315,"000")</f>
+        <f t="shared" si="4"/>
         <v>1007001</v>
       </c>
       <c r="B315" s="1" t="s">
@@ -10940,7 +10952,7 @@
     </row>
     <row r="316" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A316" s="1" t="str">
-        <f>F316 &amp; TEXT(C316,"000")</f>
+        <f t="shared" si="4"/>
         <v>1007011</v>
       </c>
       <c r="B316" s="1" t="s">
@@ -10964,7 +10976,7 @@
     </row>
     <row r="317" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A317" s="1" t="str">
-        <f>F317 &amp; TEXT(C317,"000")</f>
+        <f t="shared" si="4"/>
         <v>1007085</v>
       </c>
       <c r="B317" s="1" t="s">
@@ -10988,7 +11000,7 @@
     </row>
     <row r="318" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A318" s="1" t="str">
-        <f>F318 &amp; TEXT(C318,"000")</f>
+        <f t="shared" si="4"/>
         <v>1007094</v>
       </c>
       <c r="B318" s="1" t="s">
@@ -11012,7 +11024,7 @@
     </row>
     <row r="319" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A319" s="1" t="str">
-        <f>F319 &amp; TEXT(C319,"000")</f>
+        <f t="shared" si="4"/>
         <v>1007086</v>
       </c>
       <c r="B319" s="1" t="s">
@@ -11036,7 +11048,7 @@
     </row>
     <row r="320" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A320" s="1" t="str">
-        <f>F320 &amp; TEXT(C320,"000")</f>
+        <f t="shared" si="4"/>
         <v>1007095</v>
       </c>
       <c r="B320" s="1" t="s">
@@ -11060,7 +11072,7 @@
     </row>
     <row r="321" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A321" s="1" t="str">
-        <f>F321 &amp; TEXT(C321,"000")</f>
+        <f t="shared" si="4"/>
         <v>1007105</v>
       </c>
       <c r="B321" s="1" t="s">
@@ -11084,7 +11096,7 @@
     </row>
     <row r="322" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A322" s="1" t="str">
-        <f>F322 &amp; TEXT(C322,"000")</f>
+        <f t="shared" ref="A322:A385" si="5">F322 &amp; TEXT(C322,"000")</f>
         <v>1007002</v>
       </c>
       <c r="B322" s="1" t="s">
@@ -11108,7 +11120,7 @@
     </row>
     <row r="323" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A323" s="1" t="str">
-        <f>F323 &amp; TEXT(C323,"000")</f>
+        <f t="shared" si="5"/>
         <v>1007004</v>
       </c>
       <c r="B323" s="1" t="s">
@@ -11132,7 +11144,7 @@
     </row>
     <row r="324" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A324" s="1" t="str">
-        <f>F324 &amp; TEXT(C324,"000")</f>
+        <f t="shared" si="5"/>
         <v>1007106</v>
       </c>
       <c r="B324" s="1" t="s">
@@ -11156,7 +11168,7 @@
     </row>
     <row r="325" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A325" s="1" t="str">
-        <f>F325 &amp; TEXT(C325,"000")</f>
+        <f t="shared" si="5"/>
         <v>1007003</v>
       </c>
       <c r="B325" s="1" t="s">
@@ -11180,7 +11192,7 @@
     </row>
     <row r="326" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A326" s="1" t="str">
-        <f>F326 &amp; TEXT(C326,"000")</f>
+        <f t="shared" si="5"/>
         <v>1007001</v>
       </c>
       <c r="B326" s="1" t="s">
@@ -11204,7 +11216,7 @@
     </row>
     <row r="327" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A327" s="1" t="str">
-        <f>F327 &amp; TEXT(C327,"000")</f>
+        <f t="shared" si="5"/>
         <v>1007107</v>
       </c>
       <c r="B327" s="1" t="s">
@@ -11228,7 +11240,7 @@
     </row>
     <row r="328" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A328" s="1" t="str">
-        <f>F328 &amp; TEXT(C328,"000")</f>
+        <f t="shared" si="5"/>
         <v>1006001</v>
       </c>
       <c r="B328" s="1" t="s">
@@ -11252,7 +11264,7 @@
     </row>
     <row r="329" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A329" s="1" t="str">
-        <f>F329 &amp; TEXT(C329,"000")</f>
+        <f t="shared" si="5"/>
         <v>1006051</v>
       </c>
       <c r="B329" s="1" t="s">
@@ -11276,7 +11288,7 @@
     </row>
     <row r="330" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A330" s="1" t="str">
-        <f>F330 &amp; TEXT(C330,"000")</f>
+        <f t="shared" si="5"/>
         <v>1006012</v>
       </c>
       <c r="B330" s="1" t="s">
@@ -11300,7 +11312,7 @@
     </row>
     <row r="331" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A331" s="1" t="str">
-        <f>F331 &amp; TEXT(C331,"000")</f>
+        <f t="shared" si="5"/>
         <v>1006025</v>
       </c>
       <c r="B331" s="1" t="s">
@@ -11324,7 +11336,7 @@
     </row>
     <row r="332" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A332" s="1" t="str">
-        <f>F332 &amp; TEXT(C332,"000")</f>
+        <f t="shared" si="5"/>
         <v>1006015</v>
       </c>
       <c r="B332" s="1" t="s">
@@ -11348,7 +11360,7 @@
     </row>
     <row r="333" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A333" s="1" t="str">
-        <f>F333 &amp; TEXT(C333,"000")</f>
+        <f t="shared" si="5"/>
         <v>1006004</v>
       </c>
       <c r="B333" s="1" t="s">
@@ -11372,7 +11384,7 @@
     </row>
     <row r="334" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A334" s="1" t="str">
-        <f>F334 &amp; TEXT(C334,"000")</f>
+        <f t="shared" si="5"/>
         <v>1006013</v>
       </c>
       <c r="B334" s="1" t="s">
@@ -11396,7 +11408,7 @@
     </row>
     <row r="335" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A335" s="1" t="str">
-        <f>F335 &amp; TEXT(C335,"000")</f>
+        <f t="shared" si="5"/>
         <v>1006062</v>
       </c>
       <c r="B335" s="1" t="s">
@@ -11420,7 +11432,7 @@
     </row>
     <row r="336" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A336" s="1" t="str">
-        <f>F336 &amp; TEXT(C336,"000")</f>
+        <f t="shared" si="5"/>
         <v>1006026</v>
       </c>
       <c r="B336" s="1" t="s">
@@ -11444,7 +11456,7 @@
     </row>
     <row r="337" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A337" s="1" t="str">
-        <f>F337 &amp; TEXT(C337,"000")</f>
+        <f t="shared" si="5"/>
         <v>1006003</v>
       </c>
       <c r="B337" s="1" t="s">
@@ -11468,7 +11480,7 @@
     </row>
     <row r="338" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A338" s="1" t="str">
-        <f>F338 &amp; TEXT(C338,"000")</f>
+        <f t="shared" si="5"/>
         <v>1006002</v>
       </c>
       <c r="B338" s="1" t="s">
@@ -11492,7 +11504,7 @@
     </row>
     <row r="339" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A339" s="1" t="str">
-        <f>F339 &amp; TEXT(C339,"000")</f>
+        <f t="shared" si="5"/>
         <v>1006006</v>
       </c>
       <c r="B339" s="1" t="s">
@@ -11516,7 +11528,7 @@
     </row>
     <row r="340" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A340" s="1" t="str">
-        <f>F340 &amp; TEXT(C340,"000")</f>
+        <f t="shared" si="5"/>
         <v>1006011</v>
       </c>
       <c r="B340" s="1" t="s">
@@ -11540,7 +11552,7 @@
     </row>
     <row r="341" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A341" s="1" t="str">
-        <f>F341 &amp; TEXT(C341,"000")</f>
+        <f t="shared" si="5"/>
         <v>1006008</v>
       </c>
       <c r="B341" s="1" t="s">
@@ -11564,7 +11576,7 @@
     </row>
     <row r="342" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A342" s="1" t="str">
-        <f>F342 &amp; TEXT(C342,"000")</f>
+        <f t="shared" si="5"/>
         <v>1006005</v>
       </c>
       <c r="B342" s="1" t="s">
@@ -11588,7 +11600,7 @@
     </row>
     <row r="343" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A343" s="1" t="str">
-        <f>F343 &amp; TEXT(C343,"000")</f>
+        <f t="shared" si="5"/>
         <v>1006018</v>
       </c>
       <c r="B343" s="1" t="s">
@@ -11612,7 +11624,7 @@
     </row>
     <row r="344" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A344" s="1" t="str">
-        <f>F344 &amp; TEXT(C344,"000")</f>
+        <f t="shared" si="5"/>
         <v>1006007</v>
       </c>
       <c r="B344" s="1" t="s">
@@ -11636,7 +11648,7 @@
     </row>
     <row r="345" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A345" s="1" t="str">
-        <f>F345 &amp; TEXT(C345,"000")</f>
+        <f t="shared" si="5"/>
         <v>1006016</v>
       </c>
       <c r="B345" s="1" t="s">
@@ -11660,7 +11672,7 @@
     </row>
     <row r="346" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A346" s="1" t="str">
-        <f>F346 &amp; TEXT(C346,"000")</f>
+        <f t="shared" si="5"/>
         <v>1006020</v>
       </c>
       <c r="B346" s="1" t="s">
@@ -11684,7 +11696,7 @@
     </row>
     <row r="347" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A347" s="1" t="str">
-        <f>F347 &amp; TEXT(C347,"000")</f>
+        <f t="shared" si="5"/>
         <v>1006022</v>
       </c>
       <c r="B347" s="1" t="s">
@@ -11708,7 +11720,7 @@
     </row>
     <row r="348" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A348" s="1" t="str">
-        <f>F348 &amp; TEXT(C348,"000")</f>
+        <f t="shared" si="5"/>
         <v>1006017</v>
       </c>
       <c r="B348" s="1" t="s">
@@ -11732,7 +11744,7 @@
     </row>
     <row r="349" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A349" s="1" t="str">
-        <f>F349 &amp; TEXT(C349,"000")</f>
+        <f t="shared" si="5"/>
         <v>1006021</v>
       </c>
       <c r="B349" s="1" t="s">
@@ -11756,7 +11768,7 @@
     </row>
     <row r="350" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A350" s="1" t="str">
-        <f>F350 &amp; TEXT(C350,"000")</f>
+        <f t="shared" si="5"/>
         <v>1006014</v>
       </c>
       <c r="B350" s="1" t="s">
@@ -11780,7 +11792,7 @@
     </row>
     <row r="351" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A351" s="1" t="str">
-        <f>F351 &amp; TEXT(C351,"000")</f>
+        <f t="shared" si="5"/>
         <v>1006065</v>
       </c>
       <c r="B351" s="1" t="s">
@@ -11804,7 +11816,7 @@
     </row>
     <row r="352" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A352" s="1" t="str">
-        <f>F352 &amp; TEXT(C352,"000")</f>
+        <f t="shared" si="5"/>
         <v>1006141</v>
       </c>
       <c r="B352" s="1" t="s">
@@ -11828,7 +11840,7 @@
     </row>
     <row r="353" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A353" s="1" t="str">
-        <f>F353 &amp; TEXT(C353,"000")</f>
+        <f t="shared" si="5"/>
         <v>1006142</v>
       </c>
       <c r="B353" s="1" t="s">
@@ -11852,7 +11864,7 @@
     </row>
     <row r="354" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A354" s="1" t="str">
-        <f>F354 &amp; TEXT(C354,"000")</f>
+        <f t="shared" si="5"/>
         <v>1006009</v>
       </c>
       <c r="B354" s="1" t="s">
@@ -11876,7 +11888,7 @@
     </row>
     <row r="355" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A355" s="1" t="str">
-        <f>F355 &amp; TEXT(C355,"000")</f>
+        <f t="shared" si="5"/>
         <v>1006010</v>
       </c>
       <c r="B355" s="1" t="s">
@@ -11900,7 +11912,7 @@
     </row>
     <row r="356" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A356" s="1" t="str">
-        <f>F356 &amp; TEXT(C356,"000")</f>
+        <f t="shared" si="5"/>
         <v>1006019</v>
       </c>
       <c r="B356" s="1" t="s">
@@ -11924,7 +11936,7 @@
     </row>
     <row r="357" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A357" s="1" t="str">
-        <f>F357 &amp; TEXT(C357,"000")</f>
+        <f t="shared" si="5"/>
         <v>1006143</v>
       </c>
       <c r="B357" s="1" t="s">
@@ -11948,7 +11960,7 @@
     </row>
     <row r="358" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A358" s="1" t="str">
-        <f>F358 &amp; TEXT(C358,"000")</f>
+        <f t="shared" si="5"/>
         <v>1006023</v>
       </c>
       <c r="B358" s="1" t="s">
@@ -11972,7 +11984,7 @@
     </row>
     <row r="359" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A359" s="1" t="str">
-        <f>F359 &amp; TEXT(C359,"000")</f>
+        <f t="shared" si="5"/>
         <v>1006079</v>
       </c>
       <c r="B359" s="1" t="s">
@@ -11996,7 +12008,7 @@
     </row>
     <row r="360" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A360" s="1" t="str">
-        <f>F360 &amp; TEXT(C360,"000")</f>
+        <f t="shared" si="5"/>
         <v>1006029</v>
       </c>
       <c r="B360" s="1" t="s">
@@ -12020,7 +12032,7 @@
     </row>
     <row r="361" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A361" s="1" t="str">
-        <f>F361 &amp; TEXT(C361,"000")</f>
+        <f t="shared" si="5"/>
         <v>1004029</v>
       </c>
       <c r="B361" s="1" t="s">
@@ -12044,7 +12056,7 @@
     </row>
     <row r="362" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A362" s="1" t="str">
-        <f>F362 &amp; TEXT(C362,"000")</f>
+        <f t="shared" si="5"/>
         <v>1004030</v>
       </c>
       <c r="B362" s="1" t="s">
@@ -12068,7 +12080,7 @@
     </row>
     <row r="363" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A363" s="1" t="str">
-        <f>F363 &amp; TEXT(C363,"000")</f>
+        <f t="shared" si="5"/>
         <v>1004053</v>
       </c>
       <c r="B363" s="1" t="s">
@@ -12092,7 +12104,7 @@
     </row>
     <row r="364" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A364" s="1" t="str">
-        <f>F364 &amp; TEXT(C364,"000")</f>
+        <f t="shared" si="5"/>
         <v>1004027</v>
       </c>
       <c r="B364" s="1" t="s">
@@ -12116,7 +12128,7 @@
     </row>
     <row r="365" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A365" s="1" t="str">
-        <f>F365 &amp; TEXT(C365,"000")</f>
+        <f t="shared" si="5"/>
         <v>1004019</v>
       </c>
       <c r="B365" s="1" t="s">
@@ -12140,7 +12152,7 @@
     </row>
     <row r="366" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A366" s="1" t="str">
-        <f>F366 &amp; TEXT(C366,"000")</f>
+        <f t="shared" si="5"/>
         <v>1004016</v>
       </c>
       <c r="B366" s="1" t="s">
@@ -12164,7 +12176,7 @@
     </row>
     <row r="367" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A367" s="1" t="str">
-        <f>F367 &amp; TEXT(C367,"000")</f>
+        <f t="shared" si="5"/>
         <v>1004002</v>
       </c>
       <c r="B367" s="1" t="s">
@@ -12188,7 +12200,7 @@
     </row>
     <row r="368" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A368" s="1" t="str">
-        <f>F368 &amp; TEXT(C368,"000")</f>
+        <f t="shared" si="5"/>
         <v>1004017</v>
       </c>
       <c r="B368" s="1" t="s">
@@ -12212,7 +12224,7 @@
     </row>
     <row r="369" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A369" s="1" t="str">
-        <f>F369 &amp; TEXT(C369,"000")</f>
+        <f t="shared" si="5"/>
         <v>1004021</v>
       </c>
       <c r="B369" s="1" t="s">
@@ -12236,7 +12248,7 @@
     </row>
     <row r="370" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A370" s="1" t="str">
-        <f>F370 &amp; TEXT(C370,"000")</f>
+        <f t="shared" si="5"/>
         <v>1004022</v>
       </c>
       <c r="B370" s="1" t="s">
@@ -12260,7 +12272,7 @@
     </row>
     <row r="371" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A371" s="1" t="str">
-        <f>F371 &amp; TEXT(C371,"000")</f>
+        <f t="shared" si="5"/>
         <v>1004014</v>
       </c>
       <c r="B371" s="1" t="s">
@@ -12284,7 +12296,7 @@
     </row>
     <row r="372" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A372" s="1" t="str">
-        <f>F372 &amp; TEXT(C372,"000")</f>
+        <f t="shared" si="5"/>
         <v>1004013</v>
       </c>
       <c r="B372" s="1" t="s">
@@ -12308,7 +12320,7 @@
     </row>
     <row r="373" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A373" s="1" t="str">
-        <f>F373 &amp; TEXT(C373,"000")</f>
+        <f t="shared" si="5"/>
         <v>1004004</v>
       </c>
       <c r="B373" s="1" t="s">
@@ -12332,7 +12344,7 @@
     </row>
     <row r="374" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A374" s="1" t="str">
-        <f>F374 &amp; TEXT(C374,"000")</f>
+        <f t="shared" si="5"/>
         <v>1004020</v>
       </c>
       <c r="B374" s="1" t="s">
@@ -12356,7 +12368,7 @@
     </row>
     <row r="375" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A375" s="1" t="str">
-        <f>F375 &amp; TEXT(C375,"000")</f>
+        <f t="shared" si="5"/>
         <v>1004007</v>
       </c>
       <c r="B375" s="1" t="s">
@@ -12380,7 +12392,7 @@
     </row>
     <row r="376" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A376" s="1" t="str">
-        <f>F376 &amp; TEXT(C376,"000")</f>
+        <f t="shared" si="5"/>
         <v>1004015</v>
       </c>
       <c r="B376" s="1" t="s">
@@ -12404,7 +12416,7 @@
     </row>
     <row r="377" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A377" s="1" t="str">
-        <f>F377 &amp; TEXT(C377,"000")</f>
+        <f t="shared" si="5"/>
         <v>1004005</v>
       </c>
       <c r="B377" s="1" t="s">
@@ -12428,7 +12440,7 @@
     </row>
     <row r="378" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A378" s="1" t="str">
-        <f>F378 &amp; TEXT(C378,"000")</f>
+        <f t="shared" si="5"/>
         <v>1004012</v>
       </c>
       <c r="B378" s="1" t="s">
@@ -12452,7 +12464,7 @@
     </row>
     <row r="379" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A379" s="1" t="str">
-        <f>F379 &amp; TEXT(C379,"000")</f>
+        <f t="shared" si="5"/>
         <v>1004018</v>
       </c>
       <c r="B379" s="1" t="s">
@@ -12476,7 +12488,7 @@
     </row>
     <row r="380" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A380" s="1" t="str">
-        <f>F380 &amp; TEXT(C380,"000")</f>
+        <f t="shared" si="5"/>
         <v>1004031</v>
       </c>
       <c r="B380" s="1" t="s">
@@ -12500,7 +12512,7 @@
     </row>
     <row r="381" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A381" s="1" t="str">
-        <f>F381 &amp; TEXT(C381,"000")</f>
+        <f t="shared" si="5"/>
         <v>1004008</v>
       </c>
       <c r="B381" s="1" t="s">
@@ -12524,7 +12536,7 @@
     </row>
     <row r="382" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A382" s="1" t="str">
-        <f>F382 &amp; TEXT(C382,"000")</f>
+        <f t="shared" si="5"/>
         <v>1004002</v>
       </c>
       <c r="B382" s="1" t="s">
@@ -12548,7 +12560,7 @@
     </row>
     <row r="383" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A383" s="1" t="str">
-        <f>F383 &amp; TEXT(C383,"000")</f>
+        <f t="shared" si="5"/>
         <v>1004009</v>
       </c>
       <c r="B383" s="1" t="s">
@@ -12572,7 +12584,7 @@
     </row>
     <row r="384" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A384" s="1" t="str">
-        <f>F384 &amp; TEXT(C384,"000")</f>
+        <f t="shared" si="5"/>
         <v>1004006</v>
       </c>
       <c r="B384" s="1" t="s">
@@ -12596,7 +12608,7 @@
     </row>
     <row r="385" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A385" s="1" t="str">
-        <f>F385 &amp; TEXT(C385,"000")</f>
+        <f t="shared" si="5"/>
         <v>1004003</v>
       </c>
       <c r="B385" s="1" t="s">
@@ -12620,7 +12632,7 @@
     </row>
     <row r="386" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A386" s="1" t="str">
-        <f>F386 &amp; TEXT(C386,"000")</f>
+        <f t="shared" ref="A386:A449" si="6">F386 &amp; TEXT(C386,"000")</f>
         <v>1004023</v>
       </c>
       <c r="B386" s="1" t="s">
@@ -12644,7 +12656,7 @@
     </row>
     <row r="387" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A387" s="1" t="str">
-        <f>F387 &amp; TEXT(C387,"000")</f>
+        <f t="shared" si="6"/>
         <v>1004011</v>
       </c>
       <c r="B387" s="1" t="s">
@@ -12668,7 +12680,7 @@
     </row>
     <row r="388" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A388" s="1" t="str">
-        <f>F388 &amp; TEXT(C388,"000")</f>
+        <f t="shared" si="6"/>
         <v>1004025</v>
       </c>
       <c r="B388" s="1" t="s">
@@ -12692,7 +12704,7 @@
     </row>
     <row r="389" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A389" s="1" t="str">
-        <f>F389 &amp; TEXT(C389,"000")</f>
+        <f t="shared" si="6"/>
         <v>1004024</v>
       </c>
       <c r="B389" s="1" t="s">
@@ -12716,7 +12728,7 @@
     </row>
     <row r="390" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A390" s="1" t="str">
-        <f>F390 &amp; TEXT(C390,"000")</f>
+        <f t="shared" si="6"/>
         <v>1004028</v>
       </c>
       <c r="B390" s="1" t="s">
@@ -12740,7 +12752,7 @@
     </row>
     <row r="391" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A391" s="1" t="str">
-        <f>F391 &amp; TEXT(C391,"000")</f>
+        <f t="shared" si="6"/>
         <v>1004151</v>
       </c>
       <c r="B391" s="1" t="s">
@@ -12764,7 +12776,7 @@
     </row>
     <row r="392" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A392" s="1" t="str">
-        <f>F392 &amp; TEXT(C392,"000")</f>
+        <f t="shared" si="6"/>
         <v>1005120</v>
       </c>
       <c r="B392" s="1" t="s">
@@ -12788,7 +12800,7 @@
     </row>
     <row r="393" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A393" s="1" t="str">
-        <f>F393 &amp; TEXT(C393,"000")</f>
+        <f t="shared" si="6"/>
         <v>1005012</v>
       </c>
       <c r="B393" s="1" t="s">
@@ -12812,7 +12824,7 @@
     </row>
     <row r="394" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A394" s="1" t="str">
-        <f>F394 &amp; TEXT(C394,"000")</f>
+        <f t="shared" si="6"/>
         <v>1005001</v>
       </c>
       <c r="B394" s="1" t="s">
@@ -12836,7 +12848,7 @@
     </row>
     <row r="395" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A395" s="1" t="str">
-        <f>F395 &amp; TEXT(C395,"000")</f>
+        <f t="shared" si="6"/>
         <v>1005023</v>
       </c>
       <c r="B395" s="1" t="s">
@@ -12860,7 +12872,7 @@
     </row>
     <row r="396" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A396" s="1" t="str">
-        <f>F396 &amp; TEXT(C396,"000")</f>
+        <f t="shared" si="6"/>
         <v>1005005</v>
       </c>
       <c r="B396" s="1" t="s">
@@ -12884,7 +12896,7 @@
     </row>
     <row r="397" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A397" s="1" t="str">
-        <f>F397 &amp; TEXT(C397,"000")</f>
+        <f t="shared" si="6"/>
         <v>1005018</v>
       </c>
       <c r="B397" s="1" t="s">
@@ -12908,7 +12920,7 @@
     </row>
     <row r="398" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A398" s="1" t="str">
-        <f>F398 &amp; TEXT(C398,"000")</f>
+        <f t="shared" si="6"/>
         <v>1005041</v>
       </c>
       <c r="B398" s="1" t="s">
@@ -12932,7 +12944,7 @@
     </row>
     <row r="399" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A399" s="1" t="str">
-        <f>F399 &amp; TEXT(C399,"000")</f>
+        <f t="shared" si="6"/>
         <v>1005002</v>
       </c>
       <c r="B399" s="1" t="s">
@@ -12956,7 +12968,7 @@
     </row>
     <row r="400" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A400" s="1" t="str">
-        <f>F400 &amp; TEXT(C400,"000")</f>
+        <f t="shared" si="6"/>
         <v>1005013</v>
       </c>
       <c r="B400" s="1" t="s">
@@ -12980,7 +12992,7 @@
     </row>
     <row r="401" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A401" s="1" t="str">
-        <f>F401 &amp; TEXT(C401,"000")</f>
+        <f t="shared" si="6"/>
         <v>1005025</v>
       </c>
       <c r="B401" s="1" t="s">
@@ -13004,7 +13016,7 @@
     </row>
     <row r="402" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A402" s="1" t="str">
-        <f>F402 &amp; TEXT(C402,"000")</f>
+        <f t="shared" si="6"/>
         <v>1005016</v>
       </c>
       <c r="B402" s="1" t="s">
@@ -13028,7 +13040,7 @@
     </row>
     <row r="403" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A403" s="1" t="str">
-        <f>F403 &amp; TEXT(C403,"000")</f>
+        <f t="shared" si="6"/>
         <v>1005022</v>
       </c>
       <c r="B403" s="1" t="s">
@@ -13052,7 +13064,7 @@
     </row>
     <row r="404" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A404" s="1" t="str">
-        <f>F404 &amp; TEXT(C404,"000")</f>
+        <f t="shared" si="6"/>
         <v>1005010</v>
       </c>
       <c r="B404" s="1" t="s">
@@ -13076,7 +13088,7 @@
     </row>
     <row r="405" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A405" s="1" t="str">
-        <f>F405 &amp; TEXT(C405,"000")</f>
+        <f t="shared" si="6"/>
         <v>1005032</v>
       </c>
       <c r="B405" s="1" t="s">
@@ -13100,7 +13112,7 @@
     </row>
     <row r="406" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A406" s="1" t="str">
-        <f>F406 &amp; TEXT(C406,"000")</f>
+        <f t="shared" si="6"/>
         <v>1005033</v>
       </c>
       <c r="B406" s="1" t="s">
@@ -13124,7 +13136,7 @@
     </row>
     <row r="407" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A407" s="1" t="str">
-        <f>F407 &amp; TEXT(C407,"000")</f>
+        <f t="shared" si="6"/>
         <v>1005014</v>
       </c>
       <c r="B407" s="1" t="s">
@@ -13148,7 +13160,7 @@
     </row>
     <row r="408" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A408" s="1" t="str">
-        <f>F408 &amp; TEXT(C408,"000")</f>
+        <f t="shared" si="6"/>
         <v>1005007</v>
       </c>
       <c r="B408" s="1" t="s">
@@ -13172,7 +13184,7 @@
     </row>
     <row r="409" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A409" s="1" t="str">
-        <f>F409 &amp; TEXT(C409,"000")</f>
+        <f t="shared" si="6"/>
         <v>1005029</v>
       </c>
       <c r="B409" s="1" t="s">
@@ -13196,7 +13208,7 @@
     </row>
     <row r="410" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A410" s="1" t="str">
-        <f>F410 &amp; TEXT(C410,"000")</f>
+        <f t="shared" si="6"/>
         <v>1005008</v>
       </c>
       <c r="B410" s="1" t="s">
@@ -13220,7 +13232,7 @@
     </row>
     <row r="411" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A411" s="1" t="str">
-        <f>F411 &amp; TEXT(C411,"000")</f>
+        <f t="shared" si="6"/>
         <v>1005024</v>
       </c>
       <c r="B411" s="1" t="s">
@@ -13244,7 +13256,7 @@
     </row>
     <row r="412" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A412" s="1" t="str">
-        <f>F412 &amp; TEXT(C412,"000")</f>
+        <f t="shared" si="6"/>
         <v>1005019</v>
       </c>
       <c r="B412" s="1" t="s">
@@ -13268,7 +13280,7 @@
     </row>
     <row r="413" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A413" s="1" t="str">
-        <f>F413 &amp; TEXT(C413,"000")</f>
+        <f t="shared" si="6"/>
         <v>1005021</v>
       </c>
       <c r="B413" s="1" t="s">
@@ -13292,7 +13304,7 @@
     </row>
     <row r="414" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A414" s="1" t="str">
-        <f>F414 &amp; TEXT(C414,"000")</f>
+        <f t="shared" si="6"/>
         <v>1005020</v>
       </c>
       <c r="B414" s="1" t="s">
@@ -13316,7 +13328,7 @@
     </row>
     <row r="415" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A415" s="1" t="str">
-        <f>F415 &amp; TEXT(C415,"000")</f>
+        <f t="shared" si="6"/>
         <v>1005011</v>
       </c>
       <c r="B415" s="1" t="s">
@@ -13340,7 +13352,7 @@
     </row>
     <row r="416" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A416" s="1" t="str">
-        <f>F416 &amp; TEXT(C416,"000")</f>
+        <f t="shared" si="6"/>
         <v>1005009</v>
       </c>
       <c r="B416" s="1" t="s">
@@ -13364,7 +13376,7 @@
     </row>
     <row r="417" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A417" s="1" t="str">
-        <f>F417 &amp; TEXT(C417,"000")</f>
+        <f t="shared" si="6"/>
         <v>1005017</v>
       </c>
       <c r="B417" s="1" t="s">
@@ -13388,7 +13400,7 @@
     </row>
     <row r="418" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A418" s="1" t="str">
-        <f>F418 &amp; TEXT(C418,"000")</f>
+        <f t="shared" si="6"/>
         <v>1005015</v>
       </c>
       <c r="B418" s="1" t="s">
@@ -13412,7 +13424,7 @@
     </row>
     <row r="419" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A419" s="1" t="str">
-        <f>F419 &amp; TEXT(C419,"000")</f>
+        <f t="shared" si="6"/>
         <v>1005121</v>
       </c>
       <c r="B419" s="1" t="s">
@@ -13436,7 +13448,7 @@
     </row>
     <row r="420" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A420" s="1" t="str">
-        <f>F420 &amp; TEXT(C420,"000")</f>
+        <f t="shared" si="6"/>
         <v>1003001</v>
       </c>
       <c r="B420" s="1" t="s">
@@ -13460,7 +13472,7 @@
     </row>
     <row r="421" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A421" s="1" t="str">
-        <f>F421 &amp; TEXT(C421,"000")</f>
+        <f t="shared" si="6"/>
         <v>1003028</v>
       </c>
       <c r="B421" s="1" t="s">
@@ -13484,7 +13496,7 @@
     </row>
     <row r="422" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A422" s="1" t="str">
-        <f>F422 &amp; TEXT(C422,"000")</f>
+        <f t="shared" si="6"/>
         <v>1003023</v>
       </c>
       <c r="B422" s="1" t="s">
@@ -13508,7 +13520,7 @@
     </row>
     <row r="423" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A423" s="1" t="str">
-        <f>F423 &amp; TEXT(C423,"000")</f>
+        <f t="shared" si="6"/>
         <v>1003126</v>
       </c>
       <c r="B423" s="1" t="s">
@@ -13532,7 +13544,7 @@
     </row>
     <row r="424" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A424" s="1" t="str">
-        <f>F424 &amp; TEXT(C424,"000")</f>
+        <f t="shared" si="6"/>
         <v>1003019</v>
       </c>
       <c r="B424" s="1" t="s">
@@ -13556,7 +13568,7 @@
     </row>
     <row r="425" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A425" s="1" t="str">
-        <f>F425 &amp; TEXT(C425,"000")</f>
+        <f t="shared" si="6"/>
         <v>1003004</v>
       </c>
       <c r="B425" s="1" t="s">
@@ -13580,7 +13592,7 @@
     </row>
     <row r="426" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A426" s="1" t="str">
-        <f>F426 &amp; TEXT(C426,"000")</f>
+        <f t="shared" si="6"/>
         <v>1003013</v>
       </c>
       <c r="B426" s="1" t="s">
@@ -13604,7 +13616,7 @@
     </row>
     <row r="427" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A427" s="1" t="str">
-        <f>F427 &amp; TEXT(C427,"000")</f>
+        <f t="shared" si="6"/>
         <v>1003127</v>
       </c>
       <c r="B427" s="1" t="s">
@@ -13628,7 +13640,7 @@
     </row>
     <row r="428" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A428" s="1" t="str">
-        <f>F428 &amp; TEXT(C428,"000")</f>
+        <f t="shared" si="6"/>
         <v>1003002</v>
       </c>
       <c r="B428" s="1" t="s">
@@ -13652,7 +13664,7 @@
     </row>
     <row r="429" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A429" s="1" t="str">
-        <f>F429 &amp; TEXT(C429,"000")</f>
+        <f t="shared" si="6"/>
         <v>1003007</v>
       </c>
       <c r="B429" s="1" t="s">
@@ -13676,7 +13688,7 @@
     </row>
     <row r="430" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A430" s="1" t="str">
-        <f>F430 &amp; TEXT(C430,"000")</f>
+        <f t="shared" si="6"/>
         <v>1003030</v>
       </c>
       <c r="B430" s="1" t="s">
@@ -13700,7 +13712,7 @@
     </row>
     <row r="431" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A431" s="1" t="str">
-        <f>F431 &amp; TEXT(C431,"000")</f>
+        <f t="shared" si="6"/>
         <v>1003024</v>
       </c>
       <c r="B431" s="1" t="s">
@@ -13724,7 +13736,7 @@
     </row>
     <row r="432" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A432" s="1" t="str">
-        <f>F432 &amp; TEXT(C432,"000")</f>
+        <f t="shared" si="6"/>
         <v>1003027</v>
       </c>
       <c r="B432" s="1" t="s">
@@ -13748,7 +13760,7 @@
     </row>
     <row r="433" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A433" s="1" t="str">
-        <f>F433 &amp; TEXT(C433,"000")</f>
+        <f t="shared" si="6"/>
         <v>1003005</v>
       </c>
       <c r="B433" s="1" t="s">
@@ -13772,7 +13784,7 @@
     </row>
     <row r="434" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A434" s="1" t="str">
-        <f>F434 &amp; TEXT(C434,"000")</f>
+        <f t="shared" si="6"/>
         <v>1003025</v>
       </c>
       <c r="B434" s="1" t="s">
@@ -13796,7 +13808,7 @@
     </row>
     <row r="435" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A435" s="1" t="str">
-        <f>F435 &amp; TEXT(C435,"000")</f>
+        <f t="shared" si="6"/>
         <v>1003026</v>
       </c>
       <c r="B435" s="1" t="s">
@@ -13820,7 +13832,7 @@
     </row>
     <row r="436" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A436" s="1" t="str">
-        <f>F436 &amp; TEXT(C436,"000")</f>
+        <f t="shared" si="6"/>
         <v>1003016</v>
       </c>
       <c r="B436" s="1" t="s">
@@ -13844,7 +13856,7 @@
     </row>
     <row r="437" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A437" s="1" t="str">
-        <f>F437 &amp; TEXT(C437,"000")</f>
+        <f t="shared" si="6"/>
         <v>1003010</v>
       </c>
       <c r="B437" s="1" t="s">
@@ -13868,7 +13880,7 @@
     </row>
     <row r="438" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A438" s="1" t="str">
-        <f>F438 &amp; TEXT(C438,"000")</f>
+        <f t="shared" si="6"/>
         <v>1003036</v>
       </c>
       <c r="B438" s="1" t="s">
@@ -13892,7 +13904,7 @@
     </row>
     <row r="439" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A439" s="1" t="str">
-        <f>F439 &amp; TEXT(C439,"000")</f>
+        <f t="shared" si="6"/>
         <v>1003017</v>
       </c>
       <c r="B439" s="1" t="s">
@@ -13916,7 +13928,7 @@
     </row>
     <row r="440" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A440" s="1" t="str">
-        <f>F440 &amp; TEXT(C440,"000")</f>
+        <f t="shared" si="6"/>
         <v>1003008</v>
       </c>
       <c r="B440" s="1" t="s">
@@ -13940,7 +13952,7 @@
     </row>
     <row r="441" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A441" s="1" t="str">
-        <f>F441 &amp; TEXT(C441,"000")</f>
+        <f t="shared" si="6"/>
         <v>1003014</v>
       </c>
       <c r="B441" s="1" t="s">
@@ -13964,7 +13976,7 @@
     </row>
     <row r="442" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A442" s="1" t="str">
-        <f>F442 &amp; TEXT(C442,"000")</f>
+        <f t="shared" si="6"/>
         <v>1003003</v>
       </c>
       <c r="B442" s="1" t="s">
@@ -13988,7 +14000,7 @@
     </row>
     <row r="443" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A443" s="1" t="str">
-        <f>F443 &amp; TEXT(C443,"000")</f>
+        <f t="shared" si="6"/>
         <v>1003006</v>
       </c>
       <c r="B443" s="1" t="s">
@@ -14012,7 +14024,7 @@
     </row>
     <row r="444" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A444" s="1" t="str">
-        <f>F444 &amp; TEXT(C444,"000")</f>
+        <f t="shared" si="6"/>
         <v>1003011</v>
       </c>
       <c r="B444" s="1" t="s">
@@ -14036,7 +14048,7 @@
     </row>
     <row r="445" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A445" s="1" t="str">
-        <f>F445 &amp; TEXT(C445,"000")</f>
+        <f t="shared" si="6"/>
         <v>1003021</v>
       </c>
       <c r="B445" s="1" t="s">
@@ -14060,7 +14072,7 @@
     </row>
     <row r="446" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A446" s="1" t="str">
-        <f>F446 &amp; TEXT(C446,"000")</f>
+        <f t="shared" si="6"/>
         <v>1003033</v>
       </c>
       <c r="B446" s="1" t="s">
@@ -14084,7 +14096,7 @@
     </row>
     <row r="447" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A447" s="1" t="str">
-        <f>F447 &amp; TEXT(C447,"000")</f>
+        <f t="shared" si="6"/>
         <v>1003015</v>
       </c>
       <c r="B447" s="1" t="s">
@@ -14108,7 +14120,7 @@
     </row>
     <row r="448" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A448" s="1" t="str">
-        <f>F448 &amp; TEXT(C448,"000")</f>
+        <f t="shared" si="6"/>
         <v>1003009</v>
       </c>
       <c r="B448" s="1" t="s">
@@ -14132,7 +14144,7 @@
     </row>
     <row r="449" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A449" s="1" t="str">
-        <f>F449 &amp; TEXT(C449,"000")</f>
+        <f t="shared" si="6"/>
         <v>1003018</v>
       </c>
       <c r="B449" s="1" t="s">
@@ -14156,7 +14168,7 @@
     </row>
     <row r="450" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A450" s="1" t="str">
-        <f>F450 &amp; TEXT(C450,"000")</f>
+        <f t="shared" ref="A450:A513" si="7">F450 &amp; TEXT(C450,"000")</f>
         <v>1003029</v>
       </c>
       <c r="B450" s="1" t="s">
@@ -14180,7 +14192,7 @@
     </row>
     <row r="451" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A451" s="1" t="str">
-        <f>F451 &amp; TEXT(C451,"000")</f>
+        <f t="shared" si="7"/>
         <v>1003131</v>
       </c>
       <c r="B451" s="1" t="s">
@@ -14204,7 +14216,7 @@
     </row>
     <row r="452" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A452" s="1" t="str">
-        <f>F452 &amp; TEXT(C452,"000")</f>
+        <f t="shared" si="7"/>
         <v>1003022</v>
       </c>
       <c r="B452" s="1" t="s">
@@ -14228,7 +14240,7 @@
     </row>
     <row r="453" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A453" s="1" t="str">
-        <f>F453 &amp; TEXT(C453,"000")</f>
+        <f t="shared" si="7"/>
         <v>1003020</v>
       </c>
       <c r="B453" s="1" t="s">
@@ -14252,7 +14264,7 @@
     </row>
     <row r="454" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A454" s="1" t="str">
-        <f>F454 &amp; TEXT(C454,"000")</f>
+        <f t="shared" si="7"/>
         <v>1003132</v>
       </c>
       <c r="B454" s="1" t="s">
@@ -14274,9 +14286,9 @@
         <v>441</v>
       </c>
     </row>
-    <row r="455" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A455" t="str">
-        <f>F455 &amp; TEXT(C455,"000")</f>
+        <f t="shared" si="7"/>
         <v>1003041</v>
       </c>
       <c r="B455" t="s">
@@ -14298,9 +14310,9 @@
         <v>441</v>
       </c>
     </row>
-    <row r="456" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A456" t="str">
-        <f>F456 &amp; TEXT(C456,"000")</f>
+        <f t="shared" si="7"/>
         <v>1003038</v>
       </c>
       <c r="B456" t="s">
@@ -14322,9 +14334,9 @@
         <v>441</v>
       </c>
     </row>
-    <row r="457" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A457" t="str">
-        <f>F457 &amp; TEXT(C457,"000")</f>
+        <f t="shared" si="7"/>
         <v>1003039</v>
       </c>
       <c r="B457" t="s">
@@ -14346,9 +14358,9 @@
         <v>441</v>
       </c>
     </row>
-    <row r="458" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A458" t="str">
-        <f>F458 &amp; TEXT(C458,"000")</f>
+        <f t="shared" si="7"/>
         <v>1003040</v>
       </c>
       <c r="B458" t="s">
@@ -14367,7 +14379,7 @@
     </row>
     <row r="459" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A459" s="1" t="str">
-        <f>F459 &amp; TEXT(C459,"000")</f>
+        <f t="shared" si="7"/>
         <v>1002021</v>
       </c>
       <c r="B459" s="1" t="s">
@@ -14391,7 +14403,7 @@
     </row>
     <row r="460" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A460" s="1" t="str">
-        <f>F460 &amp; TEXT(C460,"000")</f>
+        <f t="shared" si="7"/>
         <v>1002025</v>
       </c>
       <c r="B460" s="1" t="s">
@@ -14415,7 +14427,7 @@
     </row>
     <row r="461" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A461" s="1" t="str">
-        <f>F461 &amp; TEXT(C461,"000")</f>
+        <f t="shared" si="7"/>
         <v>1002001</v>
       </c>
       <c r="B461" s="1" t="s">
@@ -14439,7 +14451,7 @@
     </row>
     <row r="462" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A462" s="1" t="str">
-        <f>F462 &amp; TEXT(C462,"000")</f>
+        <f t="shared" si="7"/>
         <v>1002108</v>
       </c>
       <c r="B462" s="1" t="s">
@@ -14463,7 +14475,7 @@
     </row>
     <row r="463" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A463" s="1" t="str">
-        <f>F463 &amp; TEXT(C463,"000")</f>
+        <f t="shared" si="7"/>
         <v>1002019</v>
       </c>
       <c r="B463" s="1" t="s">
@@ -14487,7 +14499,7 @@
     </row>
     <row r="464" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A464" s="1" t="str">
-        <f>F464 &amp; TEXT(C464,"000")</f>
+        <f t="shared" si="7"/>
         <v>1002007</v>
       </c>
       <c r="B464" s="1" t="s">
@@ -14511,7 +14523,7 @@
     </row>
     <row r="465" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A465" s="1" t="str">
-        <f>F465 &amp; TEXT(C465,"000")</f>
+        <f t="shared" si="7"/>
         <v>1002003</v>
       </c>
       <c r="B465" s="1" t="s">
@@ -14535,7 +14547,7 @@
     </row>
     <row r="466" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A466" s="1" t="str">
-        <f>F466 &amp; TEXT(C466,"000")</f>
+        <f t="shared" si="7"/>
         <v>1002024</v>
       </c>
       <c r="B466" s="1" t="s">
@@ -14559,7 +14571,7 @@
     </row>
     <row r="467" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A467" s="1" t="str">
-        <f>F467 &amp; TEXT(C467,"000")</f>
+        <f t="shared" si="7"/>
         <v>1002004</v>
       </c>
       <c r="B467" s="1" t="s">
@@ -14583,7 +14595,7 @@
     </row>
     <row r="468" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A468" s="1" t="str">
-        <f>F468 &amp; TEXT(C468,"000")</f>
+        <f t="shared" si="7"/>
         <v>1002018</v>
       </c>
       <c r="B468" s="1" t="s">
@@ -14607,7 +14619,7 @@
     </row>
     <row r="469" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A469" s="1" t="str">
-        <f>F469 &amp; TEXT(C469,"000")</f>
+        <f t="shared" si="7"/>
         <v>1002008</v>
       </c>
       <c r="B469" s="1" t="s">
@@ -14631,7 +14643,7 @@
     </row>
     <row r="470" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A470" s="1" t="str">
-        <f>F470 &amp; TEXT(C470,"000")</f>
+        <f t="shared" si="7"/>
         <v>1002002</v>
       </c>
       <c r="B470" s="1" t="s">
@@ -14655,7 +14667,7 @@
     </row>
     <row r="471" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A471" s="1" t="str">
-        <f>F471 &amp; TEXT(C471,"000")</f>
+        <f t="shared" si="7"/>
         <v>1002006</v>
       </c>
       <c r="B471" s="1" t="s">
@@ -14679,7 +14691,7 @@
     </row>
     <row r="472" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A472" s="1" t="str">
-        <f>F472 &amp; TEXT(C472,"000")</f>
+        <f t="shared" si="7"/>
         <v>1002015</v>
       </c>
       <c r="B472" s="1" t="s">
@@ -14703,7 +14715,7 @@
     </row>
     <row r="473" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A473" s="1" t="str">
-        <f>F473 &amp; TEXT(C473,"000")</f>
+        <f t="shared" si="7"/>
         <v>1002013</v>
       </c>
       <c r="B473" s="1" t="s">
@@ -14727,7 +14739,7 @@
     </row>
     <row r="474" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A474" s="1" t="str">
-        <f>F474 &amp; TEXT(C474,"000")</f>
+        <f t="shared" si="7"/>
         <v>1002012</v>
       </c>
       <c r="B474" s="1" t="s">
@@ -14751,7 +14763,7 @@
     </row>
     <row r="475" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A475" s="1" t="str">
-        <f>F475 &amp; TEXT(C475,"000")</f>
+        <f t="shared" si="7"/>
         <v>1002011</v>
       </c>
       <c r="B475" s="1" t="s">
@@ -14775,7 +14787,7 @@
     </row>
     <row r="476" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A476" s="1" t="str">
-        <f>F476 &amp; TEXT(C476,"000")</f>
+        <f t="shared" si="7"/>
         <v>1002027</v>
       </c>
       <c r="B476" s="1" t="s">
@@ -14799,7 +14811,7 @@
     </row>
     <row r="477" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A477" s="1" t="str">
-        <f>F477 &amp; TEXT(C477,"000")</f>
+        <f t="shared" si="7"/>
         <v>1002005</v>
       </c>
       <c r="B477" s="1" t="s">
@@ -14823,7 +14835,7 @@
     </row>
     <row r="478" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A478" s="1" t="str">
-        <f>F478 &amp; TEXT(C478,"000")</f>
+        <f t="shared" si="7"/>
         <v>1002109</v>
       </c>
       <c r="B478" s="1" t="s">
@@ -14847,7 +14859,7 @@
     </row>
     <row r="479" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A479" s="1" t="str">
-        <f>F479 &amp; TEXT(C479,"000")</f>
+        <f t="shared" si="7"/>
         <v>1002022</v>
       </c>
       <c r="B479" s="1" t="s">
@@ -14871,7 +14883,7 @@
     </row>
     <row r="480" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A480" s="1" t="str">
-        <f>F480 &amp; TEXT(C480,"000")</f>
+        <f t="shared" si="7"/>
         <v>1002009</v>
       </c>
       <c r="B480" s="1" t="s">
@@ -14895,7 +14907,7 @@
     </row>
     <row r="481" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A481" s="1" t="str">
-        <f>F481 &amp; TEXT(C481,"000")</f>
+        <f t="shared" si="7"/>
         <v>1002017</v>
       </c>
       <c r="B481" s="1" t="s">
@@ -14919,7 +14931,7 @@
     </row>
     <row r="482" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A482" s="1" t="str">
-        <f>F482 &amp; TEXT(C482,"000")</f>
+        <f t="shared" si="7"/>
         <v>1002110</v>
       </c>
       <c r="B482" s="1" t="s">
@@ -14943,7 +14955,7 @@
     </row>
     <row r="483" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A483" s="1" t="str">
-        <f>F483 &amp; TEXT(C483,"000")</f>
+        <f t="shared" si="7"/>
         <v>1002020</v>
       </c>
       <c r="B483" s="1" t="s">
@@ -14967,7 +14979,7 @@
     </row>
     <row r="484" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A484" s="1" t="str">
-        <f>F484 &amp; TEXT(C484,"000")</f>
+        <f t="shared" si="7"/>
         <v>1002014</v>
       </c>
       <c r="B484" s="1" t="s">
@@ -14991,7 +15003,7 @@
     </row>
     <row r="485" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A485" s="1" t="str">
-        <f>F485 &amp; TEXT(C485,"000")</f>
+        <f t="shared" si="7"/>
         <v>1002023</v>
       </c>
       <c r="B485" s="1" t="s">
@@ -15015,7 +15027,7 @@
     </row>
     <row r="486" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A486" s="1" t="str">
-        <f>F486 &amp; TEXT(C486,"000")</f>
+        <f t="shared" si="7"/>
         <v>1002016</v>
       </c>
       <c r="B486" s="1" t="s">
@@ -15039,7 +15051,7 @@
     </row>
     <row r="487" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A487" s="1" t="str">
-        <f>F487 &amp; TEXT(C487,"000")</f>
+        <f t="shared" si="7"/>
         <v>1002026</v>
       </c>
       <c r="B487" s="1" t="s">
@@ -15063,7 +15075,7 @@
     </row>
     <row r="488" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A488" s="1" t="str">
-        <f>F488 &amp; TEXT(C488,"000")</f>
+        <f t="shared" si="7"/>
         <v>1002111</v>
       </c>
       <c r="B488" s="1" t="s">
@@ -15087,7 +15099,7 @@
     </row>
     <row r="489" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A489" t="str">
-        <f>F489 &amp; TEXT(C489,"000")</f>
+        <f t="shared" si="7"/>
         <v>1002029</v>
       </c>
       <c r="B489" t="s">
@@ -15111,7 +15123,7 @@
     </row>
     <row r="490" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A490" s="1" t="str">
-        <f>F490 &amp; TEXT(C490,"000")</f>
+        <f t="shared" si="7"/>
         <v>1001001</v>
       </c>
       <c r="B490" s="1" t="s">
@@ -15135,7 +15147,7 @@
     </row>
     <row r="491" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A491" s="1" t="str">
-        <f>F491 &amp; TEXT(C491,"000")</f>
+        <f t="shared" si="7"/>
         <v>1001001</v>
       </c>
       <c r="B491" s="1" t="s">
@@ -15159,7 +15171,7 @@
     </row>
     <row r="492" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A492" s="1" t="str">
-        <f>F492 &amp; TEXT(C492,"000")</f>
+        <f t="shared" si="7"/>
         <v>1001021</v>
       </c>
       <c r="B492" s="1" t="s">
@@ -15183,7 +15195,7 @@
     </row>
     <row r="493" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A493" s="1" t="str">
-        <f>F493 &amp; TEXT(C493,"000")</f>
+        <f t="shared" si="7"/>
         <v>1001152</v>
       </c>
       <c r="B493" s="1" t="s">
@@ -15207,7 +15219,7 @@
     </row>
     <row r="494" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A494" s="1" t="str">
-        <f>F494 &amp; TEXT(C494,"000")</f>
+        <f t="shared" si="7"/>
         <v>1001001</v>
       </c>
       <c r="B494" s="1" t="s">
@@ -15231,7 +15243,7 @@
     </row>
     <row r="495" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A495" s="1" t="str">
-        <f>F495 &amp; TEXT(C495,"000")</f>
+        <f t="shared" si="7"/>
         <v>1001029</v>
       </c>
       <c r="B495" s="1" t="s">
@@ -15255,7 +15267,7 @@
     </row>
     <row r="496" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A496" s="1" t="str">
-        <f>F496 &amp; TEXT(C496,"000")</f>
+        <f t="shared" si="7"/>
         <v>1001023</v>
       </c>
       <c r="B496" s="1" t="s">
@@ -15279,7 +15291,7 @@
     </row>
     <row r="497" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A497" s="1" t="str">
-        <f>F497 &amp; TEXT(C497,"000")</f>
+        <f t="shared" si="7"/>
         <v>1001153</v>
       </c>
       <c r="B497" s="1" t="s">
@@ -15303,7 +15315,7 @@
     </row>
     <row r="498" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A498" s="1" t="str">
-        <f>F498 &amp; TEXT(C498,"000")</f>
+        <f t="shared" si="7"/>
         <v>1001020</v>
       </c>
       <c r="B498" s="1" t="s">
@@ -15327,7 +15339,7 @@
     </row>
     <row r="499" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A499" s="1" t="str">
-        <f>F499 &amp; TEXT(C499,"000")</f>
+        <f t="shared" si="7"/>
         <v>1001013</v>
       </c>
       <c r="B499" s="1" t="s">
@@ -15351,7 +15363,7 @@
     </row>
     <row r="500" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A500" s="1" t="str">
-        <f>F500 &amp; TEXT(C500,"000")</f>
+        <f t="shared" si="7"/>
         <v>1001024</v>
       </c>
       <c r="B500" s="1" t="s">
@@ -15375,7 +15387,7 @@
     </row>
     <row r="501" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A501" s="1" t="str">
-        <f>F501 &amp; TEXT(C501,"000")</f>
+        <f t="shared" si="7"/>
         <v>1001002</v>
       </c>
       <c r="B501" s="1" t="s">
@@ -15399,7 +15411,7 @@
     </row>
     <row r="502" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A502" s="1" t="str">
-        <f>F502 &amp; TEXT(C502,"000")</f>
+        <f t="shared" si="7"/>
         <v>1001043</v>
       </c>
       <c r="B502" s="1" t="s">
@@ -15423,7 +15435,7 @@
     </row>
     <row r="503" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A503" s="1" t="str">
-        <f>F503 &amp; TEXT(C503,"000")</f>
+        <f t="shared" si="7"/>
         <v>1001041</v>
       </c>
       <c r="B503" s="1" t="s">
@@ -15447,7 +15459,7 @@
     </row>
     <row r="504" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A504" s="1" t="str">
-        <f>F504 &amp; TEXT(C504,"000")</f>
+        <f t="shared" si="7"/>
         <v>1001025</v>
       </c>
       <c r="B504" s="1" t="s">
@@ -15471,7 +15483,7 @@
     </row>
     <row r="505" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A505" s="1" t="str">
-        <f>F505 &amp; TEXT(C505,"000")</f>
+        <f t="shared" si="7"/>
         <v>1001012</v>
       </c>
       <c r="B505" s="1" t="s">
@@ -15495,7 +15507,7 @@
     </row>
     <row r="506" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A506" s="1" t="str">
-        <f>F506 &amp; TEXT(C506,"000")</f>
+        <f t="shared" si="7"/>
         <v>1001045</v>
       </c>
       <c r="B506" s="1" t="s">
@@ -15519,7 +15531,7 @@
     </row>
     <row r="507" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A507" s="1" t="str">
-        <f>F507 &amp; TEXT(C507,"000")</f>
+        <f t="shared" si="7"/>
         <v>1001003</v>
       </c>
       <c r="B507" s="1" t="s">
@@ -15543,7 +15555,7 @@
     </row>
     <row r="508" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A508" s="1" t="str">
-        <f>F508 &amp; TEXT(C508,"000")</f>
+        <f t="shared" si="7"/>
         <v>1001154</v>
       </c>
       <c r="B508" s="1" t="s">
@@ -15567,7 +15579,7 @@
     </row>
     <row r="509" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A509" s="1" t="str">
-        <f>F509 &amp; TEXT(C509,"000")</f>
+        <f t="shared" si="7"/>
         <v>1001155</v>
       </c>
       <c r="B509" s="1" t="s">
@@ -15591,7 +15603,7 @@
     </row>
     <row r="510" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A510" s="1" t="str">
-        <f>F510 &amp; TEXT(C510,"000")</f>
+        <f t="shared" si="7"/>
         <v>1001010</v>
       </c>
       <c r="B510" s="1" t="s">
@@ -15615,7 +15627,7 @@
     </row>
     <row r="511" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A511" s="1" t="str">
-        <f>F511 &amp; TEXT(C511,"000")</f>
+        <f t="shared" si="7"/>
         <v>1001011</v>
       </c>
       <c r="B511" s="1" t="s">
@@ -15639,7 +15651,7 @@
     </row>
     <row r="512" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A512" s="1" t="str">
-        <f>F512 &amp; TEXT(C512,"000")</f>
+        <f t="shared" si="7"/>
         <v>1001005</v>
       </c>
       <c r="B512" s="1" t="s">
@@ -15663,7 +15675,7 @@
     </row>
     <row r="513" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A513" s="1" t="str">
-        <f>F513 &amp; TEXT(C513,"000")</f>
+        <f t="shared" si="7"/>
         <v>1001004</v>
       </c>
       <c r="B513" s="1" t="s">
@@ -15687,7 +15699,7 @@
     </row>
     <row r="514" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A514" s="1" t="str">
-        <f>F514 &amp; TEXT(C514,"000")</f>
+        <f t="shared" ref="A514:A533" si="8">F514 &amp; TEXT(C514,"000")</f>
         <v>1001018</v>
       </c>
       <c r="B514" s="1" t="s">
@@ -15711,7 +15723,7 @@
     </row>
     <row r="515" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A515" s="1" t="str">
-        <f>F515 &amp; TEXT(C515,"000")</f>
+        <f t="shared" si="8"/>
         <v>1001016</v>
       </c>
       <c r="B515" s="1" t="s">
@@ -15735,7 +15747,7 @@
     </row>
     <row r="516" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A516" s="1" t="str">
-        <f>F516 &amp; TEXT(C516,"000")</f>
+        <f t="shared" si="8"/>
         <v>1001006</v>
       </c>
       <c r="B516" s="1" t="s">
@@ -15759,7 +15771,7 @@
     </row>
     <row r="517" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A517" s="1" t="str">
-        <f>F517 &amp; TEXT(C517,"000")</f>
+        <f t="shared" si="8"/>
         <v>1001008</v>
       </c>
       <c r="B517" s="1" t="s">
@@ -15783,7 +15795,7 @@
     </row>
     <row r="518" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A518" s="1" t="str">
-        <f>F518 &amp; TEXT(C518,"000")</f>
+        <f t="shared" si="8"/>
         <v>1001156</v>
       </c>
       <c r="B518" s="1" t="s">
@@ -15807,7 +15819,7 @@
     </row>
     <row r="519" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A519" s="1" t="str">
-        <f>F519 &amp; TEXT(C519,"000")</f>
+        <f t="shared" si="8"/>
         <v>1001030</v>
       </c>
       <c r="B519" s="1" t="s">
@@ -15831,7 +15843,7 @@
     </row>
     <row r="520" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A520" s="1" t="str">
-        <f>F520 &amp; TEXT(C520,"000")</f>
+        <f t="shared" si="8"/>
         <v>1001022</v>
       </c>
       <c r="B520" s="1" t="s">
@@ -15855,7 +15867,7 @@
     </row>
     <row r="521" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A521" s="1" t="str">
-        <f>F521 &amp; TEXT(C521,"000")</f>
+        <f t="shared" si="8"/>
         <v>1001044</v>
       </c>
       <c r="B521" s="1" t="s">
@@ -15879,7 +15891,7 @@
     </row>
     <row r="522" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A522" s="1" t="str">
-        <f>F522 &amp; TEXT(C522,"000")</f>
+        <f t="shared" si="8"/>
         <v>1001007</v>
       </c>
       <c r="B522" s="1" t="s">
@@ -15903,7 +15915,7 @@
     </row>
     <row r="523" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A523" s="1" t="str">
-        <f>F523 &amp; TEXT(C523,"000")</f>
+        <f t="shared" si="8"/>
         <v>1001033</v>
       </c>
       <c r="B523" s="1" t="s">
@@ -15927,7 +15939,7 @@
     </row>
     <row r="524" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A524" s="1" t="str">
-        <f>F524 &amp; TEXT(C524,"000")</f>
+        <f t="shared" si="8"/>
         <v>1001157</v>
       </c>
       <c r="B524" s="1" t="s">
@@ -15951,7 +15963,7 @@
     </row>
     <row r="525" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A525" s="1" t="str">
-        <f>F525 &amp; TEXT(C525,"000")</f>
+        <f t="shared" si="8"/>
         <v>1001158</v>
       </c>
       <c r="B525" s="1" t="s">
@@ -15975,7 +15987,7 @@
     </row>
     <row r="526" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A526" s="1" t="str">
-        <f>F526 &amp; TEXT(C526,"000")</f>
+        <f t="shared" si="8"/>
         <v>1001039</v>
       </c>
       <c r="B526" s="1" t="s">
@@ -15999,7 +16011,7 @@
     </row>
     <row r="527" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A527" s="1" t="str">
-        <f>F527 &amp; TEXT(C527,"000")</f>
+        <f t="shared" si="8"/>
         <v>1001009</v>
       </c>
       <c r="B527" s="1" t="s">
@@ -16023,7 +16035,7 @@
     </row>
     <row r="528" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A528" s="1" t="str">
-        <f>F528 &amp; TEXT(C528,"000")</f>
+        <f t="shared" si="8"/>
         <v>1001046</v>
       </c>
       <c r="B528" s="1" t="s">
@@ -16047,7 +16059,7 @@
     </row>
     <row r="529" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A529" s="1" t="str">
-        <f>F529 &amp; TEXT(C529,"000")</f>
+        <f t="shared" si="8"/>
         <v>1001028</v>
       </c>
       <c r="B529" s="1" t="s">
@@ -16071,7 +16083,7 @@
     </row>
     <row r="530" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A530" s="1" t="str">
-        <f>F530 &amp; TEXT(C530,"000")</f>
+        <f t="shared" si="8"/>
         <v>1001159</v>
       </c>
       <c r="B530" s="1" t="s">
@@ -16095,7 +16107,7 @@
     </row>
     <row r="531" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A531" s="1" t="str">
-        <f>F531 &amp; TEXT(C531,"000")</f>
+        <f t="shared" si="8"/>
         <v>1001017</v>
       </c>
       <c r="B531" s="1" t="s">
@@ -16119,7 +16131,7 @@
     </row>
     <row r="532" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A532" s="1" t="str">
-        <f>F532 &amp; TEXT(C532,"000")</f>
+        <f t="shared" si="8"/>
         <v>1001160</v>
       </c>
       <c r="B532" s="1" t="s">
@@ -16143,7 +16155,7 @@
     </row>
     <row r="533" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A533" s="1" t="str">
-        <f>F533 &amp; TEXT(C533,"000")</f>
+        <f t="shared" si="8"/>
         <v>1001161</v>
       </c>
       <c r="B533" s="1" t="s">
@@ -16165,9 +16177,66 @@
         <v>748</v>
       </c>
     </row>
-    <row r="534" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="535" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="536" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="534" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A534" s="7" t="str">
+        <f>F534 &amp; TEXT(C534,"000")</f>
+        <v>1010004</v>
+      </c>
+      <c r="B534" s="7" t="s">
+        <v>938</v>
+      </c>
+      <c r="C534" s="7">
+        <v>4</v>
+      </c>
+      <c r="D534" s="3"/>
+      <c r="E534" s="7"/>
+      <c r="F534" s="1">
+        <v>1010</v>
+      </c>
+      <c r="G534" s="1" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="535" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A535" s="7" t="str">
+        <f>F535 &amp; TEXT(C535,"000")</f>
+        <v>1010010</v>
+      </c>
+      <c r="B535" s="7" t="s">
+        <v>939</v>
+      </c>
+      <c r="C535" s="7">
+        <v>10</v>
+      </c>
+      <c r="D535" s="3"/>
+      <c r="E535" s="7"/>
+      <c r="F535" s="1">
+        <v>1010</v>
+      </c>
+      <c r="G535" s="1" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="536" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A536" s="7" t="str">
+        <f>F536 &amp; TEXT(C536,"000")</f>
+        <v>1010031</v>
+      </c>
+      <c r="B536" s="7" t="s">
+        <v>940</v>
+      </c>
+      <c r="C536" s="7">
+        <v>31</v>
+      </c>
+      <c r="D536" s="3"/>
+      <c r="E536" s="7"/>
+      <c r="F536" s="1">
+        <v>1010</v>
+      </c>
+      <c r="G536" s="1" t="s">
+        <v>347</v>
+      </c>
+    </row>
     <row r="537" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="538" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="539" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/backend/data/LigaPremier.xlsx
+++ b/backend/data/LigaPremier.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danyl\Downloads\E\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{17F66FC4-7ED5-4490-97D4-5D9BE67B0E87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F34475F7-B005-4D1D-8E8A-35328689D795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2139" uniqueCount="941">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2143" uniqueCount="943">
   <si>
     <t>Id_jugador</t>
   </si>
@@ -1073,9 +1073,6 @@
     <t>https://cdn.resfu.com/img_data/players/medium/982545.jpg?size=120x&amp;lossy=1</t>
   </si>
   <si>
-    <t>C. Bermúdez</t>
-  </si>
-  <si>
     <t>Lobos ULMX</t>
   </si>
   <si>
@@ -2852,10 +2849,19 @@
     <t>Andres Mares</t>
   </si>
   <si>
-    <t>Jonarhan Gonzales</t>
-  </si>
-  <si>
     <t>Jovanny Zepeda</t>
+  </si>
+  <si>
+    <t>Cristopher Bermudez</t>
+  </si>
+  <si>
+    <t>Jonathan Gonzales</t>
+  </si>
+  <si>
+    <t>Ricardo Contreras</t>
+  </si>
+  <si>
+    <t>Israel Ibarra</t>
   </si>
 </sst>
 </file>
@@ -3154,8 +3160,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{32A8CF84-C284-4FB9-BA95-EA038AE71CB6}" name="Tabla1" displayName="Tabla1" ref="A1:G536" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7">
-  <autoFilter ref="A1:G536" xr:uid="{32A8CF84-C284-4FB9-BA95-EA038AE71CB6}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{32A8CF84-C284-4FB9-BA95-EA038AE71CB6}" name="Tabla1" displayName="Tabla1" ref="A1:G538" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7">
+  <autoFilter ref="A1:G538" xr:uid="{32A8CF84-C284-4FB9-BA95-EA038AE71CB6}">
     <filterColumn colId="6">
       <filters>
         <filter val="Lobos ULMX"/>
@@ -3420,13 +3426,13 @@
         <v>1017001</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>13</v>
@@ -3435,7 +3441,7 @@
         <v>1017</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
@@ -3444,13 +3450,13 @@
         <v>1017101</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="C3" s="1">
         <v>101</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>13</v>
@@ -3459,7 +3465,7 @@
         <v>1017</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
@@ -3468,7 +3474,7 @@
         <v>1017102</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="C4" s="1">
         <v>102</v>
@@ -3483,7 +3489,7 @@
         <v>1017</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
@@ -3492,13 +3498,13 @@
         <v>1017103</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="C5" s="1">
         <v>103</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>20</v>
@@ -3507,7 +3513,7 @@
         <v>1017</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
@@ -3516,13 +3522,13 @@
         <v>1017015</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="C6" s="1">
         <v>15</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>20</v>
@@ -3531,7 +3537,7 @@
         <v>1017</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
@@ -3540,13 +3546,13 @@
         <v>1017004</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C7" s="1">
         <v>4</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>20</v>
@@ -3555,7 +3561,7 @@
         <v>1017</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
@@ -3564,13 +3570,13 @@
         <v>1017013</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="C8" s="1">
         <v>13</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>20</v>
@@ -3579,7 +3585,7 @@
         <v>1017</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
@@ -3588,13 +3594,13 @@
         <v>1017006</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="C9" s="1">
         <v>6</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>20</v>
@@ -3603,7 +3609,7 @@
         <v>1017</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
@@ -3612,13 +3618,13 @@
         <v>1017002</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="C10" s="1">
         <v>2</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>20</v>
@@ -3627,7 +3633,7 @@
         <v>1017</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
@@ -3636,13 +3642,13 @@
         <v>1017104</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="C11" s="1">
         <v>104</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>20</v>
@@ -3651,7 +3657,7 @@
         <v>1017</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
@@ -3660,13 +3666,13 @@
         <v>1017024</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C12" s="1">
         <v>24</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>20</v>
@@ -3675,7 +3681,7 @@
         <v>1017</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
@@ -3684,13 +3690,13 @@
         <v>1017005</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="C13" s="1">
         <v>5</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>20</v>
@@ -3699,7 +3705,7 @@
         <v>1017</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
@@ -3708,13 +3714,13 @@
         <v>1017012</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="C14" s="1">
         <v>12</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>20</v>
@@ -3723,7 +3729,7 @@
         <v>1017</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
@@ -3732,13 +3738,13 @@
         <v>1017023</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="C15" s="1">
         <v>23</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>20</v>
@@ -3747,7 +3753,7 @@
         <v>1017</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
@@ -3756,7 +3762,7 @@
         <v>1017057</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C16" s="1">
         <v>57</v>
@@ -3771,7 +3777,7 @@
         <v>1017</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
@@ -3780,13 +3786,13 @@
         <v>1017106</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C17" s="1">
         <v>106</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>20</v>
@@ -3795,7 +3801,7 @@
         <v>1017</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
@@ -3804,13 +3810,13 @@
         <v>1017019</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="C18" s="1">
         <v>19</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>33</v>
@@ -3819,7 +3825,7 @@
         <v>1017</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
@@ -3828,13 +3834,13 @@
         <v>1017007</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="C19" s="1">
         <v>7</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>33</v>
@@ -3843,7 +3849,7 @@
         <v>1017</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
@@ -3852,13 +3858,13 @@
         <v>1017008</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="C20" s="1">
         <v>8</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>33</v>
@@ -3867,7 +3873,7 @@
         <v>1017</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -3876,13 +3882,13 @@
         <v>1017029</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="C21" s="1">
         <v>29</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>33</v>
@@ -3891,7 +3897,7 @@
         <v>1017</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -3900,13 +3906,13 @@
         <v>1017016</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="C22" s="1">
         <v>16</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>33</v>
@@ -3915,7 +3921,7 @@
         <v>1017</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -3924,13 +3930,13 @@
         <v>1017010</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C23" s="1">
         <v>10</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>33</v>
@@ -3939,7 +3945,7 @@
         <v>1017</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -3948,13 +3954,13 @@
         <v>1017021</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="C24" s="1">
         <v>21</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>33</v>
@@ -3963,7 +3969,7 @@
         <v>1017</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -3972,7 +3978,7 @@
         <v>1017067</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="C25" s="1">
         <v>67</v>
@@ -3987,7 +3993,7 @@
         <v>1017</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -3996,13 +4002,13 @@
         <v>1017011</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="C26" s="1">
         <v>11</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>58</v>
@@ -4011,7 +4017,7 @@
         <v>1017</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -4020,13 +4026,13 @@
         <v>1017113</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="C27" s="1">
         <v>113</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>58</v>
@@ -4035,7 +4041,7 @@
         <v>1017</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -4044,13 +4050,13 @@
         <v>1017009</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="C28" s="1">
         <v>9</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>58</v>
@@ -4059,7 +4065,7 @@
         <v>1017</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -4068,13 +4074,13 @@
         <v>1017018</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="C29" s="1">
         <v>18</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>58</v>
@@ -4083,7 +4089,7 @@
         <v>1017</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -4092,13 +4098,13 @@
         <v>1017026</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="C30" s="1">
         <v>26</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>58</v>
@@ -4107,7 +4113,7 @@
         <v>1017</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -4116,13 +4122,13 @@
         <v>1016001</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C31" s="1">
         <v>1</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>13</v>
@@ -4131,7 +4137,7 @@
         <v>1016</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -4140,7 +4146,7 @@
         <v>1016012</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C32" s="1">
         <v>12</v>
@@ -4155,7 +4161,7 @@
         <v>1016</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -4164,7 +4170,7 @@
         <v>1016101</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="C33" s="1">
         <v>101</v>
@@ -4179,7 +4185,7 @@
         <v>1016</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -4188,7 +4194,7 @@
         <v>1016102</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C34" s="1">
         <v>102</v>
@@ -4203,7 +4209,7 @@
         <v>1016</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -4212,7 +4218,7 @@
         <v>1016103</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C35" s="1">
         <v>103</v>
@@ -4227,7 +4233,7 @@
         <v>1016</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -4236,13 +4242,13 @@
         <v>1016004</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C36" s="1">
         <v>4</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>20</v>
@@ -4251,7 +4257,7 @@
         <v>1016</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -4260,13 +4266,13 @@
         <v>1016005</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C37" s="1">
         <v>5</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>20</v>
@@ -4275,7 +4281,7 @@
         <v>1016</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -4284,13 +4290,13 @@
         <v>1016104</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C38" s="1">
         <v>104</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>20</v>
@@ -4299,7 +4305,7 @@
         <v>1016</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -4308,13 +4314,13 @@
         <v>1016003</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="C39" s="1">
         <v>3</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>20</v>
@@ -4323,7 +4329,7 @@
         <v>1016</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -4332,13 +4338,13 @@
         <v>1016052</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="C40" s="1">
         <v>52</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>20</v>
@@ -4347,7 +4353,7 @@
         <v>1016</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -4356,13 +4362,13 @@
         <v>1016020</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="C41" s="1">
         <v>20</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>20</v>
@@ -4371,7 +4377,7 @@
         <v>1016</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -4380,13 +4386,13 @@
         <v>1016002</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C42" s="1">
         <v>2</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>20</v>
@@ -4395,7 +4401,7 @@
         <v>1016</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -4404,7 +4410,7 @@
         <v>1016015</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="C43" s="1">
         <v>15</v>
@@ -4419,7 +4425,7 @@
         <v>1016</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -4428,7 +4434,7 @@
         <v>1016037</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="C44" s="1">
         <v>37</v>
@@ -4443,7 +4449,7 @@
         <v>1016</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -4452,13 +4458,13 @@
         <v>1016033</v>
       </c>
       <c r="B45" s="1" t="s">
+        <v>835</v>
+      </c>
+      <c r="C45" s="1">
+        <v>33</v>
+      </c>
+      <c r="D45" s="3" t="s">
         <v>836</v>
-      </c>
-      <c r="C45" s="1">
-        <v>33</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>837</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>20</v>
@@ -4467,7 +4473,7 @@
         <v>1016</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -4476,13 +4482,13 @@
         <v>1016106</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C46" s="1">
         <v>106</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>20</v>
@@ -4491,7 +4497,7 @@
         <v>1016</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -4500,13 +4506,13 @@
         <v>1016107</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C47" s="1">
         <v>107</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>20</v>
@@ -4515,7 +4521,7 @@
         <v>1016</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -4524,13 +4530,13 @@
         <v>1016108</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="C48" s="1">
         <v>108</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>33</v>
@@ -4539,7 +4545,7 @@
         <v>1016</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -4548,13 +4554,13 @@
         <v>1016010</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C49" s="1">
         <v>10</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>33</v>
@@ -4563,7 +4569,7 @@
         <v>1016</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -4572,13 +4578,13 @@
         <v>1016024</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C50" s="1">
         <v>24</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>33</v>
@@ -4587,7 +4593,7 @@
         <v>1016</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -4596,13 +4602,13 @@
         <v>1016007</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C51" s="1">
         <v>7</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>33</v>
@@ -4611,7 +4617,7 @@
         <v>1016</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -4620,7 +4626,7 @@
         <v>1016023</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="C52" s="1">
         <v>23</v>
@@ -4635,7 +4641,7 @@
         <v>1016</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -4644,13 +4650,13 @@
         <v>1016053</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C53" s="1">
         <v>53</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>33</v>
@@ -4659,7 +4665,7 @@
         <v>1016</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -4668,7 +4674,7 @@
         <v>1016009</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="C54" s="1">
         <v>9</v>
@@ -4683,7 +4689,7 @@
         <v>1016</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -4692,7 +4698,7 @@
         <v>1016006</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C55" s="1">
         <v>6</v>
@@ -4707,7 +4713,7 @@
         <v>1016</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -4716,7 +4722,7 @@
         <v>1016019</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="C56" s="1">
         <v>19</v>
@@ -4731,7 +4737,7 @@
         <v>1016</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -4740,13 +4746,13 @@
         <v>1016016</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="C57" s="1">
         <v>16</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>33</v>
@@ -4755,7 +4761,7 @@
         <v>1016</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -4764,7 +4770,7 @@
         <v>1016018</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="C58" s="1">
         <v>18</v>
@@ -4779,7 +4785,7 @@
         <v>1016</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -4788,7 +4794,7 @@
         <v>1016025</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="C59" s="1">
         <v>25</v>
@@ -4803,7 +4809,7 @@
         <v>1016</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -4812,13 +4818,13 @@
         <v>1016017</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="C60" s="1">
         <v>17</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>33</v>
@@ -4827,7 +4833,7 @@
         <v>1016</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -4836,7 +4842,7 @@
         <v>1016026</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="C61" s="1">
         <v>26</v>
@@ -4851,7 +4857,7 @@
         <v>1016</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -4860,7 +4866,7 @@
         <v>1016038</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="C62" s="1">
         <v>38</v>
@@ -4875,7 +4881,7 @@
         <v>1016</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -4884,7 +4890,7 @@
         <v>1016057</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="C63" s="1">
         <v>57</v>
@@ -4899,7 +4905,7 @@
         <v>1016</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -4908,13 +4914,13 @@
         <v>1016109</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="C64" s="1">
         <v>109</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>33</v>
@@ -4923,7 +4929,7 @@
         <v>1016</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -4932,13 +4938,13 @@
         <v>1016110</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C65" s="1">
         <v>110</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>33</v>
@@ -4947,7 +4953,7 @@
         <v>1016</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -4956,7 +4962,7 @@
         <v>1016111</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="C66" s="1">
         <v>111</v>
@@ -4971,7 +4977,7 @@
         <v>1016</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -4980,7 +4986,7 @@
         <v>1016112</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="C67" s="1">
         <v>112</v>
@@ -4995,7 +5001,7 @@
         <v>1016</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -5004,7 +5010,7 @@
         <v>1016113</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="C68" s="1">
         <v>113</v>
@@ -5019,7 +5025,7 @@
         <v>1016</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -5028,7 +5034,7 @@
         <v>1016114</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="C69" s="1">
         <v>114</v>
@@ -5043,7 +5049,7 @@
         <v>1016</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -5052,13 +5058,13 @@
         <v>1016011</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="C70" s="1">
         <v>11</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>58</v>
@@ -5067,7 +5073,7 @@
         <v>1016</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -5076,13 +5082,13 @@
         <v>1016008</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="C71" s="1">
         <v>8</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>58</v>
@@ -5091,7 +5097,7 @@
         <v>1016</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -5100,7 +5106,7 @@
         <v>1016115</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="C72" s="1">
         <v>115</v>
@@ -5115,7 +5121,7 @@
         <v>1016</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -5124,13 +5130,13 @@
         <v>1016055</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="C73" s="1">
         <v>55</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>58</v>
@@ -5139,7 +5145,7 @@
         <v>1016</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -5148,7 +5154,7 @@
         <v>1016116</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="C74" s="1">
         <v>116</v>
@@ -5163,7 +5169,7 @@
         <v>1016</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -5172,7 +5178,7 @@
         <v>1016117</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="C75" s="1">
         <v>117</v>
@@ -5187,7 +5193,7 @@
         <v>1016</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -5196,7 +5202,7 @@
         <v>1014146</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C76" s="1">
         <v>146</v>
@@ -5211,7 +5217,7 @@
         <v>1014</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -5220,13 +5226,13 @@
         <v>1014001</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C77" s="1">
         <v>1</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>13</v>
@@ -5235,7 +5241,7 @@
         <v>1014</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -5244,13 +5250,13 @@
         <v>1014031</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C78" s="1">
         <v>31</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>13</v>
@@ -5259,7 +5265,7 @@
         <v>1014</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -5268,13 +5274,13 @@
         <v>1014012</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C79" s="1">
         <v>12</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>20</v>
@@ -5283,7 +5289,7 @@
         <v>1014</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -5292,13 +5298,13 @@
         <v>1014023</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C80" s="1">
         <v>23</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>20</v>
@@ -5307,7 +5313,7 @@
         <v>1014</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -5316,13 +5322,13 @@
         <v>1014004</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C81" s="1">
         <v>4</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>20</v>
@@ -5331,7 +5337,7 @@
         <v>1014</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -5340,13 +5346,13 @@
         <v>1014005</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C82" s="1">
         <v>5</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>20</v>
@@ -5355,7 +5361,7 @@
         <v>1014</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -5364,13 +5370,13 @@
         <v>1014003</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C83" s="1">
         <v>3</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>20</v>
@@ -5379,7 +5385,7 @@
         <v>1014</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="84" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -5388,13 +5394,13 @@
         <v>1014006</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C84" s="1">
         <v>6</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>20</v>
@@ -5403,7 +5409,7 @@
         <v>1014</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="85" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -5412,13 +5418,13 @@
         <v>1014147</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C85" s="1">
         <v>147</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>20</v>
@@ -5427,7 +5433,7 @@
         <v>1014</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -5436,13 +5442,13 @@
         <v>1014024</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C86" s="1">
         <v>24</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>20</v>
@@ -5451,7 +5457,7 @@
         <v>1014</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="87" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -5460,7 +5466,7 @@
         <v>1014018</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C87" s="1">
         <v>18</v>
@@ -5475,7 +5481,7 @@
         <v>1014</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="88" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -5484,13 +5490,13 @@
         <v>1014063</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C88" s="1">
         <v>63</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>20</v>
@@ -5499,7 +5505,7 @@
         <v>1014</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -5508,13 +5514,13 @@
         <v>1014148</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C89" s="1">
         <v>148</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>20</v>
@@ -5523,7 +5529,7 @@
         <v>1014</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="90" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -5532,13 +5538,13 @@
         <v>1014002</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C90" s="1">
         <v>2</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>33</v>
@@ -5547,7 +5553,7 @@
         <v>1014</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="91" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -5556,13 +5562,13 @@
         <v>1014010</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C91" s="1">
         <v>10</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>33</v>
@@ -5571,7 +5577,7 @@
         <v>1014</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -5580,13 +5586,13 @@
         <v>1014017</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C92" s="1">
         <v>17</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>33</v>
@@ -5595,7 +5601,7 @@
         <v>1014</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -5604,13 +5610,13 @@
         <v>1014014</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C93" s="1">
         <v>14</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>33</v>
@@ -5619,7 +5625,7 @@
         <v>1014</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -5628,13 +5634,13 @@
         <v>1014020</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C94" s="1">
         <v>20</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>33</v>
@@ -5643,7 +5649,7 @@
         <v>1014</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -5652,13 +5658,13 @@
         <v>1014058</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C95" s="1">
         <v>58</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>33</v>
@@ -5667,7 +5673,7 @@
         <v>1014</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="96" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -5676,7 +5682,7 @@
         <v>1014149</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C96" s="1">
         <v>149</v>
@@ -5691,7 +5697,7 @@
         <v>1014</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="97" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -5700,13 +5706,13 @@
         <v>1014016</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C97" s="1">
         <v>16</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>33</v>
@@ -5715,7 +5721,7 @@
         <v>1014</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -5724,13 +5730,13 @@
         <v>1014027</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C98" s="1">
         <v>27</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>33</v>
@@ -5739,7 +5745,7 @@
         <v>1014</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="99" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -5748,7 +5754,7 @@
         <v>1014015</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="C99" s="1">
         <v>15</v>
@@ -5763,7 +5769,7 @@
         <v>1014</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="100" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -5772,7 +5778,7 @@
         <v>1014150</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C100" s="1">
         <v>150</v>
@@ -5787,7 +5793,7 @@
         <v>1014</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="101" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -5796,13 +5802,13 @@
         <v>1014072</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C101" s="1">
         <v>72</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>33</v>
@@ -5811,7 +5817,7 @@
         <v>1014</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -5820,13 +5826,13 @@
         <v>1014052</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="C102" s="1">
         <v>52</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>33</v>
@@ -5835,7 +5841,7 @@
         <v>1014</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="103" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -5844,7 +5850,7 @@
         <v>1014008</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C103" s="1">
         <v>8</v>
@@ -5859,7 +5865,7 @@
         <v>1014</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="104" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -5868,13 +5874,13 @@
         <v>1014026</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C104" s="1">
         <v>26</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>33</v>
@@ -5883,7 +5889,7 @@
         <v>1014</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="105" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -5898,7 +5904,7 @@
         <v>19</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>33</v>
@@ -5907,7 +5913,7 @@
         <v>1014</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="106" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -5916,13 +5922,13 @@
         <v>1014059</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C106" s="1">
         <v>59</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>58</v>
@@ -5931,7 +5937,7 @@
         <v>1014</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="107" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -5940,13 +5946,13 @@
         <v>1014007</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="C107" s="1">
         <v>7</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>58</v>
@@ -5955,7 +5961,7 @@
         <v>1014</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="108" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -5964,13 +5970,13 @@
         <v>1014003</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C108" s="1">
         <v>3</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>58</v>
@@ -5979,7 +5985,7 @@
         <v>1014</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="109" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -5988,13 +5994,13 @@
         <v>1014033</v>
       </c>
       <c r="B109" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="C109" s="1">
+        <v>33</v>
+      </c>
+      <c r="D109" s="2" t="s">
         <v>688</v>
-      </c>
-      <c r="C109" s="1">
-        <v>33</v>
-      </c>
-      <c r="D109" s="2" t="s">
-        <v>689</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>58</v>
@@ -6003,7 +6009,7 @@
         <v>1014</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="110" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -6012,7 +6018,7 @@
         <v>1014056</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C110" s="1">
         <v>56</v>
@@ -6027,7 +6033,7 @@
         <v>1014</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="111" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -6036,13 +6042,13 @@
         <v>1014035</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C111" s="1">
         <v>35</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>58</v>
@@ -6051,7 +6057,7 @@
         <v>1014</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="112" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -6060,7 +6066,7 @@
         <v>1014150</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C112" s="1">
         <v>150</v>
@@ -6075,7 +6081,7 @@
         <v>1014</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="113" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -6084,13 +6090,13 @@
         <v>1013012</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C113" s="1">
         <v>12</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>13</v>
@@ -6099,7 +6105,7 @@
         <v>1013</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="114" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -6108,7 +6114,7 @@
         <v>1013022</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C114" s="1">
         <v>22</v>
@@ -6123,7 +6129,7 @@
         <v>1013</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="115" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -6132,13 +6138,13 @@
         <v>1013004</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C115" s="1">
         <v>4</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>20</v>
@@ -6147,7 +6153,7 @@
         <v>1013</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="116" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -6156,13 +6162,13 @@
         <v>1013028</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C116" s="1">
         <v>28</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>20</v>
@@ -6171,7 +6177,7 @@
         <v>1013</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="117" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -6180,7 +6186,7 @@
         <v>1013020</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C117" s="1">
         <v>20</v>
@@ -6195,7 +6201,7 @@
         <v>1013</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="118" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -6204,13 +6210,13 @@
         <v>1013024</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C118" s="1">
         <v>24</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>20</v>
@@ -6219,7 +6225,7 @@
         <v>1013</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="119" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -6228,13 +6234,13 @@
         <v>1013005</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C119" s="1">
         <v>5</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>20</v>
@@ -6243,7 +6249,7 @@
         <v>1013</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="120" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -6252,13 +6258,13 @@
         <v>1013014</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C120" s="1">
         <v>14</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>20</v>
@@ -6267,7 +6273,7 @@
         <v>1013</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="121" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -6276,13 +6282,13 @@
         <v>1013006</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C121" s="1">
         <v>6</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>20</v>
@@ -6291,7 +6297,7 @@
         <v>1013</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="122" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -6300,13 +6306,13 @@
         <v>1013010</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C122" s="1">
         <v>10</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>33</v>
@@ -6315,7 +6321,7 @@
         <v>1013</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="123" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -6324,13 +6330,13 @@
         <v>1013008</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C123" s="1">
         <v>8</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>33</v>
@@ -6339,7 +6345,7 @@
         <v>1013</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="124" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -6348,13 +6354,13 @@
         <v>1013007</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C124" s="1">
         <v>7</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>33</v>
@@ -6363,7 +6369,7 @@
         <v>1013</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="125" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -6372,13 +6378,13 @@
         <v>1013023</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C125" s="1">
         <v>23</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>33</v>
@@ -6387,7 +6393,7 @@
         <v>1013</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="126" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -6396,13 +6402,13 @@
         <v>1013018</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C126" s="1">
         <v>18</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>33</v>
@@ -6411,7 +6417,7 @@
         <v>1013</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="127" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -6420,13 +6426,13 @@
         <v>1013011</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C127" s="1">
         <v>11</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E127" s="1" t="s">
         <v>33</v>
@@ -6435,7 +6441,7 @@
         <v>1013</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="128" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -6444,7 +6450,7 @@
         <v>1013021</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C128" s="1">
         <v>21</v>
@@ -6459,7 +6465,7 @@
         <v>1013</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="129" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -6468,7 +6474,7 @@
         <v>1013016</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C129" s="1">
         <v>16</v>
@@ -6483,7 +6489,7 @@
         <v>1013</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="130" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -6492,7 +6498,7 @@
         <v>1013031</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C130" s="1">
         <v>31</v>
@@ -6507,7 +6513,7 @@
         <v>1013</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="131" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -6516,13 +6522,13 @@
         <v>1013015</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C131" s="1">
         <v>15</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>33</v>
@@ -6531,7 +6537,7 @@
         <v>1013</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -6540,7 +6546,7 @@
         <v>1013013</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C132" s="1">
         <v>13</v>
@@ -6555,7 +6561,7 @@
         <v>1013</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="133" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -6564,13 +6570,13 @@
         <v>1013019</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C133" s="1">
         <v>19</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>33</v>
@@ -6579,7 +6585,7 @@
         <v>1013</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="134" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -6588,13 +6594,13 @@
         <v>1013002</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C134" s="1">
         <v>2</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E134" s="1" t="s">
         <v>58</v>
@@ -6603,7 +6609,7 @@
         <v>1013</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="135" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -6612,13 +6618,13 @@
         <v>1013030</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C135" s="1">
         <v>30</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>58</v>
@@ -6627,7 +6633,7 @@
         <v>1013</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="136" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -6636,7 +6642,7 @@
         <v>1013029</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C136" s="1">
         <v>29</v>
@@ -6651,7 +6657,7 @@
         <v>1013</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="137" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -6660,13 +6666,13 @@
         <v>1013017</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C137" s="1">
         <v>17</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>58</v>
@@ -6675,7 +6681,7 @@
         <v>1013</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="138" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -6684,13 +6690,13 @@
         <v>1013124</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C138" s="1">
         <v>124</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E138" s="1" t="s">
         <v>58</v>
@@ -6699,7 +6705,7 @@
         <v>1013</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="139" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -8268,7 +8274,7 @@
         <v>1010008</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>346</v>
+        <v>941</v>
       </c>
       <c r="C204" s="1">
         <v>8</v>
@@ -8283,7 +8289,7 @@
         <v>1010</v>
       </c>
       <c r="G204" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="205" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8292,13 +8298,13 @@
         <v>1010025</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C205" s="1">
         <v>25</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E205" s="1" t="s">
         <v>13</v>
@@ -8307,7 +8313,7 @@
         <v>1010</v>
       </c>
       <c r="G205" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="206" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8316,13 +8322,13 @@
         <v>1010033</v>
       </c>
       <c r="B206" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="C206" s="1">
+        <v>33</v>
+      </c>
+      <c r="D206" s="2" t="s">
         <v>350</v>
-      </c>
-      <c r="C206" s="1">
-        <v>33</v>
-      </c>
-      <c r="D206" s="2" t="s">
-        <v>351</v>
       </c>
       <c r="E206" s="1" t="s">
         <v>13</v>
@@ -8331,7 +8337,7 @@
         <v>1010</v>
       </c>
       <c r="G206" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="207" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8340,13 +8346,13 @@
         <v>1010020</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C207" s="1">
         <v>20</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E207" s="1" t="s">
         <v>20</v>
@@ -8355,7 +8361,7 @@
         <v>1010</v>
       </c>
       <c r="G207" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="208" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8364,13 +8370,13 @@
         <v>1010003</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C208" s="1">
         <v>3</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E208" s="1" t="s">
         <v>20</v>
@@ -8379,7 +8385,7 @@
         <v>1010</v>
       </c>
       <c r="G208" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="209" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8388,13 +8394,13 @@
         <v>1010007</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C209" s="1">
         <v>7</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E209" s="1" t="s">
         <v>20</v>
@@ -8403,7 +8409,7 @@
         <v>1010</v>
       </c>
       <c r="G209" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="210" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8412,13 +8418,13 @@
         <v>1010023</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C210" s="1">
         <v>23</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E210" s="1" t="s">
         <v>20</v>
@@ -8427,7 +8433,7 @@
         <v>1010</v>
       </c>
       <c r="G210" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="211" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8436,13 +8442,13 @@
         <v>1010017</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C211" s="1">
         <v>17</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E211" s="1" t="s">
         <v>20</v>
@@ -8451,7 +8457,7 @@
         <v>1010</v>
       </c>
       <c r="G211" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="212" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8460,13 +8466,13 @@
         <v>1010122</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C212" s="1">
         <v>122</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E212" s="1" t="s">
         <v>20</v>
@@ -8475,7 +8481,7 @@
         <v>1010</v>
       </c>
       <c r="G212" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="213" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8484,13 +8490,13 @@
         <v>1010022</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C213" s="1">
         <v>22</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E213" s="1" t="s">
         <v>20</v>
@@ -8499,7 +8505,7 @@
         <v>1010</v>
       </c>
       <c r="G213" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="214" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8508,13 +8514,13 @@
         <v>1010013</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C214" s="1">
         <v>13</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E214" s="1" t="s">
         <v>20</v>
@@ -8523,7 +8529,7 @@
         <v>1010</v>
       </c>
       <c r="G214" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="215" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8532,13 +8538,13 @@
         <v>1010005</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C215" s="1">
         <v>5</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E215" s="1" t="s">
         <v>33</v>
@@ -8547,7 +8553,7 @@
         <v>1010</v>
       </c>
       <c r="G215" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="216" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8562,7 +8568,7 @@
         <v>12</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E216" s="1" t="s">
         <v>33</v>
@@ -8571,7 +8577,7 @@
         <v>1010</v>
       </c>
       <c r="G216" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="217" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8580,13 +8586,13 @@
         <v>1010012</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C217" s="1">
         <v>12</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E217" s="1" t="s">
         <v>33</v>
@@ -8595,7 +8601,7 @@
         <v>1010</v>
       </c>
       <c r="G217" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="218" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8604,13 +8610,13 @@
         <v>1010018</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C218" s="1">
         <v>18</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E218" s="1" t="s">
         <v>33</v>
@@ -8619,7 +8625,7 @@
         <v>1010</v>
       </c>
       <c r="G218" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="219" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8628,13 +8634,13 @@
         <v>1010019</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C219" s="1">
         <v>19</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E219" s="1" t="s">
         <v>33</v>
@@ -8643,7 +8649,7 @@
         <v>1010</v>
       </c>
       <c r="G219" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="220" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8652,13 +8658,13 @@
         <v>1010014</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C220" s="1">
         <v>14</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E220" s="1" t="s">
         <v>33</v>
@@ -8667,7 +8673,7 @@
         <v>1010</v>
       </c>
       <c r="G220" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="221" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8676,13 +8682,13 @@
         <v>1010009</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C221" s="1">
         <v>9</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E221" s="1" t="s">
         <v>33</v>
@@ -8691,7 +8697,7 @@
         <v>1010</v>
       </c>
       <c r="G221" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="222" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8700,13 +8706,13 @@
         <v>1010030</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C222" s="1">
         <v>30</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E222" s="1" t="s">
         <v>33</v>
@@ -8715,7 +8721,7 @@
         <v>1010</v>
       </c>
       <c r="G222" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="223" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8724,7 +8730,7 @@
         <v>1010024</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C223" s="1">
         <v>24</v>
@@ -8739,7 +8745,7 @@
         <v>1010</v>
       </c>
       <c r="G223" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="224" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8748,7 +8754,7 @@
         <v>1010027</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C224" s="1">
         <v>27</v>
@@ -8763,7 +8769,7 @@
         <v>1010</v>
       </c>
       <c r="G224" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="225" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8778,7 +8784,7 @@
         <v>21</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E225" s="1" t="s">
         <v>58</v>
@@ -8787,7 +8793,7 @@
         <v>1010</v>
       </c>
       <c r="G225" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="226" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8796,13 +8802,13 @@
         <v>1010011</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C226" s="1">
         <v>11</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E226" s="1" t="s">
         <v>58</v>
@@ -8811,7 +8817,7 @@
         <v>1010</v>
       </c>
       <c r="G226" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="227" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8820,13 +8826,13 @@
         <v>1010016</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C227" s="1">
         <v>16</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E227" s="1" t="s">
         <v>58</v>
@@ -8835,7 +8841,7 @@
         <v>1010</v>
       </c>
       <c r="G227" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="228" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8844,13 +8850,13 @@
         <v>1010036</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C228" s="1">
         <v>36</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E228" s="1" t="s">
         <v>58</v>
@@ -8859,7 +8865,7 @@
         <v>1010</v>
       </c>
       <c r="G228" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="229" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8868,13 +8874,13 @@
         <v>1010029</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C229" s="1">
         <v>29</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E229" s="1" t="s">
         <v>58</v>
@@ -8883,7 +8889,7 @@
         <v>1010</v>
       </c>
       <c r="G229" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="230" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8892,13 +8898,13 @@
         <v>1010123</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C230" s="1">
         <v>123</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E230" s="1" t="s">
         <v>58</v>
@@ -8907,7 +8913,7 @@
         <v>1010</v>
       </c>
       <c r="G230" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="231" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -9540,13 +9546,13 @@
         <v>1008001</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C257" s="1">
         <v>1</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E257" s="1" t="s">
         <v>13</v>
@@ -9555,7 +9561,7 @@
         <v>1008</v>
       </c>
       <c r="G257" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="258" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -9564,13 +9570,13 @@
         <v>1008023</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C258" s="1">
         <v>23</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E258" s="1" t="s">
         <v>13</v>
@@ -9579,7 +9585,7 @@
         <v>1008</v>
       </c>
       <c r="G258" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="259" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -9588,13 +9594,13 @@
         <v>1008070</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C259" s="1">
         <v>70</v>
       </c>
       <c r="D259" s="2" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E259" s="1" t="s">
         <v>13</v>
@@ -9603,7 +9609,7 @@
         <v>1008</v>
       </c>
       <c r="G259" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="260" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -9612,13 +9618,13 @@
         <v>1008003</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C260" s="1">
         <v>3</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E260" s="1" t="s">
         <v>20</v>
@@ -9627,7 +9633,7 @@
         <v>1008</v>
       </c>
       <c r="G260" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="261" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -9636,13 +9642,13 @@
         <v>1008022</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C261" s="1">
         <v>22</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="E261" s="1" t="s">
         <v>20</v>
@@ -9651,7 +9657,7 @@
         <v>1008</v>
       </c>
       <c r="G261" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="262" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -9660,13 +9666,13 @@
         <v>1008002</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C262" s="1">
         <v>2</v>
       </c>
       <c r="D262" s="2" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E262" s="1" t="s">
         <v>20</v>
@@ -9675,7 +9681,7 @@
         <v>1008</v>
       </c>
       <c r="G262" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="263" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -9684,13 +9690,13 @@
         <v>1008020</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C263" s="1">
         <v>20</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="E263" s="1" t="s">
         <v>20</v>
@@ -9699,7 +9705,7 @@
         <v>1008</v>
       </c>
       <c r="G263" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="264" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -9708,13 +9714,13 @@
         <v>1008006</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C264" s="1">
         <v>6</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="E264" s="1" t="s">
         <v>20</v>
@@ -9723,7 +9729,7 @@
         <v>1008</v>
       </c>
       <c r="G264" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="265" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -9732,13 +9738,13 @@
         <v>1008004</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C265" s="1">
         <v>4</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E265" s="1" t="s">
         <v>20</v>
@@ -9747,7 +9753,7 @@
         <v>1008</v>
       </c>
       <c r="G265" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="266" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -9756,13 +9762,13 @@
         <v>1008015</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C266" s="1">
         <v>15</v>
       </c>
       <c r="D266" s="2" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E266" s="1" t="s">
         <v>20</v>
@@ -9771,7 +9777,7 @@
         <v>1008</v>
       </c>
       <c r="G266" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="267" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -9780,13 +9786,13 @@
         <v>1008061</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C267" s="1">
         <v>61</v>
       </c>
       <c r="D267" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E267" s="1" t="s">
         <v>20</v>
@@ -9795,7 +9801,7 @@
         <v>1008</v>
       </c>
       <c r="G267" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="268" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -9804,7 +9810,7 @@
         <v>1008067</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C268" s="1">
         <v>67</v>
@@ -9819,7 +9825,7 @@
         <v>1008</v>
       </c>
       <c r="G268" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="269" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -9828,13 +9834,13 @@
         <v>1008001</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C269" s="1">
         <v>1</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E269" s="1" t="s">
         <v>33</v>
@@ -9843,7 +9849,7 @@
         <v>1008</v>
       </c>
       <c r="G269" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="270" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -9852,13 +9858,13 @@
         <v>1008017</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C270" s="1">
         <v>17</v>
       </c>
       <c r="D270" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E270" s="1" t="s">
         <v>33</v>
@@ -9867,7 +9873,7 @@
         <v>1008</v>
       </c>
       <c r="G270" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="271" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -9876,13 +9882,13 @@
         <v>1008008</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C271" s="1">
         <v>8</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="E271" s="1" t="s">
         <v>33</v>
@@ -9891,7 +9897,7 @@
         <v>1008</v>
       </c>
       <c r="G271" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="272" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -9900,13 +9906,13 @@
         <v>1008011</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C272" s="1">
         <v>11</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E272" s="1" t="s">
         <v>33</v>
@@ -9915,7 +9921,7 @@
         <v>1008</v>
       </c>
       <c r="G272" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="273" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -9924,13 +9930,13 @@
         <v>1008005</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C273" s="1">
         <v>5</v>
       </c>
       <c r="D273" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E273" s="1" t="s">
         <v>33</v>
@@ -9939,7 +9945,7 @@
         <v>1008</v>
       </c>
       <c r="G273" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="274" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -9948,13 +9954,13 @@
         <v>1008007</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C274" s="1">
         <v>7</v>
       </c>
       <c r="D274" s="2" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E274" s="1" t="s">
         <v>33</v>
@@ -9963,7 +9969,7 @@
         <v>1008</v>
       </c>
       <c r="G274" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="275" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -9987,7 +9993,7 @@
         <v>1008</v>
       </c>
       <c r="G275" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="276" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -9996,13 +10002,13 @@
         <v>1008016</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C276" s="1">
         <v>16</v>
       </c>
       <c r="D276" s="2" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E276" s="1" t="s">
         <v>33</v>
@@ -10011,7 +10017,7 @@
         <v>1008</v>
       </c>
       <c r="G276" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="277" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -10020,13 +10026,13 @@
         <v>1008134</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C277" s="1">
         <v>134</v>
       </c>
       <c r="D277" s="2" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="E277" s="1" t="s">
         <v>33</v>
@@ -10035,7 +10041,7 @@
         <v>1008</v>
       </c>
       <c r="G277" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="278" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -10044,13 +10050,13 @@
         <v>1008013</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C278" s="1">
         <v>13</v>
       </c>
       <c r="D278" s="2" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="E278" s="1" t="s">
         <v>33</v>
@@ -10059,7 +10065,7 @@
         <v>1008</v>
       </c>
       <c r="G278" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="279" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -10068,13 +10074,13 @@
         <v>1008014</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C279" s="1">
         <v>14</v>
       </c>
       <c r="D279" s="2" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E279" s="1" t="s">
         <v>33</v>
@@ -10083,7 +10089,7 @@
         <v>1008</v>
       </c>
       <c r="G279" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="280" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -10092,13 +10098,13 @@
         <v>1008012</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C280" s="1">
         <v>12</v>
       </c>
       <c r="D280" s="2" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="E280" s="1" t="s">
         <v>33</v>
@@ -10107,7 +10113,7 @@
         <v>1008</v>
       </c>
       <c r="G280" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="281" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -10116,13 +10122,13 @@
         <v>1008019</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C281" s="1">
         <v>19</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E281" s="1" t="s">
         <v>33</v>
@@ -10131,7 +10137,7 @@
         <v>1008</v>
       </c>
       <c r="G281" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="282" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -10140,13 +10146,13 @@
         <v>1008018</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C282" s="1">
         <v>18</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E282" s="1" t="s">
         <v>33</v>
@@ -10155,7 +10161,7 @@
         <v>1008</v>
       </c>
       <c r="G282" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="283" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -10164,13 +10170,13 @@
         <v>1008135</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C283" s="1">
         <v>135</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="E283" s="1" t="s">
         <v>33</v>
@@ -10179,7 +10185,7 @@
         <v>1008</v>
       </c>
       <c r="G283" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="284" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -10188,13 +10194,13 @@
         <v>1008027</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C284" s="1">
         <v>27</v>
       </c>
       <c r="D284" s="2" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E284" s="1" t="s">
         <v>58</v>
@@ -10203,7 +10209,7 @@
         <v>1008</v>
       </c>
       <c r="G284" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="285" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -10212,13 +10218,13 @@
         <v>1008136</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C285" s="1">
         <v>136</v>
       </c>
       <c r="D285" s="2" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E285" s="1" t="s">
         <v>58</v>
@@ -10227,7 +10233,7 @@
         <v>1008</v>
       </c>
       <c r="G285" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="286" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -10236,13 +10242,13 @@
         <v>1008010</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C286" s="1">
         <v>10</v>
       </c>
       <c r="D286" s="2" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E286" s="1" t="s">
         <v>58</v>
@@ -10251,7 +10257,7 @@
         <v>1008</v>
       </c>
       <c r="G286" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="287" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -10260,13 +10266,13 @@
         <v>1008137</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C287" s="1">
         <v>137</v>
       </c>
       <c r="D287" s="2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="E287" s="1" t="s">
         <v>58</v>
@@ -10275,7 +10281,7 @@
         <v>1008</v>
       </c>
       <c r="G287" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="288" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -10284,13 +10290,13 @@
         <v>1008138</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C288" s="1">
         <v>138</v>
       </c>
       <c r="D288" s="2" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="E288" s="1" t="s">
         <v>58</v>
@@ -10299,7 +10305,7 @@
         <v>1008</v>
       </c>
       <c r="G288" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="289" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -10314,7 +10320,7 @@
         <v>9</v>
       </c>
       <c r="D289" s="2" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="E289" s="1" t="s">
         <v>58</v>
@@ -10323,7 +10329,7 @@
         <v>1008</v>
       </c>
       <c r="G289" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="290" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -10332,13 +10338,13 @@
         <v>1008029</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C290" s="1">
         <v>29</v>
       </c>
       <c r="D290" s="2" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="E290" s="1" t="s">
         <v>58</v>
@@ -10347,7 +10353,7 @@
         <v>1008</v>
       </c>
       <c r="G290" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="291" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -10356,13 +10362,13 @@
         <v>1008025</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C291" s="1">
         <v>25</v>
       </c>
       <c r="D291" s="2" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E291" s="1" t="s">
         <v>58</v>
@@ -10371,7 +10377,7 @@
         <v>1008</v>
       </c>
       <c r="G291" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="292" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -10380,13 +10386,13 @@
         <v>1008139</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C292" s="1">
         <v>139</v>
       </c>
       <c r="D292" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E292" s="1" t="s">
         <v>58</v>
@@ -10395,7 +10401,7 @@
         <v>1008</v>
       </c>
       <c r="G292" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="293" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -11244,13 +11250,13 @@
         <v>1006001</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C328" s="1">
         <v>1</v>
       </c>
       <c r="D328" s="2" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E328" s="1" t="s">
         <v>13</v>
@@ -11259,7 +11265,7 @@
         <v>1006</v>
       </c>
       <c r="G328" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="329" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -11274,7 +11280,7 @@
         <v>51</v>
       </c>
       <c r="D329" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E329" s="1" t="s">
         <v>13</v>
@@ -11283,7 +11289,7 @@
         <v>1006</v>
       </c>
       <c r="G329" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="330" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -11292,13 +11298,13 @@
         <v>1006012</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C330" s="1">
         <v>12</v>
       </c>
       <c r="D330" s="2" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E330" s="1" t="s">
         <v>13</v>
@@ -11307,7 +11313,7 @@
         <v>1006</v>
       </c>
       <c r="G330" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="331" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -11316,13 +11322,13 @@
         <v>1006025</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C331" s="1">
         <v>25</v>
       </c>
       <c r="D331" s="2" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E331" s="1" t="s">
         <v>20</v>
@@ -11331,7 +11337,7 @@
         <v>1006</v>
       </c>
       <c r="G331" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="332" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -11340,13 +11346,13 @@
         <v>1006015</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C332" s="1">
         <v>15</v>
       </c>
       <c r="D332" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E332" s="1" t="s">
         <v>20</v>
@@ -11355,7 +11361,7 @@
         <v>1006</v>
       </c>
       <c r="G332" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="333" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -11364,13 +11370,13 @@
         <v>1006004</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C333" s="1">
         <v>4</v>
       </c>
       <c r="D333" s="2" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E333" s="1" t="s">
         <v>20</v>
@@ -11379,7 +11385,7 @@
         <v>1006</v>
       </c>
       <c r="G333" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="334" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -11388,13 +11394,13 @@
         <v>1006013</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C334" s="1">
         <v>13</v>
       </c>
       <c r="D334" s="2" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E334" s="1" t="s">
         <v>20</v>
@@ -11403,7 +11409,7 @@
         <v>1006</v>
       </c>
       <c r="G334" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="335" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -11412,13 +11418,13 @@
         <v>1006062</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C335" s="1">
         <v>62</v>
       </c>
       <c r="D335" s="2" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E335" s="1" t="s">
         <v>20</v>
@@ -11427,7 +11433,7 @@
         <v>1006</v>
       </c>
       <c r="G335" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="336" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -11436,13 +11442,13 @@
         <v>1006026</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C336" s="1">
         <v>26</v>
       </c>
       <c r="D336" s="2" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E336" s="1" t="s">
         <v>20</v>
@@ -11451,7 +11457,7 @@
         <v>1006</v>
       </c>
       <c r="G336" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="337" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -11460,13 +11466,13 @@
         <v>1006003</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C337" s="1">
         <v>3</v>
       </c>
       <c r="D337" s="2" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E337" s="1" t="s">
         <v>20</v>
@@ -11475,7 +11481,7 @@
         <v>1006</v>
       </c>
       <c r="G337" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="338" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -11484,13 +11490,13 @@
         <v>1006002</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C338" s="1">
         <v>2</v>
       </c>
       <c r="D338" s="2" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="E338" s="1" t="s">
         <v>33</v>
@@ -11499,7 +11505,7 @@
         <v>1006</v>
       </c>
       <c r="G338" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="339" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -11508,13 +11514,13 @@
         <v>1006006</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C339" s="1">
         <v>6</v>
       </c>
       <c r="D339" s="2" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E339" s="1" t="s">
         <v>33</v>
@@ -11523,7 +11529,7 @@
         <v>1006</v>
       </c>
       <c r="G339" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="340" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -11532,13 +11538,13 @@
         <v>1006011</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C340" s="1">
         <v>11</v>
       </c>
       <c r="D340" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E340" s="1" t="s">
         <v>33</v>
@@ -11547,7 +11553,7 @@
         <v>1006</v>
       </c>
       <c r="G340" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="341" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -11556,13 +11562,13 @@
         <v>1006008</v>
       </c>
       <c r="B341" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C341" s="1">
         <v>8</v>
       </c>
       <c r="D341" s="2" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E341" s="1" t="s">
         <v>33</v>
@@ -11571,7 +11577,7 @@
         <v>1006</v>
       </c>
       <c r="G341" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="342" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -11580,13 +11586,13 @@
         <v>1006005</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C342" s="1">
         <v>5</v>
       </c>
       <c r="D342" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E342" s="1" t="s">
         <v>33</v>
@@ -11595,7 +11601,7 @@
         <v>1006</v>
       </c>
       <c r="G342" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="343" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -11604,13 +11610,13 @@
         <v>1006018</v>
       </c>
       <c r="B343" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C343" s="1">
         <v>18</v>
       </c>
       <c r="D343" s="2" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E343" s="1" t="s">
         <v>33</v>
@@ -11619,7 +11625,7 @@
         <v>1006</v>
       </c>
       <c r="G343" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="344" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -11628,13 +11634,13 @@
         <v>1006007</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C344" s="1">
         <v>7</v>
       </c>
       <c r="D344" s="2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E344" s="1" t="s">
         <v>33</v>
@@ -11643,7 +11649,7 @@
         <v>1006</v>
       </c>
       <c r="G344" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="345" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -11652,13 +11658,13 @@
         <v>1006016</v>
       </c>
       <c r="B345" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C345" s="1">
         <v>16</v>
       </c>
       <c r="D345" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E345" s="1" t="s">
         <v>33</v>
@@ -11667,7 +11673,7 @@
         <v>1006</v>
       </c>
       <c r="G345" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="346" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -11676,13 +11682,13 @@
         <v>1006020</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C346" s="1">
         <v>20</v>
       </c>
       <c r="D346" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E346" s="1" t="s">
         <v>33</v>
@@ -11691,7 +11697,7 @@
         <v>1006</v>
       </c>
       <c r="G346" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="347" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -11700,13 +11706,13 @@
         <v>1006022</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C347" s="1">
         <v>22</v>
       </c>
       <c r="D347" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E347" s="1" t="s">
         <v>33</v>
@@ -11715,7 +11721,7 @@
         <v>1006</v>
       </c>
       <c r="G347" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="348" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -11724,13 +11730,13 @@
         <v>1006017</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C348" s="1">
         <v>17</v>
       </c>
       <c r="D348" s="2" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="E348" s="1" t="s">
         <v>33</v>
@@ -11739,7 +11745,7 @@
         <v>1006</v>
       </c>
       <c r="G348" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="349" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -11748,13 +11754,13 @@
         <v>1006021</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C349" s="1">
         <v>21</v>
       </c>
       <c r="D349" s="2" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="E349" s="1" t="s">
         <v>33</v>
@@ -11763,7 +11769,7 @@
         <v>1006</v>
       </c>
       <c r="G349" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="350" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -11772,13 +11778,13 @@
         <v>1006014</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C350" s="1">
         <v>14</v>
       </c>
       <c r="D350" s="2" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="E350" s="1" t="s">
         <v>33</v>
@@ -11787,7 +11793,7 @@
         <v>1006</v>
       </c>
       <c r="G350" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="351" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -11796,7 +11802,7 @@
         <v>1006065</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C351" s="1">
         <v>65</v>
@@ -11811,7 +11817,7 @@
         <v>1006</v>
       </c>
       <c r="G351" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="352" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -11820,13 +11826,13 @@
         <v>1006141</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C352" s="1">
         <v>141</v>
       </c>
       <c r="D352" s="2" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="E352" s="1" t="s">
         <v>33</v>
@@ -11835,7 +11841,7 @@
         <v>1006</v>
       </c>
       <c r="G352" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="353" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -11844,7 +11850,7 @@
         <v>1006142</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C353" s="1">
         <v>142</v>
@@ -11859,7 +11865,7 @@
         <v>1006</v>
       </c>
       <c r="G353" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="354" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -11868,13 +11874,13 @@
         <v>1006009</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C354" s="1">
         <v>9</v>
       </c>
       <c r="D354" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E354" s="1" t="s">
         <v>58</v>
@@ -11883,7 +11889,7 @@
         <v>1006</v>
       </c>
       <c r="G354" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="355" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -11892,13 +11898,13 @@
         <v>1006010</v>
       </c>
       <c r="B355" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C355" s="1">
         <v>10</v>
       </c>
       <c r="D355" s="2" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="E355" s="1" t="s">
         <v>58</v>
@@ -11907,7 +11913,7 @@
         <v>1006</v>
       </c>
       <c r="G355" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="356" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -11916,13 +11922,13 @@
         <v>1006019</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C356" s="1">
         <v>19</v>
       </c>
       <c r="D356" s="2" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="E356" s="1" t="s">
         <v>58</v>
@@ -11931,7 +11937,7 @@
         <v>1006</v>
       </c>
       <c r="G356" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="357" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -11940,13 +11946,13 @@
         <v>1006143</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C357" s="1">
         <v>143</v>
       </c>
       <c r="D357" s="2" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="E357" s="1" t="s">
         <v>58</v>
@@ -11955,7 +11961,7 @@
         <v>1006</v>
       </c>
       <c r="G357" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="358" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -11964,13 +11970,13 @@
         <v>1006023</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C358" s="1">
         <v>23</v>
       </c>
       <c r="D358" s="2" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="E358" s="1" t="s">
         <v>58</v>
@@ -11979,7 +11985,7 @@
         <v>1006</v>
       </c>
       <c r="G358" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="359" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -11988,13 +11994,13 @@
         <v>1006079</v>
       </c>
       <c r="B359" s="1" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C359" s="1">
         <v>79</v>
       </c>
       <c r="D359" s="2" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="E359" s="1" t="s">
         <v>58</v>
@@ -12003,7 +12009,7 @@
         <v>1006</v>
       </c>
       <c r="G359" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="360" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -12012,7 +12018,7 @@
         <v>1006029</v>
       </c>
       <c r="B360" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C360" s="1">
         <v>29</v>
@@ -12027,7 +12033,7 @@
         <v>1006</v>
       </c>
       <c r="G360" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="361" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -12036,7 +12042,7 @@
         <v>1004029</v>
       </c>
       <c r="B361" s="1" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C361" s="1">
         <v>29</v>
@@ -12051,7 +12057,7 @@
         <v>1004</v>
       </c>
       <c r="G361" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="362" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -12060,13 +12066,13 @@
         <v>1004030</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C362" s="1">
         <v>30</v>
       </c>
       <c r="D362" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="E362" s="1" t="s">
         <v>13</v>
@@ -12075,7 +12081,7 @@
         <v>1004</v>
       </c>
       <c r="G362" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="363" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -12084,7 +12090,7 @@
         <v>1004053</v>
       </c>
       <c r="B363" s="1" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C363" s="1">
         <v>53</v>
@@ -12099,7 +12105,7 @@
         <v>1004</v>
       </c>
       <c r="G363" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="364" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -12108,13 +12114,13 @@
         <v>1004027</v>
       </c>
       <c r="B364" s="1" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C364" s="1">
         <v>27</v>
       </c>
       <c r="D364" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="E364" s="1" t="s">
         <v>20</v>
@@ -12123,7 +12129,7 @@
         <v>1004</v>
       </c>
       <c r="G364" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="365" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -12132,13 +12138,13 @@
         <v>1004019</v>
       </c>
       <c r="B365" s="1" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C365" s="1">
         <v>19</v>
       </c>
       <c r="D365" s="2" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="E365" s="1" t="s">
         <v>20</v>
@@ -12147,7 +12153,7 @@
         <v>1004</v>
       </c>
       <c r="G365" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="366" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -12156,13 +12162,13 @@
         <v>1004016</v>
       </c>
       <c r="B366" s="1" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="C366" s="1">
         <v>16</v>
       </c>
       <c r="D366" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="E366" s="1" t="s">
         <v>20</v>
@@ -12171,7 +12177,7 @@
         <v>1004</v>
       </c>
       <c r="G366" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="367" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -12180,13 +12186,13 @@
         <v>1004002</v>
       </c>
       <c r="B367" s="1" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C367" s="1">
         <v>2</v>
       </c>
       <c r="D367" s="2" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="E367" s="1" t="s">
         <v>20</v>
@@ -12195,7 +12201,7 @@
         <v>1004</v>
       </c>
       <c r="G367" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="368" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -12204,13 +12210,13 @@
         <v>1004017</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C368" s="1">
         <v>17</v>
       </c>
       <c r="D368" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="E368" s="1" t="s">
         <v>20</v>
@@ -12219,7 +12225,7 @@
         <v>1004</v>
       </c>
       <c r="G368" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="369" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -12228,13 +12234,13 @@
         <v>1004021</v>
       </c>
       <c r="B369" s="1" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C369" s="1">
         <v>21</v>
       </c>
       <c r="D369" s="2" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="E369" s="1" t="s">
         <v>20</v>
@@ -12243,7 +12249,7 @@
         <v>1004</v>
       </c>
       <c r="G369" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="370" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -12258,7 +12264,7 @@
         <v>22</v>
       </c>
       <c r="D370" s="2" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="E370" s="1" t="s">
         <v>20</v>
@@ -12267,7 +12273,7 @@
         <v>1004</v>
       </c>
       <c r="G370" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="371" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -12276,13 +12282,13 @@
         <v>1004014</v>
       </c>
       <c r="B371" s="1" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C371" s="1">
         <v>14</v>
       </c>
       <c r="D371" s="2" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E371" s="1" t="s">
         <v>20</v>
@@ -12291,7 +12297,7 @@
         <v>1004</v>
       </c>
       <c r="G371" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="372" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -12300,13 +12306,13 @@
         <v>1004013</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C372" s="1">
         <v>13</v>
       </c>
       <c r="D372" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E372" s="1" t="s">
         <v>20</v>
@@ -12315,7 +12321,7 @@
         <v>1004</v>
       </c>
       <c r="G372" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="373" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -12324,13 +12330,13 @@
         <v>1004004</v>
       </c>
       <c r="B373" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C373" s="1">
         <v>4</v>
       </c>
       <c r="D373" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="E373" s="1" t="s">
         <v>33</v>
@@ -12339,7 +12345,7 @@
         <v>1004</v>
       </c>
       <c r="G373" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="374" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -12348,13 +12354,13 @@
         <v>1004020</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="C374" s="1">
         <v>20</v>
       </c>
       <c r="D374" s="2" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="E374" s="1" t="s">
         <v>33</v>
@@ -12363,7 +12369,7 @@
         <v>1004</v>
       </c>
       <c r="G374" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="375" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -12372,13 +12378,13 @@
         <v>1004007</v>
       </c>
       <c r="B375" s="1" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C375" s="1">
         <v>7</v>
       </c>
       <c r="D375" s="2" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="E375" s="1" t="s">
         <v>33</v>
@@ -12387,7 +12393,7 @@
         <v>1004</v>
       </c>
       <c r="G375" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="376" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -12396,13 +12402,13 @@
         <v>1004015</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C376" s="1">
         <v>15</v>
       </c>
       <c r="D376" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="E376" s="1" t="s">
         <v>33</v>
@@ -12411,7 +12417,7 @@
         <v>1004</v>
       </c>
       <c r="G376" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="377" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -12420,13 +12426,13 @@
         <v>1004005</v>
       </c>
       <c r="B377" s="1" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C377" s="1">
         <v>5</v>
       </c>
       <c r="D377" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="E377" s="1" t="s">
         <v>33</v>
@@ -12435,7 +12441,7 @@
         <v>1004</v>
       </c>
       <c r="G377" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="378" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -12444,13 +12450,13 @@
         <v>1004012</v>
       </c>
       <c r="B378" s="1" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="C378" s="1">
         <v>12</v>
       </c>
       <c r="D378" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E378" s="1" t="s">
         <v>33</v>
@@ -12459,7 +12465,7 @@
         <v>1004</v>
       </c>
       <c r="G378" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="379" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -12468,13 +12474,13 @@
         <v>1004018</v>
       </c>
       <c r="B379" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C379" s="1">
         <v>18</v>
       </c>
       <c r="D379" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="E379" s="1" t="s">
         <v>33</v>
@@ -12483,7 +12489,7 @@
         <v>1004</v>
       </c>
       <c r="G379" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="380" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -12492,7 +12498,7 @@
         <v>1004031</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C380" s="1">
         <v>31</v>
@@ -12507,7 +12513,7 @@
         <v>1004</v>
       </c>
       <c r="G380" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="381" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -12516,13 +12522,13 @@
         <v>1004008</v>
       </c>
       <c r="B381" s="1" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C381" s="1">
         <v>8</v>
       </c>
       <c r="D381" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E381" s="1" t="s">
         <v>33</v>
@@ -12531,7 +12537,7 @@
         <v>1004</v>
       </c>
       <c r="G381" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="382" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -12540,13 +12546,13 @@
         <v>1004002</v>
       </c>
       <c r="B382" s="1" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C382" s="1">
         <v>2</v>
       </c>
       <c r="D382" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="E382" s="1" t="s">
         <v>58</v>
@@ -12555,7 +12561,7 @@
         <v>1004</v>
       </c>
       <c r="G382" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="383" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -12564,13 +12570,13 @@
         <v>1004009</v>
       </c>
       <c r="B383" s="1" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="C383" s="1">
         <v>9</v>
       </c>
       <c r="D383" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="E383" s="1" t="s">
         <v>58</v>
@@ -12579,7 +12585,7 @@
         <v>1004</v>
       </c>
       <c r="G383" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="384" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -12594,7 +12600,7 @@
         <v>6</v>
       </c>
       <c r="D384" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="E384" s="1" t="s">
         <v>58</v>
@@ -12603,7 +12609,7 @@
         <v>1004</v>
       </c>
       <c r="G384" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="385" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -12612,7 +12618,7 @@
         <v>1004003</v>
       </c>
       <c r="B385" s="1" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C385" s="1">
         <v>3</v>
@@ -12627,7 +12633,7 @@
         <v>1004</v>
       </c>
       <c r="G385" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="386" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -12636,13 +12642,13 @@
         <v>1004023</v>
       </c>
       <c r="B386" s="1" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C386" s="1">
         <v>23</v>
       </c>
       <c r="D386" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="E386" s="1" t="s">
         <v>58</v>
@@ -12651,7 +12657,7 @@
         <v>1004</v>
       </c>
       <c r="G386" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="387" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -12660,13 +12666,13 @@
         <v>1004011</v>
       </c>
       <c r="B387" s="1" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C387" s="1">
         <v>11</v>
       </c>
       <c r="D387" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E387" s="1" t="s">
         <v>58</v>
@@ -12675,7 +12681,7 @@
         <v>1004</v>
       </c>
       <c r="G387" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="388" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -12684,13 +12690,13 @@
         <v>1004025</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="C388" s="1">
         <v>25</v>
       </c>
       <c r="D388" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="E388" s="1" t="s">
         <v>58</v>
@@ -12699,7 +12705,7 @@
         <v>1004</v>
       </c>
       <c r="G388" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="389" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -12708,13 +12714,13 @@
         <v>1004024</v>
       </c>
       <c r="B389" s="1" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="C389" s="1">
         <v>24</v>
       </c>
       <c r="D389" s="2" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E389" s="1" t="s">
         <v>58</v>
@@ -12723,7 +12729,7 @@
         <v>1004</v>
       </c>
       <c r="G389" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="390" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -12732,7 +12738,7 @@
         <v>1004028</v>
       </c>
       <c r="B390" s="1" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="C390" s="1">
         <v>28</v>
@@ -12747,7 +12753,7 @@
         <v>1004</v>
       </c>
       <c r="G390" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="391" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -12756,13 +12762,13 @@
         <v>1004151</v>
       </c>
       <c r="B391" s="1" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="C391" s="1">
         <v>151</v>
       </c>
       <c r="D391" s="2" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="E391" s="1" t="s">
         <v>58</v>
@@ -12771,7 +12777,7 @@
         <v>1004</v>
       </c>
       <c r="G391" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="392" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -13452,7 +13458,7 @@
         <v>1003001</v>
       </c>
       <c r="B420" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C420" s="1">
         <v>1</v>
@@ -13467,7 +13473,7 @@
         <v>1003</v>
       </c>
       <c r="G420" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="421" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -13476,7 +13482,7 @@
         <v>1003028</v>
       </c>
       <c r="B421" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C421" s="1">
         <v>28</v>
@@ -13491,7 +13497,7 @@
         <v>1003</v>
       </c>
       <c r="G421" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="422" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -13500,7 +13506,7 @@
         <v>1003023</v>
       </c>
       <c r="B422" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C422" s="1">
         <v>23</v>
@@ -13515,7 +13521,7 @@
         <v>1003</v>
       </c>
       <c r="G422" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="423" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -13524,13 +13530,13 @@
         <v>1003126</v>
       </c>
       <c r="B423" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C423" s="1">
         <v>126</v>
       </c>
       <c r="D423" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E423" s="1" t="s">
         <v>20</v>
@@ -13539,7 +13545,7 @@
         <v>1003</v>
       </c>
       <c r="G423" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="424" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -13548,13 +13554,13 @@
         <v>1003019</v>
       </c>
       <c r="B424" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C424" s="1">
         <v>19</v>
       </c>
       <c r="D424" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E424" s="1" t="s">
         <v>20</v>
@@ -13563,7 +13569,7 @@
         <v>1003</v>
       </c>
       <c r="G424" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="425" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -13572,13 +13578,13 @@
         <v>1003004</v>
       </c>
       <c r="B425" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C425" s="1">
         <v>4</v>
       </c>
       <c r="D425" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E425" s="1" t="s">
         <v>20</v>
@@ -13587,7 +13593,7 @@
         <v>1003</v>
       </c>
       <c r="G425" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="426" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -13596,13 +13602,13 @@
         <v>1003013</v>
       </c>
       <c r="B426" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C426" s="1">
         <v>13</v>
       </c>
       <c r="D426" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E426" s="1" t="s">
         <v>20</v>
@@ -13611,7 +13617,7 @@
         <v>1003</v>
       </c>
       <c r="G426" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="427" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -13620,13 +13626,13 @@
         <v>1003127</v>
       </c>
       <c r="B427" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C427" s="1">
         <v>127</v>
       </c>
       <c r="D427" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E427" s="1" t="s">
         <v>20</v>
@@ -13635,7 +13641,7 @@
         <v>1003</v>
       </c>
       <c r="G427" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="428" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -13644,7 +13650,7 @@
         <v>1003002</v>
       </c>
       <c r="B428" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C428" s="1">
         <v>2</v>
@@ -13659,7 +13665,7 @@
         <v>1003</v>
       </c>
       <c r="G428" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="429" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -13668,13 +13674,13 @@
         <v>1003007</v>
       </c>
       <c r="B429" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C429" s="1">
         <v>7</v>
       </c>
       <c r="D429" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E429" s="1" t="s">
         <v>20</v>
@@ -13683,7 +13689,7 @@
         <v>1003</v>
       </c>
       <c r="G429" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="430" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -13692,7 +13698,7 @@
         <v>1003030</v>
       </c>
       <c r="B430" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C430" s="1">
         <v>30</v>
@@ -13707,7 +13713,7 @@
         <v>1003</v>
       </c>
       <c r="G430" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="431" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -13716,13 +13722,13 @@
         <v>1003024</v>
       </c>
       <c r="B431" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C431" s="1">
         <v>24</v>
       </c>
       <c r="D431" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E431" s="1" t="s">
         <v>20</v>
@@ -13731,7 +13737,7 @@
         <v>1003</v>
       </c>
       <c r="G431" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="432" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -13740,7 +13746,7 @@
         <v>1003027</v>
       </c>
       <c r="B432" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C432" s="1">
         <v>27</v>
@@ -13755,7 +13761,7 @@
         <v>1003</v>
       </c>
       <c r="G432" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="433" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -13764,7 +13770,7 @@
         <v>1003005</v>
       </c>
       <c r="B433" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C433" s="1">
         <v>5</v>
@@ -13779,7 +13785,7 @@
         <v>1003</v>
       </c>
       <c r="G433" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="434" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -13788,7 +13794,7 @@
         <v>1003025</v>
       </c>
       <c r="B434" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C434" s="1">
         <v>25</v>
@@ -13803,7 +13809,7 @@
         <v>1003</v>
       </c>
       <c r="G434" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="435" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -13812,13 +13818,13 @@
         <v>1003026</v>
       </c>
       <c r="B435" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C435" s="1">
         <v>26</v>
       </c>
       <c r="D435" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E435" s="1" t="s">
         <v>20</v>
@@ -13827,7 +13833,7 @@
         <v>1003</v>
       </c>
       <c r="G435" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="436" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -13836,7 +13842,7 @@
         <v>1003016</v>
       </c>
       <c r="B436" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C436" s="1">
         <v>16</v>
@@ -13851,7 +13857,7 @@
         <v>1003</v>
       </c>
       <c r="G436" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="437" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -13860,13 +13866,13 @@
         <v>1003010</v>
       </c>
       <c r="B437" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C437" s="1">
         <v>10</v>
       </c>
       <c r="D437" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E437" s="1" t="s">
         <v>33</v>
@@ -13875,7 +13881,7 @@
         <v>1003</v>
       </c>
       <c r="G437" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="438" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -13884,13 +13890,13 @@
         <v>1003036</v>
       </c>
       <c r="B438" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C438" s="1">
         <v>36</v>
       </c>
       <c r="D438" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E438" s="1" t="s">
         <v>33</v>
@@ -13899,7 +13905,7 @@
         <v>1003</v>
       </c>
       <c r="G438" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="439" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -13908,13 +13914,13 @@
         <v>1003017</v>
       </c>
       <c r="B439" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C439" s="1">
         <v>17</v>
       </c>
       <c r="D439" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E439" s="1" t="s">
         <v>33</v>
@@ -13923,7 +13929,7 @@
         <v>1003</v>
       </c>
       <c r="G439" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="440" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -13932,13 +13938,13 @@
         <v>1003008</v>
       </c>
       <c r="B440" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C440" s="1">
         <v>8</v>
       </c>
       <c r="D440" s="2" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E440" s="1" t="s">
         <v>33</v>
@@ -13947,7 +13953,7 @@
         <v>1003</v>
       </c>
       <c r="G440" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="441" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -13956,13 +13962,13 @@
         <v>1003014</v>
       </c>
       <c r="B441" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C441" s="1">
         <v>14</v>
       </c>
       <c r="D441" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E441" s="1" t="s">
         <v>33</v>
@@ -13971,7 +13977,7 @@
         <v>1003</v>
       </c>
       <c r="G441" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="442" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -13980,7 +13986,7 @@
         <v>1003003</v>
       </c>
       <c r="B442" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C442" s="1">
         <v>3</v>
@@ -13995,7 +14001,7 @@
         <v>1003</v>
       </c>
       <c r="G442" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="443" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -14004,7 +14010,7 @@
         <v>1003006</v>
       </c>
       <c r="B443" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C443" s="1">
         <v>6</v>
@@ -14019,7 +14025,7 @@
         <v>1003</v>
       </c>
       <c r="G443" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="444" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -14043,7 +14049,7 @@
         <v>1003</v>
       </c>
       <c r="G444" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="445" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -14052,13 +14058,13 @@
         <v>1003021</v>
       </c>
       <c r="B445" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C445" s="1">
         <v>21</v>
       </c>
       <c r="D445" s="2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E445" s="1" t="s">
         <v>33</v>
@@ -14067,7 +14073,7 @@
         <v>1003</v>
       </c>
       <c r="G445" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="446" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -14076,13 +14082,13 @@
         <v>1003033</v>
       </c>
       <c r="B446" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C446" s="1">
+        <v>33</v>
+      </c>
+      <c r="D446" s="2" t="s">
         <v>482</v>
-      </c>
-      <c r="C446" s="1">
-        <v>33</v>
-      </c>
-      <c r="D446" s="2" t="s">
-        <v>483</v>
       </c>
       <c r="E446" s="1" t="s">
         <v>33</v>
@@ -14091,7 +14097,7 @@
         <v>1003</v>
       </c>
       <c r="G446" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="447" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -14100,7 +14106,7 @@
         <v>1003015</v>
       </c>
       <c r="B447" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C447" s="1">
         <v>15</v>
@@ -14115,7 +14121,7 @@
         <v>1003</v>
       </c>
       <c r="G447" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="448" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -14124,13 +14130,13 @@
         <v>1003009</v>
       </c>
       <c r="B448" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C448" s="1">
         <v>9</v>
       </c>
       <c r="D448" s="2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="E448" s="1" t="s">
         <v>58</v>
@@ -14139,7 +14145,7 @@
         <v>1003</v>
       </c>
       <c r="G448" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="449" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -14148,13 +14154,13 @@
         <v>1003018</v>
       </c>
       <c r="B449" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C449" s="1">
         <v>18</v>
       </c>
       <c r="D449" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E449" s="1" t="s">
         <v>58</v>
@@ -14163,7 +14169,7 @@
         <v>1003</v>
       </c>
       <c r="G449" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="450" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -14172,13 +14178,13 @@
         <v>1003029</v>
       </c>
       <c r="B450" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C450" s="1">
         <v>29</v>
       </c>
       <c r="D450" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E450" s="1" t="s">
         <v>58</v>
@@ -14187,7 +14193,7 @@
         <v>1003</v>
       </c>
       <c r="G450" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="451" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -14211,7 +14217,7 @@
         <v>1003</v>
       </c>
       <c r="G451" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="452" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -14220,13 +14226,13 @@
         <v>1003022</v>
       </c>
       <c r="B452" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C452" s="1">
         <v>22</v>
       </c>
       <c r="D452" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E452" s="1" t="s">
         <v>58</v>
@@ -14235,7 +14241,7 @@
         <v>1003</v>
       </c>
       <c r="G452" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="453" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -14244,13 +14250,13 @@
         <v>1003020</v>
       </c>
       <c r="B453" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C453" s="1">
         <v>20</v>
       </c>
       <c r="D453" s="2" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E453" s="1" t="s">
         <v>58</v>
@@ -14259,7 +14265,7 @@
         <v>1003</v>
       </c>
       <c r="G453" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="454" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -14268,13 +14274,13 @@
         <v>1003132</v>
       </c>
       <c r="B454" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C454" s="1">
         <v>132</v>
       </c>
       <c r="D454" s="2" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E454" s="1" t="s">
         <v>58</v>
@@ -14283,7 +14289,7 @@
         <v>1003</v>
       </c>
       <c r="G454" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="455" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -14292,13 +14298,13 @@
         <v>1003041</v>
       </c>
       <c r="B455" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C455">
         <v>41</v>
       </c>
       <c r="D455" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E455" t="s">
         <v>13</v>
@@ -14307,7 +14313,7 @@
         <v>1003</v>
       </c>
       <c r="G455" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="456" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -14316,7 +14322,7 @@
         <v>1003038</v>
       </c>
       <c r="B456" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="C456">
         <v>38</v>
@@ -14331,7 +14337,7 @@
         <v>1003</v>
       </c>
       <c r="G456" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="457" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -14340,7 +14346,7 @@
         <v>1003039</v>
       </c>
       <c r="B457" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C457">
         <v>39</v>
@@ -14355,7 +14361,7 @@
         <v>1003</v>
       </c>
       <c r="G457" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="458" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -14364,7 +14370,7 @@
         <v>1003040</v>
       </c>
       <c r="B458" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="C458">
         <v>40</v>
@@ -14374,7 +14380,7 @@
         <v>1003</v>
       </c>
       <c r="G458" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="459" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -15103,7 +15109,7 @@
         <v>1002029</v>
       </c>
       <c r="B489" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="C489">
         <v>29</v>
@@ -15127,7 +15133,7 @@
         <v>1001001</v>
       </c>
       <c r="B490" s="1" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="C490" s="1">
         <v>1</v>
@@ -15142,7 +15148,7 @@
         <v>1001</v>
       </c>
       <c r="G490" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="491" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -15151,7 +15157,7 @@
         <v>1001001</v>
       </c>
       <c r="B491" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="C491" s="1">
         <v>1</v>
@@ -15166,7 +15172,7 @@
         <v>1001</v>
       </c>
       <c r="G491" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="492" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -15175,13 +15181,13 @@
         <v>1001021</v>
       </c>
       <c r="B492" s="1" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="C492" s="1">
         <v>21</v>
       </c>
       <c r="D492" s="2" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="E492" s="1" t="s">
         <v>13</v>
@@ -15190,7 +15196,7 @@
         <v>1001</v>
       </c>
       <c r="G492" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="493" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -15199,7 +15205,7 @@
         <v>1001152</v>
       </c>
       <c r="B493" s="1" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C493" s="1">
         <v>152</v>
@@ -15214,7 +15220,7 @@
         <v>1001</v>
       </c>
       <c r="G493" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="494" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -15223,7 +15229,7 @@
         <v>1001001</v>
       </c>
       <c r="B494" s="1" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C494" s="1">
         <v>1</v>
@@ -15238,7 +15244,7 @@
         <v>1001</v>
       </c>
       <c r="G494" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="495" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -15247,13 +15253,13 @@
         <v>1001029</v>
       </c>
       <c r="B495" s="1" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C495" s="1">
         <v>29</v>
       </c>
       <c r="D495" s="2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="E495" s="1" t="s">
         <v>13</v>
@@ -15262,7 +15268,7 @@
         <v>1001</v>
       </c>
       <c r="G495" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="496" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -15271,13 +15277,13 @@
         <v>1001023</v>
       </c>
       <c r="B496" s="1" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C496" s="1">
         <v>23</v>
       </c>
       <c r="D496" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="E496" s="1" t="s">
         <v>20</v>
@@ -15286,7 +15292,7 @@
         <v>1001</v>
       </c>
       <c r="G496" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="497" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -15295,13 +15301,13 @@
         <v>1001153</v>
       </c>
       <c r="B497" s="1" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C497" s="1">
         <v>153</v>
       </c>
       <c r="D497" s="2" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E497" s="1" t="s">
         <v>20</v>
@@ -15310,7 +15316,7 @@
         <v>1001</v>
       </c>
       <c r="G497" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="498" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -15319,13 +15325,13 @@
         <v>1001020</v>
       </c>
       <c r="B498" s="1" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="C498" s="1">
         <v>20</v>
       </c>
       <c r="D498" s="2" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="E498" s="1" t="s">
         <v>20</v>
@@ -15334,7 +15340,7 @@
         <v>1001</v>
       </c>
       <c r="G498" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="499" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -15343,13 +15349,13 @@
         <v>1001013</v>
       </c>
       <c r="B499" s="1" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="C499" s="1">
         <v>13</v>
       </c>
       <c r="D499" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E499" s="1" t="s">
         <v>20</v>
@@ -15358,7 +15364,7 @@
         <v>1001</v>
       </c>
       <c r="G499" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="500" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -15367,13 +15373,13 @@
         <v>1001024</v>
       </c>
       <c r="B500" s="1" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C500" s="1">
         <v>24</v>
       </c>
       <c r="D500" s="2" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="E500" s="1" t="s">
         <v>20</v>
@@ -15382,7 +15388,7 @@
         <v>1001</v>
       </c>
       <c r="G500" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="501" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -15391,13 +15397,13 @@
         <v>1001002</v>
       </c>
       <c r="B501" s="1" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="C501" s="1">
         <v>2</v>
       </c>
       <c r="D501" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E501" s="1" t="s">
         <v>20</v>
@@ -15406,7 +15412,7 @@
         <v>1001</v>
       </c>
       <c r="G501" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="502" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -15415,13 +15421,13 @@
         <v>1001043</v>
       </c>
       <c r="B502" s="1" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C502" s="1">
         <v>43</v>
       </c>
       <c r="D502" s="2" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="E502" s="1" t="s">
         <v>20</v>
@@ -15430,7 +15436,7 @@
         <v>1001</v>
       </c>
       <c r="G502" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="503" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -15454,7 +15460,7 @@
         <v>1001</v>
       </c>
       <c r="G503" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="504" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -15463,13 +15469,13 @@
         <v>1001025</v>
       </c>
       <c r="B504" s="1" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C504" s="1">
         <v>25</v>
       </c>
       <c r="D504" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="E504" s="1" t="s">
         <v>20</v>
@@ -15478,7 +15484,7 @@
         <v>1001</v>
       </c>
       <c r="G504" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="505" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -15487,7 +15493,7 @@
         <v>1001012</v>
       </c>
       <c r="B505" s="1" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C505" s="1">
         <v>12</v>
@@ -15502,7 +15508,7 @@
         <v>1001</v>
       </c>
       <c r="G505" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="506" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -15511,13 +15517,13 @@
         <v>1001045</v>
       </c>
       <c r="B506" s="1" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C506" s="1">
         <v>45</v>
       </c>
       <c r="D506" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="E506" s="1" t="s">
         <v>20</v>
@@ -15526,7 +15532,7 @@
         <v>1001</v>
       </c>
       <c r="G506" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="507" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -15535,13 +15541,13 @@
         <v>1001003</v>
       </c>
       <c r="B507" s="1" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="C507" s="1">
         <v>3</v>
       </c>
       <c r="D507" s="2" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="E507" s="1" t="s">
         <v>20</v>
@@ -15550,7 +15556,7 @@
         <v>1001</v>
       </c>
       <c r="G507" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="508" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -15559,7 +15565,7 @@
         <v>1001154</v>
       </c>
       <c r="B508" s="1" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="C508" s="1">
         <v>154</v>
@@ -15574,7 +15580,7 @@
         <v>1001</v>
       </c>
       <c r="G508" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="509" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -15583,13 +15589,13 @@
         <v>1001155</v>
       </c>
       <c r="B509" s="1" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="C509" s="1">
         <v>155</v>
       </c>
       <c r="D509" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="E509" s="1" t="s">
         <v>20</v>
@@ -15598,7 +15604,7 @@
         <v>1001</v>
       </c>
       <c r="G509" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="510" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -15607,13 +15613,13 @@
         <v>1001010</v>
       </c>
       <c r="B510" s="1" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C510" s="1">
         <v>10</v>
       </c>
       <c r="D510" s="2" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="E510" s="1" t="s">
         <v>33</v>
@@ -15622,7 +15628,7 @@
         <v>1001</v>
       </c>
       <c r="G510" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="511" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -15631,13 +15637,13 @@
         <v>1001011</v>
       </c>
       <c r="B511" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C511" s="1">
         <v>11</v>
       </c>
       <c r="D511" s="2" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="E511" s="1" t="s">
         <v>33</v>
@@ -15646,7 +15652,7 @@
         <v>1001</v>
       </c>
       <c r="G511" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="512" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -15655,13 +15661,13 @@
         <v>1001005</v>
       </c>
       <c r="B512" s="1" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C512" s="1">
         <v>5</v>
       </c>
       <c r="D512" s="2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="E512" s="1" t="s">
         <v>33</v>
@@ -15670,7 +15676,7 @@
         <v>1001</v>
       </c>
       <c r="G512" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="513" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -15679,13 +15685,13 @@
         <v>1001004</v>
       </c>
       <c r="B513" s="1" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="C513" s="1">
         <v>4</v>
       </c>
       <c r="D513" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="E513" s="1" t="s">
         <v>33</v>
@@ -15694,7 +15700,7 @@
         <v>1001</v>
       </c>
       <c r="G513" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="514" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -15703,13 +15709,13 @@
         <v>1001018</v>
       </c>
       <c r="B514" s="1" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="C514" s="1">
         <v>18</v>
       </c>
       <c r="D514" s="2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="E514" s="1" t="s">
         <v>33</v>
@@ -15718,7 +15724,7 @@
         <v>1001</v>
       </c>
       <c r="G514" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="515" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -15727,13 +15733,13 @@
         <v>1001016</v>
       </c>
       <c r="B515" s="1" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C515" s="1">
         <v>16</v>
       </c>
       <c r="D515" s="2" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E515" s="1" t="s">
         <v>33</v>
@@ -15742,7 +15748,7 @@
         <v>1001</v>
       </c>
       <c r="G515" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="516" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -15751,13 +15757,13 @@
         <v>1001006</v>
       </c>
       <c r="B516" s="1" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C516" s="1">
         <v>6</v>
       </c>
       <c r="D516" s="2" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="E516" s="1" t="s">
         <v>33</v>
@@ -15766,7 +15772,7 @@
         <v>1001</v>
       </c>
       <c r="G516" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="517" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -15775,13 +15781,13 @@
         <v>1001008</v>
       </c>
       <c r="B517" s="1" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="C517" s="1">
         <v>8</v>
       </c>
       <c r="D517" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="E517" s="1" t="s">
         <v>33</v>
@@ -15790,7 +15796,7 @@
         <v>1001</v>
       </c>
       <c r="G517" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="518" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -15799,7 +15805,7 @@
         <v>1001156</v>
       </c>
       <c r="B518" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="C518" s="1">
         <v>156</v>
@@ -15814,7 +15820,7 @@
         <v>1001</v>
       </c>
       <c r="G518" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="519" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -15823,13 +15829,13 @@
         <v>1001030</v>
       </c>
       <c r="B519" s="1" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="C519" s="1">
         <v>30</v>
       </c>
       <c r="D519" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="E519" s="1" t="s">
         <v>33</v>
@@ -15838,7 +15844,7 @@
         <v>1001</v>
       </c>
       <c r="G519" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="520" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -15847,7 +15853,7 @@
         <v>1001022</v>
       </c>
       <c r="B520" s="1" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="C520" s="1">
         <v>22</v>
@@ -15862,7 +15868,7 @@
         <v>1001</v>
       </c>
       <c r="G520" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="521" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -15871,7 +15877,7 @@
         <v>1001044</v>
       </c>
       <c r="B521" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C521" s="1">
         <v>44</v>
@@ -15886,7 +15892,7 @@
         <v>1001</v>
       </c>
       <c r="G521" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="522" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -15895,7 +15901,7 @@
         <v>1001007</v>
       </c>
       <c r="B522" s="1" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="C522" s="1">
         <v>7</v>
@@ -15910,7 +15916,7 @@
         <v>1001</v>
       </c>
       <c r="G522" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="523" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -15919,7 +15925,7 @@
         <v>1001033</v>
       </c>
       <c r="B523" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C523" s="1">
         <v>33</v>
@@ -15934,7 +15940,7 @@
         <v>1001</v>
       </c>
       <c r="G523" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="524" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -15943,7 +15949,7 @@
         <v>1001157</v>
       </c>
       <c r="B524" s="1" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="C524" s="1">
         <v>157</v>
@@ -15958,7 +15964,7 @@
         <v>1001</v>
       </c>
       <c r="G524" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="525" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -15967,7 +15973,7 @@
         <v>1001158</v>
       </c>
       <c r="B525" s="1" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="C525" s="1">
         <v>158</v>
@@ -15982,7 +15988,7 @@
         <v>1001</v>
       </c>
       <c r="G525" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="526" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -15991,13 +15997,13 @@
         <v>1001039</v>
       </c>
       <c r="B526" s="1" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="C526" s="1">
         <v>39</v>
       </c>
       <c r="D526" s="2" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="E526" s="1" t="s">
         <v>58</v>
@@ -16006,7 +16012,7 @@
         <v>1001</v>
       </c>
       <c r="G526" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="527" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -16015,13 +16021,13 @@
         <v>1001009</v>
       </c>
       <c r="B527" s="1" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C527" s="1">
         <v>9</v>
       </c>
       <c r="D527" s="2" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="E527" s="1" t="s">
         <v>58</v>
@@ -16030,7 +16036,7 @@
         <v>1001</v>
       </c>
       <c r="G527" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="528" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -16039,13 +16045,13 @@
         <v>1001046</v>
       </c>
       <c r="B528" s="1" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="C528" s="1">
         <v>46</v>
       </c>
       <c r="D528" s="2" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="E528" s="1" t="s">
         <v>58</v>
@@ -16054,7 +16060,7 @@
         <v>1001</v>
       </c>
       <c r="G528" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="529" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -16063,13 +16069,13 @@
         <v>1001028</v>
       </c>
       <c r="B529" s="1" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="C529" s="1">
         <v>28</v>
       </c>
       <c r="D529" s="2" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="E529" s="1" t="s">
         <v>58</v>
@@ -16078,7 +16084,7 @@
         <v>1001</v>
       </c>
       <c r="G529" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="530" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -16087,7 +16093,7 @@
         <v>1001159</v>
       </c>
       <c r="B530" s="1" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="C530" s="1">
         <v>159</v>
@@ -16102,7 +16108,7 @@
         <v>1001</v>
       </c>
       <c r="G530" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="531" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -16111,13 +16117,13 @@
         <v>1001017</v>
       </c>
       <c r="B531" s="1" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="C531" s="1">
         <v>17</v>
       </c>
       <c r="D531" s="2" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="E531" s="1" t="s">
         <v>58</v>
@@ -16126,7 +16132,7 @@
         <v>1001</v>
       </c>
       <c r="G531" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="532" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -16150,7 +16156,7 @@
         <v>1001</v>
       </c>
       <c r="G532" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="533" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -16159,13 +16165,13 @@
         <v>1001161</v>
       </c>
       <c r="B533" s="1" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="C533" s="1">
         <v>161</v>
       </c>
       <c r="D533" s="2" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="E533" s="1" t="s">
         <v>58</v>
@@ -16174,7 +16180,7 @@
         <v>1001</v>
       </c>
       <c r="G533" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="534" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -16183,7 +16189,7 @@
         <v>1010004</v>
       </c>
       <c r="B534" s="7" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="C534" s="7">
         <v>4</v>
@@ -16194,7 +16200,7 @@
         <v>1010</v>
       </c>
       <c r="G534" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="535" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -16203,7 +16209,7 @@
         <v>1010010</v>
       </c>
       <c r="B535" s="7" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="C535" s="7">
         <v>10</v>
@@ -16214,7 +16220,7 @@
         <v>1010</v>
       </c>
       <c r="G535" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="536" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -16223,7 +16229,7 @@
         <v>1010031</v>
       </c>
       <c r="B536" s="7" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="C536" s="7">
         <v>31</v>
@@ -16234,11 +16240,49 @@
         <v>1010</v>
       </c>
       <c r="G536" s="1" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="537" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="538" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+        <v>346</v>
+      </c>
+    </row>
+    <row r="537" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A537" s="7" t="str">
+        <f>F537 &amp; TEXT(C537,"000")</f>
+        <v>1010028</v>
+      </c>
+      <c r="B537" s="7" t="s">
+        <v>939</v>
+      </c>
+      <c r="C537" s="7">
+        <v>28</v>
+      </c>
+      <c r="D537" s="3"/>
+      <c r="E537" s="7"/>
+      <c r="F537" s="1">
+        <v>1010</v>
+      </c>
+      <c r="G537" s="1" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="538" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A538" s="7" t="str">
+        <f>F538 &amp; TEXT(C538,"000")</f>
+        <v>1010079</v>
+      </c>
+      <c r="B538" s="7" t="s">
+        <v>942</v>
+      </c>
+      <c r="C538" s="7">
+        <v>79</v>
+      </c>
+      <c r="D538" s="3"/>
+      <c r="E538" s="7"/>
+      <c r="F538" s="7">
+        <v>1010</v>
+      </c>
+      <c r="G538" s="1" t="s">
+        <v>346</v>
+      </c>
+    </row>
     <row r="539" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="540" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="541" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/backend/data/LigaPremier.xlsx
+++ b/backend/data/LigaPremier.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danyl\Downloads\E\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1f6951c0e601b7a9/Desktop/DEMO/Protoype/datastrike/backend/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F34475F7-B005-4D1D-8E8A-35328689D795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{F34475F7-B005-4D1D-8E8A-35328689D795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A43A0D2F-827A-44A2-BD29-5F66F2EFF0C2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2143" uniqueCount="943">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2145" uniqueCount="944">
   <si>
     <t>Id_jugador</t>
   </si>
@@ -2862,6 +2862,9 @@
   </si>
   <si>
     <t>Israel Ibarra</t>
+  </si>
+  <si>
+    <t>Andre Santana</t>
   </si>
 </sst>
 </file>
@@ -3160,11 +3163,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{32A8CF84-C284-4FB9-BA95-EA038AE71CB6}" name="Tabla1" displayName="Tabla1" ref="A1:G538" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7">
-  <autoFilter ref="A1:G538" xr:uid="{32A8CF84-C284-4FB9-BA95-EA038AE71CB6}">
-    <filterColumn colId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{32A8CF84-C284-4FB9-BA95-EA038AE71CB6}" name="Tabla1" displayName="Tabla1" ref="A1:G539" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7">
+  <autoFilter ref="A1:G539" xr:uid="{32A8CF84-C284-4FB9-BA95-EA038AE71CB6}">
+    <filterColumn colId="5">
       <filters>
-        <filter val="Lobos ULMX"/>
+        <filter val="1006"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -8268,7 +8271,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="204" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1010008</v>
@@ -8292,7 +8295,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="205" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1010025</v>
@@ -8316,7 +8319,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="206" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1010033</v>
@@ -8340,7 +8343,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="207" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1010020</v>
@@ -8364,7 +8367,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="208" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1010003</v>
@@ -8388,7 +8391,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="209" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1010007</v>
@@ -8412,7 +8415,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="210" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1010023</v>
@@ -8436,7 +8439,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="211" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1010017</v>
@@ -8460,7 +8463,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="212" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1010122</v>
@@ -8484,7 +8487,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="213" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1010022</v>
@@ -8508,7 +8511,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="214" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1010013</v>
@@ -8532,7 +8535,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="215" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1010005</v>
@@ -8556,7 +8559,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="216" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1010012</v>
@@ -8580,7 +8583,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="217" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1010012</v>
@@ -8604,7 +8607,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="218" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1010018</v>
@@ -8628,7 +8631,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="219" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1010019</v>
@@ -8652,7 +8655,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="220" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1010014</v>
@@ -8676,7 +8679,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="221" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1010009</v>
@@ -8700,7 +8703,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="222" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1010030</v>
@@ -8724,7 +8727,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="223" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1010024</v>
@@ -8748,7 +8751,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="224" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1010027</v>
@@ -8772,7 +8775,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="225" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1010021</v>
@@ -8796,7 +8799,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="226" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1010011</v>
@@ -8820,7 +8823,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="227" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1010016</v>
@@ -8844,7 +8847,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="228" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1010036</v>
@@ -8868,7 +8871,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="229" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1010029</v>
@@ -8892,7 +8895,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="230" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1010123</v>
@@ -11244,7 +11247,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="328" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A328" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006001</v>
@@ -11268,7 +11271,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="329" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A329" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006051</v>
@@ -11292,7 +11295,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="330" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A330" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006012</v>
@@ -11316,7 +11319,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="331" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A331" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006025</v>
@@ -11340,7 +11343,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="332" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A332" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006015</v>
@@ -11364,7 +11367,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="333" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A333" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006004</v>
@@ -11388,7 +11391,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="334" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A334" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006013</v>
@@ -11412,7 +11415,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="335" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A335" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006062</v>
@@ -11436,7 +11439,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="336" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A336" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006026</v>
@@ -11460,7 +11463,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="337" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A337" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006003</v>
@@ -11484,7 +11487,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="338" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A338" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006002</v>
@@ -11508,7 +11511,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="339" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A339" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006006</v>
@@ -11532,7 +11535,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="340" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A340" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006011</v>
@@ -11556,7 +11559,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="341" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A341" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006008</v>
@@ -11580,7 +11583,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="342" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A342" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006005</v>
@@ -11604,7 +11607,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="343" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A343" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006018</v>
@@ -11628,7 +11631,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="344" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A344" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006007</v>
@@ -11652,7 +11655,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="345" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A345" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006016</v>
@@ -11676,7 +11679,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="346" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A346" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006020</v>
@@ -11700,7 +11703,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="347" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A347" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006022</v>
@@ -11724,7 +11727,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="348" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A348" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006017</v>
@@ -11748,7 +11751,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="349" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A349" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006021</v>
@@ -11772,7 +11775,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="350" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A350" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006014</v>
@@ -11796,7 +11799,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="351" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A351" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006065</v>
@@ -11820,7 +11823,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="352" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A352" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006141</v>
@@ -11844,7 +11847,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="353" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A353" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006142</v>
@@ -11868,7 +11871,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="354" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A354" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006009</v>
@@ -11892,7 +11895,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="355" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A355" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006010</v>
@@ -11916,7 +11919,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="356" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A356" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006019</v>
@@ -11940,7 +11943,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="357" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A357" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006143</v>
@@ -11964,7 +11967,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="358" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A358" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006023</v>
@@ -11988,7 +11991,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="359" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A359" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006079</v>
@@ -12012,7 +12015,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="360" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A360" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006029</v>
@@ -16183,19 +16186,18 @@
         <v>747</v>
       </c>
     </row>
-    <row r="534" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A534" s="7" t="str">
+    <row r="534" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A534" t="str">
         <f>F534 &amp; TEXT(C534,"000")</f>
         <v>1010004</v>
       </c>
-      <c r="B534" s="7" t="s">
+      <c r="B534" t="s">
         <v>937</v>
       </c>
-      <c r="C534" s="7">
+      <c r="C534">
         <v>4</v>
       </c>
       <c r="D534" s="3"/>
-      <c r="E534" s="7"/>
       <c r="F534" s="1">
         <v>1010</v>
       </c>
@@ -16203,19 +16205,18 @@
         <v>346</v>
       </c>
     </row>
-    <row r="535" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A535" s="7" t="str">
+    <row r="535" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A535" t="str">
         <f>F535 &amp; TEXT(C535,"000")</f>
         <v>1010010</v>
       </c>
-      <c r="B535" s="7" t="s">
+      <c r="B535" t="s">
         <v>940</v>
       </c>
-      <c r="C535" s="7">
+      <c r="C535">
         <v>10</v>
       </c>
       <c r="D535" s="3"/>
-      <c r="E535" s="7"/>
       <c r="F535" s="1">
         <v>1010</v>
       </c>
@@ -16223,19 +16224,18 @@
         <v>346</v>
       </c>
     </row>
-    <row r="536" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A536" s="7" t="str">
+    <row r="536" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A536" t="str">
         <f>F536 &amp; TEXT(C536,"000")</f>
         <v>1010031</v>
       </c>
-      <c r="B536" s="7" t="s">
+      <c r="B536" t="s">
         <v>938</v>
       </c>
-      <c r="C536" s="7">
+      <c r="C536">
         <v>31</v>
       </c>
       <c r="D536" s="3"/>
-      <c r="E536" s="7"/>
       <c r="F536" s="1">
         <v>1010</v>
       </c>
@@ -16243,19 +16243,18 @@
         <v>346</v>
       </c>
     </row>
-    <row r="537" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A537" s="7" t="str">
+    <row r="537" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A537" t="str">
         <f>F537 &amp; TEXT(C537,"000")</f>
         <v>1010028</v>
       </c>
-      <c r="B537" s="7" t="s">
+      <c r="B537" t="s">
         <v>939</v>
       </c>
-      <c r="C537" s="7">
+      <c r="C537">
         <v>28</v>
       </c>
       <c r="D537" s="3"/>
-      <c r="E537" s="7"/>
       <c r="F537" s="1">
         <v>1010</v>
       </c>
@@ -16263,27 +16262,45 @@
         <v>346</v>
       </c>
     </row>
-    <row r="538" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A538" s="7" t="str">
+    <row r="538" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A538" t="str">
         <f>F538 &amp; TEXT(C538,"000")</f>
         <v>1010079</v>
       </c>
-      <c r="B538" s="7" t="s">
+      <c r="B538" t="s">
         <v>942</v>
       </c>
-      <c r="C538" s="7">
+      <c r="C538">
         <v>79</v>
       </c>
       <c r="D538" s="3"/>
-      <c r="E538" s="7"/>
-      <c r="F538" s="7">
+      <c r="F538">
         <v>1010</v>
       </c>
       <c r="G538" s="1" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="539" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="539" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A539" s="7" t="str">
+        <f>F539 &amp; TEXT(C539,"000")</f>
+        <v>1006030</v>
+      </c>
+      <c r="B539" s="7" t="s">
+        <v>943</v>
+      </c>
+      <c r="C539" s="7">
+        <v>30</v>
+      </c>
+      <c r="D539" s="3"/>
+      <c r="E539" s="7"/>
+      <c r="F539" s="7">
+        <v>1006</v>
+      </c>
+      <c r="G539" s="1" t="s">
+        <v>566</v>
+      </c>
+    </row>
     <row r="540" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="541" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="542" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/backend/data/LigaPremier.xlsx
+++ b/backend/data/LigaPremier.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1f6951c0e601b7a9/Desktop/DEMO/Protoype/datastrike/backend/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{F34475F7-B005-4D1D-8E8A-35328689D795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A43A0D2F-827A-44A2-BD29-5F66F2EFF0C2}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="8_{F34475F7-B005-4D1D-8E8A-35328689D795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{73216108-C6F6-4C4E-963D-4F89ECAFB5B7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2145" uniqueCount="944">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2151" uniqueCount="947">
   <si>
     <t>Id_jugador</t>
   </si>
@@ -2865,6 +2865,15 @@
   </si>
   <si>
     <t>Andre Santana</t>
+  </si>
+  <si>
+    <t>Jordy Pizano</t>
+  </si>
+  <si>
+    <t>Ramon salas</t>
+  </si>
+  <si>
+    <t>Sagir Arce</t>
   </si>
 </sst>
 </file>
@@ -3162,12 +3171,16 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{32A8CF84-C284-4FB9-BA95-EA038AE71CB6}" name="Tabla1" displayName="Tabla1" ref="A1:G539" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7">
-  <autoFilter ref="A1:G539" xr:uid="{32A8CF84-C284-4FB9-BA95-EA038AE71CB6}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{32A8CF84-C284-4FB9-BA95-EA038AE71CB6}" name="Tabla1" displayName="Tabla1" ref="A1:G542" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7">
+  <autoFilter ref="A1:G542" xr:uid="{32A8CF84-C284-4FB9-BA95-EA038AE71CB6}">
     <filterColumn colId="5">
       <filters>
-        <filter val="1006"/>
+        <filter val="1009"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -3391,7 +3404,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.109375" customWidth="1"/>
-    <col min="2" max="2" width="9.77734375" customWidth="1"/>
+    <col min="2" max="2" width="17.33203125" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
     <col min="4" max="4" width="16.77734375" customWidth="1"/>
     <col min="5" max="5" width="8.6640625" customWidth="1"/>
@@ -8919,7 +8932,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="231" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1009028</v>
@@ -8943,7 +8956,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="232" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1009021</v>
@@ -8967,7 +8980,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="233" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1009012</v>
@@ -8991,7 +9004,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="234" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1009036</v>
@@ -9015,7 +9028,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="235" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1009017</v>
@@ -9039,7 +9052,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="236" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1009004</v>
@@ -9063,7 +9076,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="237" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1009024</v>
@@ -9087,7 +9100,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="238" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1009005</v>
@@ -9111,7 +9124,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="239" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1009014</v>
@@ -9135,7 +9148,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="240" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1009020</v>
@@ -9159,7 +9172,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="241" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1009025</v>
@@ -9183,7 +9196,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="242" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1009027</v>
@@ -9207,7 +9220,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="243" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1009023</v>
@@ -9231,7 +9244,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="244" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1009006</v>
@@ -9255,7 +9268,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="245" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1009010</v>
@@ -9279,7 +9292,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="246" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1009007</v>
@@ -9303,7 +9316,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="247" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1009022</v>
@@ -9327,7 +9340,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="248" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1009015</v>
@@ -9351,7 +9364,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="249" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1009019</v>
@@ -9375,7 +9388,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="250" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1009056</v>
@@ -9399,7 +9412,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="251" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1009013</v>
@@ -9423,7 +9436,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="252" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1009009</v>
@@ -9447,7 +9460,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="253" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1009008</v>
@@ -9471,7 +9484,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="254" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1009011</v>
@@ -9495,7 +9508,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="255" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1009016</v>
@@ -9519,7 +9532,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="256" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="str">
         <f t="shared" si="3"/>
         <v>1009112</v>
@@ -11247,7 +11260,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="328" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A328" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006001</v>
@@ -11271,7 +11284,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="329" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A329" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006051</v>
@@ -11295,7 +11308,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="330" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A330" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006012</v>
@@ -11319,7 +11332,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="331" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A331" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006025</v>
@@ -11343,7 +11356,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="332" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A332" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006015</v>
@@ -11367,7 +11380,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="333" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A333" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006004</v>
@@ -11391,7 +11404,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="334" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A334" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006013</v>
@@ -11415,7 +11428,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="335" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A335" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006062</v>
@@ -11439,7 +11452,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="336" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A336" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006026</v>
@@ -11463,7 +11476,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="337" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A337" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006003</v>
@@ -11487,7 +11500,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="338" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A338" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006002</v>
@@ -11511,7 +11524,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="339" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A339" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006006</v>
@@ -11535,7 +11548,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="340" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A340" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006011</v>
@@ -11559,7 +11572,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="341" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A341" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006008</v>
@@ -11583,7 +11596,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="342" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A342" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006005</v>
@@ -11607,7 +11620,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="343" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A343" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006018</v>
@@ -11631,7 +11644,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="344" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A344" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006007</v>
@@ -11655,7 +11668,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="345" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A345" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006016</v>
@@ -11679,7 +11692,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="346" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A346" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006020</v>
@@ -11703,7 +11716,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="347" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A347" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006022</v>
@@ -11727,7 +11740,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="348" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A348" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006017</v>
@@ -11751,7 +11764,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="349" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A349" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006021</v>
@@ -11775,7 +11788,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="350" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A350" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006014</v>
@@ -11799,7 +11812,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="351" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A351" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006065</v>
@@ -11823,7 +11836,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="352" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A352" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006141</v>
@@ -11847,7 +11860,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="353" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A353" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006142</v>
@@ -11871,7 +11884,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="354" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A354" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006009</v>
@@ -11895,7 +11908,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="355" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A355" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006010</v>
@@ -11919,7 +11932,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="356" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A356" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006019</v>
@@ -11943,7 +11956,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="357" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A357" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006143</v>
@@ -11967,7 +11980,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="358" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A358" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006023</v>
@@ -11991,7 +12004,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="359" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A359" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006079</v>
@@ -12015,7 +12028,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="360" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A360" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1006029</v>
@@ -16188,7 +16201,7 @@
     </row>
     <row r="534" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A534" t="str">
-        <f>F534 &amp; TEXT(C534,"000")</f>
+        <f t="shared" ref="A534:A539" si="9">F534 &amp; TEXT(C534,"000")</f>
         <v>1010004</v>
       </c>
       <c r="B534" t="s">
@@ -16207,7 +16220,7 @@
     </row>
     <row r="535" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A535" t="str">
-        <f>F535 &amp; TEXT(C535,"000")</f>
+        <f t="shared" si="9"/>
         <v>1010010</v>
       </c>
       <c r="B535" t="s">
@@ -16226,7 +16239,7 @@
     </row>
     <row r="536" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A536" t="str">
-        <f>F536 &amp; TEXT(C536,"000")</f>
+        <f t="shared" si="9"/>
         <v>1010031</v>
       </c>
       <c r="B536" t="s">
@@ -16245,7 +16258,7 @@
     </row>
     <row r="537" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A537" t="str">
-        <f>F537 &amp; TEXT(C537,"000")</f>
+        <f t="shared" si="9"/>
         <v>1010028</v>
       </c>
       <c r="B537" t="s">
@@ -16264,7 +16277,7 @@
     </row>
     <row r="538" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A538" t="str">
-        <f>F538 &amp; TEXT(C538,"000")</f>
+        <f t="shared" si="9"/>
         <v>1010079</v>
       </c>
       <c r="B538" t="s">
@@ -16281,29 +16294,85 @@
         <v>346</v>
       </c>
     </row>
-    <row r="539" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A539" s="7" t="str">
-        <f>F539 &amp; TEXT(C539,"000")</f>
+    <row r="539" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A539" t="str">
+        <f t="shared" si="9"/>
         <v>1006030</v>
       </c>
-      <c r="B539" s="7" t="s">
+      <c r="B539" t="s">
         <v>943</v>
       </c>
-      <c r="C539" s="7">
+      <c r="C539">
         <v>30</v>
       </c>
       <c r="D539" s="3"/>
-      <c r="E539" s="7"/>
-      <c r="F539" s="7">
+      <c r="F539">
         <v>1006</v>
       </c>
       <c r="G539" s="1" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="540" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="541" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="542" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="540" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A540" s="7" t="str">
+        <f>F540 &amp; TEXT(C540,"000")</f>
+        <v>1009002</v>
+      </c>
+      <c r="B540" s="7" t="s">
+        <v>944</v>
+      </c>
+      <c r="C540" s="7">
+        <v>2</v>
+      </c>
+      <c r="D540" s="3"/>
+      <c r="E540" s="7"/>
+      <c r="F540" s="1">
+        <v>1009</v>
+      </c>
+      <c r="G540" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="541" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A541" s="7" t="str">
+        <f>F541 &amp; TEXT(C541,"000")</f>
+        <v>1009018</v>
+      </c>
+      <c r="B541" s="7" t="s">
+        <v>945</v>
+      </c>
+      <c r="C541" s="7">
+        <v>18</v>
+      </c>
+      <c r="D541" s="3"/>
+      <c r="E541" s="7"/>
+      <c r="F541" s="1">
+        <v>1009</v>
+      </c>
+      <c r="G541" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="542" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A542" s="7" t="str">
+        <f>F542 &amp; TEXT(C542,"000")</f>
+        <v>1009029</v>
+      </c>
+      <c r="B542" s="7" t="s">
+        <v>946</v>
+      </c>
+      <c r="C542" s="7">
+        <v>29</v>
+      </c>
+      <c r="D542" s="3"/>
+      <c r="E542" s="7"/>
+      <c r="F542" s="1">
+        <v>1009</v>
+      </c>
+      <c r="G542" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
     <row r="543" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="544" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
